--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925687789917</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577291488647</t>
+    <t xml:space="preserve">11.1577272415161</t>
   </si>
   <si>
     <t xml:space="preserve">11.3654918670654</t>
@@ -59,52 +59,52 @@
     <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729797363281</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653886795044</t>
+    <t xml:space="preserve">11.0653896331787</t>
   </si>
   <si>
     <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732574462891</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
     <t xml:space="preserve">11.1192531585693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194257736206</t>
+    <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.3116273880005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948375701904</t>
+    <t xml:space="preserve">11.6948366165161</t>
   </si>
   <si>
     <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501005172729</t>
+    <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.810263633728</t>
   </si>
   <si>
     <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963748931885</t>
+    <t xml:space="preserve">11.6963768005371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657011032104</t>
+    <t xml:space="preserve">11.9657001495361</t>
   </si>
   <si>
     <t xml:space="preserve">11.657901763916</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751779556274</t>
+    <t xml:space="preserve">11.2751770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086194992065</t>
+    <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683450698853</t>
+    <t xml:space="preserve">10.0683441162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.1087799072266</t>
@@ -131,40 +131,40 @@
     <t xml:space="preserve">9.95326042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998023986816</t>
+    <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
     <t xml:space="preserve">9.11345386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683917999268</t>
+    <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51780414581299</t>
+    <t xml:space="preserve">9.51780605316162</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907295227051</t>
+    <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
     <t xml:space="preserve">12.0278921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950807571411</t>
+    <t xml:space="preserve">11.6950798034668</t>
   </si>
   <si>
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028560638428</t>
   </si>
   <si>
-    <t xml:space="preserve">11.586217880249</t>
+    <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
     <t xml:space="preserve">11.5084571838379</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">11.6639776229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529376983643</t>
+    <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
     <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863792419434</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975786209106</t>
+    <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4198198318481</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332458496094</t>
+    <t xml:space="preserve">9.67332363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449283599854</t>
@@ -206,34 +206,34 @@
     <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550067901611</t>
+    <t xml:space="preserve">9.8754997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476612091064</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420581817627</t>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887166976929</t>
+    <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
     <t xml:space="preserve">9.79773998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670196533203</t>
+    <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662033081055</t>
+    <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892475128174</t>
+    <t xml:space="preserve">9.47892379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074668884277</t>
+    <t xml:space="preserve">9.29074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">8.97815132141113</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842479705811</t>
+    <t xml:space="preserve">9.71842575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087797164917</t>
+    <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274564743042</t>
+    <t xml:space="preserve">10.2745628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">10.349835395813</t>
+    <t xml:space="preserve">10.3498373031616</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
@@ -260,19 +260,19 @@
     <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919784545898</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353733062744</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181255340576</t>
+    <t xml:space="preserve">10.5181264877319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834913253784</t>
   </si>
   <si>
     <t xml:space="preserve">10.257345199585</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963745117188</t>
+    <t xml:space="preserve">9.90963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193256378174</t>
+    <t xml:space="preserve">9.56193161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344543457031</t>
+    <t xml:space="preserve">8.95344638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651992797852</t>
+    <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
     <t xml:space="preserve">8.77959251403809</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920139312744</t>
+    <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037284851074</t>
+    <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271194458008</t>
+    <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266117095947</t>
+    <t xml:space="preserve">11.126612663269</t>
   </si>
   <si>
-    <t xml:space="preserve">11.300464630127</t>
+    <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658313751221</t>
+    <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
     <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9965648651123</t>
+    <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.605052947998</t>
+    <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311990737915</t>
+    <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500514984131</t>
+    <t xml:space="preserve">9.47500610351562</t>
   </si>
   <si>
     <t xml:space="preserve">9.3880786895752</t>
@@ -347,37 +347,37 @@
     <t xml:space="preserve">9.12729835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578548431396</t>
+    <t xml:space="preserve">9.73578453063965</t>
   </si>
   <si>
     <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115127563477</t>
+    <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725294113159</t>
+    <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876581192017</t>
+    <t xml:space="preserve">7.38876628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183887481689</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
     <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530210494995</t>
+    <t xml:space="preserve">7.34530162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569370269775</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339906692505</t>
+    <t xml:space="preserve">7.82340002059937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378828048706</t>
+    <t xml:space="preserve">7.95378875732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.34496021270752</t>
@@ -386,40 +386,40 @@
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087146759033</t>
+    <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585216522217</t>
+    <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4772777557373</t>
+    <t xml:space="preserve">9.47727870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870620727539</t>
+    <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85726928710938</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
     <t xml:space="preserve">8.76869678497314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441619873047</t>
+    <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012428283691</t>
+    <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7244119644165</t>
+    <t xml:space="preserve">8.72441101074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12298774719238</t>
+    <t xml:space="preserve">9.1229887008667</t>
   </si>
   <si>
     <t xml:space="preserve">8.50298023223877</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0715866088867</t>
+    <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944425582886</t>
+    <t xml:space="preserve">10.8944416046143</t>
   </si>
   <si>
     <t xml:space="preserve">10.9830141067505</t>
@@ -446,37 +446,37 @@
     <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972871780396</t>
+    <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74299716949463</t>
+    <t xml:space="preserve">9.74299621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014217376709</t>
+    <t xml:space="preserve">9.92014122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744331359863</t>
+    <t xml:space="preserve">10.274432182312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487316131592</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144500732422</t>
+    <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
     <t xml:space="preserve">11.425877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8058700561523</t>
+    <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287250518799</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
     <t xml:space="preserve">10.3630056381226</t>
@@ -485,22 +485,22 @@
     <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193992614746</t>
+    <t xml:space="preserve">10.4193983078003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5100030899048</t>
+    <t xml:space="preserve">10.5100011825562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006050109863</t>
+    <t xml:space="preserve">10.6006059646606</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475887298584</t>
+    <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
     <t xml:space="preserve">10.7818126678467</t>
@@ -509,31 +509,31 @@
     <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517532348633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502614974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4160375595093</t>
+    <t xml:space="preserve">11.416036605835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442260742188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690538406372</t>
+    <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
     <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878480911255</t>
+    <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314691543579</t>
+    <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
     <t xml:space="preserve">12.6844844818115</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">12.5032787322998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.775089263916</t>
+    <t xml:space="preserve">12.7750902175903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375017166138</t>
+    <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562950134277</t>
+    <t xml:space="preserve">12.9562969207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435380935669</t>
+    <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
     <t xml:space="preserve">13.6811237335205</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401754379272</t>
+    <t xml:space="preserve">15.0401763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.402587890625</t>
+    <t xml:space="preserve">15.4025897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556079864502</t>
+    <t xml:space="preserve">15.8556051254272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462099075317</t>
+    <t xml:space="preserve">15.9462108612061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650022506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307811737061</t>
+    <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
     <t xml:space="preserve">15.2213821411133</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341409683228</t>
+    <t xml:space="preserve">14.1341400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4093132019043</t>
+    <t xml:space="preserve">13.40931224823</t>
   </si>
   <si>
     <t xml:space="preserve">12.5938816070557</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9529333114624</t>
+    <t xml:space="preserve">13.9529342651367</t>
   </si>
   <si>
     <t xml:space="preserve">14.2247438430786</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">15.3119840621948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264242172241</t>
+    <t xml:space="preserve">13.7264251708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512519836426</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.127025604248</t>
+    <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2659797668457</t>
+    <t xml:space="preserve">14.26598072052</t>
   </si>
   <si>
     <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196636199951</t>
+    <t xml:space="preserve">14.2196626663208</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6828441619873</t>
+    <t xml:space="preserve">14.682843208313</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880714416504</t>
+    <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248908996582</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">13.3859357833862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396167755127</t>
+    <t xml:space="preserve">13.339617729187</t>
   </si>
   <si>
     <t xml:space="preserve">13.4322538375854</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">13.7101621627808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0617094039917</t>
+    <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469816207886</t>
+    <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
     <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712080001831</t>
+    <t xml:space="preserve">13.5712070465088</t>
   </si>
   <si>
     <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9417543411255</t>
+    <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
     <t xml:space="preserve">15.0533876419067</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555233001709</t>
+    <t xml:space="preserve">15.6555223464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
     <t xml:space="preserve">15.1923427581787</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407974243164</t>
+    <t xml:space="preserve">15.8407964706421</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944765090942</t>
+    <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702529907227</t>
+    <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460247039795</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.016695022583</t>
+    <t xml:space="preserve">15.0166959762573</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5414838790894</t>
+    <t xml:space="preserve">14.541482925415</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968658447266</t>
+    <t xml:space="preserve">15.3968648910522</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572017669678</t>
+    <t xml:space="preserve">16.1572036743164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720779418945</t>
+    <t xml:space="preserve">15.8720769882202</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315683364868</t>
+    <t xml:space="preserve">14.7315673828125</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522468566895</t>
+    <t xml:space="preserve">16.2522449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -51158,7 +51158,7 @@
     </row>
     <row r="1918">
       <c r="A1918" s="1" t="n">
-        <v>45943.5655555556</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B1918" t="n">
         <v>400</v>
@@ -51179,6 +51179,32 @@
         <v>311</v>
       </c>
       <c r="H1918" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="1" t="n">
+        <v>45944.5178240741</v>
+      </c>
+      <c r="B1919" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1919" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D1919" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F1919" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G1919" t="s">
+        <v>311</v>
+      </c>
+      <c r="H1919" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118375778198</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">11.9256858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577272415161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654918670654</t>
+    <t xml:space="preserve">11.3654899597168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699003219604</t>
+    <t xml:space="preserve">10.7698993682861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007139205933</t>
+    <t xml:space="preserve">10.9007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729778289795</t>
+    <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653867721558</t>
+    <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962032318115</t>
+    <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732555389404</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
     <t xml:space="preserve">11.119252204895</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">11.6194257736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116292953491</t>
+    <t xml:space="preserve">11.3116273880005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948385238647</t>
+    <t xml:space="preserve">11.6948366165161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501024246216</t>
+    <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
     <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733268737793</t>
+    <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">11.9657020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579008102417</t>
+    <t xml:space="preserve">11.6579027175903</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751779556274</t>
+    <t xml:space="preserve">11.2751789093018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086166381836</t>
+    <t xml:space="preserve">10.8086194992065</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349035263062</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">10.0683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087789535522</t>
+    <t xml:space="preserve">10.1087808609009</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326042175293</t>
+    <t xml:space="preserve">9.95325946807861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71997928619385</t>
+    <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11345386505127</t>
@@ -140,64 +140,64 @@
     <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683917999268</t>
   </si>
   <si>
     <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2642993927002</t>
+    <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
     <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278940200806</t>
+    <t xml:space="preserve">12.0278921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950798034668</t>
+    <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028560638428</t>
+    <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
     <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084581375122</t>
+    <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639757156372</t>
+    <t xml:space="preserve">11.6639776229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529376983643</t>
+    <t xml:space="preserve">11.3529386520386</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8863773345947</t>
+    <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641380310059</t>
+    <t xml:space="preserve">10.9641370773315</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310201644897</t>
+    <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4089412689209</t>
+    <t xml:space="preserve">9.40894222259521</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449378967285</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550163269043</t>
+    <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476602554321</t>
+    <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342059135437</t>
+    <t xml:space="preserve">10.3420610427856</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887166976929</t>
@@ -230,85 +230,85 @@
     <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892379760742</t>
+    <t xml:space="preserve">9.47892570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074668884277</t>
+    <t xml:space="preserve">9.29074573516846</t>
   </si>
   <si>
     <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945678710938</t>
+    <t xml:space="preserve">9.09945583343506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842575073242</t>
+    <t xml:space="preserve">9.71842670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087778091431</t>
+    <t xml:space="preserve">10.3087797164917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274564743042</t>
+    <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
     <t xml:space="preserve">10.349835395813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076923370361</t>
+    <t xml:space="preserve">10.0076913833618</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064424514771</t>
+    <t xml:space="preserve">10.6064443588257</t>
   </si>
   <si>
     <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353713989258</t>
+    <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778904914856</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.257345199585</t>
+    <t xml:space="preserve">10.2573461532593</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885997772217</t>
+    <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963840484619</t>
+    <t xml:space="preserve">9.90963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193161010742</t>
+    <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.95344638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8665189743042</t>
+    <t xml:space="preserve">8.86651992797852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959156036377</t>
+    <t xml:space="preserve">8.7795934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266700744629</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920139312744</t>
+    <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037284851074</t>
+    <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271289825439</t>
+    <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266117095947</t>
+    <t xml:space="preserve">11.126612663269</t>
   </si>
   <si>
     <t xml:space="preserve">11.3004655838013</t>
@@ -323,19 +323,19 @@
     <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9965648651123</t>
+    <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
     <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311981201172</t>
+    <t xml:space="preserve">10.4311990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500419616699</t>
+    <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3880786895752</t>
+    <t xml:space="preserve">9.38807773590088</t>
   </si>
   <si>
     <t xml:space="preserve">9.21422672271729</t>
@@ -347,52 +347,52 @@
     <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442726135254</t>
+    <t xml:space="preserve">10.3442735671997</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3011531829834</t>
+    <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725198745728</t>
+    <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876628875732</t>
+    <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183887481689</t>
+    <t xml:space="preserve">7.30183982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837564468384</t>
+    <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530258178711</t>
+    <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569370269775</t>
+    <t xml:space="preserve">7.47569227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339906692505</t>
+    <t xml:space="preserve">7.82339954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378923416138</t>
+    <t xml:space="preserve">7.95378971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34496021270752</t>
+    <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727966308594</t>
+    <t xml:space="preserve">9.47727870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870620727539</t>
+    <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.94584178924561</t>
@@ -407,46 +407,46 @@
     <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012428283691</t>
+    <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7244119644165</t>
+    <t xml:space="preserve">8.72441005706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21156024932861</t>
+    <t xml:space="preserve">9.2115592956543</t>
   </si>
   <si>
     <t xml:space="preserve">9.1229887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50298023223877</t>
+    <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013370513916</t>
+    <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944425582886</t>
+    <t xml:space="preserve">10.8944416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830141067505</t>
+    <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515781402588</t>
+    <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972881317139</t>
+    <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83157062530518</t>
+    <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.74299621582031</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">9.92014217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744331359863</t>
+    <t xml:space="preserve">10.274432182312</t>
   </si>
   <si>
     <t xml:space="preserve">11.2487325668335</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
     <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401515960693</t>
+    <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193983078003</t>
+    <t xml:space="preserve">10.4193992614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100021362305</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475887298584</t>
+    <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
     <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502605438232</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878471374512</t>
+    <t xml:space="preserve">11.6878461837769</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314682006836</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281055450439</t>
+    <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
     <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811237335205</t>
+    <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931917190552</t>
+    <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401754379272</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.221381187439</t>
+    <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871591567993</t>
+    <t xml:space="preserve">14.587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,34 +596,34 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495706558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999151229858</t>
+    <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341409683228</t>
+    <t xml:space="preserve">14.1341400146484</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938816070557</t>
+    <t xml:space="preserve">12.5938806533813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468997955322</t>
+    <t xml:space="preserve">13.0468978881836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5905199050903</t>
+    <t xml:space="preserve">13.590518951416</t>
   </si>
   <si>
     <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656911849976</t>
+    <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
     <t xml:space="preserve">13.9529333114624</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230625152588</t>
+    <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2659797668457</t>
+    <t xml:space="preserve">14.26598072052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365261077881</t>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
     <t xml:space="preserve">14.2196626663208</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6828441619873</t>
+    <t xml:space="preserve">14.682843208313</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070705413818</t>
+    <t xml:space="preserve">15.0070714950562</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586158752441</t>
+    <t xml:space="preserve">14.3586168289185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733436584473</t>
+    <t xml:space="preserve">14.1733446121216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564821243286</t>
+    <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248899459839</t>
+    <t xml:space="preserve">13.5248908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027982711792</t>
+    <t xml:space="preserve">13.8027992248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101631164551</t>
+    <t xml:space="preserve">13.7101621627808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0617094039917</t>
+    <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469816207886</t>
+    <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006645202637</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712080001831</t>
+    <t xml:space="preserve">13.5712070465088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543445587158</t>
+    <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
     <t xml:space="preserve">13.9417533874512</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.404935836792</t>
+    <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555233001709</t>
+    <t xml:space="preserve">15.6555223464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407955169678</t>
+    <t xml:space="preserve">15.8407964706421</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944784164429</t>
+    <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
     <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460237503052</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975709915161</t>
+    <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
     <t xml:space="preserve">15.0166959762573</t>
@@ -801,9 +801,6 @@
   </si>
   <si>
     <t xml:space="preserve">14.541482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -975,6 +972,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -35313,7 +35313,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35339,7 +35339,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35365,7 +35365,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35391,7 +35391,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35417,7 +35417,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35443,7 +35443,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35469,7 +35469,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35495,7 +35495,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35521,7 +35521,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35547,7 +35547,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35573,7 +35573,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35599,7 +35599,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35625,7 +35625,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35651,7 +35651,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35677,7 +35677,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35703,7 +35703,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35729,7 +35729,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35755,7 +35755,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35781,7 +35781,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35807,7 +35807,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35833,7 +35833,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35859,7 +35859,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35885,7 +35885,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35911,7 +35911,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35937,7 +35937,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35963,7 +35963,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35989,7 +35989,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36015,7 +36015,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36041,7 +36041,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36067,7 +36067,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36093,7 +36093,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36119,7 +36119,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36145,7 +36145,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36171,7 +36171,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36197,7 +36197,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36223,7 +36223,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36249,7 +36249,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36275,7 +36275,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36301,7 +36301,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36327,7 +36327,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36353,7 +36353,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36379,7 +36379,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36405,7 +36405,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36431,7 +36431,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36509,7 +36509,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36535,7 +36535,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36561,7 +36561,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36587,7 +36587,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36639,7 +36639,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36665,7 +36665,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36717,7 +36717,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36743,7 +36743,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36769,7 +36769,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36795,7 +36795,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36821,7 +36821,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36847,7 +36847,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36873,7 +36873,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36899,7 +36899,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36925,7 +36925,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36951,7 +36951,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36977,7 +36977,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37003,7 +37003,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37107,7 +37107,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37133,7 +37133,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37159,7 +37159,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37185,7 +37185,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37211,7 +37211,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37237,7 +37237,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37263,7 +37263,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37289,7 +37289,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37315,7 +37315,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37341,7 +37341,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37367,7 +37367,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37393,7 +37393,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37419,7 +37419,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37445,7 +37445,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37471,7 +37471,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37497,7 +37497,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37523,7 +37523,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37627,7 +37627,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37653,7 +37653,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37679,7 +37679,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37705,7 +37705,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37731,7 +37731,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37757,7 +37757,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37783,7 +37783,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37809,7 +37809,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37835,7 +37835,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38173,7 +38173,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38199,7 +38199,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38225,7 +38225,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38381,7 +38381,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38407,7 +38407,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38433,7 +38433,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38459,7 +38459,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38485,7 +38485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38511,7 +38511,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38537,7 +38537,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38563,7 +38563,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38589,7 +38589,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38615,7 +38615,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38641,7 +38641,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38667,7 +38667,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38693,7 +38693,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38719,7 +38719,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38771,7 +38771,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38797,7 +38797,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39005,7 +39005,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39031,7 +39031,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39057,7 +39057,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39083,7 +39083,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39109,7 +39109,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39135,7 +39135,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39161,7 +39161,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39187,7 +39187,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39213,7 +39213,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39239,7 +39239,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39265,7 +39265,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39291,7 +39291,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39317,7 +39317,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39343,7 +39343,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39369,7 +39369,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39395,7 +39395,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39421,7 +39421,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39447,7 +39447,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39473,7 +39473,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39499,7 +39499,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39525,7 +39525,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39551,7 +39551,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39577,7 +39577,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39603,7 +39603,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39629,7 +39629,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39655,7 +39655,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39681,7 +39681,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39707,7 +39707,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39733,7 +39733,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39759,7 +39759,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39785,7 +39785,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39811,7 +39811,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39837,7 +39837,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39863,7 +39863,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39889,7 +39889,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39915,7 +39915,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39941,7 +39941,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39967,7 +39967,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39993,7 +39993,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40019,7 +40019,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40045,7 +40045,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40071,7 +40071,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40097,7 +40097,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40123,7 +40123,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40253,7 +40253,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40409,7 +40409,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40435,7 +40435,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1505" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40461,7 +40461,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40487,7 +40487,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40513,7 +40513,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40539,7 +40539,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40565,7 +40565,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1510" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -40591,7 +40591,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -40617,7 +40617,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>263</v>
+        <v>212</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -40669,7 +40669,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40695,7 +40695,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40877,7 +40877,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40903,7 +40903,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40929,7 +40929,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40955,7 +40955,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40981,7 +40981,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41007,7 +41007,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41033,7 +41033,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41059,7 +41059,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41085,7 +41085,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41111,7 +41111,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41137,7 +41137,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41163,7 +41163,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41189,7 +41189,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41215,7 +41215,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41241,7 +41241,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41267,7 +41267,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41293,7 +41293,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41319,7 +41319,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41345,7 +41345,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41371,7 +41371,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41397,7 +41397,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41423,7 +41423,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41449,7 +41449,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41475,7 +41475,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41501,7 +41501,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41527,7 +41527,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41553,7 +41553,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41579,7 +41579,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41605,7 +41605,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41631,7 +41631,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41657,7 +41657,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41683,7 +41683,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41709,7 +41709,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41735,7 +41735,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41761,7 +41761,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41787,7 +41787,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41813,7 +41813,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41839,7 +41839,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41865,7 +41865,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41891,7 +41891,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41917,7 +41917,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41943,7 +41943,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41969,7 +41969,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -41995,7 +41995,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42021,7 +42021,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42047,7 +42047,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42073,7 +42073,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42099,7 +42099,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42125,7 +42125,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42151,7 +42151,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42177,7 +42177,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42203,7 +42203,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42229,7 +42229,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42255,7 +42255,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42281,7 +42281,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42307,7 +42307,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42333,7 +42333,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42359,7 +42359,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42385,7 +42385,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42411,7 +42411,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42437,7 +42437,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42463,7 +42463,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42489,7 +42489,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42515,7 +42515,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42541,7 +42541,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42567,7 +42567,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42593,7 +42593,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42619,7 +42619,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42645,7 +42645,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42671,7 +42671,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42697,7 +42697,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42723,7 +42723,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42749,7 +42749,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42775,7 +42775,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42801,7 +42801,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42827,7 +42827,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42853,7 +42853,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42879,7 +42879,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42905,7 +42905,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42931,7 +42931,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42957,7 +42957,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42983,7 +42983,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43009,7 +43009,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43035,7 +43035,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43061,7 +43061,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43087,7 +43087,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43113,7 +43113,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43139,7 +43139,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43165,7 +43165,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43191,7 +43191,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43217,7 +43217,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43243,7 +43243,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43269,7 +43269,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43295,7 +43295,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43321,7 +43321,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43347,7 +43347,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43373,7 +43373,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43399,7 +43399,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43425,7 +43425,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43451,7 +43451,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43477,7 +43477,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43503,7 +43503,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43529,7 +43529,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43555,7 +43555,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43581,7 +43581,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43607,7 +43607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43633,7 +43633,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43659,7 +43659,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43685,7 +43685,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43711,7 +43711,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43737,7 +43737,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43763,7 +43763,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43789,7 +43789,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43815,7 +43815,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43841,7 +43841,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43867,7 +43867,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43893,7 +43893,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43919,7 +43919,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43945,7 +43945,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43971,7 +43971,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -43997,7 +43997,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44023,7 +44023,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44049,7 +44049,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44075,7 +44075,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44101,7 +44101,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44127,7 +44127,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44153,7 +44153,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44179,7 +44179,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44205,7 +44205,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44231,7 +44231,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44257,7 +44257,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44283,7 +44283,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44309,7 +44309,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44335,7 +44335,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44361,7 +44361,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44387,7 +44387,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44413,7 +44413,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44439,7 +44439,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44465,7 +44465,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44491,7 +44491,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44517,7 +44517,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44543,7 +44543,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44569,7 +44569,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44595,7 +44595,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44621,7 +44621,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44647,7 +44647,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44673,7 +44673,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44699,7 +44699,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44725,7 +44725,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44751,7 +44751,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44777,7 +44777,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44803,7 +44803,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44829,7 +44829,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44855,7 +44855,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44881,7 +44881,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44907,7 +44907,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44933,7 +44933,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44959,7 +44959,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44985,7 +44985,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45011,7 +45011,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45037,7 +45037,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45063,7 +45063,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45089,7 +45089,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45115,7 +45115,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45141,7 +45141,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45167,7 +45167,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45193,7 +45193,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45219,7 +45219,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45245,7 +45245,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45271,7 +45271,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45297,7 +45297,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45323,7 +45323,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45349,7 +45349,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45375,7 +45375,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45401,7 +45401,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45427,7 +45427,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45453,7 +45453,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45479,7 +45479,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45505,7 +45505,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45531,7 +45531,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45557,7 +45557,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45583,7 +45583,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45609,7 +45609,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45635,7 +45635,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45661,7 +45661,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45687,7 +45687,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45713,7 +45713,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45739,7 +45739,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45765,7 +45765,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45791,7 +45791,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45817,7 +45817,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45843,7 +45843,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45869,7 +45869,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45895,7 +45895,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45921,7 +45921,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45947,7 +45947,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45973,7 +45973,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -45999,7 +45999,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46025,7 +46025,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46051,7 +46051,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46077,7 +46077,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46103,7 +46103,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46129,7 +46129,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46155,7 +46155,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46181,7 +46181,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46207,7 +46207,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46233,7 +46233,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46259,7 +46259,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46285,7 +46285,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46311,7 +46311,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46337,7 +46337,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46363,7 +46363,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46389,7 +46389,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46415,7 +46415,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46441,7 +46441,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46467,7 +46467,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46493,7 +46493,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46519,7 +46519,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46545,7 +46545,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46571,7 +46571,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46597,7 +46597,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46623,7 +46623,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46649,7 +46649,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46675,7 +46675,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46701,7 +46701,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46727,7 +46727,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46753,7 +46753,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46779,7 +46779,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46805,7 +46805,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46831,7 +46831,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46857,7 +46857,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46883,7 +46883,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46909,7 +46909,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46935,7 +46935,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46961,7 +46961,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46987,7 +46987,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47013,7 +47013,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47039,7 +47039,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47065,7 +47065,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47091,7 +47091,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47117,7 +47117,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47143,7 +47143,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47169,7 +47169,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47195,7 +47195,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47221,7 +47221,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47247,7 +47247,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47273,7 +47273,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47299,7 +47299,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47325,7 +47325,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47351,7 +47351,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47377,7 +47377,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47403,7 +47403,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47429,7 +47429,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47455,7 +47455,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47481,7 +47481,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47507,7 +47507,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47533,7 +47533,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47559,7 +47559,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47585,7 +47585,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47611,7 +47611,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47637,7 +47637,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47663,7 +47663,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47689,7 +47689,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47715,7 +47715,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47741,7 +47741,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47767,7 +47767,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47793,7 +47793,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47819,7 +47819,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47845,7 +47845,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47871,7 +47871,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47897,7 +47897,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47923,7 +47923,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47949,7 +47949,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47975,7 +47975,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48001,7 +48001,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48027,7 +48027,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48053,7 +48053,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48079,7 +48079,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48105,7 +48105,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48131,7 +48131,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48157,7 +48157,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48183,7 +48183,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48209,7 +48209,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48235,7 +48235,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48261,7 +48261,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48287,7 +48287,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48313,7 +48313,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48339,7 +48339,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48365,7 +48365,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48391,7 +48391,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48417,7 +48417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48443,7 +48443,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48469,7 +48469,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48495,7 +48495,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48521,7 +48521,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48547,7 +48547,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48573,7 +48573,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48599,7 +48599,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48625,7 +48625,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48651,7 +48651,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48677,7 +48677,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48703,7 +48703,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48729,7 +48729,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48755,7 +48755,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48781,7 +48781,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48807,7 +48807,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48833,7 +48833,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48859,7 +48859,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48885,7 +48885,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48911,7 +48911,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48937,7 +48937,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48963,7 +48963,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48989,7 +48989,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49015,7 +49015,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49041,7 +49041,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49067,7 +49067,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49093,7 +49093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49119,7 +49119,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49145,7 +49145,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49171,7 +49171,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49197,7 +49197,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49223,7 +49223,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49249,7 +49249,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49275,7 +49275,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49301,7 +49301,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49327,7 +49327,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49353,7 +49353,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49379,7 +49379,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49405,7 +49405,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49431,7 +49431,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49457,7 +49457,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49483,7 +49483,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49509,7 +49509,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49535,7 +49535,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49561,7 +49561,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49587,7 +49587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49613,7 +49613,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49639,7 +49639,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49665,7 +49665,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49691,7 +49691,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49717,7 +49717,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49743,7 +49743,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49769,7 +49769,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49795,7 +49795,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49821,7 +49821,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49847,7 +49847,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49873,7 +49873,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49899,7 +49899,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49925,7 +49925,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49951,7 +49951,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49977,7 +49977,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50003,7 +50003,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50029,7 +50029,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50055,7 +50055,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50081,7 +50081,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50107,7 +50107,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50133,7 +50133,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50159,7 +50159,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50185,7 +50185,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50211,7 +50211,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50237,7 +50237,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50263,7 +50263,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50289,7 +50289,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50315,7 +50315,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50341,7 +50341,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50367,7 +50367,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50393,7 +50393,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50419,7 +50419,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50445,7 +50445,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50471,7 +50471,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50497,7 +50497,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50523,7 +50523,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50549,7 +50549,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50575,7 +50575,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50601,7 +50601,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50627,7 +50627,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50653,7 +50653,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50679,7 +50679,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50705,7 +50705,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50731,7 +50731,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50757,7 +50757,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50783,7 +50783,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50809,7 +50809,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50835,7 +50835,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50861,7 +50861,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50887,7 +50887,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50913,7 +50913,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50939,7 +50939,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50965,7 +50965,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50991,7 +50991,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51017,7 +51017,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51043,7 +51043,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51069,7 +51069,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51095,7 +51095,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51121,7 +51121,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51147,7 +51147,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51173,7 +51173,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51199,7 +51199,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51207,7 +51207,7 @@
     </row>
     <row r="1920">
       <c r="A1920" s="1" t="n">
-        <v>45945.6139467593</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B1920" t="n">
         <v>100</v>
@@ -51225,9 +51225,35 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1920" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="1" t="n">
+        <v>45946.4526967593</v>
+      </c>
+      <c r="B1921" t="n">
+        <v>15600</v>
+      </c>
+      <c r="C1921" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D1921" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F1921" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="G1921" t="s">
+        <v>320</v>
+      </c>
+      <c r="H1921" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118366241455</t>
+    <t xml:space="preserve">11.9118356704712</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256858825684</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577272415161</t>
+    <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654899597168</t>
+    <t xml:space="preserve">11.3654909133911</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7698993682861</t>
+    <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653877258301</t>
+    <t xml:space="preserve">11.0653886795044</t>
   </si>
   <si>
     <t xml:space="preserve">11.1962022781372</t>
@@ -83,49 +83,49 @@
     <t xml:space="preserve">11.6194257736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116273880005</t>
+    <t xml:space="preserve">11.3116264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948366165161</t>
+    <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424776077271</t>
+    <t xml:space="preserve">11.5424766540527</t>
   </si>
   <si>
     <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.8102617263794</t>
   </si>
   <si>
     <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963758468628</t>
+    <t xml:space="preserve">11.6963768005371</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657020568848</t>
+    <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579027175903</t>
+    <t xml:space="preserve">11.657901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807781219482</t>
+    <t xml:space="preserve">11.0807790756226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751789093018</t>
+    <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086194992065</t>
+    <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087808609009</t>
+    <t xml:space="preserve">10.1087789535522</t>
   </si>
   <si>
     <t xml:space="preserve">9.95325946807861</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683917999268</t>
+    <t xml:space="preserve">9.85683727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5178050994873</t>
+    <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
     <t xml:space="preserve">10.2643003463745</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278921127319</t>
+    <t xml:space="preserve">12.0278940200806</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
@@ -161,25 +161,25 @@
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028579711914</t>
+    <t xml:space="preserve">11.7028589248657</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862169265747</t>
+    <t xml:space="preserve">11.586217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084571838379</t>
+    <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639776229858</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529386520386</t>
+    <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196575164795</t>
+    <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863773345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641370773315</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310192108154</t>
+    <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
     <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449378967285</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550067901611</t>
+    <t xml:space="preserve">9.87550163269043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420610427856</t>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887166976929</t>
+    <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
     <t xml:space="preserve">9.7977409362793</t>
@@ -230,34 +230,34 @@
     <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892570495605</t>
+    <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074573516846</t>
+    <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945583343506</t>
+    <t xml:space="preserve">9.09945487976074</t>
   </si>
   <si>
     <t xml:space="preserve">9.71842670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087797164917</t>
+    <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2745637893677</t>
+    <t xml:space="preserve">10.274564743042</t>
   </si>
   <si>
     <t xml:space="preserve">10.349835395813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076913833618</t>
+    <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064443588257</t>
+    <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
     <t xml:space="preserve">10.6919794082642</t>
@@ -266,37 +266,37 @@
     <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7789058685303</t>
+    <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834932327271</t>
+    <t xml:space="preserve">10.0834922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2573461532593</t>
+    <t xml:space="preserve">10.257345199585</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963935852051</t>
+    <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193256378174</t>
+    <t xml:space="preserve">9.56193161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651992797852</t>
+    <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7795934677124</t>
+    <t xml:space="preserve">8.77959156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266605377197</t>
+    <t xml:space="preserve">8.69266700744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
@@ -305,37 +305,37 @@
     <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271194458008</t>
+    <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
     <t xml:space="preserve">11.126612663269</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004655838013</t>
+    <t xml:space="preserve">11.300464630127</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527587890625</t>
+    <t xml:space="preserve">10.9527597427368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704187393188</t>
+    <t xml:space="preserve">10.1704196929932</t>
   </si>
   <si>
     <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6050519943237</t>
+    <t xml:space="preserve">10.6050510406494</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500514984131</t>
+    <t xml:space="preserve">9.47500610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38807773590088</t>
+    <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
     <t xml:space="preserve">9.21422672271729</t>
@@ -347,34 +347,34 @@
     <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442735671997</t>
+    <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725198745728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876581192017</t>
+    <t xml:space="preserve">7.38876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183982849121</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530210494995</t>
+    <t xml:space="preserve">7.34530305862427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569227218628</t>
+    <t xml:space="preserve">7.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339954376221</t>
+    <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378971099854</t>
+    <t xml:space="preserve">7.95378923416138</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087146759033</t>
+    <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585121154785</t>
+    <t xml:space="preserve">9.56585216522217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727870941162</t>
+    <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870716094971</t>
+    <t xml:space="preserve">9.38870525360107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584178924561</t>
+    <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869678497314</t>
+    <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441524505615</t>
@@ -410,52 +410,52 @@
     <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72441005706787</t>
+    <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
     <t xml:space="preserve">9.2115592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858606338501</t>
+    <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944416046143</t>
+    <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
     <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972871780396</t>
+    <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74299621582031</t>
+    <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014217376709</t>
+    <t xml:space="preserve">9.92014122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274432182312</t>
+    <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
     <t xml:space="preserve">11.2487325668335</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287231445312</t>
+    <t xml:space="preserve">10.6287250518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172975540161</t>
+    <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
     <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.540150642395</t>
+    <t xml:space="preserve">10.5401515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193992614746</t>
+    <t xml:space="preserve">10.4193983078003</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100021362305</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475877761841</t>
+    <t xml:space="preserve">10.1475887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818126678467</t>
+    <t xml:space="preserve">10.7818117141724</t>
   </si>
   <si>
-    <t xml:space="preserve">10.963020324707</t>
+    <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
     <t xml:space="preserve">9.78517436981201</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502605438232</t>
+    <t xml:space="preserve">12.0502614974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408634185791</t>
+    <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878461837769</t>
+    <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314682006836</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375026702881</t>
+    <t xml:space="preserve">13.1375017166138</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562959671021</t>
+    <t xml:space="preserve">12.9562950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281064987183</t>
+    <t xml:space="preserve">13.2281055450439</t>
   </si>
   <si>
     <t xml:space="preserve">14.0435371398926</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153476715088</t>
+    <t xml:space="preserve">14.3153486251831</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931926727295</t>
@@ -575,16 +575,16 @@
     <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650012969971</t>
   </si>
   <si>
     <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2213821411133</t>
+    <t xml:space="preserve">15.2213802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.587158203125</t>
+    <t xml:space="preserve">14.5871591567993</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495706558228</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341400146484</t>
+    <t xml:space="preserve">14.1341409683228</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938806533813</t>
+    <t xml:space="preserve">12.5938816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468978881836</t>
+    <t xml:space="preserve">13.0468988418579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.590518951416</t>
+    <t xml:space="preserve">13.5905208587646</t>
   </si>
   <si>
     <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656921386719</t>
+    <t xml:space="preserve">12.8656911849976</t>
   </si>
   <si>
     <t xml:space="preserve">13.9529333114624</t>
@@ -632,25 +632,25 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119850158691</t>
+    <t xml:space="preserve">15.3119859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264242172241</t>
+    <t xml:space="preserve">13.7264251708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512519836426</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.26598072052</t>
+    <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365251541138</t>
+    <t xml:space="preserve">14.6365261077881</t>
   </si>
   <si>
     <t xml:space="preserve">14.2196626663208</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">14.682843208313</t>
+    <t xml:space="preserve">14.6828441619873</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070714950562</t>
+    <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586168289185</t>
+    <t xml:space="preserve">14.3586158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733446121216</t>
+    <t xml:space="preserve">14.1733436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564811706543</t>
+    <t xml:space="preserve">13.7564821243286</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248908996582</t>
+    <t xml:space="preserve">13.5248899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027992248535</t>
+    <t xml:space="preserve">13.8027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101621627808</t>
+    <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.061710357666</t>
+    <t xml:space="preserve">13.0617094039917</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469825744629</t>
+    <t xml:space="preserve">13.2469816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006635665894</t>
+    <t xml:space="preserve">13.2006645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712070465088</t>
+    <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543455123901</t>
+    <t xml:space="preserve">13.1543445587158</t>
   </si>
   <si>
     <t xml:space="preserve">13.9417533874512</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4049348831177</t>
+    <t xml:space="preserve">14.404935836792</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555223464966</t>
+    <t xml:space="preserve">15.6555233001709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628871917725</t>
+    <t xml:space="preserve">15.5628862380981</t>
   </si>
   <si>
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165691375732</t>
+    <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407964706421</t>
+    <t xml:space="preserve">15.8407955169678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944774627686</t>
+    <t xml:space="preserve">15.7944784164429</t>
   </si>
   <si>
     <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460256576538</t>
+    <t xml:space="preserve">15.1460237503052</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975700378418</t>
+    <t xml:space="preserve">14.4975709915161</t>
   </si>
   <si>
     <t xml:space="preserve">15.0166959762573</t>
@@ -801,6 +801,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.541482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -35313,7 +35316,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35339,7 +35342,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35365,7 +35368,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35391,7 +35394,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35417,7 +35420,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35443,7 +35446,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35469,7 +35472,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35495,7 +35498,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35521,7 +35524,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35547,7 +35550,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35573,7 +35576,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35599,7 +35602,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35625,7 +35628,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35651,7 +35654,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35677,7 +35680,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35703,7 +35706,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35729,7 +35732,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35755,7 +35758,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35781,7 +35784,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35807,7 +35810,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35833,7 +35836,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35859,7 +35862,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35885,7 +35888,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35911,7 +35914,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35937,7 +35940,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35963,7 +35966,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35989,7 +35992,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36015,7 +36018,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36041,7 +36044,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36067,7 +36070,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36093,7 +36096,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36119,7 +36122,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36145,7 +36148,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36171,7 +36174,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36197,7 +36200,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36223,7 +36226,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36249,7 +36252,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36275,7 +36278,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36301,7 +36304,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36327,7 +36330,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36353,7 +36356,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36379,7 +36382,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36405,7 +36408,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36431,7 +36434,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36509,7 +36512,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36535,7 +36538,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36561,7 +36564,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36587,7 +36590,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36639,7 +36642,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36665,7 +36668,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36717,7 +36720,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36743,7 +36746,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36769,7 +36772,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36795,7 +36798,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36821,7 +36824,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36847,7 +36850,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36873,7 +36876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36899,7 +36902,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36925,7 +36928,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36951,7 +36954,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36977,7 +36980,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37003,7 +37006,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37107,7 +37110,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37133,7 +37136,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37159,7 +37162,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37185,7 +37188,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37211,7 +37214,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37237,7 +37240,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37263,7 +37266,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37289,7 +37292,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37315,7 +37318,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37341,7 +37344,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37367,7 +37370,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37393,7 +37396,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37419,7 +37422,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37445,7 +37448,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37471,7 +37474,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37497,7 +37500,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37523,7 +37526,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37627,7 +37630,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37653,7 +37656,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37679,7 +37682,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37705,7 +37708,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37731,7 +37734,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37757,7 +37760,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37783,7 +37786,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37809,7 +37812,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37835,7 +37838,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38173,7 +38176,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38199,7 +38202,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38225,7 +38228,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38381,7 +38384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38407,7 +38410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38433,7 +38436,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38459,7 +38462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38485,7 +38488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38511,7 +38514,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38537,7 +38540,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38563,7 +38566,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38589,7 +38592,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38615,7 +38618,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38641,7 +38644,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38667,7 +38670,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38693,7 +38696,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38719,7 +38722,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38771,7 +38774,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38797,7 +38800,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39005,7 +39008,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39031,7 +39034,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39057,7 +39060,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39083,7 +39086,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39109,7 +39112,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39135,7 +39138,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39161,7 +39164,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39187,7 +39190,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39213,7 +39216,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39239,7 +39242,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39265,7 +39268,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39291,7 +39294,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39317,7 +39320,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39343,7 +39346,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39369,7 +39372,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39395,7 +39398,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39421,7 +39424,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39447,7 +39450,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39473,7 +39476,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39499,7 +39502,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39525,7 +39528,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39551,7 +39554,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39577,7 +39580,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39603,7 +39606,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39629,7 +39632,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39655,7 +39658,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39681,7 +39684,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39707,7 +39710,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39733,7 +39736,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39759,7 +39762,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39785,7 +39788,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39811,7 +39814,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39837,7 +39840,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39863,7 +39866,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39889,7 +39892,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39915,7 +39918,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39941,7 +39944,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39967,7 +39970,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39993,7 +39996,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40019,7 +40022,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40045,7 +40048,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40071,7 +40074,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40097,7 +40100,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40123,7 +40126,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40253,7 +40256,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40409,7 +40412,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40435,7 +40438,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1505" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40461,7 +40464,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40487,7 +40490,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40513,7 +40516,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40539,7 +40542,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40565,7 +40568,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1510" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -40591,7 +40594,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -40617,7 +40620,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -40669,7 +40672,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40695,7 +40698,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40877,7 +40880,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40903,7 +40906,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40929,7 +40932,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40955,7 +40958,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40981,7 +40984,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41007,7 +41010,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41033,7 +41036,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41059,7 +41062,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41085,7 +41088,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41111,7 +41114,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41137,7 +41140,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41163,7 +41166,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41189,7 +41192,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41215,7 +41218,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41241,7 +41244,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41267,7 +41270,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41293,7 +41296,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41319,7 +41322,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41345,7 +41348,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41371,7 +41374,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41397,7 +41400,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41423,7 +41426,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41449,7 +41452,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41475,7 +41478,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41501,7 +41504,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41527,7 +41530,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41553,7 +41556,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41579,7 +41582,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41605,7 +41608,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41631,7 +41634,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41657,7 +41660,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41683,7 +41686,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41709,7 +41712,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41735,7 +41738,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41761,7 +41764,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41787,7 +41790,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41813,7 +41816,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41839,7 +41842,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41865,7 +41868,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41891,7 +41894,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41917,7 +41920,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41943,7 +41946,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41969,7 +41972,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -41995,7 +41998,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42021,7 +42024,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42047,7 +42050,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42073,7 +42076,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42099,7 +42102,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42125,7 +42128,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42151,7 +42154,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42177,7 +42180,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42203,7 +42206,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42229,7 +42232,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42255,7 +42258,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42281,7 +42284,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42307,7 +42310,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42333,7 +42336,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42359,7 +42362,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42385,7 +42388,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42411,7 +42414,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42437,7 +42440,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42463,7 +42466,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42489,7 +42492,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42515,7 +42518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42541,7 +42544,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42567,7 +42570,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42593,7 +42596,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42619,7 +42622,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42645,7 +42648,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42671,7 +42674,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42697,7 +42700,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42723,7 +42726,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42749,7 +42752,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42775,7 +42778,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42801,7 +42804,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42827,7 +42830,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42853,7 +42856,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42879,7 +42882,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42905,7 +42908,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42931,7 +42934,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42957,7 +42960,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42983,7 +42986,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43009,7 +43012,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43035,7 +43038,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43061,7 +43064,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43087,7 +43090,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43113,7 +43116,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43139,7 +43142,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43165,7 +43168,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43191,7 +43194,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43217,7 +43220,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43243,7 +43246,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43269,7 +43272,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43295,7 +43298,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43321,7 +43324,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43347,7 +43350,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43373,7 +43376,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43399,7 +43402,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43425,7 +43428,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43451,7 +43454,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43477,7 +43480,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43503,7 +43506,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43529,7 +43532,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43555,7 +43558,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43581,7 +43584,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43607,7 +43610,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43633,7 +43636,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43659,7 +43662,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43685,7 +43688,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43711,7 +43714,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43737,7 +43740,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43763,7 +43766,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43789,7 +43792,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43815,7 +43818,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43841,7 +43844,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43867,7 +43870,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43893,7 +43896,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43919,7 +43922,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43945,7 +43948,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43971,7 +43974,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -43997,7 +44000,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44023,7 +44026,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44049,7 +44052,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44075,7 +44078,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44101,7 +44104,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44127,7 +44130,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44153,7 +44156,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44179,7 +44182,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44205,7 +44208,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44231,7 +44234,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44257,7 +44260,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44283,7 +44286,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44309,7 +44312,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44335,7 +44338,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44361,7 +44364,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44387,7 +44390,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44413,7 +44416,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44439,7 +44442,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44465,7 +44468,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44491,7 +44494,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44517,7 +44520,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44543,7 +44546,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44569,7 +44572,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44595,7 +44598,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44621,7 +44624,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44647,7 +44650,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44673,7 +44676,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44699,7 +44702,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44725,7 +44728,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44751,7 +44754,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44777,7 +44780,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44803,7 +44806,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44829,7 +44832,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44855,7 +44858,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44881,7 +44884,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44907,7 +44910,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44933,7 +44936,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44959,7 +44962,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44985,7 +44988,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45011,7 +45014,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45037,7 +45040,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45063,7 +45066,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45089,7 +45092,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45115,7 +45118,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45141,7 +45144,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45167,7 +45170,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45193,7 +45196,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45219,7 +45222,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45245,7 +45248,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45271,7 +45274,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45297,7 +45300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45323,7 +45326,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45349,7 +45352,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45375,7 +45378,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45401,7 +45404,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45427,7 +45430,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45453,7 +45456,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45479,7 +45482,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45505,7 +45508,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45531,7 +45534,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45557,7 +45560,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45583,7 +45586,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45609,7 +45612,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45635,7 +45638,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45661,7 +45664,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45687,7 +45690,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45713,7 +45716,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45739,7 +45742,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45765,7 +45768,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45791,7 +45794,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45817,7 +45820,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45843,7 +45846,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45869,7 +45872,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45895,7 +45898,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45921,7 +45924,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45947,7 +45950,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45973,7 +45976,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -45999,7 +46002,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46025,7 +46028,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46051,7 +46054,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46077,7 +46080,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46103,7 +46106,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46129,7 +46132,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46155,7 +46158,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46181,7 +46184,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46207,7 +46210,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46233,7 +46236,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46259,7 +46262,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46285,7 +46288,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46311,7 +46314,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46337,7 +46340,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46363,7 +46366,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46389,7 +46392,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46415,7 +46418,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46441,7 +46444,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46467,7 +46470,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46493,7 +46496,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46519,7 +46522,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46545,7 +46548,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46571,7 +46574,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46597,7 +46600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46623,7 +46626,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46649,7 +46652,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46675,7 +46678,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46701,7 +46704,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46727,7 +46730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46753,7 +46756,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46779,7 +46782,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46805,7 +46808,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46831,7 +46834,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46857,7 +46860,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46883,7 +46886,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46909,7 +46912,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46935,7 +46938,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46961,7 +46964,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46987,7 +46990,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47013,7 +47016,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47039,7 +47042,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47065,7 +47068,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47091,7 +47094,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47117,7 +47120,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47143,7 +47146,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47169,7 +47172,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47195,7 +47198,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47221,7 +47224,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47247,7 +47250,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47273,7 +47276,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47299,7 +47302,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47325,7 +47328,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47351,7 +47354,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47377,7 +47380,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47403,7 +47406,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47429,7 +47432,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47455,7 +47458,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47481,7 +47484,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47507,7 +47510,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47533,7 +47536,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47559,7 +47562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47585,7 +47588,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47611,7 +47614,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47637,7 +47640,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47663,7 +47666,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47689,7 +47692,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47715,7 +47718,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47741,7 +47744,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47767,7 +47770,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47793,7 +47796,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47819,7 +47822,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47845,7 +47848,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47871,7 +47874,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47897,7 +47900,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47923,7 +47926,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47949,7 +47952,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47975,7 +47978,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48001,7 +48004,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48027,7 +48030,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48053,7 +48056,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48079,7 +48082,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48105,7 +48108,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48131,7 +48134,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48157,7 +48160,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48183,7 +48186,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48209,7 +48212,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48235,7 +48238,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48261,7 +48264,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48287,7 +48290,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48313,7 +48316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48339,7 +48342,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48365,7 +48368,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48391,7 +48394,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48417,7 +48420,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48443,7 +48446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48469,7 +48472,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48495,7 +48498,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48521,7 +48524,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48547,7 +48550,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48573,7 +48576,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48599,7 +48602,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48625,7 +48628,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48651,7 +48654,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48677,7 +48680,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48703,7 +48706,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48729,7 +48732,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48755,7 +48758,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48781,7 +48784,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48807,7 +48810,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48833,7 +48836,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48859,7 +48862,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48885,7 +48888,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48911,7 +48914,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48937,7 +48940,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48963,7 +48966,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48989,7 +48992,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49015,7 +49018,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49041,7 +49044,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49067,7 +49070,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49093,7 +49096,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49119,7 +49122,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49145,7 +49148,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49171,7 +49174,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49197,7 +49200,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49223,7 +49226,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49249,7 +49252,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49275,7 +49278,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49301,7 +49304,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49327,7 +49330,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49353,7 +49356,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49379,7 +49382,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49405,7 +49408,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49431,7 +49434,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49457,7 +49460,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49483,7 +49486,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49509,7 +49512,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49535,7 +49538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49561,7 +49564,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49587,7 +49590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49613,7 +49616,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49639,7 +49642,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49665,7 +49668,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49691,7 +49694,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49717,7 +49720,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49743,7 +49746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49769,7 +49772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49795,7 +49798,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49821,7 +49824,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49847,7 +49850,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49873,7 +49876,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49899,7 +49902,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49925,7 +49928,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49951,7 +49954,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49977,7 +49980,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50003,7 +50006,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50029,7 +50032,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50055,7 +50058,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50081,7 +50084,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50107,7 +50110,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50133,7 +50136,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50159,7 +50162,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50185,7 +50188,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50211,7 +50214,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50237,7 +50240,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50263,7 +50266,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50289,7 +50292,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50315,7 +50318,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50341,7 +50344,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50367,7 +50370,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50393,7 +50396,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50419,7 +50422,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50445,7 +50448,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50471,7 +50474,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50497,7 +50500,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50523,7 +50526,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50549,7 +50552,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50575,7 +50578,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50601,7 +50604,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50627,7 +50630,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50653,7 +50656,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50679,7 +50682,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50705,7 +50708,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50731,7 +50734,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50757,7 +50760,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50783,7 +50786,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50809,7 +50812,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50835,7 +50838,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50861,7 +50864,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50887,7 +50890,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50913,7 +50916,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50939,7 +50942,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50965,7 +50968,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50991,7 +50994,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51017,7 +51020,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51043,7 +51046,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51069,7 +51072,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51095,7 +51098,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51121,7 +51124,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51147,7 +51150,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51173,7 +51176,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51199,7 +51202,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51225,7 +51228,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51233,7 +51236,7 @@
     </row>
     <row r="1921">
       <c r="A1921" s="1" t="n">
-        <v>45946.4526967593</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B1921" t="n">
         <v>15600</v>
@@ -51251,9 +51254,35 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1921" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="1" t="n">
+        <v>45947.4495486111</v>
+      </c>
+      <c r="B1922" t="n">
+        <v>300</v>
+      </c>
+      <c r="C1922" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1922" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1922" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1922" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118366241455</t>
+    <t xml:space="preserve">11.9118356704712</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502750396729</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654928207397</t>
+    <t xml:space="preserve">11.3654909133911</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699003219604</t>
+    <t xml:space="preserve">10.7699012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653877258301</t>
+    <t xml:space="preserve">11.0653886795044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962022781372</t>
+    <t xml:space="preserve">11.1962032318115</t>
   </si>
   <si>
     <t xml:space="preserve">11.5732555389404</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">11.119252204895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194257736206</t>
+    <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.3116264343262</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424757003784</t>
   </si>
   <si>
     <t xml:space="preserve">11.3501024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.810263633728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733268737793</t>
+    <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086185455322</t>
+    <t xml:space="preserve">10.8086194992065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683460235596</t>
+    <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087808609009</t>
+    <t xml:space="preserve">10.1087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326042175293</t>
+    <t xml:space="preserve">9.95325946807861</t>
   </si>
   <si>
     <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345386505127</t>
+    <t xml:space="preserve">9.11345481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790134429932</t>
   </si>
   <si>
     <t xml:space="preserve">9.85683822631836</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907304763794</t>
+    <t xml:space="preserve">11.2907314300537</t>
   </si>
   <si>
     <t xml:space="preserve">12.0278940200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950807571411</t>
+    <t xml:space="preserve">11.6950798034668</t>
   </si>
   <si>
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028560638428</t>
+    <t xml:space="preserve">11.7028570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862159729004</t>
+    <t xml:space="preserve">11.586217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084571838379</t>
+    <t xml:space="preserve">11.5084562301636</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639776229858</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863792419434</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641380310059</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198179244995</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310192108154</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449188232422</t>
+    <t xml:space="preserve">9.42449378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222145080566</t>
+    <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887147903442</t>
+    <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
     <t xml:space="preserve">9.7977409362793</t>
@@ -224,31 +224,31 @@
     <t xml:space="preserve">9.48670196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118057250977</t>
+    <t xml:space="preserve">9.3311824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662128448486</t>
+    <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892570495605</t>
+    <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074668884277</t>
+    <t xml:space="preserve">9.29074573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815227508545</t>
+    <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945774078369</t>
+    <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842575073242</t>
+    <t xml:space="preserve">9.71842479705811</t>
   </si>
   <si>
     <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274564743042</t>
+    <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
     <t xml:space="preserve">10.3498363494873</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064424514771</t>
+    <t xml:space="preserve">10.6064443588257</t>
   </si>
   <si>
     <t xml:space="preserve">10.6919794082642</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778904914856</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181264877319</t>
+    <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
     <t xml:space="preserve">10.0834932327271</t>
@@ -278,34 +278,34 @@
     <t xml:space="preserve">10.257345199585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885902404785</t>
+    <t xml:space="preserve">9.64885997772217</t>
   </si>
   <si>
     <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193351745605</t>
+    <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.953444480896</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959251403809</t>
+    <t xml:space="preserve">8.7795934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266510009766</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920234680176</t>
+    <t xml:space="preserve">8.64920330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037189483643</t>
+    <t xml:space="preserve">9.04037284851074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271289825439</t>
+    <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
     <t xml:space="preserve">11.1266117095947</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527587890625</t>
+    <t xml:space="preserve">10.9527597427368</t>
   </si>
   <si>
     <t xml:space="preserve">10.1704187393188</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.4311990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500419616699</t>
+    <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
     <t xml:space="preserve">9.3880786895752</t>
@@ -341,52 +341,52 @@
     <t xml:space="preserve">9.21422481536865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729740142822</t>
+    <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578548431396</t>
+    <t xml:space="preserve">9.73578453063965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442716598511</t>
+    <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115222930908</t>
+    <t xml:space="preserve">9.3011531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876581192017</t>
+    <t xml:space="preserve">7.38876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183887481689</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530305862427</t>
+    <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4756932258606</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
     <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378875732422</t>
+    <t xml:space="preserve">7.95378971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34496021270752</t>
+    <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573959350586</t>
+    <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585121154785</t>
+    <t xml:space="preserve">9.56585025787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.4772777557373</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869773864746</t>
+    <t xml:space="preserve">8.76869678497314</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441429138184</t>
@@ -416,22 +416,22 @@
     <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12298774719238</t>
+    <t xml:space="preserve">9.1229887008667</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858615875244</t>
+    <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.071587562561</t>
+    <t xml:space="preserve">11.0715866088867</t>
   </si>
   <si>
     <t xml:space="preserve">10.8944425582886</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515781402588</t>
+    <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972881317139</t>
+    <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
     <t xml:space="preserve">9.83157062530518</t>
@@ -452,19 +452,19 @@
     <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014312744141</t>
+    <t xml:space="preserve">9.92014217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744340896606</t>
+    <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487316131592</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144510269165</t>
+    <t xml:space="preserve">11.5144519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.425877571106</t>
+    <t xml:space="preserve">11.4258766174316</t>
   </si>
   <si>
     <t xml:space="preserve">10.805869102478</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630056381226</t>
+    <t xml:space="preserve">10.3630065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401496887207</t>
+    <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
     <t xml:space="preserve">10.4193983078003</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">10.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912088394165</t>
+    <t xml:space="preserve">10.6912097930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.6006059646606</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381916046143</t>
+    <t xml:space="preserve">10.2381906509399</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502614974976</t>
@@ -521,25 +521,25 @@
     <t xml:space="preserve">11.1442270278931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690557479858</t>
+    <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408643722534</t>
+    <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
     <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314682006836</t>
+    <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844854354858</t>
+    <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032787322998</t>
+    <t xml:space="preserve">12.5032796859741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.775089263916</t>
+    <t xml:space="preserve">12.7750902175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.1375026702881</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811237335205</t>
+    <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
     <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931945800781</t>
+    <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401744842529</t>
+    <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
     <t xml:space="preserve">15.4025897979736</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">15.8556051254272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462089538574</t>
+    <t xml:space="preserve">15.9462108612061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650012969971</t>
+    <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
     <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2213821411133</t>
+    <t xml:space="preserve">15.221381187439</t>
   </si>
   <si>
     <t xml:space="preserve">14.587158203125</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495706558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999151229858</t>
+    <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
     <t xml:space="preserve">14.1341409683228</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9529333114624</t>
+    <t xml:space="preserve">13.9529342651367</t>
   </si>
   <si>
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119869232178</t>
+    <t xml:space="preserve">15.3119850158691</t>
   </si>
   <si>
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230644226074</t>
+    <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196636199951</t>
+    <t xml:space="preserve">14.2196626663208</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776159286499</t>
+    <t xml:space="preserve">15.3776149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586168289185</t>
+    <t xml:space="preserve">14.3586158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733446121216</t>
+    <t xml:space="preserve">14.1733436584473</t>
   </si>
   <si>
     <t xml:space="preserve">13.7564811706543</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491163253784</t>
+    <t xml:space="preserve">13.8491172790527</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880714416504</t>
+    <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248908996582</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0617094039917</t>
+    <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.200662612915</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533885955811</t>
+    <t xml:space="preserve">15.0533876419067</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -752,28 +752,25 @@
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512538909912</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
     <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2849788665771</t>
+    <t xml:space="preserve">15.2849779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555242538452</t>
+    <t xml:space="preserve">15.6555223464966</t>
   </si>
   <si>
     <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.192343711853</t>
+    <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
     <t xml:space="preserve">15.8407974243164</t>
@@ -782,10 +779,10 @@
     <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702529907227</t>
+    <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460256576538</t>
+    <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
@@ -33317,7 +33314,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33343,7 +33340,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33369,7 +33366,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33395,7 +33392,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33447,7 +33444,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33473,7 +33470,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33499,7 +33496,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33525,7 +33522,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33551,7 +33548,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33577,7 +33574,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33603,7 +33600,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33629,7 +33626,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33655,7 +33652,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33681,7 +33678,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33707,7 +33704,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33733,7 +33730,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33759,7 +33756,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33785,7 +33782,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33811,7 +33808,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33837,7 +33834,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33889,7 +33886,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33915,7 +33912,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33941,7 +33938,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33967,7 +33964,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33993,7 +33990,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34019,7 +34016,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34045,7 +34042,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34409,7 +34406,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34435,7 +34432,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34461,7 +34458,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34747,7 +34744,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34773,7 +34770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34799,7 +34796,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34903,7 +34900,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35059,7 +35056,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35111,7 +35108,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35137,7 +35134,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35163,7 +35160,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35189,7 +35186,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35215,7 +35212,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35241,7 +35238,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35267,7 +35264,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35293,7 +35290,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35371,7 +35368,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35397,7 +35394,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35423,7 +35420,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35449,7 +35446,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35475,7 +35472,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35501,7 +35498,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35527,7 +35524,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35553,7 +35550,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35579,7 +35576,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35605,7 +35602,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35631,7 +35628,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35657,7 +35654,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35683,7 +35680,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35709,7 +35706,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35735,7 +35732,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35761,7 +35758,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35787,7 +35784,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35813,7 +35810,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35839,7 +35836,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35865,7 +35862,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35891,7 +35888,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35917,7 +35914,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35943,7 +35940,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35969,7 +35966,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35995,7 +35992,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36021,7 +36018,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36047,7 +36044,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36073,7 +36070,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36099,7 +36096,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36125,7 +36122,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36151,7 +36148,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36177,7 +36174,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36203,7 +36200,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36229,7 +36226,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36255,7 +36252,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36281,7 +36278,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36307,7 +36304,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36333,7 +36330,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36359,7 +36356,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36385,7 +36382,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36411,7 +36408,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36437,7 +36434,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36463,7 +36460,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36489,7 +36486,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36515,7 +36512,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36541,7 +36538,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36567,7 +36564,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36593,7 +36590,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36619,7 +36616,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36645,7 +36642,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36671,7 +36668,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36697,7 +36694,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -36723,7 +36720,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36749,7 +36746,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36775,7 +36772,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36801,7 +36798,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36827,7 +36824,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36853,7 +36850,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36879,7 +36876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36905,7 +36902,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36931,7 +36928,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36957,7 +36954,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36983,7 +36980,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37009,7 +37006,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37035,7 +37032,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37061,7 +37058,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37087,7 +37084,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37113,7 +37110,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37139,7 +37136,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37165,7 +37162,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37191,7 +37188,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37217,7 +37214,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37243,7 +37240,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37269,7 +37266,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37295,7 +37292,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37321,7 +37318,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37347,7 +37344,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37373,7 +37370,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37399,7 +37396,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37425,7 +37422,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37451,7 +37448,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37477,7 +37474,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37503,7 +37500,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37529,7 +37526,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37555,7 +37552,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37581,7 +37578,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37607,7 +37604,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37633,7 +37630,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37659,7 +37656,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37685,7 +37682,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37711,7 +37708,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37737,7 +37734,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37763,7 +37760,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37789,7 +37786,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37815,7 +37812,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37841,7 +37838,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -37867,7 +37864,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37893,7 +37890,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37919,7 +37916,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37945,7 +37942,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37971,7 +37968,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -37997,7 +37994,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38023,7 +38020,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38049,7 +38046,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38075,7 +38072,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38101,7 +38098,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38127,7 +38124,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38153,7 +38150,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38179,7 +38176,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38205,7 +38202,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38231,7 +38228,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38257,7 +38254,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38283,7 +38280,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38309,7 +38306,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38335,7 +38332,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38361,7 +38358,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38387,7 +38384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38413,7 +38410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38439,7 +38436,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38465,7 +38462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38491,7 +38488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38517,7 +38514,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38543,7 +38540,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38569,7 +38566,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38595,7 +38592,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38621,7 +38618,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38647,7 +38644,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38673,7 +38670,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38699,7 +38696,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38725,7 +38722,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38751,7 +38748,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38777,7 +38774,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38803,7 +38800,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -38829,7 +38826,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38855,7 +38852,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38881,7 +38878,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38907,7 +38904,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38933,7 +38930,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38959,7 +38956,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38985,7 +38982,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39011,7 +39008,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39037,7 +39034,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39063,7 +39060,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39089,7 +39086,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39115,7 +39112,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39141,7 +39138,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39167,7 +39164,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39193,7 +39190,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39219,7 +39216,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39245,7 +39242,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39271,7 +39268,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39297,7 +39294,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39323,7 +39320,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39349,7 +39346,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39375,7 +39372,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39401,7 +39398,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39427,7 +39424,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39453,7 +39450,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39479,7 +39476,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39505,7 +39502,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39531,7 +39528,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39557,7 +39554,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39583,7 +39580,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39609,7 +39606,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39635,7 +39632,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39661,7 +39658,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39687,7 +39684,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39713,7 +39710,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39739,7 +39736,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39765,7 +39762,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39791,7 +39788,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39817,7 +39814,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39843,7 +39840,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39869,7 +39866,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39895,7 +39892,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39921,7 +39918,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39947,7 +39944,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39973,7 +39970,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39999,7 +39996,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40025,7 +40022,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40051,7 +40048,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40077,7 +40074,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40103,7 +40100,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40129,7 +40126,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40155,7 +40152,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40181,7 +40178,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40207,7 +40204,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40233,7 +40230,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40259,7 +40256,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40285,7 +40282,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40311,7 +40308,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40337,7 +40334,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40363,7 +40360,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40389,7 +40386,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40649,7 +40646,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40675,7 +40672,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40701,7 +40698,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40727,7 +40724,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40753,7 +40750,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40779,7 +40776,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40805,7 +40802,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40831,7 +40828,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40857,7 +40854,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -40883,7 +40880,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40909,7 +40906,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40935,7 +40932,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40961,7 +40958,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40987,7 +40984,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41013,7 +41010,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41039,7 +41036,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41065,7 +41062,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41091,7 +41088,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41117,7 +41114,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41143,7 +41140,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41169,7 +41166,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41195,7 +41192,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41221,7 +41218,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41247,7 +41244,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41273,7 +41270,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41299,7 +41296,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41325,7 +41322,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41351,7 +41348,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41377,7 +41374,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41403,7 +41400,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41429,7 +41426,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41455,7 +41452,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41481,7 +41478,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41507,7 +41504,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41533,7 +41530,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41559,7 +41556,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41585,7 +41582,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41611,7 +41608,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41637,7 +41634,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41663,7 +41660,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41689,7 +41686,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41715,7 +41712,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41741,7 +41738,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41767,7 +41764,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41793,7 +41790,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41819,7 +41816,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41845,7 +41842,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41871,7 +41868,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41897,7 +41894,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41923,7 +41920,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41949,7 +41946,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41975,7 +41972,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42001,7 +41998,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42027,7 +42024,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42053,7 +42050,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42079,7 +42076,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42105,7 +42102,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42131,7 +42128,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42157,7 +42154,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42183,7 +42180,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42209,7 +42206,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42235,7 +42232,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42261,7 +42258,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42287,7 +42284,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42313,7 +42310,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42339,7 +42336,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42365,7 +42362,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42391,7 +42388,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42417,7 +42414,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42443,7 +42440,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42469,7 +42466,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42495,7 +42492,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42521,7 +42518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42547,7 +42544,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42573,7 +42570,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42599,7 +42596,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42625,7 +42622,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42651,7 +42648,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42677,7 +42674,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42703,7 +42700,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42729,7 +42726,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42755,7 +42752,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42781,7 +42778,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42807,7 +42804,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42833,7 +42830,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42859,7 +42856,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42885,7 +42882,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42911,7 +42908,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42937,7 +42934,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42963,7 +42960,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42989,7 +42986,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43015,7 +43012,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43041,7 +43038,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43067,7 +43064,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43093,7 +43090,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43119,7 +43116,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43145,7 +43142,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43171,7 +43168,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43197,7 +43194,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43223,7 +43220,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43249,7 +43246,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43275,7 +43272,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43301,7 +43298,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43327,7 +43324,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43353,7 +43350,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43379,7 +43376,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43405,7 +43402,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43431,7 +43428,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43457,7 +43454,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43483,7 +43480,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43509,7 +43506,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43535,7 +43532,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43561,7 +43558,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43587,7 +43584,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43613,7 +43610,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43639,7 +43636,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43665,7 +43662,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43691,7 +43688,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43717,7 +43714,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43743,7 +43740,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43769,7 +43766,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43795,7 +43792,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43821,7 +43818,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43847,7 +43844,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43873,7 +43870,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43899,7 +43896,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43925,7 +43922,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43951,7 +43948,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43977,7 +43974,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44003,7 +44000,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44029,7 +44026,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44055,7 +44052,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44081,7 +44078,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44107,7 +44104,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44133,7 +44130,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44159,7 +44156,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44185,7 +44182,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44211,7 +44208,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44237,7 +44234,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44263,7 +44260,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44289,7 +44286,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44315,7 +44312,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44341,7 +44338,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44367,7 +44364,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44393,7 +44390,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44419,7 +44416,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44445,7 +44442,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44471,7 +44468,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44497,7 +44494,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44523,7 +44520,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44549,7 +44546,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44575,7 +44572,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44601,7 +44598,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44627,7 +44624,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44653,7 +44650,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44679,7 +44676,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44705,7 +44702,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44731,7 +44728,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44757,7 +44754,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44783,7 +44780,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44809,7 +44806,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44835,7 +44832,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44861,7 +44858,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44887,7 +44884,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44913,7 +44910,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44939,7 +44936,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44965,7 +44962,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44991,7 +44988,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45017,7 +45014,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45043,7 +45040,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45069,7 +45066,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45095,7 +45092,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45121,7 +45118,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45147,7 +45144,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45173,7 +45170,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45199,7 +45196,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45225,7 +45222,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45251,7 +45248,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45277,7 +45274,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45303,7 +45300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45329,7 +45326,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45355,7 +45352,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45381,7 +45378,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45407,7 +45404,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45433,7 +45430,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45459,7 +45456,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45485,7 +45482,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45511,7 +45508,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45537,7 +45534,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45563,7 +45560,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45589,7 +45586,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45615,7 +45612,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45641,7 +45638,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45667,7 +45664,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45693,7 +45690,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45719,7 +45716,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45745,7 +45742,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45771,7 +45768,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45797,7 +45794,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45823,7 +45820,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45849,7 +45846,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45875,7 +45872,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45901,7 +45898,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45927,7 +45924,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45953,7 +45950,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45979,7 +45976,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46005,7 +46002,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46031,7 +46028,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46057,7 +46054,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46083,7 +46080,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46109,7 +46106,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46135,7 +46132,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46161,7 +46158,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46187,7 +46184,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46213,7 +46210,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46239,7 +46236,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46265,7 +46262,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46291,7 +46288,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46317,7 +46314,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46343,7 +46340,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46369,7 +46366,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46395,7 +46392,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46421,7 +46418,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46447,7 +46444,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46473,7 +46470,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46499,7 +46496,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46525,7 +46522,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46551,7 +46548,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46577,7 +46574,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46603,7 +46600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46629,7 +46626,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46655,7 +46652,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46681,7 +46678,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46707,7 +46704,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46733,7 +46730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46759,7 +46756,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46785,7 +46782,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46811,7 +46808,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46837,7 +46834,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46863,7 +46860,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46889,7 +46886,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46915,7 +46912,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46941,7 +46938,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46967,7 +46964,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46993,7 +46990,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47019,7 +47016,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47045,7 +47042,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47071,7 +47068,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47097,7 +47094,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47123,7 +47120,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47149,7 +47146,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47175,7 +47172,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47201,7 +47198,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47227,7 +47224,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47253,7 +47250,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47279,7 +47276,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47305,7 +47302,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47331,7 +47328,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47357,7 +47354,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47383,7 +47380,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47409,7 +47406,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47435,7 +47432,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47461,7 +47458,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47487,7 +47484,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47513,7 +47510,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47539,7 +47536,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47565,7 +47562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47591,7 +47588,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47617,7 +47614,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47643,7 +47640,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47669,7 +47666,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47695,7 +47692,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47721,7 +47718,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47747,7 +47744,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47773,7 +47770,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47799,7 +47796,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47825,7 +47822,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47851,7 +47848,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47877,7 +47874,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47903,7 +47900,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47929,7 +47926,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47955,7 +47952,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47981,7 +47978,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48007,7 +48004,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48033,7 +48030,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48059,7 +48056,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48085,7 +48082,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48111,7 +48108,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48137,7 +48134,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48163,7 +48160,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48189,7 +48186,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48215,7 +48212,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48241,7 +48238,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48267,7 +48264,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48293,7 +48290,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48319,7 +48316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48345,7 +48342,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48371,7 +48368,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48397,7 +48394,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48423,7 +48420,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48449,7 +48446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48475,7 +48472,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48501,7 +48498,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48527,7 +48524,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48553,7 +48550,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48579,7 +48576,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48605,7 +48602,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48631,7 +48628,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48657,7 +48654,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48683,7 +48680,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48709,7 +48706,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48735,7 +48732,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48761,7 +48758,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48787,7 +48784,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48813,7 +48810,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48839,7 +48836,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48865,7 +48862,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48891,7 +48888,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48917,7 +48914,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48943,7 +48940,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48969,7 +48966,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48995,7 +48992,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49021,7 +49018,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49047,7 +49044,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49073,7 +49070,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49099,7 +49096,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49125,7 +49122,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49151,7 +49148,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49177,7 +49174,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49203,7 +49200,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49229,7 +49226,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49255,7 +49252,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49281,7 +49278,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49307,7 +49304,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49333,7 +49330,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49359,7 +49356,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49385,7 +49382,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49411,7 +49408,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49437,7 +49434,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49463,7 +49460,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49489,7 +49486,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49515,7 +49512,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49541,7 +49538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49567,7 +49564,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49593,7 +49590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49619,7 +49616,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49645,7 +49642,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49671,7 +49668,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49697,7 +49694,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49723,7 +49720,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49749,7 +49746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49775,7 +49772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49801,7 +49798,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49827,7 +49824,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49853,7 +49850,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49879,7 +49876,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49905,7 +49902,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49931,7 +49928,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49957,7 +49954,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49983,7 +49980,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50009,7 +50006,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50035,7 +50032,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50061,7 +50058,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50087,7 +50084,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50113,7 +50110,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50139,7 +50136,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50165,7 +50162,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50191,7 +50188,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50217,7 +50214,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50243,7 +50240,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50269,7 +50266,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50295,7 +50292,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50321,7 +50318,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50347,7 +50344,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50373,7 +50370,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50399,7 +50396,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50425,7 +50422,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50451,7 +50448,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50477,7 +50474,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50503,7 +50500,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50529,7 +50526,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50555,7 +50552,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50581,7 +50578,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50607,7 +50604,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50633,7 +50630,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50659,7 +50656,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50685,7 +50682,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50711,7 +50708,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50737,7 +50734,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50763,7 +50760,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50789,7 +50786,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50815,7 +50812,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50841,7 +50838,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50867,7 +50864,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50893,7 +50890,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50919,7 +50916,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50945,7 +50942,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50971,7 +50968,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50997,7 +50994,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51023,7 +51020,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51049,7 +51046,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51075,7 +51072,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51101,7 +51098,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51127,7 +51124,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51153,7 +51150,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51179,7 +51176,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51205,7 +51202,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51231,7 +51228,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51257,7 +51254,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51283,7 +51280,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51309,7 +51306,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51317,7 +51314,7 @@
     </row>
     <row r="1924">
       <c r="A1924" s="1" t="n">
-        <v>45951.5329398148</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B1924" t="n">
         <v>1800</v>
@@ -51335,9 +51332,35 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1924" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="1" t="n">
+        <v>45952.5757291667</v>
+      </c>
+      <c r="B1925" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1925" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1925" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1925" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1925" t="s">
+        <v>313</v>
+      </c>
+      <c r="H1925" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -47,46 +47,46 @@
     <t xml:space="preserve">11.9256858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577272415161</t>
+    <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654918670654</t>
+    <t xml:space="preserve">11.3654909133911</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699003219604</t>
+    <t xml:space="preserve">10.7699012756348</t>
   </si>
   <si>
     <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729797363281</t>
+    <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653877258301</t>
+    <t xml:space="preserve">11.0653886795044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962022781372</t>
+    <t xml:space="preserve">11.1962032318115</t>
   </si>
   <si>
     <t xml:space="preserve">11.5732574462891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.119252204895</t>
+    <t xml:space="preserve">11.1192531585693</t>
   </si>
   <si>
     <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116254806519</t>
+    <t xml:space="preserve">11.3116273880005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948385238647</t>
+    <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
     <t xml:space="preserve">11.5424776077271</t>
@@ -95,109 +95,109 @@
     <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102617263794</t>
+    <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
     <t xml:space="preserve">11.7733249664307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963758468628</t>
+    <t xml:space="preserve">11.6963768005371</t>
   </si>
   <si>
     <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579027175903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807790756226</t>
+    <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
     <t xml:space="preserve">11.2751770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086185455322</t>
+    <t xml:space="preserve">10.8086194992065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349044799805</t>
+    <t xml:space="preserve">10.5349035263062</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087789535522</t>
+    <t xml:space="preserve">10.1087779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326042175293</t>
+    <t xml:space="preserve">9.9532585144043</t>
   </si>
   <si>
     <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345386505127</t>
+    <t xml:space="preserve">9.11345291137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683822631836</t>
+    <t xml:space="preserve">9.85683727264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2642993927002</t>
+    <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
     <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278930664062</t>
+    <t xml:space="preserve">12.0278921127319</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750156402588</t>
+    <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862159729004</t>
+    <t xml:space="preserve">11.586217880249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084571838379</t>
+    <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639776229858</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8863792419434</t>
+    <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641380310059</t>
+    <t xml:space="preserve">10.9641389846802</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332363128662</t>
+    <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.40894031524658</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449378967285</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420610427856</t>
+    <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7977409362793</t>
+    <t xml:space="preserve">9.79773998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670196533203</t>
+    <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.33118057250977</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074573516846</t>
+    <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
     <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945487976074</t>
+    <t xml:space="preserve">9.09945583343506</t>
   </si>
   <si>
     <t xml:space="preserve">9.71842575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087797164917</t>
+    <t xml:space="preserve">10.3087778091431</t>
   </si>
   <si>
     <t xml:space="preserve">10.2745637893677</t>
@@ -260,43 +260,43 @@
     <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919803619385</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353713989258</t>
+    <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7789039611816</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181255340576</t>
+    <t xml:space="preserve">10.5181264877319</t>
   </si>
   <si>
     <t xml:space="preserve">10.0834922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.257345199585</t>
+    <t xml:space="preserve">10.2573461532593</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885997772217</t>
+    <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963840484619</t>
+    <t xml:space="preserve">9.90963745117188</t>
   </si>
   <si>
     <t xml:space="preserve">9.56193161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.86651992797852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959251403809</t>
+    <t xml:space="preserve">8.77959156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266605377197</t>
+    <t xml:space="preserve">8.69266700744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271194458008</t>
+    <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266117095947</t>
+    <t xml:space="preserve">11.126612663269</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004655838013</t>
+    <t xml:space="preserve">11.300464630127</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527597427368</t>
+    <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704187393188</t>
+    <t xml:space="preserve">10.1704196929932</t>
   </si>
   <si>
     <t xml:space="preserve">9.99656677246094</t>
@@ -341,37 +341,37 @@
     <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422576904297</t>
+    <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729835510254</t>
+    <t xml:space="preserve">9.12729740142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578548431396</t>
+    <t xml:space="preserve">9.73578453063965</t>
   </si>
   <si>
     <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115127563477</t>
+    <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725151062012</t>
+    <t xml:space="preserve">7.99725198745728</t>
   </si>
   <si>
     <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183887481689</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.25837564468384</t>
   </si>
   <si>
     <t xml:space="preserve">7.34530162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4756932258606</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
     <t xml:space="preserve">7.82339906692505</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">7.95378923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3449592590332</t>
+    <t xml:space="preserve">8.34496021270752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573863983154</t>
+    <t xml:space="preserve">8.60573959350586</t>
   </si>
   <si>
     <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585216522217</t>
+    <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4772777557373</t>
+    <t xml:space="preserve">9.47727870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870525360107</t>
+    <t xml:space="preserve">9.38870620727539</t>
   </si>
   <si>
     <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85726928710938</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
     <t xml:space="preserve">8.76869773864746</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72441101074219</t>
+    <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21156024932861</t>
+    <t xml:space="preserve">9.2115592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298679351807</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
@@ -428,40 +428,40 @@
     <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013275146484</t>
+    <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858606338501</t>
+    <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944416046143</t>
+    <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
     <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
     <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83157062530518</t>
+    <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74299716949463</t>
+    <t xml:space="preserve">9.74299621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014122009277</t>
+    <t xml:space="preserve">9.92014217376709</t>
   </si>
   <si>
     <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487316131592</t>
+    <t xml:space="preserve">11.2487335205078</t>
   </si>
   <si>
     <t xml:space="preserve">11.5144510269165</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287250518799</t>
   </si>
   <si>
     <t xml:space="preserve">10.7172966003418</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">10.1475887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818117141724</t>
+    <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
     <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78517436981201</t>
+    <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381916046143</t>
+    <t xml:space="preserve">10.2381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502614974976</t>
+    <t xml:space="preserve">12.0502605438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408643722534</t>
+    <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
     <t xml:space="preserve">11.6878471374512</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375017166138</t>
+    <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562950134277</t>
+    <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281055450439</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811246871948</t>
+    <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
     <t xml:space="preserve">14.3153486251831</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931926727295</t>
+    <t xml:space="preserve">15.4931917190552</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401754379272</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650012969971</t>
+    <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
     <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2213802337646</t>
+    <t xml:space="preserve">15.221381187439</t>
   </si>
   <si>
     <t xml:space="preserve">14.5871591567993</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999160766602</t>
+    <t xml:space="preserve">13.4999151229858</t>
   </si>
   <si>
     <t xml:space="preserve">14.1341409683228</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">12.5938816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468988418579</t>
+    <t xml:space="preserve">13.0468997955322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5905208587646</t>
+    <t xml:space="preserve">13.5905199050903</t>
   </si>
   <si>
     <t xml:space="preserve">13.3187093734741</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119859695435</t>
+    <t xml:space="preserve">15.3119850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264251708984</t>
+    <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230634689331</t>
+    <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>
@@ -51372,7 +51372,7 @@
     </row>
     <row r="1926">
       <c r="A1926" s="1" t="n">
-        <v>45953.4383449074</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B1926" t="n">
         <v>700</v>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -44,37 +44,37 @@
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256858825684</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654909133911</t>
+    <t xml:space="preserve">11.3654928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699012756348</t>
+    <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314947128296</t>
+    <t xml:space="preserve">10.9314937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653886795044</t>
+    <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962032318115</t>
+    <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732574462891</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
     <t xml:space="preserve">11.1192531585693</t>
@@ -83,31 +83,31 @@
     <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116273880005</t>
+    <t xml:space="preserve">11.3116283416748</t>
   </si>
   <si>
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424776077271</t>
+    <t xml:space="preserve">11.5424766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501014709473</t>
+    <t xml:space="preserve">11.3501024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.810263633728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733249664307</t>
+    <t xml:space="preserve">11.7733268737793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963768005371</t>
+    <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657011032104</t>
+    <t xml:space="preserve">11.9657001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579027175903</t>
+    <t xml:space="preserve">11.6579008102417</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807781219482</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">11.2751770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086194992065</t>
+    <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349035263062</t>
@@ -128,58 +128,58 @@
     <t xml:space="preserve">10.1087779998779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9532585144043</t>
+    <t xml:space="preserve">9.95326042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998023986816</t>
+    <t xml:space="preserve">9.71997928619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345291137695</t>
+    <t xml:space="preserve">9.11345481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790134429932</t>
   </si>
   <si>
     <t xml:space="preserve">9.85683727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51780414581299</t>
+    <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
     <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278921127319</t>
+    <t xml:space="preserve">12.0278940200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950807571411</t>
+    <t xml:space="preserve">11.6950798034668</t>
   </si>
   <si>
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028579711914</t>
+    <t xml:space="preserve">11.7028570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.586217880249</t>
+    <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
     <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639757156372</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196575164795</t>
+    <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863773345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641389846802</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310201644897</t>
+    <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332458496094</t>
+    <t xml:space="preserve">9.67332363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894031524658</t>
+    <t xml:space="preserve">9.40894222259521</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449378967285</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">9.64222145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550067901611</t>
+    <t xml:space="preserve">9.8754997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476602554321</t>
+    <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342059135437</t>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79773998260498</t>
+    <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.48670101165771</t>
@@ -230,13 +230,13 @@
     <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892475128174</t>
+    <t xml:space="preserve">9.47892379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074668884277</t>
+    <t xml:space="preserve">9.29074573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815227508545</t>
   </si>
   <si>
     <t xml:space="preserve">9.09945583343506</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353723526001</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7789058685303</t>
+    <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
     <t xml:space="preserve">10.5181264877319</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963745117188</t>
+    <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193161010742</t>
+    <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344543457031</t>
+    <t xml:space="preserve">8.95344638824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651992797852</t>
+    <t xml:space="preserve">8.86652088165283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959156036377</t>
+    <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266700744629</t>
+    <t xml:space="preserve">8.69266510009766</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
@@ -305,28 +305,28 @@
     <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271289825439</t>
+    <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126612663269</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.300464630127</t>
+    <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658323287964</t>
+    <t xml:space="preserve">10.8658332824707</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919784545898</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704196929932</t>
+    <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99656677246094</t>
+    <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
     <t xml:space="preserve">10.6050519943237</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729740142822</t>
+    <t xml:space="preserve">9.12729835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578453063965</t>
+    <t xml:space="preserve">9.73578357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442726135254</t>
+    <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
     <t xml:space="preserve">9.30115222930908</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183935165405</t>
+    <t xml:space="preserve">7.30183839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837564468384</t>
+    <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530162811279</t>
+    <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569274902344</t>
+    <t xml:space="preserve">7.47569227218628</t>
   </si>
   <si>
     <t xml:space="preserve">7.82339906692505</t>
@@ -380,58 +380,58 @@
     <t xml:space="preserve">7.95378923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34496021270752</t>
+    <t xml:space="preserve">8.34495830535889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573959350586</t>
+    <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585121154785</t>
+    <t xml:space="preserve">9.56585216522217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727870941162</t>
+    <t xml:space="preserve">9.47727966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870620727539</t>
+    <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85727024078369</t>
+    <t xml:space="preserve">8.85726928710938</t>
   </si>
   <si>
     <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441524505615</t>
+    <t xml:space="preserve">9.03441619873047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012523651123</t>
+    <t xml:space="preserve">8.68012428283691</t>
   </si>
   <si>
     <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2115592956543</t>
+    <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12298679351807</t>
+    <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50297927856445</t>
+    <t xml:space="preserve">8.50297832489014</t>
   </si>
   <si>
     <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013370513916</t>
+    <t xml:space="preserve">9.30013465881348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515781402588</t>
+    <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
     <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83156967163086</t>
+    <t xml:space="preserve">9.83157062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74299621582031</t>
+    <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
     <t xml:space="preserve">9.92014217376709</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487335205078</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">11.5144510269165</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">11.425877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.805869102478</t>
+    <t xml:space="preserve">10.8058700561523</t>
   </si>
   <si>
     <t xml:space="preserve">10.6287250518799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
     <t xml:space="preserve">10.3630056381226</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">10.5401515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193983078003</t>
+    <t xml:space="preserve">10.4193992614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100021362305</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502605438232</t>
+    <t xml:space="preserve">12.0502614974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">11.1442260742188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690547943115</t>
+    <t xml:space="preserve">11.8690538406372</t>
   </si>
   <si>
     <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878471374512</t>
+    <t xml:space="preserve">11.6878480911255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314682006836</t>
+    <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
     <t xml:space="preserve">12.6844844818115</t>
@@ -551,25 +551,25 @@
     <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281055450439</t>
+    <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435371398926</t>
+    <t xml:space="preserve">14.0435380935669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811237335205</t>
+    <t xml:space="preserve">13.6811227798462</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931917190552</t>
+    <t xml:space="preserve">15.4931936264038</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4025897979736</t>
+    <t xml:space="preserve">15.402587890625</t>
   </si>
   <si>
     <t xml:space="preserve">15.8556060791016</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307792663574</t>
+    <t xml:space="preserve">15.1307802200317</t>
   </si>
   <si>
     <t xml:space="preserve">15.221381187439</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">14.5871591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8623304367065</t>
+    <t xml:space="preserve">13.8623313903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4965543746948</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999151229858</t>
+    <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
     <t xml:space="preserve">14.1341409683228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4093132019043</t>
+    <t xml:space="preserve">13.40931224823</t>
   </si>
   <si>
     <t xml:space="preserve">12.5938816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468997955322</t>
+    <t xml:space="preserve">13.0468988418579</t>
   </si>
   <si>
     <t xml:space="preserve">13.5905199050903</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656911849976</t>
+    <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
     <t xml:space="preserve">13.9529333114624</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512519836426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1270265579224</t>
+    <t xml:space="preserve">14.127025604248</t>
   </si>
   <si>
     <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365261077881</t>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196626663208</t>
+    <t xml:space="preserve">14.2196636199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070705413818</t>
+    <t xml:space="preserve">15.0070714950562</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586158752441</t>
+    <t xml:space="preserve">14.3586168289185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733436584473</t>
+    <t xml:space="preserve">14.1733446121216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564821243286</t>
+    <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880723953247</t>
+    <t xml:space="preserve">13.9880714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248899459839</t>
+    <t xml:space="preserve">13.5248908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027982711792</t>
+    <t xml:space="preserve">13.8027992248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">13.3859357833862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.339617729187</t>
+    <t xml:space="preserve">13.3396167755127</t>
   </si>
   <si>
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101631164551</t>
+    <t xml:space="preserve">13.7101621627808</t>
   </si>
   <si>
     <t xml:space="preserve">13.0617094039917</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">13.2469816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006645202637</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543445587158</t>
+    <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9417533874512</t>
+    <t xml:space="preserve">13.9417543411255</t>
   </si>
   <si>
     <t xml:space="preserve">15.0533876419067</t>
@@ -749,10 +749,13 @@
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.404935836792</t>
+    <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
@@ -773,28 +776,28 @@
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407955169678</t>
+    <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944784164429</t>
+    <t xml:space="preserve">15.7944765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702520370483</t>
+    <t xml:space="preserve">15.4702529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460237503052</t>
+    <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975709915161</t>
+    <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0166959762573</t>
+    <t xml:space="preserve">15.016695022583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -803,10 +806,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365251541138</t>
+    <t xml:space="preserve">14.5414838790894</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968648910522</t>
+    <t xml:space="preserve">15.3968658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572036743164</t>
+    <t xml:space="preserve">16.1572017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720769882202</t>
+    <t xml:space="preserve">15.8720779418945</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315673828125</t>
+    <t xml:space="preserve">14.7315683364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522449493408</t>
+    <t xml:space="preserve">16.2522468566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -33320,7 +33320,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33346,7 +33346,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33372,7 +33372,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33398,7 +33398,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33450,7 +33450,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33476,7 +33476,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33502,7 +33502,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33528,7 +33528,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33554,7 +33554,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33580,7 +33580,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33606,7 +33606,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33632,7 +33632,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33658,7 +33658,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33684,7 +33684,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33710,7 +33710,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33736,7 +33736,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33762,7 +33762,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33788,7 +33788,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33814,7 +33814,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33840,7 +33840,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33892,7 +33892,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33918,7 +33918,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33944,7 +33944,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33970,7 +33970,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33996,7 +33996,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34022,7 +34022,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34048,7 +34048,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34412,7 +34412,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34438,7 +34438,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34464,7 +34464,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34750,7 +34750,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34776,7 +34776,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34802,7 +34802,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34906,7 +34906,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35062,7 +35062,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35114,7 +35114,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35140,7 +35140,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35166,7 +35166,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35192,7 +35192,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35218,7 +35218,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35244,7 +35244,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35270,7 +35270,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35296,7 +35296,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35322,7 +35322,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35348,7 +35348,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36466,7 +36466,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36492,7 +36492,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36622,7 +36622,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36700,7 +36700,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37038,7 +37038,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37064,7 +37064,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37090,7 +37090,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37558,7 +37558,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37584,7 +37584,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37610,7 +37610,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37870,7 +37870,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37896,7 +37896,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37922,7 +37922,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37948,7 +37948,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37974,7 +37974,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38000,7 +38000,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38026,7 +38026,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38052,7 +38052,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38078,7 +38078,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38104,7 +38104,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38130,7 +38130,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38156,7 +38156,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38260,7 +38260,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38286,7 +38286,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38312,7 +38312,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38338,7 +38338,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38364,7 +38364,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38754,7 +38754,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38832,7 +38832,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38858,7 +38858,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38884,7 +38884,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38910,7 +38910,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38936,7 +38936,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38962,7 +38962,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38988,7 +38988,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40158,7 +40158,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40184,7 +40184,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40210,7 +40210,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40236,7 +40236,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40288,7 +40288,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40314,7 +40314,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40340,7 +40340,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40366,7 +40366,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40392,7 +40392,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40418,7 +40418,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40444,7 +40444,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1505" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40470,7 +40470,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40496,7 +40496,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40522,7 +40522,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40548,7 +40548,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40574,7 +40574,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1510" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -40600,7 +40600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -40626,7 +40626,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>264</v>
+        <v>213</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -40652,7 +40652,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40730,7 +40730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40756,7 +40756,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40782,7 +40782,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40808,7 +40808,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40834,7 +40834,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40860,7 +40860,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -51393,6 +51393,58 @@
         <v>315</v>
       </c>
       <c r="H1926" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="1" t="n">
+        <v>45954.2916666667</v>
+      </c>
+      <c r="B1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1927" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1927" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1927" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="1" t="n">
+        <v>45957.5609027778</v>
+      </c>
+      <c r="B1928" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C1928" t="n">
+        <v>16</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1928" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1928" t="s">
+        <v>323</v>
+      </c>
+      <c r="H1928" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256868362427</t>
+    <t xml:space="preserve">11.9256858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577281951904</t>
+    <t xml:space="preserve">11.1577272415161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654928207397</t>
+    <t xml:space="preserve">11.3654909133911</t>
   </si>
   <si>
     <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007158279419</t>
+    <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314937591553</t>
+    <t xml:space="preserve">10.9314956665039</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653877258301</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192531585693</t>
+    <t xml:space="preserve">11.119252204895</t>
   </si>
   <si>
     <t xml:space="preserve">11.6194267272949</t>
@@ -89,34 +89,34 @@
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501024246216</t>
+    <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
     <t xml:space="preserve">11.810263633728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733268737793</t>
+    <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963758468628</t>
+    <t xml:space="preserve">11.6963748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657001495361</t>
+    <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6579008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807781219482</t>
+    <t xml:space="preserve">11.0807771682739</t>
   </si>
   <si>
     <t xml:space="preserve">11.2751770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086185455322</t>
+    <t xml:space="preserve">10.8086194992065</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349035263062</t>
@@ -125,31 +125,31 @@
     <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087779998779</t>
+    <t xml:space="preserve">10.1087789535522</t>
   </si>
   <si>
     <t xml:space="preserve">9.95326042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71997928619385</t>
+    <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345481872559</t>
+    <t xml:space="preserve">9.11345386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790134429932</t>
+    <t xml:space="preserve">9.09790325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5178050994873</t>
+    <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2642993927002</t>
+    <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907295227051</t>
+    <t xml:space="preserve">11.2907285690308</t>
   </si>
   <si>
     <t xml:space="preserve">12.0278940200806</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028589248657</t>
   </si>
   <si>
     <t xml:space="preserve">11.5862169265747</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639757156372</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529376983643</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8863773345947</t>
+    <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641389846802</t>
+    <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975786209106</t>
+    <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198188781738</t>
+    <t xml:space="preserve">10.4198198318481</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332363128662</t>
+    <t xml:space="preserve">9.67332553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449378967285</t>
@@ -206,61 +206,61 @@
     <t xml:space="preserve">9.64222145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8754997253418</t>
+    <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420600891113</t>
+    <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7977409362793</t>
+    <t xml:space="preserve">9.79774188995361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670101165771</t>
+    <t xml:space="preserve">9.4867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118057250977</t>
+    <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
     <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892379760742</t>
+    <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074573516846</t>
+    <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815227508545</t>
+    <t xml:space="preserve">8.97815036773682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945583343506</t>
+    <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842575073242</t>
+    <t xml:space="preserve">9.71842479705811</t>
   </si>
   <si>
     <t xml:space="preserve">10.3087778091431</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2745637893677</t>
+    <t xml:space="preserve">10.2745628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498363494873</t>
+    <t xml:space="preserve">10.3498344421387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076923370361</t>
+    <t xml:space="preserve">10.0076932907104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064424514771</t>
+    <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919803619385</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
     <t xml:space="preserve">10.4353713989258</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181264877319</t>
+    <t xml:space="preserve">10.5181245803833</t>
   </si>
   <si>
     <t xml:space="preserve">10.0834922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2573461532593</t>
+    <t xml:space="preserve">10.257345199585</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885902404785</t>
@@ -284,28 +284,28 @@
     <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193256378174</t>
+    <t xml:space="preserve">9.56193161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86652088165283</t>
+    <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
     <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266510009766</t>
+    <t xml:space="preserve">8.69266700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920234680176</t>
+    <t xml:space="preserve">8.64920139312744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037189483643</t>
+    <t xml:space="preserve">9.04037284851074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271194458008</t>
+    <t xml:space="preserve">9.82271099090576</t>
   </si>
   <si>
     <t xml:space="preserve">11.1266117095947</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658332824707</t>
+    <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
     <t xml:space="preserve">10.1704187393188</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311981201172</t>
+    <t xml:space="preserve">10.4311990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500610351562</t>
+    <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3880786895752</t>
+    <t xml:space="preserve">9.38807964324951</t>
   </si>
   <si>
     <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729835510254</t>
+    <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578357696533</t>
+    <t xml:space="preserve">9.73578453063965</t>
   </si>
   <si>
     <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115222930908</t>
+    <t xml:space="preserve">9.3011531829834</t>
   </si>
   <si>
     <t xml:space="preserve">7.99725198745728</t>
@@ -362,58 +362,58 @@
     <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183839797974</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
     <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530210494995</t>
+    <t xml:space="preserve">7.34530305862427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569227218628</t>
+    <t xml:space="preserve">7.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339906692505</t>
+    <t xml:space="preserve">7.82339954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378923416138</t>
+    <t xml:space="preserve">7.95378875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34495830535889</t>
+    <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585216522217</t>
+    <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727966308594</t>
+    <t xml:space="preserve">9.47727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584274291992</t>
+    <t xml:space="preserve">8.94584178924561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85726928710938</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869773864746</t>
+    <t xml:space="preserve">8.76869678497314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441619873047</t>
+    <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.68012428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7244119644165</t>
+    <t xml:space="preserve">8.72441101074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.21156024932861</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50297832489014</t>
+    <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013465881348</t>
+    <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
     <t xml:space="preserve">10.1858606338501</t>
@@ -437,25 +437,25 @@
     <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944425582886</t>
+    <t xml:space="preserve">10.8944416046143</t>
   </si>
   <si>
     <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
     <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83157062530518</t>
+    <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014217376709</t>
+    <t xml:space="preserve">9.92014122009277</t>
   </si>
   <si>
     <t xml:space="preserve">10.2744331359863</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">11.425877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8058700561523</t>
+    <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287250518799</t>
+    <t xml:space="preserve">10.6287240982056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172975540161</t>
+    <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630056381226</t>
+    <t xml:space="preserve">10.3630065917969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401515960693</t>
+    <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
     <t xml:space="preserve">10.4193992614746</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475887298584</t>
+    <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
     <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.963020324707</t>
+    <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
     <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502614974976</t>
+    <t xml:space="preserve">12.0502624511719</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">11.8690538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408634185791</t>
+    <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878480911255</t>
+    <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314691543579</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032787322998</t>
+    <t xml:space="preserve">12.5032777786255</t>
   </si>
   <si>
     <t xml:space="preserve">12.775089263916</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562959671021</t>
+    <t xml:space="preserve">12.9562969207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435380935669</t>
+    <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
     <t xml:space="preserve">13.6811227798462</t>
@@ -566,31 +566,31 @@
     <t xml:space="preserve">15.4931936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401754379272</t>
+    <t xml:space="preserve">15.0401763916016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.402587890625</t>
+    <t xml:space="preserve">15.4025888442993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556060791016</t>
+    <t xml:space="preserve">15.8556070327759</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462099075317</t>
+    <t xml:space="preserve">15.9462108612061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650022506714</t>
   </si>
   <si>
     <t xml:space="preserve">15.1307802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.221381187439</t>
+    <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871591567993</t>
+    <t xml:space="preserve">14.5871572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8623313903809</t>
+    <t xml:space="preserve">13.8623304367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4965543746948</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341409683228</t>
+    <t xml:space="preserve">14.1341419219971</t>
   </si>
   <si>
-    <t xml:space="preserve">13.40931224823</t>
+    <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
     <t xml:space="preserve">12.5938816070557</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119850158691</t>
+    <t xml:space="preserve">15.3119859695435</t>
   </si>
   <si>
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230625152588</t>
+    <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512519836426</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.127025604248</t>
+    <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
     <t xml:space="preserve">14.2659797668457</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343894958496</t>
+    <t xml:space="preserve">14.0343885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6828441619873</t>
+    <t xml:space="preserve">14.682843208313</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070714950562</t>
+    <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491172790527</t>
+    <t xml:space="preserve">13.8491163253784</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
@@ -710,16 +710,16 @@
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859357833862</t>
+    <t xml:space="preserve">13.3859367370605</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396167755127</t>
+    <t xml:space="preserve">13.339617729187</t>
   </si>
   <si>
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101621627808</t>
+    <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
     <t xml:space="preserve">13.0617094039917</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469816207886</t>
+    <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006635665894</t>
+    <t xml:space="preserve">13.200662612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9417543411255</t>
+    <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533876419067</t>
+    <t xml:space="preserve">15.0533885955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -755,40 +755,40 @@
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512538909912</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144344329834</t>
+    <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555233001709</t>
+    <t xml:space="preserve">15.6555242538452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1923427581787</t>
+    <t xml:space="preserve">15.192343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165691375732</t>
+    <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
     <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944765090942</t>
+    <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
     <t xml:space="preserve">15.4702529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460247039795</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
@@ -51424,7 +51424,7 @@
     </row>
     <row r="1928">
       <c r="A1928" s="1" t="n">
-        <v>45957.5609027778</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B1928" t="n">
         <v>2400</v>
@@ -51445,6 +51445,32 @@
         <v>323</v>
       </c>
       <c r="H1928" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="1" t="n">
+        <v>45958.6386805556</v>
+      </c>
+      <c r="B1929" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C1929" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1929" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1929" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118366241455</t>
+    <t xml:space="preserve">11.9118356704712</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256868362427</t>
+    <t xml:space="preserve">11.9256858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7698993682861</t>
+    <t xml:space="preserve">10.7698984146118</t>
   </si>
   <si>
     <t xml:space="preserve">10.9007148742676</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314947128296</t>
+    <t xml:space="preserve">10.9314937591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653877258301</t>
@@ -74,31 +74,31 @@
     <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732555389404</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
     <t xml:space="preserve">11.119252204895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194257736206</t>
+    <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.3116283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948385238647</t>
+    <t xml:space="preserve">11.6948366165161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424776077271</t>
+    <t xml:space="preserve">11.5424766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501033782959</t>
+    <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.810263633728</t>
+    <t xml:space="preserve">11.8102617263794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733278274536</t>
+    <t xml:space="preserve">11.7733268737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086194992065</t>
+    <t xml:space="preserve">10.8086175918579</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349035263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683441162109</t>
+    <t xml:space="preserve">10.0683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087799072266</t>
+    <t xml:space="preserve">10.1087808609009</t>
   </si>
   <si>
     <t xml:space="preserve">9.95325946807861</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345291137695</t>
+    <t xml:space="preserve">9.11345386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.097900390625</t>
+    <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
     <t xml:space="preserve">9.5178050994873</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907304763794</t>
+    <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278940200806</t>
+    <t xml:space="preserve">12.0278921127319</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750156402588</t>
+    <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862169265747</t>
+    <t xml:space="preserve">11.5862159729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529367446899</t>
+    <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863773345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641380310059</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198179244995</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310182571411</t>
+    <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
     <t xml:space="preserve">9.67332363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4089412689209</t>
+    <t xml:space="preserve">9.40894222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449283599854</t>
+    <t xml:space="preserve">9.42449188232422</t>
   </si>
   <si>
     <t xml:space="preserve">9.64222049713135</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476602554321</t>
+    <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
     <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887166976929</t>
+    <t xml:space="preserve">10.3887147903442</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79773998260498</t>
+    <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4867000579834</t>
+    <t xml:space="preserve">9.48670196533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.33118152618408</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074668884277</t>
+    <t xml:space="preserve">9.29074573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815227508545</t>
+    <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945678710938</t>
+    <t xml:space="preserve">9.09945583343506</t>
   </si>
   <si>
     <t xml:space="preserve">9.71842670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087778091431</t>
+    <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2745637893677</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064443588257</t>
+    <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
     <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778904914856</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181264877319</t>
+    <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2573461532593</t>
+    <t xml:space="preserve">10.257345199585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885997772217</t>
+    <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
     <t xml:space="preserve">9.90963935852051</t>
@@ -287,61 +287,61 @@
     <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344543457031</t>
+    <t xml:space="preserve">8.95344638824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7795934677124</t>
+    <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
     <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920330047607</t>
+    <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037284851074</t>
+    <t xml:space="preserve">9.04037094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271289825439</t>
+    <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266117095947</t>
+    <t xml:space="preserve">11.126612663269</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004665374756</t>
+    <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658323287964</t>
+    <t xml:space="preserve">10.8658313751221</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704196929932</t>
+    <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9965648651123</t>
+    <t xml:space="preserve">9.99656772613525</t>
   </si>
   <si>
     <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311990737915</t>
+    <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500514984131</t>
+    <t xml:space="preserve">9.47500419616699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3880786895752</t>
+    <t xml:space="preserve">9.38807964324951</t>
   </si>
   <si>
     <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729835510254</t>
+    <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
     <t xml:space="preserve">9.73578453063965</t>
@@ -350,22 +350,22 @@
     <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115222930908</t>
+    <t xml:space="preserve">9.3011531829834</t>
   </si>
   <si>
     <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876628875732</t>
+    <t xml:space="preserve">7.38876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183839797974</t>
+    <t xml:space="preserve">7.30183887481689</t>
   </si>
   <si>
     <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530210494995</t>
+    <t xml:space="preserve">7.34530258178711</t>
   </si>
   <si>
     <t xml:space="preserve">7.47569274902344</t>
@@ -374,40 +374,40 @@
     <t xml:space="preserve">7.82339954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9537878036499</t>
+    <t xml:space="preserve">7.95378971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34495830535889</t>
+    <t xml:space="preserve">8.34496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585025787354</t>
+    <t xml:space="preserve">9.56585216522217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4772777557373</t>
+    <t xml:space="preserve">9.47727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584274291992</t>
+    <t xml:space="preserve">8.94584178924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869773864746</t>
+    <t xml:space="preserve">8.76869678497314</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012523651123</t>
+    <t xml:space="preserve">8.68012428283691</t>
   </si>
   <si>
     <t xml:space="preserve">8.72441101074219</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12298774719238</t>
+    <t xml:space="preserve">9.1229887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50297832489014</t>
+    <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013370513916</t>
+    <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858615875244</t>
   </si>
   <si>
     <t xml:space="preserve">11.0715866088867</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830150604248</t>
+    <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972871780396</t>
+    <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83157062530518</t>
+    <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.74299716949463</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">9.92014217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744331359863</t>
+    <t xml:space="preserve">10.2744340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487335205078</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144519805908</t>
+    <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4258766174316</t>
+    <t xml:space="preserve">11.4258785247803</t>
   </si>
   <si>
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630065917969</t>
+    <t xml:space="preserve">10.3630046844482</t>
   </si>
   <si>
     <t xml:space="preserve">10.540150642395</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006059646606</t>
+    <t xml:space="preserve">10.6006050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287944793701</t>
+    <t xml:space="preserve">10.3287954330444</t>
   </si>
   <si>
     <t xml:space="preserve">10.1475877761841</t>
@@ -503,40 +503,40 @@
     <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381906509399</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502624511719</t>
+    <t xml:space="preserve">12.0502614974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.416036605835</t>
+    <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442260742188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690538406372</t>
+    <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408643722534</t>
+    <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
     <t xml:space="preserve">11.6878461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314691543579</t>
+    <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844854354858</t>
+    <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032796859741</t>
+    <t xml:space="preserve">12.5032787322998</t>
   </si>
   <si>
     <t xml:space="preserve">12.775089263916</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562969207764</t>
+    <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281064987183</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931936264038</t>
+    <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401754379272</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">15.4025888442993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556051254272</t>
+    <t xml:space="preserve">15.8556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462089538574</t>
+    <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
     <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307792663574</t>
+    <t xml:space="preserve">15.1307802200317</t>
   </si>
   <si>
     <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871572494507</t>
+    <t xml:space="preserve">14.587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495706558228</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938816070557</t>
+    <t xml:space="preserve">12.5938806533813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468988418579</t>
+    <t xml:space="preserve">13.0468978881836</t>
   </si>
   <si>
     <t xml:space="preserve">13.5905199050903</t>
@@ -629,25 +629,25 @@
     <t xml:space="preserve">13.9529333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2247438430786</t>
+    <t xml:space="preserve">14.2247447967529</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119840621948</t>
+    <t xml:space="preserve">15.3119850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264242172241</t>
+    <t xml:space="preserve">13.7264251708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2659797668457</t>
+    <t xml:space="preserve">14.26598072052</t>
   </si>
   <si>
     <t xml:space="preserve">14.6365251541138</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343885421753</t>
+    <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
     <t xml:space="preserve">14.682843208313</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070705413818</t>
+    <t xml:space="preserve">15.0070714950562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776149749756</t>
+    <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586158752441</t>
+    <t xml:space="preserve">14.3586168289185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733436584473</t>
+    <t xml:space="preserve">14.1733446121216</t>
   </si>
   <si>
     <t xml:space="preserve">13.7564811706543</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859367370605</t>
+    <t xml:space="preserve">13.3859357833862</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101631164551</t>
+    <t xml:space="preserve">13.7101621627808</t>
   </si>
   <si>
     <t xml:space="preserve">13.061710357666</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712080001831</t>
+    <t xml:space="preserve">13.5712070465088</t>
   </si>
   <si>
     <t xml:space="preserve">13.1543455123901</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144334793091</t>
+    <t xml:space="preserve">14.9144344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2849779129028</t>
+    <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
     <t xml:space="preserve">15.6555223464966</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407974243164</t>
+    <t xml:space="preserve">15.8407964706421</t>
   </si>
   <si>
     <t xml:space="preserve">15.7944774627686</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460247039795</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.016695022583</t>
+    <t xml:space="preserve">15.0166959762573</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5414838790894</t>
+    <t xml:space="preserve">14.541482925415</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968658447266</t>
+    <t xml:space="preserve">15.3968648910522</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572017669678</t>
+    <t xml:space="preserve">16.1572036743164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720779418945</t>
+    <t xml:space="preserve">15.8720769882202</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315683364868</t>
+    <t xml:space="preserve">14.7315673828125</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522468566895</t>
+    <t xml:space="preserve">16.2522449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -51470,7 +51470,7 @@
     </row>
     <row r="1930">
       <c r="A1930" s="1" t="n">
-        <v>45959.5542708333</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B1930" t="n">
         <v>4900</v>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,31 +44,31 @@
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256858825684</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654918670654</t>
+    <t xml:space="preserve">11.3654928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7698984146118</t>
+    <t xml:space="preserve">10.7698993682861</t>
   </si>
   <si>
     <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729778289795</t>
+    <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314937591553</t>
+    <t xml:space="preserve">10.9314956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653877258301</t>
+    <t xml:space="preserve">11.0653886795044</t>
   </si>
   <si>
     <t xml:space="preserve">11.1962022781372</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.119252204895</t>
+    <t xml:space="preserve">11.1192512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194267272949</t>
+    <t xml:space="preserve">11.6194276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116283416748</t>
+    <t xml:space="preserve">11.3116264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948366165161</t>
+    <t xml:space="preserve">11.6948385238647</t>
   </si>
   <si>
     <t xml:space="preserve">11.5424766540527</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102617263794</t>
+    <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733268737793</t>
+    <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657020568848</t>
+    <t xml:space="preserve">11.9656991958618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579027175903</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807781219482</t>
@@ -116,70 +116,70 @@
     <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086175918579</t>
+    <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349025726318</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087808609009</t>
+    <t xml:space="preserve">10.1087789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95325946807861</t>
+    <t xml:space="preserve">9.95326137542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345386505127</t>
+    <t xml:space="preserve">9.11345195770264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683822631836</t>
+    <t xml:space="preserve">9.85683727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5178050994873</t>
+    <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907295227051</t>
+    <t xml:space="preserve">11.2907314300537</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278921127319</t>
+    <t xml:space="preserve">12.0278930664062</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750165939331</t>
+    <t xml:space="preserve">11.9750156402588</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028579711914</t>
+    <t xml:space="preserve">11.7028570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862159729004</t>
+    <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084571838379</t>
+    <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639747619629</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529376983643</t>
+    <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
     <t xml:space="preserve">11.1196575164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8863773345947</t>
+    <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641380310059</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198188781738</t>
+    <t xml:space="preserve">10.4198198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310201644897</t>
+    <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.67332363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.40894031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449188232422</t>
+    <t xml:space="preserve">9.42449283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222049713135</t>
+    <t xml:space="preserve">9.64222145080566</t>
   </si>
   <si>
     <t xml:space="preserve">9.87550067901611</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887147903442</t>
+    <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
     <t xml:space="preserve">9.7977409362793</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892475128174</t>
+    <t xml:space="preserve">9.47892570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074573516846</t>
+    <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
     <t xml:space="preserve">8.97815132141113</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">9.71842670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087787628174</t>
+    <t xml:space="preserve">10.3087778091431</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2745637893677</t>
+    <t xml:space="preserve">10.274564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.349835395813</t>
+    <t xml:space="preserve">10.3498363494873</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919784545898</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353713989258</t>
+    <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7789058685303</t>
+    <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
     <t xml:space="preserve">10.5181255340576</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.257345199585</t>
+    <t xml:space="preserve">10.2573442459106</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963935852051</t>
+    <t xml:space="preserve">9.90963745117188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193256378174</t>
+    <t xml:space="preserve">9.56193161010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.95344638824463</t>
@@ -296,61 +296,61 @@
     <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266605377197</t>
+    <t xml:space="preserve">8.69266510009766</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037094116211</t>
+    <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271194458008</t>
+    <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126612663269</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
     <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658313751221</t>
+    <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704187393188</t>
+    <t xml:space="preserve">10.1704177856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99656772613525</t>
+    <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6050519943237</t>
+    <t xml:space="preserve">10.605052947998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311981201172</t>
+    <t xml:space="preserve">10.4311990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500419616699</t>
+    <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38807964324951</t>
+    <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422672271729</t>
+    <t xml:space="preserve">9.21422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729930877686</t>
+    <t xml:space="preserve">9.12729835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578453063965</t>
+    <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3011531829834</t>
+    <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
     <t xml:space="preserve">7.99725246429443</t>
@@ -365,31 +365,31 @@
     <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530258178711</t>
+    <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569274902344</t>
+    <t xml:space="preserve">7.4756932258606</t>
   </si>
   <si>
     <t xml:space="preserve">7.82339954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378971099854</t>
+    <t xml:space="preserve">7.9537878036499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34496021270752</t>
+    <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573863983154</t>
+    <t xml:space="preserve">8.60573959350586</t>
   </si>
   <si>
     <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585216522217</t>
+    <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727870941162</t>
+    <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869678497314</t>
+    <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441524505615</t>
@@ -422,37 +422,37 @@
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858615875244</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0715866088867</t>
+    <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
     <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830141067505</t>
+    <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
     <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972881317139</t>
+    <t xml:space="preserve">10.0972862243652</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74299716949463</t>
+    <t xml:space="preserve">9.74299621582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014217376709</t>
+    <t xml:space="preserve">9.92014312744141</t>
   </si>
   <si>
     <t xml:space="preserve">10.2744340896606</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4258785247803</t>
+    <t xml:space="preserve">11.4258794784546</t>
   </si>
   <si>
-    <t xml:space="preserve">10.805869102478</t>
+    <t xml:space="preserve">10.8058700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287231445312</t>
+    <t xml:space="preserve">10.6287240982056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172975540161</t>
+    <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
     <t xml:space="preserve">10.3630046844482</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">10.6006050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3287954330444</t>
+    <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
     <t xml:space="preserve">10.1475877761841</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78517436981201</t>
+    <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
     <t xml:space="preserve">10.2381916046143</t>
@@ -518,22 +518,22 @@
     <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1442260742188</t>
+    <t xml:space="preserve">11.1442270278931</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408634185791</t>
+    <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878461837769</t>
+    <t xml:space="preserve">11.6878480911255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314682006836</t>
+    <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844844818115</t>
+    <t xml:space="preserve">12.6844854354858</t>
   </si>
   <si>
     <t xml:space="preserve">12.5032787322998</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375026702881</t>
+    <t xml:space="preserve">13.1375017166138</t>
   </si>
   <si>
     <t xml:space="preserve">12.9562959671021</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153476715088</t>
+    <t xml:space="preserve">14.3153467178345</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931926727295</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4025888442993</t>
+    <t xml:space="preserve">15.402587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556060791016</t>
+    <t xml:space="preserve">15.8556070327759</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462099075317</t>
+    <t xml:space="preserve">15.9462089538574</t>
   </si>
   <si>
     <t xml:space="preserve">15.7650032043457</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.587158203125</t>
+    <t xml:space="preserve">14.5871572494507</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495706558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341400146484</t>
+    <t xml:space="preserve">14.1341409683228</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938806533813</t>
+    <t xml:space="preserve">12.5938816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468978881836</t>
+    <t xml:space="preserve">13.0468988418579</t>
   </si>
   <si>
     <t xml:space="preserve">13.5905199050903</t>
@@ -629,37 +629,37 @@
     <t xml:space="preserve">13.9529333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2247447967529</t>
+    <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
     <t xml:space="preserve">15.3119850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264251708984</t>
+    <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230625152588</t>
+    <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512519836426</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.26598072052</t>
+    <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
     <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196626663208</t>
+    <t xml:space="preserve">14.2196636199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343894958496</t>
+    <t xml:space="preserve">14.0343885421753</t>
   </si>
   <si>
     <t xml:space="preserve">14.682843208313</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070714950562</t>
+    <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491172790527</t>
+    <t xml:space="preserve">13.8491163253784</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880723953247</t>
+    <t xml:space="preserve">13.9880714416504</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248908996582</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859357833862</t>
+    <t xml:space="preserve">13.3859367370605</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101621627808</t>
+    <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.061710357666</t>
+    <t xml:space="preserve">13.0617094039917</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006635665894</t>
+    <t xml:space="preserve">13.200662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712070465088</t>
+    <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
     <t xml:space="preserve">13.1543455123901</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533876419067</t>
+    <t xml:space="preserve">15.0533885955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -752,34 +752,37 @@
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
+    <t xml:space="preserve">14.4512538909912</t>
+  </si>
+  <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144344329834</t>
+    <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555223464966</t>
+    <t xml:space="preserve">15.6555242538452</t>
   </si>
   <si>
     <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1923427581787</t>
+    <t xml:space="preserve">15.192343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165691375732</t>
+    <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407964706421</t>
+    <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
     <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702520370483</t>
+    <t xml:space="preserve">15.4702529907227</t>
   </si>
   <si>
     <t xml:space="preserve">15.1460256576538</t>
@@ -791,7 +794,7 @@
     <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0166959762573</t>
+    <t xml:space="preserve">15.016695022583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -800,7 +803,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541482925415</t>
+    <t xml:space="preserve">14.5414838790894</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -821,13 +824,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968648910522</t>
+    <t xml:space="preserve">15.3968658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572036743164</t>
+    <t xml:space="preserve">16.1572017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720769882202</t>
+    <t xml:space="preserve">15.8720779418945</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -836,7 +839,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315673828125</t>
+    <t xml:space="preserve">14.7315683364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -848,7 +851,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522449493408</t>
+    <t xml:space="preserve">16.2522468566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -33314,7 +33317,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33340,7 +33343,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33366,7 +33369,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33392,7 +33395,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33444,7 +33447,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33470,7 +33473,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33496,7 +33499,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33522,7 +33525,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33548,7 +33551,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33574,7 +33577,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33600,7 +33603,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33626,7 +33629,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33652,7 +33655,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33678,7 +33681,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33704,7 +33707,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33730,7 +33733,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33756,7 +33759,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33782,7 +33785,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33808,7 +33811,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33834,7 +33837,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33886,7 +33889,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33912,7 +33915,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33938,7 +33941,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33964,7 +33967,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33990,7 +33993,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34016,7 +34019,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34042,7 +34045,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34406,7 +34409,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34432,7 +34435,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34458,7 +34461,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34744,7 +34747,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34770,7 +34773,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34796,7 +34799,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34900,7 +34903,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35056,7 +35059,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35108,7 +35111,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35134,7 +35137,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35160,7 +35163,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35186,7 +35189,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35212,7 +35215,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35238,7 +35241,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35264,7 +35267,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35290,7 +35293,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35368,7 +35371,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35394,7 +35397,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35420,7 +35423,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35446,7 +35449,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35472,7 +35475,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35498,7 +35501,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35524,7 +35527,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35550,7 +35553,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35576,7 +35579,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35602,7 +35605,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35628,7 +35631,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35654,7 +35657,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35680,7 +35683,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35706,7 +35709,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35732,7 +35735,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35758,7 +35761,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35784,7 +35787,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35810,7 +35813,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35836,7 +35839,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35862,7 +35865,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35888,7 +35891,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35914,7 +35917,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35940,7 +35943,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35966,7 +35969,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35992,7 +35995,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36018,7 +36021,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36044,7 +36047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36070,7 +36073,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36096,7 +36099,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36122,7 +36125,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36148,7 +36151,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36174,7 +36177,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36200,7 +36203,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36226,7 +36229,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36252,7 +36255,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36278,7 +36281,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36304,7 +36307,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36330,7 +36333,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36356,7 +36359,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36382,7 +36385,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36408,7 +36411,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36434,7 +36437,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36460,7 +36463,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36486,7 +36489,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36512,7 +36515,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36538,7 +36541,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36564,7 +36567,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36590,7 +36593,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36616,7 +36619,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36642,7 +36645,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36668,7 +36671,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36694,7 +36697,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -36720,7 +36723,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36746,7 +36749,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36772,7 +36775,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36798,7 +36801,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36824,7 +36827,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36850,7 +36853,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36876,7 +36879,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36902,7 +36905,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36928,7 +36931,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36954,7 +36957,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36980,7 +36983,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37006,7 +37009,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37032,7 +37035,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37058,7 +37061,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37084,7 +37087,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37110,7 +37113,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37136,7 +37139,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37162,7 +37165,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37188,7 +37191,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37214,7 +37217,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37240,7 +37243,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37266,7 +37269,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37292,7 +37295,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37318,7 +37321,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37344,7 +37347,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37370,7 +37373,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37396,7 +37399,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37422,7 +37425,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37448,7 +37451,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37474,7 +37477,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37500,7 +37503,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37526,7 +37529,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37552,7 +37555,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37578,7 +37581,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37604,7 +37607,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37630,7 +37633,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37656,7 +37659,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37682,7 +37685,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37708,7 +37711,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37734,7 +37737,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37760,7 +37763,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37786,7 +37789,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37812,7 +37815,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37838,7 +37841,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -37864,7 +37867,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37890,7 +37893,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37916,7 +37919,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37942,7 +37945,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37968,7 +37971,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -37994,7 +37997,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38020,7 +38023,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38046,7 +38049,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38072,7 +38075,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38098,7 +38101,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38124,7 +38127,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38150,7 +38153,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38176,7 +38179,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38202,7 +38205,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38228,7 +38231,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38254,7 +38257,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38280,7 +38283,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38306,7 +38309,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38332,7 +38335,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38358,7 +38361,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38384,7 +38387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38410,7 +38413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38436,7 +38439,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38462,7 +38465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38488,7 +38491,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38514,7 +38517,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38540,7 +38543,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38566,7 +38569,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38592,7 +38595,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38618,7 +38621,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38644,7 +38647,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38670,7 +38673,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38696,7 +38699,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38722,7 +38725,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38748,7 +38751,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38774,7 +38777,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38800,7 +38803,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -38826,7 +38829,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38852,7 +38855,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38878,7 +38881,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38904,7 +38907,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38930,7 +38933,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38956,7 +38959,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38982,7 +38985,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39008,7 +39011,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39034,7 +39037,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39060,7 +39063,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39086,7 +39089,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39112,7 +39115,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39138,7 +39141,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39164,7 +39167,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39190,7 +39193,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39216,7 +39219,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39242,7 +39245,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39268,7 +39271,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39294,7 +39297,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39320,7 +39323,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39346,7 +39349,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39372,7 +39375,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39398,7 +39401,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39424,7 +39427,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39450,7 +39453,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39476,7 +39479,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39502,7 +39505,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39528,7 +39531,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39554,7 +39557,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39580,7 +39583,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39606,7 +39609,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39632,7 +39635,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39658,7 +39661,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39684,7 +39687,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39710,7 +39713,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39736,7 +39739,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39762,7 +39765,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39788,7 +39791,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39814,7 +39817,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39840,7 +39843,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39866,7 +39869,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39892,7 +39895,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39918,7 +39921,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39944,7 +39947,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39970,7 +39973,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39996,7 +39999,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40022,7 +40025,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40048,7 +40051,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40074,7 +40077,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40100,7 +40103,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40126,7 +40129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40152,7 +40155,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40178,7 +40181,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40204,7 +40207,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40230,7 +40233,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40256,7 +40259,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40282,7 +40285,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40308,7 +40311,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40334,7 +40337,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40360,7 +40363,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40386,7 +40389,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40646,7 +40649,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40672,7 +40675,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40698,7 +40701,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40724,7 +40727,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40750,7 +40753,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40776,7 +40779,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40802,7 +40805,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40828,7 +40831,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40854,7 +40857,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -40880,7 +40883,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40906,7 +40909,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40932,7 +40935,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40958,7 +40961,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40984,7 +40987,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41010,7 +41013,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41036,7 +41039,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41062,7 +41065,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41088,7 +41091,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41114,7 +41117,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41140,7 +41143,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41166,7 +41169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41192,7 +41195,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41218,7 +41221,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41244,7 +41247,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41270,7 +41273,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41296,7 +41299,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41322,7 +41325,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41348,7 +41351,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41374,7 +41377,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41400,7 +41403,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41426,7 +41429,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41452,7 +41455,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41478,7 +41481,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41504,7 +41507,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41530,7 +41533,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41556,7 +41559,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41582,7 +41585,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41608,7 +41611,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41634,7 +41637,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41660,7 +41663,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41686,7 +41689,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41712,7 +41715,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41738,7 +41741,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41764,7 +41767,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41790,7 +41793,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41816,7 +41819,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41842,7 +41845,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41868,7 +41871,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41894,7 +41897,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41920,7 +41923,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41946,7 +41949,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41972,7 +41975,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -41998,7 +42001,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42024,7 +42027,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42050,7 +42053,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42076,7 +42079,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42102,7 +42105,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42128,7 +42131,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42154,7 +42157,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42180,7 +42183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42206,7 +42209,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42232,7 +42235,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42258,7 +42261,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42284,7 +42287,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42310,7 +42313,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42336,7 +42339,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42362,7 +42365,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42388,7 +42391,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42414,7 +42417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42440,7 +42443,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42466,7 +42469,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42492,7 +42495,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42518,7 +42521,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42544,7 +42547,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42570,7 +42573,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42596,7 +42599,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42622,7 +42625,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42648,7 +42651,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42674,7 +42677,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42700,7 +42703,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42726,7 +42729,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42752,7 +42755,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42778,7 +42781,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42804,7 +42807,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42830,7 +42833,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42856,7 +42859,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42882,7 +42885,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42908,7 +42911,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42934,7 +42937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42960,7 +42963,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42986,7 +42989,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43012,7 +43015,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43038,7 +43041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43064,7 +43067,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43090,7 +43093,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43116,7 +43119,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43142,7 +43145,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43168,7 +43171,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43194,7 +43197,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43220,7 +43223,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43246,7 +43249,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43272,7 +43275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43298,7 +43301,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43324,7 +43327,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43350,7 +43353,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43376,7 +43379,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43402,7 +43405,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43428,7 +43431,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43454,7 +43457,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43480,7 +43483,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43506,7 +43509,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43532,7 +43535,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43558,7 +43561,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43584,7 +43587,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43610,7 +43613,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43636,7 +43639,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43662,7 +43665,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43688,7 +43691,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43714,7 +43717,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43740,7 +43743,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43766,7 +43769,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43792,7 +43795,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43818,7 +43821,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43844,7 +43847,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43870,7 +43873,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43896,7 +43899,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43922,7 +43925,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43948,7 +43951,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43974,7 +43977,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44000,7 +44003,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44026,7 +44029,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44052,7 +44055,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44078,7 +44081,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44104,7 +44107,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44130,7 +44133,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44156,7 +44159,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44182,7 +44185,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44208,7 +44211,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44234,7 +44237,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44260,7 +44263,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44286,7 +44289,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44312,7 +44315,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44338,7 +44341,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44364,7 +44367,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44390,7 +44393,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44416,7 +44419,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44442,7 +44445,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44468,7 +44471,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44494,7 +44497,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44520,7 +44523,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44546,7 +44549,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44572,7 +44575,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44598,7 +44601,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44624,7 +44627,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44650,7 +44653,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44676,7 +44679,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44702,7 +44705,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44728,7 +44731,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44754,7 +44757,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44780,7 +44783,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44806,7 +44809,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44832,7 +44835,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44858,7 +44861,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44884,7 +44887,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44910,7 +44913,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44936,7 +44939,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44962,7 +44965,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44988,7 +44991,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45014,7 +45017,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45040,7 +45043,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45066,7 +45069,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45092,7 +45095,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45118,7 +45121,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45144,7 +45147,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45170,7 +45173,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45196,7 +45199,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45222,7 +45225,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45248,7 +45251,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45274,7 +45277,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45300,7 +45303,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45326,7 +45329,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45352,7 +45355,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45378,7 +45381,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45404,7 +45407,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45430,7 +45433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45456,7 +45459,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45482,7 +45485,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45508,7 +45511,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45534,7 +45537,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45560,7 +45563,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45586,7 +45589,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45612,7 +45615,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45638,7 +45641,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45664,7 +45667,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45690,7 +45693,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45716,7 +45719,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45742,7 +45745,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45768,7 +45771,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45794,7 +45797,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45820,7 +45823,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45846,7 +45849,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45872,7 +45875,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45898,7 +45901,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45924,7 +45927,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45950,7 +45953,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45976,7 +45979,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46002,7 +46005,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46028,7 +46031,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46054,7 +46057,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46080,7 +46083,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46106,7 +46109,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46132,7 +46135,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46158,7 +46161,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46184,7 +46187,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46210,7 +46213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46236,7 +46239,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46262,7 +46265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46288,7 +46291,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46314,7 +46317,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46340,7 +46343,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46366,7 +46369,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46392,7 +46395,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46418,7 +46421,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46444,7 +46447,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46470,7 +46473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46496,7 +46499,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46522,7 +46525,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46548,7 +46551,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46574,7 +46577,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46600,7 +46603,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46626,7 +46629,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46652,7 +46655,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46678,7 +46681,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46704,7 +46707,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46730,7 +46733,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46756,7 +46759,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46782,7 +46785,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46808,7 +46811,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46834,7 +46837,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46860,7 +46863,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46886,7 +46889,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46912,7 +46915,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46938,7 +46941,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46964,7 +46967,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46990,7 +46993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47016,7 +47019,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47042,7 +47045,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47068,7 +47071,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47094,7 +47097,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47120,7 +47123,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47146,7 +47149,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47172,7 +47175,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47198,7 +47201,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47224,7 +47227,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47250,7 +47253,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47276,7 +47279,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47302,7 +47305,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47328,7 +47331,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47354,7 +47357,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47380,7 +47383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47406,7 +47409,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47432,7 +47435,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47458,7 +47461,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47484,7 +47487,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47510,7 +47513,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47536,7 +47539,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47562,7 +47565,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47588,7 +47591,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47614,7 +47617,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47640,7 +47643,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47666,7 +47669,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47692,7 +47695,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47718,7 +47721,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47744,7 +47747,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47770,7 +47773,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47796,7 +47799,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47822,7 +47825,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47848,7 +47851,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47874,7 +47877,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47900,7 +47903,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47926,7 +47929,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47952,7 +47955,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47978,7 +47981,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48004,7 +48007,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48030,7 +48033,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48056,7 +48059,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48082,7 +48085,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48108,7 +48111,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48134,7 +48137,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48160,7 +48163,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48186,7 +48189,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48212,7 +48215,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48238,7 +48241,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48264,7 +48267,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48290,7 +48293,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48316,7 +48319,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48342,7 +48345,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48368,7 +48371,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48394,7 +48397,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48420,7 +48423,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48446,7 +48449,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48472,7 +48475,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48498,7 +48501,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48524,7 +48527,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48550,7 +48553,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48576,7 +48579,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48602,7 +48605,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48628,7 +48631,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48654,7 +48657,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48680,7 +48683,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48706,7 +48709,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48732,7 +48735,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48758,7 +48761,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48784,7 +48787,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48810,7 +48813,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48836,7 +48839,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48862,7 +48865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48888,7 +48891,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48914,7 +48917,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48940,7 +48943,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48966,7 +48969,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48992,7 +48995,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49018,7 +49021,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49044,7 +49047,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49070,7 +49073,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49096,7 +49099,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49122,7 +49125,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49148,7 +49151,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49174,7 +49177,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49200,7 +49203,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49226,7 +49229,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49252,7 +49255,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49278,7 +49281,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49304,7 +49307,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49330,7 +49333,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49356,7 +49359,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49382,7 +49385,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49408,7 +49411,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49434,7 +49437,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49460,7 +49463,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49486,7 +49489,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49512,7 +49515,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49538,7 +49541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49564,7 +49567,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49590,7 +49593,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49616,7 +49619,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49642,7 +49645,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49668,7 +49671,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49694,7 +49697,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49720,7 +49723,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49746,7 +49749,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49772,7 +49775,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49798,7 +49801,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49824,7 +49827,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49850,7 +49853,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49876,7 +49879,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49902,7 +49905,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49928,7 +49931,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49954,7 +49957,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49980,7 +49983,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50006,7 +50009,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50032,7 +50035,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50058,7 +50061,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50084,7 +50087,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50110,7 +50113,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50136,7 +50139,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50162,7 +50165,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50188,7 +50191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50214,7 +50217,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50240,7 +50243,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50266,7 +50269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50292,7 +50295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50318,7 +50321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50344,7 +50347,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50370,7 +50373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50396,7 +50399,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50422,7 +50425,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50448,7 +50451,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50474,7 +50477,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50500,7 +50503,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50526,7 +50529,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50552,7 +50555,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50578,7 +50581,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50604,7 +50607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50630,7 +50633,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50656,7 +50659,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50682,7 +50685,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50708,7 +50711,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50734,7 +50737,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50760,7 +50763,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50786,7 +50789,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50812,7 +50815,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50838,7 +50841,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50864,7 +50867,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50890,7 +50893,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50916,7 +50919,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50942,7 +50945,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50968,7 +50971,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50994,7 +50997,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51020,7 +51023,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51046,7 +51049,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51072,7 +51075,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51098,7 +51101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51124,7 +51127,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51150,7 +51153,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51176,7 +51179,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51202,7 +51205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51228,7 +51231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51254,7 +51257,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51280,7 +51283,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51306,7 +51309,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51332,7 +51335,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51358,7 +51361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51384,7 +51387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51410,7 +51413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51436,7 +51439,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51462,7 +51465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51488,9 +51491,35 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1930" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="1" t="n">
+        <v>45960.3333333333</v>
+      </c>
+      <c r="B1931" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1931" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1931" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256868362427</t>
+    <t xml:space="preserve">11.925687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577281951904</t>
+    <t xml:space="preserve">11.1577272415161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654928207397</t>
+    <t xml:space="preserve">11.3654909133911</t>
   </si>
   <si>
     <t xml:space="preserve">10.7698993682861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007139205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314956665039</t>
+    <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653886795044</t>
+    <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962022781372</t>
+    <t xml:space="preserve">11.1962032318115</t>
   </si>
   <si>
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192512512207</t>
+    <t xml:space="preserve">11.1192531585693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194276809692</t>
+    <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116264343262</t>
+    <t xml:space="preserve">11.3116283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948385238647</t>
+    <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424757003784</t>
   </si>
   <si>
     <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.8102617263794</t>
   </si>
   <si>
     <t xml:space="preserve">11.773325920105</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9656991958618</t>
+    <t xml:space="preserve">11.9657001495361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579027175903</t>
+    <t xml:space="preserve">11.657901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807781219482</t>
+    <t xml:space="preserve">11.0807771682739</t>
   </si>
   <si>
     <t xml:space="preserve">11.2751779556274</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349025726318</t>
+    <t xml:space="preserve">10.5349035263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683460235596</t>
+    <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
     <t xml:space="preserve">10.1087789535522</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">9.95326137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998119354248</t>
+    <t xml:space="preserve">9.71997928619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345195770264</t>
+    <t xml:space="preserve">9.11345481872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.09790325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683917999268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51780414581299</t>
+    <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2642993927002</t>
+    <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907314300537</t>
+    <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
     <t xml:space="preserve">12.0278930664062</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750156402588</t>
+    <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028589248657</t>
   </si>
   <si>
     <t xml:space="preserve">11.5862169265747</t>
@@ -170,67 +170,67 @@
     <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639757156372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529367446899</t>
+    <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196575164795</t>
+    <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
     <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641380310059</t>
+    <t xml:space="preserve">10.9641370773315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975786209106</t>
+    <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332363128662</t>
+    <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894031524658</t>
+    <t xml:space="preserve">9.40894222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449283599854</t>
+    <t xml:space="preserve">9.42449188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222145080566</t>
+    <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342059135437</t>
+    <t xml:space="preserve">10.3420610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887157440186</t>
+    <t xml:space="preserve">10.3887138366699</t>
   </si>
   <si>
     <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670196533203</t>
+    <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118152618408</t>
+    <t xml:space="preserve">9.33118057250977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662128448486</t>
+    <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892570495605</t>
+    <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.29074668884277</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064434051514</t>
+    <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353723526001</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.778904914856</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2573442459106</t>
+    <t xml:space="preserve">10.257345199585</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963745117188</t>
+    <t xml:space="preserve">9.90963935852051</t>
   </si>
   <si>
     <t xml:space="preserve">9.56193161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.8665189743042</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266510009766</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920234680176</t>
+    <t xml:space="preserve">8.64920139312744</t>
   </si>
   <si>
     <t xml:space="preserve">9.04037189483643</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266117095947</t>
+    <t xml:space="preserve">11.1266136169434</t>
   </si>
   <si>
     <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658323287964</t>
+    <t xml:space="preserve">10.8658313751221</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704177856445</t>
+    <t xml:space="preserve">10.1704196929932</t>
   </si>
   <si>
     <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.605052947998</t>
+    <t xml:space="preserve">10.6050510406494</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311990737915</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">9.21422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729835510254</t>
+    <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
     <t xml:space="preserve">9.73578548431396</t>
@@ -353,34 +353,34 @@
     <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725151062012</t>
   </si>
   <si>
     <t xml:space="preserve">7.38876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183887481689</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
     <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530210494995</t>
+    <t xml:space="preserve">7.34530305862427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4756932258606</t>
+    <t xml:space="preserve">7.47569370269775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339954376221</t>
+    <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9537878036499</t>
+    <t xml:space="preserve">7.95378971099854</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573959350586</t>
+    <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.0087146759033</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870716094971</t>
+    <t xml:space="preserve">9.38870620727539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584178924561</t>
+    <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85727024078369</t>
+    <t xml:space="preserve">8.85727119445801</t>
   </si>
   <si>
     <t xml:space="preserve">8.76869773864746</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">8.68012428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72441101074219</t>
+    <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21156024932861</t>
+    <t xml:space="preserve">9.2115592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013275146484</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.071587562561</t>
+    <t xml:space="preserve">11.0715866088867</t>
   </si>
   <si>
     <t xml:space="preserve">10.8944425582886</t>
@@ -443,40 +443,40 @@
     <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972862243652</t>
+    <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74299621582031</t>
+    <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014312744141</t>
+    <t xml:space="preserve">9.92014217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744340896606</t>
+    <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487325668335</t>
+    <t xml:space="preserve">11.2487335205078</t>
   </si>
   <si>
     <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4258794784546</t>
+    <t xml:space="preserve">11.425877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8058700561523</t>
+    <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
     <t xml:space="preserve">10.6287240982056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630046844482</t>
+    <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
     <t xml:space="preserve">10.540150642395</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818126678467</t>
+    <t xml:space="preserve">10.7818117141724</t>
   </si>
   <si>
-    <t xml:space="preserve">10.963020324707</t>
+    <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
     <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502614974976</t>
+    <t xml:space="preserve">12.0502605438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878480911255</t>
+    <t xml:space="preserve">11.6878461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314691543579</t>
+    <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844854354858</t>
+    <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032787322998</t>
+    <t xml:space="preserve">12.5032777786255</t>
   </si>
   <si>
     <t xml:space="preserve">12.775089263916</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435371398926</t>
+    <t xml:space="preserve">14.0435361862183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811237335205</t>
+    <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153467178345</t>
+    <t xml:space="preserve">14.3153486251831</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931926727295</t>
@@ -566,25 +566,25 @@
     <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.402587890625</t>
+    <t xml:space="preserve">15.4025897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556070327759</t>
+    <t xml:space="preserve">15.8556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462089538574</t>
+    <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650012969971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307802200317</t>
+    <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2213821411133</t>
+    <t xml:space="preserve">15.221381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871572494507</t>
+    <t xml:space="preserve">14.587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">14.4965543746948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683639526367</t>
+    <t xml:space="preserve">14.768364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495706558228</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">14.1341409683228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4093132019043</t>
+    <t xml:space="preserve">13.4093141555786</t>
   </si>
   <si>
     <t xml:space="preserve">12.5938816070557</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9529333114624</t>
+    <t xml:space="preserve">13.9529323577881</t>
   </si>
   <si>
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119850158691</t>
+    <t xml:space="preserve">15.3119869232178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264242172241</t>
+    <t xml:space="preserve">13.7264251708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230634689331</t>
@@ -647,19 +647,19 @@
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2659797668457</t>
+    <t xml:space="preserve">14.26598072052</t>
   </si>
   <si>
     <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196636199951</t>
+    <t xml:space="preserve">14.2196626663208</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343885421753</t>
+    <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
     <t xml:space="preserve">14.682843208313</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776159286499</t>
+    <t xml:space="preserve">15.3776168823242</t>
   </si>
   <si>
     <t xml:space="preserve">14.3586168289185</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6638450622559</t>
+    <t xml:space="preserve">13.6638441085815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491163253784</t>
+    <t xml:space="preserve">13.8491172790527</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880714416504</t>
+    <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248908996582</t>
+    <t xml:space="preserve">13.5248899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027992248535</t>
+    <t xml:space="preserve">13.8027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859367370605</t>
+    <t xml:space="preserve">13.3859357833862</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -719,19 +719,19 @@
     <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0617094039917</t>
+    <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690723419189</t>
+    <t xml:space="preserve">12.9690732955933</t>
   </si>
   <si>
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.200662612915</t>
+    <t xml:space="preserve">13.2006645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712080001831</t>
+    <t xml:space="preserve">13.5712070465088</t>
   </si>
   <si>
     <t xml:space="preserve">13.1543455123901</t>
@@ -749,16 +749,13 @@
     <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7291612625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4512538909912</t>
+    <t xml:space="preserve">14.7291603088379</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144334793091</t>
+    <t xml:space="preserve">14.9144344329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.2849788665771</t>
@@ -767,34 +764,34 @@
     <t xml:space="preserve">15.6555242538452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628871917725</t>
+    <t xml:space="preserve">15.5628862380981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.192343711853</t>
+    <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
     <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407974243164</t>
+    <t xml:space="preserve">15.8407964706421</t>
   </si>
   <si>
     <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702529907227</t>
+    <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460256576538</t>
+    <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8681154251099</t>
+    <t xml:space="preserve">14.8681144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975700378418</t>
+    <t xml:space="preserve">14.4975709915161</t>
   </si>
   <si>
-    <t xml:space="preserve">15.016695022583</t>
+    <t xml:space="preserve">15.0166959762573</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -803,7 +800,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5414838790894</t>
+    <t xml:space="preserve">14.541482925415</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -824,13 +821,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968658447266</t>
+    <t xml:space="preserve">15.3968648910522</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572017669678</t>
+    <t xml:space="preserve">16.1572036743164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720779418945</t>
+    <t xml:space="preserve">15.8720769882202</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -839,7 +836,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315683364868</t>
+    <t xml:space="preserve">14.7315673828125</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -851,7 +848,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522468566895</t>
+    <t xml:space="preserve">16.2522449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -33317,7 +33314,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33343,7 +33340,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33369,7 +33366,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33395,7 +33392,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33447,7 +33444,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33473,7 +33470,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33499,7 +33496,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33525,7 +33522,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33551,7 +33548,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33577,7 +33574,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33603,7 +33600,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33629,7 +33626,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33655,7 +33652,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33681,7 +33678,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33707,7 +33704,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33733,7 +33730,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33759,7 +33756,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33785,7 +33782,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33811,7 +33808,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33837,7 +33834,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33889,7 +33886,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33915,7 +33912,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33941,7 +33938,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33967,7 +33964,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33993,7 +33990,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34019,7 +34016,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34045,7 +34042,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34409,7 +34406,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34435,7 +34432,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34461,7 +34458,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34747,7 +34744,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34773,7 +34770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34799,7 +34796,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34903,7 +34900,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35059,7 +35056,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35111,7 +35108,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35137,7 +35134,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35163,7 +35160,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35189,7 +35186,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35215,7 +35212,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35241,7 +35238,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35267,7 +35264,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35293,7 +35290,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35371,7 +35368,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35397,7 +35394,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35423,7 +35420,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35449,7 +35446,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35475,7 +35472,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35501,7 +35498,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35527,7 +35524,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35553,7 +35550,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35579,7 +35576,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35605,7 +35602,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35631,7 +35628,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35657,7 +35654,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35683,7 +35680,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35709,7 +35706,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35735,7 +35732,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35761,7 +35758,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35787,7 +35784,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35813,7 +35810,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35839,7 +35836,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35865,7 +35862,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35891,7 +35888,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35917,7 +35914,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35943,7 +35940,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35969,7 +35966,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35995,7 +35992,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36021,7 +36018,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36047,7 +36044,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36073,7 +36070,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36099,7 +36096,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36125,7 +36122,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36151,7 +36148,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36177,7 +36174,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36203,7 +36200,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36229,7 +36226,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36255,7 +36252,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36281,7 +36278,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36307,7 +36304,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36333,7 +36330,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36359,7 +36356,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36385,7 +36382,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36411,7 +36408,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36437,7 +36434,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36463,7 +36460,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36489,7 +36486,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36515,7 +36512,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36541,7 +36538,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36567,7 +36564,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36593,7 +36590,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36619,7 +36616,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36645,7 +36642,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36671,7 +36668,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36697,7 +36694,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -36723,7 +36720,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36749,7 +36746,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36775,7 +36772,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36801,7 +36798,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36827,7 +36824,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36853,7 +36850,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36879,7 +36876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36905,7 +36902,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36931,7 +36928,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36957,7 +36954,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36983,7 +36980,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37009,7 +37006,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37035,7 +37032,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37061,7 +37058,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37087,7 +37084,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37113,7 +37110,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37139,7 +37136,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37165,7 +37162,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37191,7 +37188,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37217,7 +37214,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37243,7 +37240,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37269,7 +37266,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37295,7 +37292,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37321,7 +37318,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37347,7 +37344,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37373,7 +37370,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37399,7 +37396,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37425,7 +37422,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37451,7 +37448,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37477,7 +37474,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37503,7 +37500,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37529,7 +37526,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37555,7 +37552,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37581,7 +37578,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37607,7 +37604,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37633,7 +37630,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37659,7 +37656,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37685,7 +37682,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37711,7 +37708,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37737,7 +37734,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37763,7 +37760,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37789,7 +37786,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37815,7 +37812,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37841,7 +37838,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -37867,7 +37864,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37893,7 +37890,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37919,7 +37916,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37945,7 +37942,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37971,7 +37968,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -37997,7 +37994,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38023,7 +38020,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38049,7 +38046,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38075,7 +38072,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38101,7 +38098,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38127,7 +38124,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38153,7 +38150,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38179,7 +38176,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38205,7 +38202,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38231,7 +38228,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38257,7 +38254,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38283,7 +38280,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38309,7 +38306,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38335,7 +38332,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38361,7 +38358,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38387,7 +38384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38413,7 +38410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38439,7 +38436,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38465,7 +38462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38491,7 +38488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38517,7 +38514,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38543,7 +38540,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38569,7 +38566,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38595,7 +38592,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38621,7 +38618,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38647,7 +38644,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38673,7 +38670,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38699,7 +38696,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38725,7 +38722,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38751,7 +38748,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38777,7 +38774,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38803,7 +38800,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -38829,7 +38826,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38855,7 +38852,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38881,7 +38878,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38907,7 +38904,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38933,7 +38930,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38959,7 +38956,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38985,7 +38982,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39011,7 +39008,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39037,7 +39034,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39063,7 +39060,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39089,7 +39086,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39115,7 +39112,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39141,7 +39138,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39167,7 +39164,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39193,7 +39190,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39219,7 +39216,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39245,7 +39242,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39271,7 +39268,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39297,7 +39294,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39323,7 +39320,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39349,7 +39346,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39375,7 +39372,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39401,7 +39398,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39427,7 +39424,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39453,7 +39450,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39479,7 +39476,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39505,7 +39502,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39531,7 +39528,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39557,7 +39554,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39583,7 +39580,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39609,7 +39606,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39635,7 +39632,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39661,7 +39658,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39687,7 +39684,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39713,7 +39710,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39739,7 +39736,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39765,7 +39762,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39791,7 +39788,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39817,7 +39814,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39843,7 +39840,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39869,7 +39866,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39895,7 +39892,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39921,7 +39918,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39947,7 +39944,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39973,7 +39970,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39999,7 +39996,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40025,7 +40022,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40051,7 +40048,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40077,7 +40074,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40103,7 +40100,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40129,7 +40126,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40155,7 +40152,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40181,7 +40178,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40207,7 +40204,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40233,7 +40230,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40259,7 +40256,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40285,7 +40282,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40311,7 +40308,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40337,7 +40334,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40363,7 +40360,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40389,7 +40386,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40649,7 +40646,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40675,7 +40672,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40701,7 +40698,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40727,7 +40724,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40753,7 +40750,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40779,7 +40776,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40805,7 +40802,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40831,7 +40828,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40857,7 +40854,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -40883,7 +40880,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40909,7 +40906,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40935,7 +40932,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40961,7 +40958,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40987,7 +40984,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41013,7 +41010,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41039,7 +41036,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41065,7 +41062,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41091,7 +41088,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41117,7 +41114,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41143,7 +41140,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41169,7 +41166,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41195,7 +41192,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41221,7 +41218,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41247,7 +41244,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41273,7 +41270,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41299,7 +41296,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41325,7 +41322,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41351,7 +41348,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41377,7 +41374,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41403,7 +41400,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41429,7 +41426,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41455,7 +41452,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41481,7 +41478,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41507,7 +41504,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41533,7 +41530,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41559,7 +41556,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41585,7 +41582,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41611,7 +41608,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41637,7 +41634,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41663,7 +41660,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41689,7 +41686,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41715,7 +41712,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41741,7 +41738,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41767,7 +41764,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41793,7 +41790,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41819,7 +41816,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41845,7 +41842,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41871,7 +41868,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41897,7 +41894,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41923,7 +41920,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41949,7 +41946,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41975,7 +41972,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42001,7 +41998,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42027,7 +42024,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42053,7 +42050,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42079,7 +42076,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42105,7 +42102,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42131,7 +42128,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42157,7 +42154,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42183,7 +42180,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42209,7 +42206,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42235,7 +42232,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42261,7 +42258,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42287,7 +42284,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42313,7 +42310,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42339,7 +42336,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42365,7 +42362,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42391,7 +42388,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42417,7 +42414,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42443,7 +42440,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42469,7 +42466,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42495,7 +42492,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42521,7 +42518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42547,7 +42544,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42573,7 +42570,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42599,7 +42596,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42625,7 +42622,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42651,7 +42648,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42677,7 +42674,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42703,7 +42700,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42729,7 +42726,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42755,7 +42752,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42781,7 +42778,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42807,7 +42804,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42833,7 +42830,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42859,7 +42856,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42885,7 +42882,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42911,7 +42908,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42937,7 +42934,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42963,7 +42960,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42989,7 +42986,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43015,7 +43012,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43041,7 +43038,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43067,7 +43064,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43093,7 +43090,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43119,7 +43116,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43145,7 +43142,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43171,7 +43168,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43197,7 +43194,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43223,7 +43220,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43249,7 +43246,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43275,7 +43272,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43301,7 +43298,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43327,7 +43324,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43353,7 +43350,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43379,7 +43376,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43405,7 +43402,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43431,7 +43428,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43457,7 +43454,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43483,7 +43480,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43509,7 +43506,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43535,7 +43532,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43561,7 +43558,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43587,7 +43584,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43613,7 +43610,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43639,7 +43636,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43665,7 +43662,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43691,7 +43688,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43717,7 +43714,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43743,7 +43740,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43769,7 +43766,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43795,7 +43792,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43821,7 +43818,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43847,7 +43844,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43873,7 +43870,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43899,7 +43896,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43925,7 +43922,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43951,7 +43948,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43977,7 +43974,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44003,7 +44000,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44029,7 +44026,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44055,7 +44052,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44081,7 +44078,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44107,7 +44104,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44133,7 +44130,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44159,7 +44156,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44185,7 +44182,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44211,7 +44208,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44237,7 +44234,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44263,7 +44260,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44289,7 +44286,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44315,7 +44312,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44341,7 +44338,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44367,7 +44364,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44393,7 +44390,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44419,7 +44416,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44445,7 +44442,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44471,7 +44468,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44497,7 +44494,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44523,7 +44520,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44549,7 +44546,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44575,7 +44572,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44601,7 +44598,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44627,7 +44624,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44653,7 +44650,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44679,7 +44676,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44705,7 +44702,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44731,7 +44728,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44757,7 +44754,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44783,7 +44780,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44809,7 +44806,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44835,7 +44832,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44861,7 +44858,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44887,7 +44884,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44913,7 +44910,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44939,7 +44936,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44965,7 +44962,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44991,7 +44988,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45017,7 +45014,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45043,7 +45040,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45069,7 +45066,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45095,7 +45092,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45121,7 +45118,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45147,7 +45144,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45173,7 +45170,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45199,7 +45196,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45225,7 +45222,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45251,7 +45248,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45277,7 +45274,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45303,7 +45300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45329,7 +45326,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45355,7 +45352,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45381,7 +45378,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45407,7 +45404,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45433,7 +45430,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45459,7 +45456,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45485,7 +45482,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45511,7 +45508,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45537,7 +45534,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45563,7 +45560,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45589,7 +45586,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45615,7 +45612,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45641,7 +45638,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45667,7 +45664,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45693,7 +45690,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45719,7 +45716,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45745,7 +45742,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45771,7 +45768,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45797,7 +45794,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45823,7 +45820,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45849,7 +45846,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45875,7 +45872,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45901,7 +45898,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45927,7 +45924,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45953,7 +45950,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45979,7 +45976,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46005,7 +46002,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46031,7 +46028,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46057,7 +46054,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46083,7 +46080,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46109,7 +46106,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46135,7 +46132,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46161,7 +46158,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46187,7 +46184,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46213,7 +46210,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46239,7 +46236,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46265,7 +46262,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46291,7 +46288,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46317,7 +46314,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46343,7 +46340,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46369,7 +46366,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46395,7 +46392,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46421,7 +46418,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46447,7 +46444,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46473,7 +46470,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46499,7 +46496,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46525,7 +46522,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46551,7 +46548,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46577,7 +46574,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46603,7 +46600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46629,7 +46626,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46655,7 +46652,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46681,7 +46678,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46707,7 +46704,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46733,7 +46730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46759,7 +46756,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46785,7 +46782,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46811,7 +46808,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46837,7 +46834,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46863,7 +46860,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46889,7 +46886,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46915,7 +46912,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46941,7 +46938,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46967,7 +46964,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46993,7 +46990,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47019,7 +47016,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47045,7 +47042,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47071,7 +47068,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47097,7 +47094,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47123,7 +47120,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47149,7 +47146,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47175,7 +47172,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47201,7 +47198,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47227,7 +47224,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47253,7 +47250,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47279,7 +47276,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47305,7 +47302,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47331,7 +47328,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47357,7 +47354,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47383,7 +47380,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47409,7 +47406,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47435,7 +47432,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47461,7 +47458,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47487,7 +47484,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47513,7 +47510,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47539,7 +47536,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47565,7 +47562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47591,7 +47588,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47617,7 +47614,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47643,7 +47640,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47669,7 +47666,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47695,7 +47692,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47721,7 +47718,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47747,7 +47744,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47773,7 +47770,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47799,7 +47796,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47825,7 +47822,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47851,7 +47848,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47877,7 +47874,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47903,7 +47900,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47929,7 +47926,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47955,7 +47952,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47981,7 +47978,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48007,7 +48004,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48033,7 +48030,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48059,7 +48056,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48085,7 +48082,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48111,7 +48108,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48137,7 +48134,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48163,7 +48160,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48189,7 +48186,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48215,7 +48212,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48241,7 +48238,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48267,7 +48264,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48293,7 +48290,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48319,7 +48316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48345,7 +48342,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48371,7 +48368,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48397,7 +48394,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48423,7 +48420,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48449,7 +48446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48475,7 +48472,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48501,7 +48498,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48527,7 +48524,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48553,7 +48550,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48579,7 +48576,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48605,7 +48602,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48631,7 +48628,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48657,7 +48654,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48683,7 +48680,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48709,7 +48706,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48735,7 +48732,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48761,7 +48758,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48787,7 +48784,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48813,7 +48810,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48839,7 +48836,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48865,7 +48862,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48891,7 +48888,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48917,7 +48914,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48943,7 +48940,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48969,7 +48966,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48995,7 +48992,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49021,7 +49018,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49047,7 +49044,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49073,7 +49070,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49099,7 +49096,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49125,7 +49122,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49151,7 +49148,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49177,7 +49174,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49203,7 +49200,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49229,7 +49226,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49255,7 +49252,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49281,7 +49278,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49307,7 +49304,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49333,7 +49330,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49359,7 +49356,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49385,7 +49382,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49411,7 +49408,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49437,7 +49434,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49463,7 +49460,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49489,7 +49486,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49515,7 +49512,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49541,7 +49538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49567,7 +49564,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49593,7 +49590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49619,7 +49616,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49645,7 +49642,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49671,7 +49668,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49697,7 +49694,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49723,7 +49720,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49749,7 +49746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49775,7 +49772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49801,7 +49798,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49827,7 +49824,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49853,7 +49850,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49879,7 +49876,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49905,7 +49902,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49931,7 +49928,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49957,7 +49954,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49983,7 +49980,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50009,7 +50006,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50035,7 +50032,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50061,7 +50058,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50087,7 +50084,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50113,7 +50110,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50139,7 +50136,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50165,7 +50162,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50191,7 +50188,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50217,7 +50214,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50243,7 +50240,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50269,7 +50266,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50295,7 +50292,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50321,7 +50318,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50347,7 +50344,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50373,7 +50370,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50399,7 +50396,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50425,7 +50422,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50451,7 +50448,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50477,7 +50474,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50503,7 +50500,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50529,7 +50526,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50555,7 +50552,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50581,7 +50578,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50607,7 +50604,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50633,7 +50630,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50659,7 +50656,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50685,7 +50682,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50711,7 +50708,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50737,7 +50734,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50763,7 +50760,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50789,7 +50786,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50815,7 +50812,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50841,7 +50838,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50867,7 +50864,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50893,7 +50890,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50919,7 +50916,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50945,7 +50942,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50971,7 +50968,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50997,7 +50994,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51023,7 +51020,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51049,7 +51046,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51075,7 +51072,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51101,7 +51098,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51127,7 +51124,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51153,7 +51150,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51179,7 +51176,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51205,7 +51202,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51231,7 +51228,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51257,7 +51254,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51283,7 +51280,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51309,7 +51306,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51335,7 +51332,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51361,7 +51358,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51387,7 +51384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51413,7 +51410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51439,7 +51436,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51465,7 +51462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51491,7 +51488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51517,9 +51514,61 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1931" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1931" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="1" t="n">
+        <v>45961.3333333333</v>
+      </c>
+      <c r="B1932" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1932" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1932" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1932" t="s">
+        <v>313</v>
+      </c>
+      <c r="H1932" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="1" t="n">
+        <v>45964.3333912037</v>
+      </c>
+      <c r="B1933" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1933" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D1933" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="E1933" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F1933" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="G1933" t="s">
+        <v>320</v>
+      </c>
+      <c r="H1933" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925687789917</t>
+    <t xml:space="preserve">11.9256858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577272415161</t>
+    <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654909133911</t>
+    <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
     <t xml:space="preserve">10.7698993682861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007139205933</t>
+    <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314947128296</t>
@@ -71,76 +71,76 @@
     <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962032318115</t>
+    <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732564926147</t>
+    <t xml:space="preserve">11.5732555389404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192531585693</t>
+    <t xml:space="preserve">11.119252204895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194267272949</t>
+    <t xml:space="preserve">11.6194257736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116283416748</t>
+    <t xml:space="preserve">11.3116292953491</t>
   </si>
   <si>
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424757003784</t>
+    <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501014709473</t>
+    <t xml:space="preserve">11.3501033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102617263794</t>
+    <t xml:space="preserve">11.810263633728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773325920105</t>
+    <t xml:space="preserve">11.7733278274536</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963758468628</t>
+    <t xml:space="preserve">11.6963748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657001495361</t>
+    <t xml:space="preserve">11.9657030105591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807771682739</t>
+    <t xml:space="preserve">11.0807790756226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751779556274</t>
+    <t xml:space="preserve">11.2751770019531</t>
   </si>
   <si>
     <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087789535522</t>
+    <t xml:space="preserve">10.1087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326137542725</t>
+    <t xml:space="preserve">9.95326042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71997928619385</t>
+    <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345481872559</t>
+    <t xml:space="preserve">9.11345291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790325164795</t>
+    <t xml:space="preserve">9.097900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683917999268</t>
+    <t xml:space="preserve">9.85683727264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.5178050994873</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278930664062</t>
+    <t xml:space="preserve">12.0278940200806</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750165939331</t>
+    <t xml:space="preserve">11.9750156402588</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028589248657</t>
+    <t xml:space="preserve">11.7028570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862169265747</t>
+    <t xml:space="preserve">11.5862159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084581375122</t>
+    <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
     <t xml:space="preserve">11.6639757156372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529376983643</t>
+    <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196575164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.886378288269</t>
@@ -188,34 +188,34 @@
     <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198188781738</t>
+    <t xml:space="preserve">10.4198179244995</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332458496094</t>
+    <t xml:space="preserve">9.67332363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449188232422</t>
+    <t xml:space="preserve">9.42449283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222049713135</t>
+    <t xml:space="preserve">9.64222145080566</t>
   </si>
   <si>
     <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476602554321</t>
+    <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420610427856</t>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887138366699</t>
+    <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
     <t xml:space="preserve">9.7977409362793</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118057250977</t>
+    <t xml:space="preserve">9.3311824798584</t>
   </si>
   <si>
     <t xml:space="preserve">9.83662033081055</t>
@@ -233,34 +233,34 @@
     <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074668884277</t>
+    <t xml:space="preserve">9.29074573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815227508545</t>
   </si>
   <si>
     <t xml:space="preserve">9.09945583343506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842670440674</t>
+    <t xml:space="preserve">9.71842575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087778091431</t>
+    <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274564743042</t>
+    <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498363494873</t>
+    <t xml:space="preserve">10.349835395813</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064424514771</t>
+    <t xml:space="preserve">10.6064443588257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919784545898</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
     <t xml:space="preserve">10.4353713989258</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834932327271</t>
+    <t xml:space="preserve">10.0834922790527</t>
   </si>
   <si>
     <t xml:space="preserve">10.257345199585</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">9.90963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193161010742</t>
+    <t xml:space="preserve">9.56193351745605</t>
   </si>
   <si>
     <t xml:space="preserve">8.95344543457031</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959251403809</t>
+    <t xml:space="preserve">8.7795934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266605377197</t>
+    <t xml:space="preserve">8.69266510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920139312744</t>
+    <t xml:space="preserve">8.64920330047607</t>
   </si>
   <si>
     <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271289825439</t>
+    <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266136169434</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004655838013</t>
+    <t xml:space="preserve">11.3004665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658313751221</t>
+    <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6050510406494</t>
+    <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311990737915</t>
@@ -338,43 +338,43 @@
     <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422576904297</t>
+    <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
     <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578548431396</t>
+    <t xml:space="preserve">9.73578453063965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442726135254</t>
+    <t xml:space="preserve">10.3442735671997</t>
   </si>
   <si>
     <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725151062012</t>
+    <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876533508301</t>
+    <t xml:space="preserve">7.38876628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183935165405</t>
+    <t xml:space="preserve">7.30183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530305862427</t>
+    <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569370269775</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
     <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378971099854</t>
+    <t xml:space="preserve">7.95378875732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
@@ -383,22 +383,22 @@
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087146759033</t>
+    <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585121154785</t>
+    <t xml:space="preserve">9.56585025787354</t>
   </si>
   <si>
     <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870620727539</t>
+    <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85727119445801</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
     <t xml:space="preserve">8.76869773864746</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012428283691</t>
+    <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7244119644165</t>
+    <t xml:space="preserve">8.72441101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2115592956543</t>
+    <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
     <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50297927856445</t>
+    <t xml:space="preserve">8.50297832489014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013275146484</t>
+    <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858606338501</t>
+    <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
     <t xml:space="preserve">11.0715866088867</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515781402588</t>
+    <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
     <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83156967163086</t>
+    <t xml:space="preserve">9.83157062530518</t>
   </si>
   <si>
     <t xml:space="preserve">9.74299716949463</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">11.2487335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144510269165</t>
+    <t xml:space="preserve">11.5144519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.425877571106</t>
+    <t xml:space="preserve">11.4258766174316</t>
   </si>
   <si>
     <t xml:space="preserve">10.805869102478</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">10.6287240982056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172975540161</t>
+    <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630056381226</t>
+    <t xml:space="preserve">10.3630065917969</t>
   </si>
   <si>
     <t xml:space="preserve">10.540150642395</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006050109863</t>
+    <t xml:space="preserve">10.6006059646606</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
@@ -500,28 +500,28 @@
     <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818117141724</t>
+    <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
     <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78517436981201</t>
+    <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381916046143</t>
+    <t xml:space="preserve">10.2381906509399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502605438232</t>
+    <t xml:space="preserve">12.0502624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4160375595093</t>
+    <t xml:space="preserve">11.416036605835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1442270278931</t>
+    <t xml:space="preserve">11.1442260742188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690547943115</t>
+    <t xml:space="preserve">11.8690538406372</t>
   </si>
   <si>
     <t xml:space="preserve">12.1408643722534</t>
@@ -530,61 +530,61 @@
     <t xml:space="preserve">11.6878461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314682006836</t>
+    <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844844818115</t>
+    <t xml:space="preserve">12.6844854354858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032777786255</t>
+    <t xml:space="preserve">12.5032796859741</t>
   </si>
   <si>
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375017166138</t>
+    <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562959671021</t>
+    <t xml:space="preserve">12.9562969207764</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435361862183</t>
+    <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811246871948</t>
+    <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931926727295</t>
+    <t xml:space="preserve">15.4931936264038</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4025897979736</t>
+    <t xml:space="preserve">15.4025888442993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556060791016</t>
+    <t xml:space="preserve">15.8556051254272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462099075317</t>
+    <t xml:space="preserve">15.9462089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650012969971</t>
+    <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
     <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.221381187439</t>
+    <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.587158203125</t>
+    <t xml:space="preserve">14.5871572494507</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">14.4965543746948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.768364906311</t>
+    <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495706558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341409683228</t>
+    <t xml:space="preserve">14.1341400146484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4093141555786</t>
+    <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
     <t xml:space="preserve">12.5938816070557</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9529323577881</t>
+    <t xml:space="preserve">13.9529333114624</t>
   </si>
   <si>
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119869232178</t>
+    <t xml:space="preserve">15.3119840621948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264251708984</t>
+    <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230634689331</t>
+    <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.26598072052</t>
+    <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
     <t xml:space="preserve">14.6365251541138</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343894958496</t>
+    <t xml:space="preserve">14.0343885421753</t>
   </si>
   <si>
     <t xml:space="preserve">14.682843208313</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776168823242</t>
+    <t xml:space="preserve">15.3776149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586168289185</t>
+    <t xml:space="preserve">14.3586158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733446121216</t>
+    <t xml:space="preserve">14.1733436584473</t>
   </si>
   <si>
     <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6638441085815</t>
+    <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
     <t xml:space="preserve">13.8491172790527</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248899459839</t>
+    <t xml:space="preserve">13.5248908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027982711792</t>
+    <t xml:space="preserve">13.8027992248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859357833862</t>
+    <t xml:space="preserve">13.3859367370605</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690732955933</t>
+    <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006645202637</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712070465088</t>
+    <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
     <t xml:space="preserve">13.1543455123901</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533885955811</t>
+    <t xml:space="preserve">15.0533876419067</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -749,31 +749,31 @@
     <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7291603088379</t>
+    <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144344329834</t>
+    <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2849788665771</t>
+    <t xml:space="preserve">15.2849779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555242538452</t>
+    <t xml:space="preserve">15.6555223464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407964706421</t>
+    <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
     <t xml:space="preserve">15.7944774627686</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8681144714355</t>
+    <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975709915161</t>
+    <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0166959762573</t>
+    <t xml:space="preserve">15.016695022583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541482925415</t>
+    <t xml:space="preserve">14.5414838790894</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968648910522</t>
+    <t xml:space="preserve">15.3968658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572036743164</t>
+    <t xml:space="preserve">16.1572017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720769882202</t>
+    <t xml:space="preserve">15.8720779418945</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315673828125</t>
+    <t xml:space="preserve">14.7315683364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522449493408</t>
+    <t xml:space="preserve">16.2522468566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -51548,7 +51548,7 @@
     </row>
     <row r="1933">
       <c r="A1933" s="1" t="n">
-        <v>45964.3333912037</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B1933" t="n">
         <v>200</v>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118366241455</t>
+    <t xml:space="preserve">11.9118356704712</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256858825684</t>
+    <t xml:space="preserve">11.925687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654918670654</t>
+    <t xml:space="preserve">11.3654928207397</t>
   </si>
   <si>
     <t xml:space="preserve">10.7698993682861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007167816162</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729778289795</t>
+    <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314947128296</t>
+    <t xml:space="preserve">10.9314956665039</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653877258301</t>
@@ -74,91 +74,91 @@
     <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732555389404</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.119252204895</t>
+    <t xml:space="preserve">11.1192512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194257736206</t>
+    <t xml:space="preserve">11.6194276809692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116292953491</t>
+    <t xml:space="preserve">11.3116283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948375701904</t>
+    <t xml:space="preserve">11.6948385238647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424776077271</t>
+    <t xml:space="preserve">11.5424766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501033782959</t>
+    <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.810263633728</t>
+    <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733278274536</t>
+    <t xml:space="preserve">11.7733268737793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963748931885</t>
+    <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657030105591</t>
+    <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579008102417</t>
+    <t xml:space="preserve">11.657901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807790756226</t>
+    <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751770019531</t>
+    <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086185455322</t>
+    <t xml:space="preserve">10.8086175918579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349044799805</t>
+    <t xml:space="preserve">10.5349035263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683450698853</t>
+    <t xml:space="preserve">10.0683460235596</t>
   </si>
   <si>
     <t xml:space="preserve">10.1087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326042175293</t>
+    <t xml:space="preserve">9.95325946807861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998119354248</t>
+    <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345291137695</t>
+    <t xml:space="preserve">9.11345386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.097900390625</t>
+    <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5178050994873</t>
+    <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
     <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278940200806</t>
+    <t xml:space="preserve">12.0278921127319</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750156402588</t>
+    <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028570175171</t>
@@ -170,49 +170,49 @@
     <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639757156372</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196575164795</t>
+    <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863792419434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641370773315</t>
+    <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.497579574585</t>
+    <t xml:space="preserve">10.4975776672363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198179244995</t>
+    <t xml:space="preserve">10.4198207855225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310192108154</t>
+    <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332363128662</t>
+    <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4089412689209</t>
+    <t xml:space="preserve">9.40894317626953</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222145080566</t>
+    <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550067901611</t>
+    <t xml:space="preserve">9.8754997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420600891113</t>
+    <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
@@ -221,22 +221,22 @@
     <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670101165771</t>
+    <t xml:space="preserve">9.4867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3311824798584</t>
+    <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662033081055</t>
+    <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892475128174</t>
+    <t xml:space="preserve">9.47892284393311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074573516846</t>
+    <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815227508545</t>
+    <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
     <t xml:space="preserve">9.09945583343506</t>
@@ -257,52 +257,52 @@
     <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064443588257</t>
+    <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353713989258</t>
+    <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778904914856</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181255340576</t>
+    <t xml:space="preserve">10.5181245803833</t>
   </si>
   <si>
     <t xml:space="preserve">10.0834922790527</t>
   </si>
   <si>
-    <t xml:space="preserve">10.257345199585</t>
+    <t xml:space="preserve">10.2573461532593</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963935852051</t>
+    <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193351745605</t>
+    <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344543457031</t>
+    <t xml:space="preserve">8.953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8665189743042</t>
+    <t xml:space="preserve">8.86651802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7795934677124</t>
+    <t xml:space="preserve">8.77959156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266510009766</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920330047607</t>
+    <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037189483643</t>
+    <t xml:space="preserve">9.04037284851074</t>
   </si>
   <si>
     <t xml:space="preserve">9.82271194458008</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004665374756</t>
+    <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658323287964</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6050519943237</t>
+    <t xml:space="preserve">10.6050510406494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311990737915</t>
+    <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
     <t xml:space="preserve">9.47500514984131</t>
@@ -344,109 +344,109 @@
     <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578453063965</t>
+    <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442735671997</t>
+    <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725198745728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876628875732</t>
+    <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183887481689</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.258376121521</t>
+    <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530210494995</t>
+    <t xml:space="preserve">7.34530305862427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569274902344</t>
+    <t xml:space="preserve">7.4756932258606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339859008789</t>
+    <t xml:space="preserve">7.82339906692505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378875732422</t>
+    <t xml:space="preserve">7.95378828048706</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573863983154</t>
+    <t xml:space="preserve">8.60573959350586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585025787354</t>
+    <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4772777557373</t>
+    <t xml:space="preserve">9.47727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584274291992</t>
+    <t xml:space="preserve">8.94584178924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869773864746</t>
+    <t xml:space="preserve">8.76869678497314</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012523651123</t>
+    <t xml:space="preserve">8.68012428283691</t>
   </si>
   <si>
     <t xml:space="preserve">8.72441101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21156024932861</t>
+    <t xml:space="preserve">9.21156120300293</t>
   </si>
   <si>
     <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50297832489014</t>
+    <t xml:space="preserve">8.50298023223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440773010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
     <t xml:space="preserve">11.0715866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944425582886</t>
+    <t xml:space="preserve">10.8944416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830150604248</t>
+    <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
     <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83157062530518</t>
+    <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.74299716949463</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487335205078</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144519805908</t>
+    <t xml:space="preserve">11.5144500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4258766174316</t>
+    <t xml:space="preserve">11.4258785247803</t>
   </si>
   <si>
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630065917969</t>
+    <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.540150642395</t>
+    <t xml:space="preserve">10.5401515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193983078003</t>
+    <t xml:space="preserve">10.4193992614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100021362305</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006059646606</t>
+    <t xml:space="preserve">10.6006050109863</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381906509399</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.416036605835</t>
+    <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442260742188</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878461837769</t>
+    <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844854354858</t>
+    <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032796859741</t>
+    <t xml:space="preserve">12.5032777786255</t>
   </si>
   <si>
     <t xml:space="preserve">12.775089263916</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811237335205</t>
+    <t xml:space="preserve">13.6811227798462</t>
   </si>
   <si>
     <t xml:space="preserve">14.3153476715088</t>
@@ -563,22 +563,22 @@
     <t xml:space="preserve">15.4931936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401754379272</t>
+    <t xml:space="preserve">15.0401763916016</t>
   </si>
   <si>
     <t xml:space="preserve">15.4025888442993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556051254272</t>
+    <t xml:space="preserve">15.8556070327759</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462089538574</t>
+    <t xml:space="preserve">15.9462108612061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650022506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307792663574</t>
+    <t xml:space="preserve">15.1307802200317</t>
   </si>
   <si>
     <t xml:space="preserve">15.2213821411133</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495706558228</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341400146484</t>
+    <t xml:space="preserve">14.1341419219971</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093132019043</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119840621948</t>
+    <t xml:space="preserve">15.3119859695435</t>
   </si>
   <si>
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230625152588</t>
+    <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196626663208</t>
+    <t xml:space="preserve">14.2196636199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776149749756</t>
+    <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586158752441</t>
+    <t xml:space="preserve">14.3586168289185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733436584473</t>
+    <t xml:space="preserve">14.1733446121216</t>
   </si>
   <si>
     <t xml:space="preserve">13.7564811706543</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491172790527</t>
+    <t xml:space="preserve">13.8491163253784</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880723953247</t>
+    <t xml:space="preserve">13.9880714416504</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248908996582</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.061710357666</t>
+    <t xml:space="preserve">13.0617094039917</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006635665894</t>
+    <t xml:space="preserve">13.200662612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533876419067</t>
+    <t xml:space="preserve">15.0533885955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -752,25 +752,28 @@
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
+    <t xml:space="preserve">14.4512538909912</t>
+  </si>
+  <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
     <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2849779129028</t>
+    <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555223464966</t>
+    <t xml:space="preserve">15.6555242538452</t>
   </si>
   <si>
     <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1923427581787</t>
+    <t xml:space="preserve">15.192343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165691375732</t>
+    <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
     <t xml:space="preserve">15.8407974243164</t>
@@ -779,10 +782,10 @@
     <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702520370483</t>
+    <t xml:space="preserve">15.4702529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460247039795</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
@@ -33314,7 +33317,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33340,7 +33343,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33366,7 +33369,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33392,7 +33395,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33444,7 +33447,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33470,7 +33473,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33496,7 +33499,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33522,7 +33525,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33548,7 +33551,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33574,7 +33577,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33600,7 +33603,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33626,7 +33629,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33652,7 +33655,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33678,7 +33681,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33704,7 +33707,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33730,7 +33733,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33756,7 +33759,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33782,7 +33785,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33808,7 +33811,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33834,7 +33837,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33886,7 +33889,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33912,7 +33915,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33938,7 +33941,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33964,7 +33967,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33990,7 +33993,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34016,7 +34019,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34042,7 +34045,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34406,7 +34409,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34432,7 +34435,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34458,7 +34461,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34744,7 +34747,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34770,7 +34773,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34796,7 +34799,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34900,7 +34903,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35056,7 +35059,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35108,7 +35111,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35134,7 +35137,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35160,7 +35163,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35186,7 +35189,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35212,7 +35215,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35238,7 +35241,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35264,7 +35267,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35290,7 +35293,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35368,7 +35371,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35394,7 +35397,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35420,7 +35423,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35446,7 +35449,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35472,7 +35475,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35498,7 +35501,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35524,7 +35527,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35550,7 +35553,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35576,7 +35579,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35602,7 +35605,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35628,7 +35631,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35654,7 +35657,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35680,7 +35683,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35706,7 +35709,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35732,7 +35735,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35758,7 +35761,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35784,7 +35787,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35810,7 +35813,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35836,7 +35839,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35862,7 +35865,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35888,7 +35891,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35914,7 +35917,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35940,7 +35943,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35966,7 +35969,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35992,7 +35995,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36018,7 +36021,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36044,7 +36047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36070,7 +36073,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36096,7 +36099,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36122,7 +36125,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36148,7 +36151,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36174,7 +36177,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36200,7 +36203,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36226,7 +36229,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36252,7 +36255,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36278,7 +36281,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36304,7 +36307,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36330,7 +36333,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36356,7 +36359,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36382,7 +36385,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36408,7 +36411,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36434,7 +36437,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36460,7 +36463,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36486,7 +36489,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36512,7 +36515,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36538,7 +36541,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36564,7 +36567,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36590,7 +36593,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36616,7 +36619,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36642,7 +36645,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36668,7 +36671,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36694,7 +36697,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -36720,7 +36723,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36746,7 +36749,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36772,7 +36775,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36798,7 +36801,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36824,7 +36827,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36850,7 +36853,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36876,7 +36879,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36902,7 +36905,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36928,7 +36931,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36954,7 +36957,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36980,7 +36983,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37006,7 +37009,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37032,7 +37035,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37058,7 +37061,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37084,7 +37087,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37110,7 +37113,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37136,7 +37139,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37162,7 +37165,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37188,7 +37191,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37214,7 +37217,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37240,7 +37243,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37266,7 +37269,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37292,7 +37295,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37318,7 +37321,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37344,7 +37347,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37370,7 +37373,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37396,7 +37399,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37422,7 +37425,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37448,7 +37451,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37474,7 +37477,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37500,7 +37503,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37526,7 +37529,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37552,7 +37555,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37578,7 +37581,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37604,7 +37607,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37630,7 +37633,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37656,7 +37659,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37682,7 +37685,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37708,7 +37711,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37734,7 +37737,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37760,7 +37763,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37786,7 +37789,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37812,7 +37815,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37838,7 +37841,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -37864,7 +37867,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37890,7 +37893,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37916,7 +37919,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37942,7 +37945,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37968,7 +37971,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -37994,7 +37997,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38020,7 +38023,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38046,7 +38049,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38072,7 +38075,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38098,7 +38101,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38124,7 +38127,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38150,7 +38153,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38176,7 +38179,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38202,7 +38205,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38228,7 +38231,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38254,7 +38257,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38280,7 +38283,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38306,7 +38309,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38332,7 +38335,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38358,7 +38361,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38384,7 +38387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38410,7 +38413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38436,7 +38439,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38462,7 +38465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38488,7 +38491,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38514,7 +38517,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38540,7 +38543,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38566,7 +38569,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38592,7 +38595,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38618,7 +38621,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38644,7 +38647,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38670,7 +38673,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38696,7 +38699,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38722,7 +38725,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38748,7 +38751,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38774,7 +38777,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38800,7 +38803,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -38826,7 +38829,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38852,7 +38855,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38878,7 +38881,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38904,7 +38907,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38930,7 +38933,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38956,7 +38959,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38982,7 +38985,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39008,7 +39011,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39034,7 +39037,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39060,7 +39063,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39086,7 +39089,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39112,7 +39115,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39138,7 +39141,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39164,7 +39167,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39190,7 +39193,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39216,7 +39219,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39242,7 +39245,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39268,7 +39271,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39294,7 +39297,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39320,7 +39323,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39346,7 +39349,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39372,7 +39375,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39398,7 +39401,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39424,7 +39427,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39450,7 +39453,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39476,7 +39479,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39502,7 +39505,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39528,7 +39531,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39554,7 +39557,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39580,7 +39583,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39606,7 +39609,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39632,7 +39635,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39658,7 +39661,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39684,7 +39687,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39710,7 +39713,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39736,7 +39739,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39762,7 +39765,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39788,7 +39791,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39814,7 +39817,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39840,7 +39843,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39866,7 +39869,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39892,7 +39895,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39918,7 +39921,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39944,7 +39947,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39970,7 +39973,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39996,7 +39999,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40022,7 +40025,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40048,7 +40051,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40074,7 +40077,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40100,7 +40103,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40126,7 +40129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40152,7 +40155,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40178,7 +40181,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40204,7 +40207,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40230,7 +40233,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40256,7 +40259,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40282,7 +40285,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40308,7 +40311,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40334,7 +40337,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40360,7 +40363,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40386,7 +40389,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40646,7 +40649,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40672,7 +40675,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40698,7 +40701,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40724,7 +40727,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40750,7 +40753,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40776,7 +40779,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40802,7 +40805,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40828,7 +40831,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40854,7 +40857,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -40880,7 +40883,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40906,7 +40909,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40932,7 +40935,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40958,7 +40961,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40984,7 +40987,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41010,7 +41013,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41036,7 +41039,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41062,7 +41065,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41088,7 +41091,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41114,7 +41117,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41140,7 +41143,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41166,7 +41169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41192,7 +41195,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41218,7 +41221,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41244,7 +41247,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41270,7 +41273,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41296,7 +41299,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41322,7 +41325,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41348,7 +41351,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41374,7 +41377,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41400,7 +41403,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41426,7 +41429,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41452,7 +41455,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41478,7 +41481,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41504,7 +41507,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41530,7 +41533,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41556,7 +41559,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41582,7 +41585,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41608,7 +41611,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41634,7 +41637,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41660,7 +41663,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41686,7 +41689,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41712,7 +41715,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41738,7 +41741,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41764,7 +41767,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41790,7 +41793,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41816,7 +41819,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41842,7 +41845,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41868,7 +41871,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41894,7 +41897,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41920,7 +41923,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41946,7 +41949,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41972,7 +41975,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -41998,7 +42001,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42024,7 +42027,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42050,7 +42053,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42076,7 +42079,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42102,7 +42105,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42128,7 +42131,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42154,7 +42157,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42180,7 +42183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42206,7 +42209,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42232,7 +42235,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42258,7 +42261,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42284,7 +42287,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42310,7 +42313,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42336,7 +42339,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42362,7 +42365,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42388,7 +42391,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42414,7 +42417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42440,7 +42443,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42466,7 +42469,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42492,7 +42495,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42518,7 +42521,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42544,7 +42547,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42570,7 +42573,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42596,7 +42599,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42622,7 +42625,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42648,7 +42651,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42674,7 +42677,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42700,7 +42703,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42726,7 +42729,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42752,7 +42755,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42778,7 +42781,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42804,7 +42807,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42830,7 +42833,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42856,7 +42859,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42882,7 +42885,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42908,7 +42911,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42934,7 +42937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42960,7 +42963,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42986,7 +42989,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43012,7 +43015,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43038,7 +43041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43064,7 +43067,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43090,7 +43093,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43116,7 +43119,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43142,7 +43145,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43168,7 +43171,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43194,7 +43197,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43220,7 +43223,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43246,7 +43249,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43272,7 +43275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43298,7 +43301,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43324,7 +43327,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43350,7 +43353,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43376,7 +43379,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43402,7 +43405,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43428,7 +43431,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43454,7 +43457,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43480,7 +43483,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43506,7 +43509,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43532,7 +43535,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43558,7 +43561,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43584,7 +43587,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43610,7 +43613,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43636,7 +43639,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43662,7 +43665,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43688,7 +43691,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43714,7 +43717,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43740,7 +43743,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43766,7 +43769,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43792,7 +43795,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43818,7 +43821,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43844,7 +43847,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43870,7 +43873,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43896,7 +43899,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43922,7 +43925,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43948,7 +43951,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43974,7 +43977,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44000,7 +44003,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44026,7 +44029,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44052,7 +44055,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44078,7 +44081,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44104,7 +44107,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44130,7 +44133,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44156,7 +44159,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44182,7 +44185,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44208,7 +44211,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44234,7 +44237,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44260,7 +44263,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44286,7 +44289,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44312,7 +44315,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44338,7 +44341,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44364,7 +44367,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44390,7 +44393,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44416,7 +44419,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44442,7 +44445,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44468,7 +44471,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44494,7 +44497,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44520,7 +44523,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44546,7 +44549,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44572,7 +44575,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44598,7 +44601,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44624,7 +44627,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44650,7 +44653,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44676,7 +44679,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44702,7 +44705,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44728,7 +44731,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44754,7 +44757,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44780,7 +44783,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44806,7 +44809,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44832,7 +44835,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44858,7 +44861,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44884,7 +44887,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44910,7 +44913,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44936,7 +44939,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44962,7 +44965,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44988,7 +44991,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45014,7 +45017,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45040,7 +45043,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45066,7 +45069,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45092,7 +45095,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45118,7 +45121,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45144,7 +45147,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45170,7 +45173,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45196,7 +45199,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45222,7 +45225,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45248,7 +45251,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45274,7 +45277,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45300,7 +45303,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45326,7 +45329,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45352,7 +45355,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45378,7 +45381,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45404,7 +45407,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45430,7 +45433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45456,7 +45459,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45482,7 +45485,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45508,7 +45511,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45534,7 +45537,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45560,7 +45563,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45586,7 +45589,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45612,7 +45615,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45638,7 +45641,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45664,7 +45667,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45690,7 +45693,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45716,7 +45719,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45742,7 +45745,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45768,7 +45771,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45794,7 +45797,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45820,7 +45823,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45846,7 +45849,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45872,7 +45875,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45898,7 +45901,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45924,7 +45927,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45950,7 +45953,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45976,7 +45979,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46002,7 +46005,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46028,7 +46031,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46054,7 +46057,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46080,7 +46083,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46106,7 +46109,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46132,7 +46135,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46158,7 +46161,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46184,7 +46187,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46210,7 +46213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46236,7 +46239,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46262,7 +46265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46288,7 +46291,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46314,7 +46317,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46340,7 +46343,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46366,7 +46369,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46392,7 +46395,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46418,7 +46421,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46444,7 +46447,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46470,7 +46473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46496,7 +46499,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46522,7 +46525,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46548,7 +46551,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46574,7 +46577,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46600,7 +46603,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46626,7 +46629,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46652,7 +46655,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46678,7 +46681,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46704,7 +46707,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46730,7 +46733,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46756,7 +46759,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46782,7 +46785,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46808,7 +46811,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46834,7 +46837,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46860,7 +46863,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46886,7 +46889,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46912,7 +46915,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46938,7 +46941,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46964,7 +46967,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46990,7 +46993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47016,7 +47019,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47042,7 +47045,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47068,7 +47071,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47094,7 +47097,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47120,7 +47123,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47146,7 +47149,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47172,7 +47175,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47198,7 +47201,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47224,7 +47227,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47250,7 +47253,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47276,7 +47279,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47302,7 +47305,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47328,7 +47331,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47354,7 +47357,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47380,7 +47383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47406,7 +47409,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47432,7 +47435,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47458,7 +47461,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47484,7 +47487,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47510,7 +47513,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47536,7 +47539,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47562,7 +47565,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47588,7 +47591,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47614,7 +47617,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47640,7 +47643,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47666,7 +47669,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47692,7 +47695,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47718,7 +47721,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47744,7 +47747,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47770,7 +47773,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47796,7 +47799,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47822,7 +47825,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47848,7 +47851,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47874,7 +47877,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47900,7 +47903,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47926,7 +47929,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47952,7 +47955,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47978,7 +47981,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48004,7 +48007,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48030,7 +48033,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48056,7 +48059,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48082,7 +48085,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48108,7 +48111,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48134,7 +48137,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48160,7 +48163,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48186,7 +48189,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48212,7 +48215,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48238,7 +48241,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48264,7 +48267,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48290,7 +48293,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48316,7 +48319,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48342,7 +48345,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48368,7 +48371,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48394,7 +48397,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48420,7 +48423,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48446,7 +48449,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48472,7 +48475,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48498,7 +48501,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48524,7 +48527,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48550,7 +48553,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48576,7 +48579,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48602,7 +48605,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48628,7 +48631,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48654,7 +48657,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48680,7 +48683,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48706,7 +48709,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48732,7 +48735,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48758,7 +48761,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48784,7 +48787,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48810,7 +48813,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48836,7 +48839,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48862,7 +48865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48888,7 +48891,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48914,7 +48917,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48940,7 +48943,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48966,7 +48969,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48992,7 +48995,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49018,7 +49021,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49044,7 +49047,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49070,7 +49073,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49096,7 +49099,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49122,7 +49125,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49148,7 +49151,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49174,7 +49177,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49200,7 +49203,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49226,7 +49229,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49252,7 +49255,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49278,7 +49281,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49304,7 +49307,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49330,7 +49333,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49356,7 +49359,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49382,7 +49385,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49408,7 +49411,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49434,7 +49437,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49460,7 +49463,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49486,7 +49489,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49512,7 +49515,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49538,7 +49541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49564,7 +49567,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49590,7 +49593,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49616,7 +49619,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49642,7 +49645,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49668,7 +49671,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49694,7 +49697,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49720,7 +49723,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49746,7 +49749,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49772,7 +49775,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49798,7 +49801,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49824,7 +49827,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49850,7 +49853,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49876,7 +49879,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49902,7 +49905,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49928,7 +49931,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49954,7 +49957,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49980,7 +49983,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50006,7 +50009,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50032,7 +50035,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50058,7 +50061,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50084,7 +50087,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50110,7 +50113,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50136,7 +50139,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50162,7 +50165,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50188,7 +50191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50214,7 +50217,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50240,7 +50243,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50266,7 +50269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50292,7 +50295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50318,7 +50321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50344,7 +50347,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50370,7 +50373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50396,7 +50399,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50422,7 +50425,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50448,7 +50451,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50474,7 +50477,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50500,7 +50503,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50526,7 +50529,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50552,7 +50555,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50578,7 +50581,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50604,7 +50607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50630,7 +50633,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50656,7 +50659,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50682,7 +50685,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50708,7 +50711,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50734,7 +50737,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50760,7 +50763,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50786,7 +50789,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50812,7 +50815,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50838,7 +50841,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50864,7 +50867,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50890,7 +50893,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50916,7 +50919,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50942,7 +50945,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50968,7 +50971,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50994,7 +50997,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51020,7 +51023,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51046,7 +51049,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51072,7 +51075,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51098,7 +51101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51124,7 +51127,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51150,7 +51153,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51176,7 +51179,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51202,7 +51205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51228,7 +51231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51254,7 +51257,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51280,7 +51283,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51306,7 +51309,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51332,7 +51335,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51358,7 +51361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51384,7 +51387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51410,7 +51413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51436,7 +51439,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51462,7 +51465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51488,7 +51491,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51514,7 +51517,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1931" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51540,7 +51543,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1932" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51566,9 +51569,35 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1933" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1933" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="1" t="n">
+        <v>45965.3333333333</v>
+      </c>
+      <c r="B1934" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1934" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="G1934" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1934" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925687789917</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502769470215</t>
@@ -53,16 +53,16 @@
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654928207397</t>
+    <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7698993682861</t>
+    <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007167816162</t>
+    <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314956665039</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962022781372</t>
+    <t xml:space="preserve">11.1962013244629</t>
   </si>
   <si>
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192512512207</t>
+    <t xml:space="preserve">11.119252204895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194276809692</t>
+    <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116283416748</t>
+    <t xml:space="preserve">11.3116273880005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948385238647</t>
+    <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424757003784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501014709473</t>
+    <t xml:space="preserve">11.3501033782959</t>
   </si>
   <si>
     <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733268737793</t>
+    <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807781219482</t>
+    <t xml:space="preserve">11.0807790756226</t>
   </si>
   <si>
     <t xml:space="preserve">11.2751779556274</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">10.1087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95325946807861</t>
+    <t xml:space="preserve">9.95326042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998023986816</t>
+    <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
     <t xml:space="preserve">9.11345386505127</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683822631836</t>
+    <t xml:space="preserve">9.85683727264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2642993927002</t>
+    <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907304763794</t>
+    <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278921127319</t>
+    <t xml:space="preserve">12.0278930664062</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
@@ -161,43 +161,43 @@
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862159729004</t>
+    <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
     <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639757156372</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196594238281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8863792419434</t>
+    <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975776672363</t>
+    <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198207855225</t>
+    <t xml:space="preserve">10.4198198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310201644897</t>
+    <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332458496094</t>
+    <t xml:space="preserve">9.67332553863525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894317626953</t>
+    <t xml:space="preserve">9.40894222259521</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449283599854</t>
@@ -212,34 +212,34 @@
     <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342059135437</t>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7977409362793</t>
+    <t xml:space="preserve">9.79773998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4867000579834</t>
+    <t xml:space="preserve">9.48670196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118152618408</t>
+    <t xml:space="preserve">9.33118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892284393311</t>
+    <t xml:space="preserve">9.47892570495605</t>
   </si>
   <si>
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815036773682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945583343506</t>
+    <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
     <t xml:space="preserve">9.71842575073242</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2745637893677</t>
+    <t xml:space="preserve">10.2745656967163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.349835395813</t>
+    <t xml:space="preserve">10.3498373031616</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919784545898</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
     <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7789058685303</t>
+    <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181245803833</t>
+    <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
     <t xml:space="preserve">10.0834922790527</t>
@@ -284,34 +284,34 @@
     <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193256378174</t>
+    <t xml:space="preserve">9.56193351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.953444480896</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651802062988</t>
+    <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959156036377</t>
+    <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266605377197</t>
+    <t xml:space="preserve">8.69266510009766</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037284851074</t>
+    <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271194458008</t>
+    <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
     <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004655838013</t>
+    <t xml:space="preserve">11.3004665374756</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658323287964</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704196929932</t>
+    <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
     <t xml:space="preserve">9.99656581878662</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">10.6050510406494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311981201172</t>
+    <t xml:space="preserve">10.4311990737915</t>
   </si>
   <si>
     <t xml:space="preserve">9.47500514984131</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422672271729</t>
+    <t xml:space="preserve">9.21422576904297</t>
   </si>
   <si>
     <t xml:space="preserve">9.12729930877686</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442726135254</t>
+    <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115222930908</t>
+    <t xml:space="preserve">9.30115127563477</t>
   </si>
   <si>
     <t xml:space="preserve">7.99725198745728</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">7.34530305862427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4756932258606</t>
+    <t xml:space="preserve">7.47569227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339906692505</t>
+    <t xml:space="preserve">7.82339811325073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378828048706</t>
+    <t xml:space="preserve">7.95378923416138</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
@@ -383,25 +383,25 @@
     <t xml:space="preserve">8.60573959350586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087146759033</t>
+    <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727870941162</t>
+    <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870716094971</t>
+    <t xml:space="preserve">9.38870620727539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584178924561</t>
+    <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85727024078369</t>
+    <t xml:space="preserve">8.85726928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869678497314</t>
+    <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441524505615</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">8.68012428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72441101074219</t>
+    <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21156120300293</t>
+    <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
     <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50298023223877</t>
+    <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440773010254</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013370513916</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0715866088867</t>
+    <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
     <t xml:space="preserve">10.8944416046143</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515781402588</t>
+    <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
     <t xml:space="preserve">10.0972871780396</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487325668335</t>
+    <t xml:space="preserve">11.2487316131592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144500732422</t>
+    <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4258785247803</t>
+    <t xml:space="preserve">11.425877571106</t>
   </si>
   <si>
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287231445312</t>
+    <t xml:space="preserve">10.6287240982056</t>
   </si>
   <si>
     <t xml:space="preserve">10.7172966003418</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401515960693</t>
+    <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
     <t xml:space="preserve">10.4193992614746</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">10.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912088394165</t>
+    <t xml:space="preserve">10.6912097930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.6006050109863</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818126678467</t>
+    <t xml:space="preserve">10.7818117141724</t>
   </si>
   <si>
     <t xml:space="preserve">10.9630193710327</t>
@@ -509,28 +509,28 @@
     <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381916046143</t>
+    <t xml:space="preserve">10.2381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502624511719</t>
+    <t xml:space="preserve">12.0502605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4160375595093</t>
+    <t xml:space="preserve">11.416036605835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442260742188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690538406372</t>
+    <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
     <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878471374512</t>
+    <t xml:space="preserve">11.6878461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314691543579</t>
+    <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
     <t xml:space="preserve">12.6844844818115</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375026702881</t>
+    <t xml:space="preserve">13.1375017166138</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562969207764</t>
+    <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281064987183</t>
@@ -554,28 +554,28 @@
     <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811227798462</t>
+    <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153476715088</t>
+    <t xml:space="preserve">14.3153486251831</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931936264038</t>
+    <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401763916016</t>
+    <t xml:space="preserve">15.0401744842529</t>
   </si>
   <si>
     <t xml:space="preserve">15.4025888442993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556070327759</t>
+    <t xml:space="preserve">15.8556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462108612061</t>
+    <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650022506714</t>
+    <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
     <t xml:space="preserve">15.1307802200317</t>
@@ -584,19 +584,19 @@
     <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871572494507</t>
+    <t xml:space="preserve">14.587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8623304367065</t>
+    <t xml:space="preserve">13.8623313903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4965543746948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7683639526367</t>
+    <t xml:space="preserve">14.768364906311</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495725631714</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -620,46 +620,46 @@
     <t xml:space="preserve">13.5905199050903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3187093734741</t>
+    <t xml:space="preserve">13.3187084197998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656921386719</t>
+    <t xml:space="preserve">12.8656930923462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9529333114624</t>
+    <t xml:space="preserve">13.9529323577881</t>
   </si>
   <si>
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119859695435</t>
+    <t xml:space="preserve">15.3119869232178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264242172241</t>
+    <t xml:space="preserve">13.7264251708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512519836426</t>
   </si>
   <si>
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2659797668457</t>
+    <t xml:space="preserve">14.26598072052</t>
   </si>
   <si>
     <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196636199951</t>
+    <t xml:space="preserve">14.2196626663208</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343885421753</t>
+    <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
     <t xml:space="preserve">14.682843208313</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776159286499</t>
+    <t xml:space="preserve">15.3776168823242</t>
   </si>
   <si>
     <t xml:space="preserve">14.3586168289185</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6638450622559</t>
+    <t xml:space="preserve">13.6638441085815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491163253784</t>
+    <t xml:space="preserve">13.8491172790527</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880714416504</t>
+    <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248908996582</t>
+    <t xml:space="preserve">13.5248899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027992248535</t>
+    <t xml:space="preserve">13.8027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859367370605</t>
+    <t xml:space="preserve">13.3859357833862</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -719,19 +719,19 @@
     <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0617094039917</t>
+    <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690723419189</t>
+    <t xml:space="preserve">12.9690732955933</t>
   </si>
   <si>
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.200662612915</t>
+    <t xml:space="preserve">13.2006645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712080001831</t>
+    <t xml:space="preserve">13.5712070465088</t>
   </si>
   <si>
     <t xml:space="preserve">13.1543455123901</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7291612625122</t>
+    <t xml:space="preserve">14.7291603088379</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512538909912</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144334793091</t>
+    <t xml:space="preserve">14.9144344329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.2849788665771</t>
@@ -767,34 +767,34 @@
     <t xml:space="preserve">15.6555242538452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628871917725</t>
+    <t xml:space="preserve">15.5628862380981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.192343711853</t>
+    <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
     <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407974243164</t>
+    <t xml:space="preserve">15.8407964706421</t>
   </si>
   <si>
     <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702529907227</t>
+    <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460256576538</t>
+    <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8681154251099</t>
+    <t xml:space="preserve">14.8681144714355</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975700378418</t>
+    <t xml:space="preserve">14.4975709915161</t>
   </si>
   <si>
-    <t xml:space="preserve">15.016695022583</t>
+    <t xml:space="preserve">15.0166959762573</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5414838790894</t>
+    <t xml:space="preserve">14.541482925415</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968658447266</t>
+    <t xml:space="preserve">15.3968648910522</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572017669678</t>
+    <t xml:space="preserve">16.1572036743164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720779418945</t>
+    <t xml:space="preserve">15.8720769882202</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315683364868</t>
+    <t xml:space="preserve">14.7315673828125</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522468566895</t>
+    <t xml:space="preserve">16.2522449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -51601,6 +51601,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1935">
+      <c r="A1935" s="1" t="n">
+        <v>45967.4698032407</v>
+      </c>
+      <c r="B1935" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1935" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1935" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1935" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,118 +38,118 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118366241455</t>
+    <t xml:space="preserve">11.9118356704712</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256868362427</t>
+    <t xml:space="preserve">11.925687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654918670654</t>
+    <t xml:space="preserve">11.3654909133911</t>
   </si>
   <si>
     <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007129669189</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314956665039</t>
+    <t xml:space="preserve">10.9314937591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962013244629</t>
+    <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.119252204895</t>
+    <t xml:space="preserve">11.1192531585693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194267272949</t>
+    <t xml:space="preserve">11.6194276809692</t>
   </si>
   <si>
     <t xml:space="preserve">11.3116273880005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948375701904</t>
+    <t xml:space="preserve">11.6948366165161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424757003784</t>
+    <t xml:space="preserve">11.5424766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501033782959</t>
+    <t xml:space="preserve">11.3501005172729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.810263633728</t>
   </si>
   <si>
     <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963758468628</t>
+    <t xml:space="preserve">11.6963768005371</t>
   </si>
   <si>
     <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579008102417</t>
+    <t xml:space="preserve">11.657901763916</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807790756226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751779556274</t>
+    <t xml:space="preserve">11.2751789093018</t>
   </si>
   <si>
     <t xml:space="preserve">10.8086175918579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683460235596</t>
+    <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
     <t xml:space="preserve">10.1087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326042175293</t>
+    <t xml:space="preserve">9.95326137542725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998119354248</t>
+    <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11345386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790325164795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51780414581299</t>
+    <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2643013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907295227051</t>
+    <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
     <t xml:space="preserve">12.0278930664062</t>
@@ -161,40 +161,40 @@
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028579711914</t>
+    <t xml:space="preserve">11.7028589248657</t>
   </si>
   <si>
     <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084571838379</t>
+    <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639757156372</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529367446899</t>
+    <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196594238281</t>
+    <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863773345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975786209106</t>
+    <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310192108154</t>
+    <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332553863525</t>
+    <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.40894222259521</t>
@@ -203,31 +203,31 @@
     <t xml:space="preserve">9.42449283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222049713135</t>
+    <t xml:space="preserve">9.64221954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8754997253418</t>
+    <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476602554321</t>
+    <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420600891113</t>
+    <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79773998260498</t>
+    <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670196533203</t>
+    <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118057250977</t>
+    <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662128448486</t>
+    <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.47892570495605</t>
@@ -236,34 +236,34 @@
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815036773682</t>
+    <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
     <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842575073242</t>
+    <t xml:space="preserve">9.71842670440674</t>
   </si>
   <si>
     <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2745656967163</t>
+    <t xml:space="preserve">10.274564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498373031616</t>
+    <t xml:space="preserve">10.3498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076923370361</t>
+    <t xml:space="preserve">10.0076913833618</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064434051514</t>
+    <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353723526001</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.778904914856</t>
@@ -272,31 +272,31 @@
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2573461532593</t>
+    <t xml:space="preserve">10.257345199585</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885902404785</t>
+    <t xml:space="preserve">9.64885997772217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963840484619</t>
+    <t xml:space="preserve">9.90963935852051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193351745605</t>
+    <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344543457031</t>
+    <t xml:space="preserve">8.95344638824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959251403809</t>
+    <t xml:space="preserve">8.7795934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266510009766</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271289825439</t>
+    <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266117095947</t>
+    <t xml:space="preserve">11.126612663269</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004665374756</t>
+    <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658323287964</t>
+    <t xml:space="preserve">10.8658313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527587890625</t>
+    <t xml:space="preserve">10.9527578353882</t>
   </si>
   <si>
     <t xml:space="preserve">10.1704187393188</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6050510406494</t>
+    <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311990737915</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3880786895752</t>
+    <t xml:space="preserve">9.38807964324951</t>
   </si>
   <si>
     <t xml:space="preserve">9.21422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729930877686</t>
+    <t xml:space="preserve">9.12729835510254</t>
   </si>
   <si>
     <t xml:space="preserve">9.73578548431396</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115127563477</t>
+    <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725198745728</t>
+    <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876581192017</t>
+    <t xml:space="preserve">7.38876628875732</t>
   </si>
   <si>
     <t xml:space="preserve">7.30183935165405</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530305862427</t>
+    <t xml:space="preserve">7.34530258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569227218628</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339811325073</t>
+    <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378923416138</t>
+    <t xml:space="preserve">7.95378875732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573959350586</t>
+    <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.0087156295776</t>
@@ -392,43 +392,43 @@
     <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870620727539</t>
+    <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85726928710938</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869773864746</t>
+    <t xml:space="preserve">8.76869583129883</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012428283691</t>
+    <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7244119644165</t>
+    <t xml:space="preserve">8.72441005706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21156024932861</t>
+    <t xml:space="preserve">9.2115592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12298774719238</t>
+    <t xml:space="preserve">9.1229887008667</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013370513916</t>
+    <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858606338501</t>
+    <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972871780396</t>
+    <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">10.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912097930908</t>
+    <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
     <t xml:space="preserve">10.6006050109863</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818117141724</t>
+    <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.78517436981201</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">12.0502605438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.416036605835</t>
+    <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442260742188</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844844818115</t>
+    <t xml:space="preserve">12.6844854354858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032777786255</t>
+    <t xml:space="preserve">12.5032787322998</t>
   </si>
   <si>
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375017166138</t>
+    <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
     <t xml:space="preserve">12.9562959671021</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401744842529</t>
+    <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
     <t xml:space="preserve">15.4025888442993</t>
@@ -593,49 +593,49 @@
     <t xml:space="preserve">14.4965543746948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.768364906311</t>
+    <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495725631714</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999160766602</t>
+    <t xml:space="preserve">13.4999151229858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341419219971</t>
+    <t xml:space="preserve">14.1341409683228</t>
   </si>
   <si>
     <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938816070557</t>
+    <t xml:space="preserve">12.5938806533813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468988418579</t>
+    <t xml:space="preserve">13.0468978881836</t>
   </si>
   <si>
     <t xml:space="preserve">13.5905199050903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3187084197998</t>
+    <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656930923462</t>
+    <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9529323577881</t>
+    <t xml:space="preserve">13.9529333114624</t>
   </si>
   <si>
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119869232178</t>
+    <t xml:space="preserve">15.3119850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264251708984</t>
+    <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230634689331</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070705413818</t>
+    <t xml:space="preserve">15.0070714950562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776168823242</t>
+    <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
     <t xml:space="preserve">14.3586168289185</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6638441085815</t>
+    <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
     <t xml:space="preserve">13.8491172790527</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248899459839</t>
+    <t xml:space="preserve">13.5248908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027982711792</t>
+    <t xml:space="preserve">13.8027992248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101631164551</t>
+    <t xml:space="preserve">13.7101621627808</t>
   </si>
   <si>
     <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9690732955933</t>
+    <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006645202637</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712070465088</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533885955811</t>
+    <t xml:space="preserve">15.0533876419067</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -749,10 +749,7 @@
     <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7291603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
@@ -764,16 +761,16 @@
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555242538452</t>
+    <t xml:space="preserve">15.6555223464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
     <t xml:space="preserve">15.8407964706421</t>
@@ -785,13 +782,13 @@
     <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460247039795</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8681144714355</t>
+    <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975709915161</t>
+    <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
     <t xml:space="preserve">15.0166959762573</t>
@@ -33317,7 +33314,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33343,7 +33340,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33369,7 +33366,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33395,7 +33392,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33447,7 +33444,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33473,7 +33470,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33499,7 +33496,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33525,7 +33522,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33551,7 +33548,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33577,7 +33574,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33603,7 +33600,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33629,7 +33626,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33655,7 +33652,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33681,7 +33678,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33707,7 +33704,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33733,7 +33730,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33759,7 +33756,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33785,7 +33782,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33811,7 +33808,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33837,7 +33834,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33889,7 +33886,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33915,7 +33912,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33941,7 +33938,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33967,7 +33964,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33993,7 +33990,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34019,7 +34016,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34045,7 +34042,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34409,7 +34406,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34435,7 +34432,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34461,7 +34458,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34747,7 +34744,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34773,7 +34770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34799,7 +34796,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34903,7 +34900,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35059,7 +35056,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35111,7 +35108,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35137,7 +35134,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35163,7 +35160,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35189,7 +35186,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35215,7 +35212,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35241,7 +35238,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35267,7 +35264,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35293,7 +35290,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35371,7 +35368,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35397,7 +35394,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35423,7 +35420,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35449,7 +35446,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35475,7 +35472,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35501,7 +35498,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35527,7 +35524,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35553,7 +35550,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35579,7 +35576,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35605,7 +35602,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35631,7 +35628,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35657,7 +35654,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35683,7 +35680,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35709,7 +35706,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35735,7 +35732,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35761,7 +35758,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35787,7 +35784,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35813,7 +35810,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35839,7 +35836,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35865,7 +35862,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35891,7 +35888,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35917,7 +35914,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35943,7 +35940,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35969,7 +35966,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35995,7 +35992,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36021,7 +36018,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36047,7 +36044,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36073,7 +36070,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36099,7 +36096,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36125,7 +36122,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36151,7 +36148,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36177,7 +36174,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36203,7 +36200,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36229,7 +36226,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36255,7 +36252,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36281,7 +36278,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36307,7 +36304,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36333,7 +36330,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36359,7 +36356,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36385,7 +36382,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36411,7 +36408,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36437,7 +36434,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36463,7 +36460,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36489,7 +36486,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36515,7 +36512,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36541,7 +36538,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36567,7 +36564,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36593,7 +36590,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36619,7 +36616,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36645,7 +36642,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36671,7 +36668,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36697,7 +36694,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -36723,7 +36720,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36749,7 +36746,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36775,7 +36772,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36801,7 +36798,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36827,7 +36824,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36853,7 +36850,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36879,7 +36876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36905,7 +36902,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36931,7 +36928,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36957,7 +36954,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36983,7 +36980,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37009,7 +37006,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37035,7 +37032,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37061,7 +37058,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37087,7 +37084,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37113,7 +37110,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37139,7 +37136,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37165,7 +37162,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37191,7 +37188,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37217,7 +37214,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37243,7 +37240,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37269,7 +37266,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37295,7 +37292,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37321,7 +37318,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37347,7 +37344,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37373,7 +37370,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37399,7 +37396,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37425,7 +37422,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37451,7 +37448,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37477,7 +37474,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37503,7 +37500,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37529,7 +37526,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37555,7 +37552,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37581,7 +37578,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37607,7 +37604,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37633,7 +37630,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37659,7 +37656,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37685,7 +37682,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37711,7 +37708,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37737,7 +37734,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37763,7 +37760,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37789,7 +37786,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37815,7 +37812,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37841,7 +37838,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -37867,7 +37864,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37893,7 +37890,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37919,7 +37916,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37945,7 +37942,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37971,7 +37968,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -37997,7 +37994,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38023,7 +38020,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38049,7 +38046,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38075,7 +38072,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38101,7 +38098,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38127,7 +38124,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38153,7 +38150,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38179,7 +38176,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38205,7 +38202,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38231,7 +38228,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38257,7 +38254,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38283,7 +38280,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38309,7 +38306,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38335,7 +38332,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38361,7 +38358,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38387,7 +38384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38413,7 +38410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38439,7 +38436,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38465,7 +38462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38491,7 +38488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38517,7 +38514,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38543,7 +38540,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38569,7 +38566,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38595,7 +38592,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38621,7 +38618,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38647,7 +38644,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38673,7 +38670,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38699,7 +38696,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38725,7 +38722,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38751,7 +38748,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38777,7 +38774,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38803,7 +38800,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -38829,7 +38826,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38855,7 +38852,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38881,7 +38878,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38907,7 +38904,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38933,7 +38930,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38959,7 +38956,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38985,7 +38982,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39011,7 +39008,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39037,7 +39034,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39063,7 +39060,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39089,7 +39086,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39115,7 +39112,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39141,7 +39138,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39167,7 +39164,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39193,7 +39190,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39219,7 +39216,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39245,7 +39242,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39271,7 +39268,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39297,7 +39294,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39323,7 +39320,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39349,7 +39346,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39375,7 +39372,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39401,7 +39398,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39427,7 +39424,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39453,7 +39450,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39479,7 +39476,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39505,7 +39502,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39531,7 +39528,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39557,7 +39554,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39583,7 +39580,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39609,7 +39606,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39635,7 +39632,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39661,7 +39658,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39687,7 +39684,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39713,7 +39710,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39739,7 +39736,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39765,7 +39762,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39791,7 +39788,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39817,7 +39814,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39843,7 +39840,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39869,7 +39866,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39895,7 +39892,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39921,7 +39918,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39947,7 +39944,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39973,7 +39970,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39999,7 +39996,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40025,7 +40022,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40051,7 +40048,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40077,7 +40074,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40103,7 +40100,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40129,7 +40126,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40155,7 +40152,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40181,7 +40178,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40207,7 +40204,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40233,7 +40230,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40259,7 +40256,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40285,7 +40282,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40311,7 +40308,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40337,7 +40334,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40363,7 +40360,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40389,7 +40386,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40649,7 +40646,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40675,7 +40672,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40701,7 +40698,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40727,7 +40724,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40753,7 +40750,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40779,7 +40776,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40805,7 +40802,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40831,7 +40828,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40857,7 +40854,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -40883,7 +40880,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40909,7 +40906,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40935,7 +40932,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40961,7 +40958,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40987,7 +40984,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41013,7 +41010,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41039,7 +41036,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41065,7 +41062,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41091,7 +41088,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41117,7 +41114,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41143,7 +41140,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41169,7 +41166,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41195,7 +41192,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41221,7 +41218,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41247,7 +41244,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41273,7 +41270,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41299,7 +41296,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41325,7 +41322,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41351,7 +41348,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41377,7 +41374,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41403,7 +41400,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41429,7 +41426,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41455,7 +41452,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41481,7 +41478,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41507,7 +41504,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41533,7 +41530,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41559,7 +41556,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41585,7 +41582,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41611,7 +41608,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41637,7 +41634,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41663,7 +41660,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41689,7 +41686,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41715,7 +41712,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41741,7 +41738,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41767,7 +41764,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41793,7 +41790,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41819,7 +41816,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41845,7 +41842,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41871,7 +41868,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41897,7 +41894,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41923,7 +41920,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41949,7 +41946,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41975,7 +41972,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42001,7 +41998,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42027,7 +42024,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42053,7 +42050,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42079,7 +42076,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42105,7 +42102,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42131,7 +42128,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42157,7 +42154,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42183,7 +42180,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42209,7 +42206,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42235,7 +42232,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42261,7 +42258,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42287,7 +42284,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42313,7 +42310,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42339,7 +42336,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42365,7 +42362,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42391,7 +42388,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42417,7 +42414,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42443,7 +42440,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42469,7 +42466,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42495,7 +42492,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42521,7 +42518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42547,7 +42544,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42573,7 +42570,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42599,7 +42596,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42625,7 +42622,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42651,7 +42648,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42677,7 +42674,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42703,7 +42700,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42729,7 +42726,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42755,7 +42752,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42781,7 +42778,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42807,7 +42804,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42833,7 +42830,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42859,7 +42856,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42885,7 +42882,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42911,7 +42908,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42937,7 +42934,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42963,7 +42960,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42989,7 +42986,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43015,7 +43012,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43041,7 +43038,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43067,7 +43064,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43093,7 +43090,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43119,7 +43116,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43145,7 +43142,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43171,7 +43168,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43197,7 +43194,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43223,7 +43220,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43249,7 +43246,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43275,7 +43272,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43301,7 +43298,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43327,7 +43324,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43353,7 +43350,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43379,7 +43376,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43405,7 +43402,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43431,7 +43428,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43457,7 +43454,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43483,7 +43480,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43509,7 +43506,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43535,7 +43532,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43561,7 +43558,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43587,7 +43584,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43613,7 +43610,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43639,7 +43636,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43665,7 +43662,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43691,7 +43688,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43717,7 +43714,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43743,7 +43740,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43769,7 +43766,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43795,7 +43792,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43821,7 +43818,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43847,7 +43844,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43873,7 +43870,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43899,7 +43896,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43925,7 +43922,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43951,7 +43948,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43977,7 +43974,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44003,7 +44000,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44029,7 +44026,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44055,7 +44052,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44081,7 +44078,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44107,7 +44104,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44133,7 +44130,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44159,7 +44156,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44185,7 +44182,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44211,7 +44208,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44237,7 +44234,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44263,7 +44260,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44289,7 +44286,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44315,7 +44312,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44341,7 +44338,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44367,7 +44364,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44393,7 +44390,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44419,7 +44416,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44445,7 +44442,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44471,7 +44468,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44497,7 +44494,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44523,7 +44520,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44549,7 +44546,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44575,7 +44572,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44601,7 +44598,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44627,7 +44624,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44653,7 +44650,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44679,7 +44676,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44705,7 +44702,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44731,7 +44728,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44757,7 +44754,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44783,7 +44780,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44809,7 +44806,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44835,7 +44832,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44861,7 +44858,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44887,7 +44884,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44913,7 +44910,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44939,7 +44936,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44965,7 +44962,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44991,7 +44988,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45017,7 +45014,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45043,7 +45040,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45069,7 +45066,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45095,7 +45092,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45121,7 +45118,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45147,7 +45144,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45173,7 +45170,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45199,7 +45196,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45225,7 +45222,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45251,7 +45248,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45277,7 +45274,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45303,7 +45300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45329,7 +45326,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45355,7 +45352,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45381,7 +45378,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45407,7 +45404,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45433,7 +45430,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45459,7 +45456,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45485,7 +45482,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45511,7 +45508,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45537,7 +45534,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45563,7 +45560,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45589,7 +45586,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45615,7 +45612,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45641,7 +45638,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45667,7 +45664,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45693,7 +45690,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45719,7 +45716,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45745,7 +45742,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45771,7 +45768,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45797,7 +45794,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45823,7 +45820,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45849,7 +45846,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45875,7 +45872,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45901,7 +45898,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45927,7 +45924,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45953,7 +45950,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45979,7 +45976,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46005,7 +46002,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46031,7 +46028,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46057,7 +46054,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46083,7 +46080,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46109,7 +46106,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46135,7 +46132,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46161,7 +46158,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46187,7 +46184,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46213,7 +46210,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46239,7 +46236,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46265,7 +46262,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46291,7 +46288,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46317,7 +46314,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46343,7 +46340,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46369,7 +46366,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46395,7 +46392,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46421,7 +46418,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46447,7 +46444,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46473,7 +46470,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46499,7 +46496,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46525,7 +46522,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46551,7 +46548,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46577,7 +46574,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46603,7 +46600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46629,7 +46626,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46655,7 +46652,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46681,7 +46678,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46707,7 +46704,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46733,7 +46730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46759,7 +46756,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46785,7 +46782,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46811,7 +46808,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46837,7 +46834,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46863,7 +46860,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46889,7 +46886,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46915,7 +46912,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46941,7 +46938,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46967,7 +46964,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46993,7 +46990,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47019,7 +47016,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47045,7 +47042,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47071,7 +47068,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47097,7 +47094,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47123,7 +47120,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47149,7 +47146,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47175,7 +47172,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47201,7 +47198,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47227,7 +47224,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47253,7 +47250,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47279,7 +47276,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47305,7 +47302,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47331,7 +47328,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47357,7 +47354,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47383,7 +47380,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47409,7 +47406,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47435,7 +47432,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47461,7 +47458,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47487,7 +47484,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47513,7 +47510,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47539,7 +47536,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47565,7 +47562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47591,7 +47588,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47617,7 +47614,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47643,7 +47640,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47669,7 +47666,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47695,7 +47692,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47721,7 +47718,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47747,7 +47744,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47773,7 +47770,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47799,7 +47796,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47825,7 +47822,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47851,7 +47848,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47877,7 +47874,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47903,7 +47900,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47929,7 +47926,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47955,7 +47952,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47981,7 +47978,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48007,7 +48004,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48033,7 +48030,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48059,7 +48056,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48085,7 +48082,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48111,7 +48108,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48137,7 +48134,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48163,7 +48160,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48189,7 +48186,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48215,7 +48212,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48241,7 +48238,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48267,7 +48264,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48293,7 +48290,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48319,7 +48316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48345,7 +48342,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48371,7 +48368,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48397,7 +48394,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48423,7 +48420,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48449,7 +48446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48475,7 +48472,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48501,7 +48498,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48527,7 +48524,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48553,7 +48550,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48579,7 +48576,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48605,7 +48602,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48631,7 +48628,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48657,7 +48654,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48683,7 +48680,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48709,7 +48706,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48735,7 +48732,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48761,7 +48758,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48787,7 +48784,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48813,7 +48810,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48839,7 +48836,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48865,7 +48862,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48891,7 +48888,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48917,7 +48914,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48943,7 +48940,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48969,7 +48966,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48995,7 +48992,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49021,7 +49018,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49047,7 +49044,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49073,7 +49070,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49099,7 +49096,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49125,7 +49122,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49151,7 +49148,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49177,7 +49174,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49203,7 +49200,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49229,7 +49226,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49255,7 +49252,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49281,7 +49278,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49307,7 +49304,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49333,7 +49330,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49359,7 +49356,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49385,7 +49382,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49411,7 +49408,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49437,7 +49434,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49463,7 +49460,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49489,7 +49486,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49515,7 +49512,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49541,7 +49538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49567,7 +49564,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49593,7 +49590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49619,7 +49616,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49645,7 +49642,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49671,7 +49668,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49697,7 +49694,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49723,7 +49720,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49749,7 +49746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49775,7 +49772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49801,7 +49798,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49827,7 +49824,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49853,7 +49850,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49879,7 +49876,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49905,7 +49902,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49931,7 +49928,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49957,7 +49954,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49983,7 +49980,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50009,7 +50006,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50035,7 +50032,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50061,7 +50058,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50087,7 +50084,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50113,7 +50110,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50139,7 +50136,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50165,7 +50162,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50191,7 +50188,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50217,7 +50214,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50243,7 +50240,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50269,7 +50266,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50295,7 +50292,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50321,7 +50318,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50347,7 +50344,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50373,7 +50370,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50399,7 +50396,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50425,7 +50422,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50451,7 +50448,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50477,7 +50474,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50503,7 +50500,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50529,7 +50526,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50555,7 +50552,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50581,7 +50578,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50607,7 +50604,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50633,7 +50630,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50659,7 +50656,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50685,7 +50682,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50711,7 +50708,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50737,7 +50734,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50763,7 +50760,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50789,7 +50786,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50815,7 +50812,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50841,7 +50838,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50867,7 +50864,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50893,7 +50890,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50919,7 +50916,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50945,7 +50942,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50971,7 +50968,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50997,7 +50994,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51023,7 +51020,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51049,7 +51046,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51075,7 +51072,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51101,7 +51098,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51127,7 +51124,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51153,7 +51150,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51179,7 +51176,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51205,7 +51202,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51231,7 +51228,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51257,7 +51254,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51283,7 +51280,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51309,7 +51306,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51335,7 +51332,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51361,7 +51358,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51387,7 +51384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51413,7 +51410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51439,7 +51436,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51465,7 +51462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51491,7 +51488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51517,7 +51514,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1931" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51543,7 +51540,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1932" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51569,7 +51566,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1933" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51595,35 +51592,9 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1934" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1934" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="1935">
-      <c r="A1935" s="1" t="n">
-        <v>45967.4698032407</v>
-      </c>
-      <c r="B1935" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C1935" t="n">
-        <v>16.1000003814697</v>
-      </c>
-      <c r="D1935" t="n">
-        <v>16.1000003814697</v>
-      </c>
-      <c r="E1935" t="n">
-        <v>16.1000003814697</v>
-      </c>
-      <c r="F1935" t="n">
-        <v>16.1000003814697</v>
-      </c>
-      <c r="G1935" t="s">
-        <v>314</v>
-      </c>
-      <c r="H1935" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
@@ -47,46 +47,46 @@
     <t xml:space="preserve">11.925687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654909133911</t>
+    <t xml:space="preserve">11.3654928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699003219604</t>
+    <t xml:space="preserve">10.7698984146118</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007129669189</t>
+    <t xml:space="preserve">10.9007167816162</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314937591553</t>
+    <t xml:space="preserve">10.9314956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653877258301</t>
+    <t xml:space="preserve">11.0653886795044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962022781372</t>
+    <t xml:space="preserve">11.1962013244629</t>
   </si>
   <si>
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192531585693</t>
+    <t xml:space="preserve">11.1192512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194276809692</t>
+    <t xml:space="preserve">11.6194257736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116273880005</t>
+    <t xml:space="preserve">11.3116283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948366165161</t>
+    <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
     <t xml:space="preserve">11.5424766540527</t>
@@ -95,40 +95,40 @@
     <t xml:space="preserve">11.3501005172729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.810263633728</t>
+    <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773325920105</t>
+    <t xml:space="preserve">11.7733268737793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963768005371</t>
+    <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657011032104</t>
+    <t xml:space="preserve">11.9657020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579008102417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807790756226</t>
+    <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751789093018</t>
+    <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086175918579</t>
+    <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349044799805</t>
+    <t xml:space="preserve">10.5349035263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683450698853</t>
+    <t xml:space="preserve">10.0683460235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087799072266</t>
+    <t xml:space="preserve">10.1087789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326137542725</t>
+    <t xml:space="preserve">9.95325946807861</t>
   </si>
   <si>
     <t xml:space="preserve">9.71998023986816</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">9.11345386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790325164795</t>
+    <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
     <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5178050994873</t>
+    <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643013000488</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
     <t xml:space="preserve">11.2907304763794</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028589248657</t>
+    <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
     <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084581375122</t>
+    <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
     <t xml:space="preserve">11.6639766693115</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196594238281</t>
   </si>
   <si>
     <t xml:space="preserve">10.8863773345947</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.497579574585</t>
+    <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198188781738</t>
+    <t xml:space="preserve">10.4198207855225</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310201644897</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">9.40894222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449283599854</t>
+    <t xml:space="preserve">9.42449378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64221954345703</t>
+    <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.342059135437</t>
@@ -224,46 +224,46 @@
     <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118152618408</t>
+    <t xml:space="preserve">9.33118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892570495605</t>
+    <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815227508545</t>
   </si>
   <si>
     <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842670440674</t>
+    <t xml:space="preserve">9.71842575073242</t>
   </si>
   <si>
     <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274564743042</t>
+    <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498363494873</t>
+    <t xml:space="preserve">10.349835395813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076913833618</t>
+    <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
     <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919784545898</t>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353713989258</t>
+    <t xml:space="preserve">10.4353704452515</t>
   </si>
   <si>
     <t xml:space="preserve">10.778904914856</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834932327271</t>
+    <t xml:space="preserve">10.0834922790527</t>
   </si>
   <si>
     <t xml:space="preserve">10.257345199585</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">9.64885997772217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963935852051</t>
+    <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8665189743042</t>
+    <t xml:space="preserve">8.86651802062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7795934677124</t>
+    <t xml:space="preserve">8.77959156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266605377197</t>
+    <t xml:space="preserve">8.69266510009766</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126612663269</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004655838013</t>
+    <t xml:space="preserve">11.3004665374756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658313751221</t>
+    <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527578353882</t>
+    <t xml:space="preserve">10.9527597427368</t>
   </si>
   <si>
     <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99656581878662</t>
+    <t xml:space="preserve">9.9965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6050519943237</t>
+    <t xml:space="preserve">10.6050510406494</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311990737915</t>
@@ -335,115 +335,115 @@
     <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38807964324951</t>
+    <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422576904297</t>
+    <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729835510254</t>
+    <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578548431396</t>
+    <t xml:space="preserve">9.73578643798828</t>
   </si>
   <si>
     <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115222930908</t>
+    <t xml:space="preserve">9.3011531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725198745728</t>
   </si>
   <si>
     <t xml:space="preserve">7.38876628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183935165405</t>
+    <t xml:space="preserve">7.30183792114258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530258178711</t>
+    <t xml:space="preserve">7.34530305862427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569274902344</t>
+    <t xml:space="preserve">7.4756932258606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339859008789</t>
+    <t xml:space="preserve">7.82339906692505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378875732422</t>
+    <t xml:space="preserve">7.95378923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3449592590332</t>
+    <t xml:space="preserve">8.34496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4772777557373</t>
+    <t xml:space="preserve">9.47727966308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584274291992</t>
+    <t xml:space="preserve">8.94584178924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869583129883</t>
+    <t xml:space="preserve">8.76869678497314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441524505615</t>
+    <t xml:space="preserve">9.03441429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012523651123</t>
+    <t xml:space="preserve">8.68012428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72441005706787</t>
+    <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2115592956543</t>
+    <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013275146484</t>
+    <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
     <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.071587562561</t>
+    <t xml:space="preserve">11.0715866088867</t>
   </si>
   <si>
     <t xml:space="preserve">10.8944416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830141067505</t>
+    <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972881317139</t>
+    <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
@@ -452,25 +452,25 @@
     <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014217376709</t>
+    <t xml:space="preserve">9.92014312744141</t>
   </si>
   <si>
     <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487316131592</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.425877571106</t>
+    <t xml:space="preserve">11.4258785247803</t>
   </si>
   <si>
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.7172966003418</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193992614746</t>
+    <t xml:space="preserve">10.4193983078003</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100021362305</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475877761841</t>
+    <t xml:space="preserve">10.1475887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818126678467</t>
+    <t xml:space="preserve">10.7818117141724</t>
   </si>
   <si>
-    <t xml:space="preserve">10.963020324707</t>
+    <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
     <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502605438232</t>
+    <t xml:space="preserve">12.0502614974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878461837769</t>
+    <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844854354858</t>
+    <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
     <t xml:space="preserve">12.5032787322998</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375026702881</t>
+    <t xml:space="preserve">13.1375017166138</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562959671021</t>
+    <t xml:space="preserve">12.9562950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281064987183</t>
+    <t xml:space="preserve">13.2281055450439</t>
   </si>
   <si>
     <t xml:space="preserve">14.0435371398926</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153476715088</t>
+    <t xml:space="preserve">14.3153486251831</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931926727295</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4025888442993</t>
+    <t xml:space="preserve">15.4025897979736</t>
   </si>
   <si>
     <t xml:space="preserve">15.8556060791016</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650012969971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307802200317</t>
+    <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2213821411133</t>
+    <t xml:space="preserve">15.2213802337646</t>
   </si>
   <si>
-    <t xml:space="preserve">14.587158203125</t>
+    <t xml:space="preserve">14.5871591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8623313903809</t>
+    <t xml:space="preserve">13.8623304367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4965543746948</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999151229858</t>
+    <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
     <t xml:space="preserve">14.1341409683228</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5938806533813</t>
+    <t xml:space="preserve">12.5938816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468978881836</t>
+    <t xml:space="preserve">13.0468988418579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5905199050903</t>
+    <t xml:space="preserve">13.5905208587646</t>
   </si>
   <si>
     <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656921386719</t>
+    <t xml:space="preserve">12.8656911849976</t>
   </si>
   <si>
     <t xml:space="preserve">13.9529333114624</t>
@@ -632,25 +632,25 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119850158691</t>
+    <t xml:space="preserve">15.3119859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264242172241</t>
+    <t xml:space="preserve">13.7264251708984</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512519836426</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
     <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.26598072052</t>
+    <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365251541138</t>
+    <t xml:space="preserve">14.6365261077881</t>
   </si>
   <si>
     <t xml:space="preserve">14.2196626663208</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">14.682843208313</t>
+    <t xml:space="preserve">14.6828441619873</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070714950562</t>
+    <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586168289185</t>
+    <t xml:space="preserve">14.3586158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733446121216</t>
+    <t xml:space="preserve">14.1733436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564811706543</t>
+    <t xml:space="preserve">13.7564821243286</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248908996582</t>
+    <t xml:space="preserve">13.5248899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027992248535</t>
+    <t xml:space="preserve">13.8027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
@@ -716,25 +716,25 @@
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101621627808</t>
+    <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.061710357666</t>
+    <t xml:space="preserve">13.0617094039917</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469825744629</t>
+    <t xml:space="preserve">13.2469816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006635665894</t>
+    <t xml:space="preserve">13.2006645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5712070465088</t>
+    <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543455123901</t>
+    <t xml:space="preserve">13.1543445587158</t>
   </si>
   <si>
     <t xml:space="preserve">13.9417533874512</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4049348831177</t>
+    <t xml:space="preserve">14.404935836792</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555223464966</t>
+    <t xml:space="preserve">15.6555233001709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628871917725</t>
+    <t xml:space="preserve">15.5628862380981</t>
   </si>
   <si>
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165691375732</t>
+    <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407964706421</t>
+    <t xml:space="preserve">15.8407955169678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944774627686</t>
+    <t xml:space="preserve">15.7944784164429</t>
   </si>
   <si>
     <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460256576538</t>
+    <t xml:space="preserve">15.1460237503052</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975700378418</t>
+    <t xml:space="preserve">14.4975709915161</t>
   </si>
   <si>
     <t xml:space="preserve">15.0166959762573</t>
@@ -801,6 +801,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.541482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -35316,7 +35319,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35342,7 +35345,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35368,7 +35371,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35394,7 +35397,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35420,7 +35423,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35446,7 +35449,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35472,7 +35475,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35498,7 +35501,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35524,7 +35527,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35550,7 +35553,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35576,7 +35579,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35602,7 +35605,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35628,7 +35631,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35654,7 +35657,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35680,7 +35683,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35706,7 +35709,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35732,7 +35735,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35758,7 +35761,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35784,7 +35787,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35810,7 +35813,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35836,7 +35839,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35862,7 +35865,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35888,7 +35891,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35914,7 +35917,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35940,7 +35943,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35966,7 +35969,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35992,7 +35995,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36018,7 +36021,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36044,7 +36047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36070,7 +36073,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36096,7 +36099,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36122,7 +36125,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36148,7 +36151,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36174,7 +36177,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36200,7 +36203,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36226,7 +36229,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36252,7 +36255,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36278,7 +36281,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36304,7 +36307,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36330,7 +36333,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36356,7 +36359,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36382,7 +36385,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36408,7 +36411,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36434,7 +36437,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36512,7 +36515,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36538,7 +36541,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36564,7 +36567,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36590,7 +36593,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36642,7 +36645,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36668,7 +36671,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36720,7 +36723,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36746,7 +36749,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36772,7 +36775,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36798,7 +36801,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36824,7 +36827,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36850,7 +36853,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36876,7 +36879,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36902,7 +36905,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36928,7 +36931,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36954,7 +36957,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36980,7 +36983,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37006,7 +37009,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37110,7 +37113,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37136,7 +37139,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37162,7 +37165,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37188,7 +37191,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37214,7 +37217,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37240,7 +37243,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37266,7 +37269,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37292,7 +37295,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37318,7 +37321,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37344,7 +37347,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37370,7 +37373,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37396,7 +37399,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37422,7 +37425,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37448,7 +37451,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37474,7 +37477,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37500,7 +37503,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37526,7 +37529,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37630,7 +37633,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37656,7 +37659,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37682,7 +37685,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37708,7 +37711,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37734,7 +37737,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37760,7 +37763,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37786,7 +37789,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37812,7 +37815,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37838,7 +37841,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38176,7 +38179,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38202,7 +38205,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38228,7 +38231,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38384,7 +38387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38410,7 +38413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38436,7 +38439,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38462,7 +38465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38488,7 +38491,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38514,7 +38517,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38540,7 +38543,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38566,7 +38569,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38592,7 +38595,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38618,7 +38621,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38644,7 +38647,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38670,7 +38673,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38696,7 +38699,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38722,7 +38725,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38774,7 +38777,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38800,7 +38803,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39008,7 +39011,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39034,7 +39037,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39060,7 +39063,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39086,7 +39089,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39112,7 +39115,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39138,7 +39141,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39164,7 +39167,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39190,7 +39193,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39216,7 +39219,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39242,7 +39245,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39268,7 +39271,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39294,7 +39297,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39320,7 +39323,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39346,7 +39349,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39372,7 +39375,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39398,7 +39401,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39424,7 +39427,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39450,7 +39453,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39476,7 +39479,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39502,7 +39505,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39528,7 +39531,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39554,7 +39557,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39580,7 +39583,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39606,7 +39609,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39632,7 +39635,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39658,7 +39661,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39684,7 +39687,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39710,7 +39713,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39736,7 +39739,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39762,7 +39765,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39788,7 +39791,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39814,7 +39817,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39840,7 +39843,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39866,7 +39869,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39892,7 +39895,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39918,7 +39921,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39944,7 +39947,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39970,7 +39973,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39996,7 +39999,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40022,7 +40025,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40048,7 +40051,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40074,7 +40077,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40100,7 +40103,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40126,7 +40129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40256,7 +40259,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40412,7 +40415,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40438,7 +40441,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1505" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40464,7 +40467,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40490,7 +40493,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40516,7 +40519,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40542,7 +40545,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40568,7 +40571,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1510" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -40594,7 +40597,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -40620,7 +40623,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -40672,7 +40675,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40698,7 +40701,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40880,7 +40883,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40906,7 +40909,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40932,7 +40935,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40958,7 +40961,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40984,7 +40987,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41010,7 +41013,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41036,7 +41039,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41062,7 +41065,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41088,7 +41091,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41114,7 +41117,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41140,7 +41143,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41166,7 +41169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41192,7 +41195,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41218,7 +41221,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41244,7 +41247,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41270,7 +41273,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41296,7 +41299,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41322,7 +41325,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41348,7 +41351,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41374,7 +41377,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41400,7 +41403,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41426,7 +41429,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41452,7 +41455,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41478,7 +41481,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41504,7 +41507,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41530,7 +41533,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41556,7 +41559,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41582,7 +41585,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41608,7 +41611,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41634,7 +41637,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41660,7 +41663,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41686,7 +41689,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41712,7 +41715,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41738,7 +41741,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41764,7 +41767,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41790,7 +41793,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41816,7 +41819,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41842,7 +41845,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41868,7 +41871,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41894,7 +41897,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41920,7 +41923,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41946,7 +41949,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41972,7 +41975,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -41998,7 +42001,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42024,7 +42027,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42050,7 +42053,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42076,7 +42079,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42102,7 +42105,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42128,7 +42131,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42154,7 +42157,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42180,7 +42183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42206,7 +42209,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42232,7 +42235,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42258,7 +42261,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42284,7 +42287,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42310,7 +42313,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42336,7 +42339,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42362,7 +42365,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42388,7 +42391,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42414,7 +42417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42440,7 +42443,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42466,7 +42469,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42492,7 +42495,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42518,7 +42521,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42544,7 +42547,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42570,7 +42573,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42596,7 +42599,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42622,7 +42625,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42648,7 +42651,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42674,7 +42677,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42700,7 +42703,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42726,7 +42729,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42752,7 +42755,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42778,7 +42781,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42804,7 +42807,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42830,7 +42833,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42856,7 +42859,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42882,7 +42885,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42908,7 +42911,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42934,7 +42937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42960,7 +42963,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42986,7 +42989,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43012,7 +43015,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43038,7 +43041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43064,7 +43067,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43090,7 +43093,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43116,7 +43119,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43142,7 +43145,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43168,7 +43171,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43194,7 +43197,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43220,7 +43223,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43246,7 +43249,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43272,7 +43275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43298,7 +43301,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43324,7 +43327,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43350,7 +43353,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43376,7 +43379,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43402,7 +43405,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43428,7 +43431,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43454,7 +43457,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43480,7 +43483,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43506,7 +43509,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43532,7 +43535,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43558,7 +43561,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43584,7 +43587,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43610,7 +43613,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43636,7 +43639,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43662,7 +43665,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43688,7 +43691,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43714,7 +43717,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43740,7 +43743,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43766,7 +43769,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43792,7 +43795,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43818,7 +43821,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43844,7 +43847,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43870,7 +43873,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43896,7 +43899,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43922,7 +43925,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43948,7 +43951,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43974,7 +43977,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44000,7 +44003,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44026,7 +44029,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44052,7 +44055,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44078,7 +44081,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44104,7 +44107,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44130,7 +44133,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44156,7 +44159,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44182,7 +44185,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44208,7 +44211,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44234,7 +44237,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44260,7 +44263,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44286,7 +44289,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44312,7 +44315,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44338,7 +44341,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44364,7 +44367,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44390,7 +44393,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44416,7 +44419,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44442,7 +44445,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44468,7 +44471,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44494,7 +44497,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44520,7 +44523,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44546,7 +44549,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44572,7 +44575,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44598,7 +44601,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44624,7 +44627,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44650,7 +44653,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44676,7 +44679,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44702,7 +44705,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44728,7 +44731,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44754,7 +44757,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44780,7 +44783,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44806,7 +44809,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44832,7 +44835,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44858,7 +44861,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44884,7 +44887,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44910,7 +44913,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44936,7 +44939,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44962,7 +44965,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44988,7 +44991,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45014,7 +45017,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45040,7 +45043,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45066,7 +45069,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45092,7 +45095,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45118,7 +45121,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45144,7 +45147,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45170,7 +45173,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45196,7 +45199,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45222,7 +45225,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45248,7 +45251,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45274,7 +45277,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45300,7 +45303,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45326,7 +45329,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45352,7 +45355,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45378,7 +45381,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45404,7 +45407,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45430,7 +45433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45456,7 +45459,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45482,7 +45485,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45508,7 +45511,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45534,7 +45537,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45560,7 +45563,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45586,7 +45589,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45612,7 +45615,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45638,7 +45641,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45664,7 +45667,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45690,7 +45693,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45716,7 +45719,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45742,7 +45745,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45768,7 +45771,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45794,7 +45797,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45820,7 +45823,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45846,7 +45849,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45872,7 +45875,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45898,7 +45901,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45924,7 +45927,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45950,7 +45953,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45976,7 +45979,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46002,7 +46005,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46028,7 +46031,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46054,7 +46057,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46080,7 +46083,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46106,7 +46109,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46132,7 +46135,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46158,7 +46161,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46184,7 +46187,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46210,7 +46213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46236,7 +46239,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46262,7 +46265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46288,7 +46291,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46314,7 +46317,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46340,7 +46343,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46366,7 +46369,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46392,7 +46395,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46418,7 +46421,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46444,7 +46447,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46470,7 +46473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46496,7 +46499,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46522,7 +46525,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46548,7 +46551,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46574,7 +46577,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46600,7 +46603,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46626,7 +46629,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46652,7 +46655,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46678,7 +46681,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46704,7 +46707,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46730,7 +46733,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46756,7 +46759,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46782,7 +46785,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46808,7 +46811,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46834,7 +46837,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46860,7 +46863,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46886,7 +46889,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46912,7 +46915,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46938,7 +46941,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46964,7 +46967,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46990,7 +46993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47016,7 +47019,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47042,7 +47045,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47068,7 +47071,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47094,7 +47097,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47120,7 +47123,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47146,7 +47149,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47172,7 +47175,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47198,7 +47201,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47224,7 +47227,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47250,7 +47253,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47276,7 +47279,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47302,7 +47305,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47328,7 +47331,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47354,7 +47357,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47380,7 +47383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47406,7 +47409,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47432,7 +47435,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47458,7 +47461,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47484,7 +47487,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47510,7 +47513,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47536,7 +47539,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47562,7 +47565,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47588,7 +47591,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47614,7 +47617,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47640,7 +47643,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47666,7 +47669,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47692,7 +47695,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47718,7 +47721,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47744,7 +47747,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47770,7 +47773,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47796,7 +47799,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47822,7 +47825,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47848,7 +47851,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47874,7 +47877,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47900,7 +47903,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47926,7 +47929,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47952,7 +47955,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47978,7 +47981,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48004,7 +48007,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48030,7 +48033,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48056,7 +48059,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48082,7 +48085,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48108,7 +48111,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48134,7 +48137,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48160,7 +48163,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48186,7 +48189,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48212,7 +48215,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48238,7 +48241,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48264,7 +48267,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48290,7 +48293,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48316,7 +48319,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48342,7 +48345,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48368,7 +48371,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48394,7 +48397,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48420,7 +48423,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48446,7 +48449,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48472,7 +48475,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48498,7 +48501,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48524,7 +48527,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48550,7 +48553,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48576,7 +48579,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48602,7 +48605,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48628,7 +48631,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48654,7 +48657,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48680,7 +48683,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48706,7 +48709,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48732,7 +48735,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48758,7 +48761,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48784,7 +48787,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48810,7 +48813,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48836,7 +48839,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48862,7 +48865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48888,7 +48891,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48914,7 +48917,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48940,7 +48943,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48966,7 +48969,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48992,7 +48995,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49018,7 +49021,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49044,7 +49047,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49070,7 +49073,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49096,7 +49099,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49122,7 +49125,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49148,7 +49151,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49174,7 +49177,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49200,7 +49203,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49226,7 +49229,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49252,7 +49255,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49278,7 +49281,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49304,7 +49307,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49330,7 +49333,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49356,7 +49359,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49382,7 +49385,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49408,7 +49411,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49434,7 +49437,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49460,7 +49463,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49486,7 +49489,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49512,7 +49515,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49538,7 +49541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49564,7 +49567,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49590,7 +49593,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49616,7 +49619,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49642,7 +49645,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49668,7 +49671,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49694,7 +49697,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49720,7 +49723,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49746,7 +49749,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49772,7 +49775,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49798,7 +49801,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49824,7 +49827,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49850,7 +49853,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49876,7 +49879,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49902,7 +49905,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49928,7 +49931,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49954,7 +49957,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49980,7 +49983,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50006,7 +50009,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50032,7 +50035,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50058,7 +50061,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50084,7 +50087,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50110,7 +50113,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50136,7 +50139,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50162,7 +50165,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50188,7 +50191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50214,7 +50217,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50240,7 +50243,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50266,7 +50269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50292,7 +50295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50318,7 +50321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50344,7 +50347,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50370,7 +50373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50396,7 +50399,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50422,7 +50425,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50448,7 +50451,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50474,7 +50477,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50500,7 +50503,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50526,7 +50529,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50552,7 +50555,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50578,7 +50581,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50604,7 +50607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50630,7 +50633,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50656,7 +50659,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50682,7 +50685,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50708,7 +50711,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50734,7 +50737,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50760,7 +50763,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50786,7 +50789,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50812,7 +50815,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50838,7 +50841,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50864,7 +50867,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50890,7 +50893,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50916,7 +50919,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50942,7 +50945,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50968,7 +50971,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50994,7 +50997,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51020,7 +51023,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51046,7 +51049,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51072,7 +51075,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51098,7 +51101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51124,7 +51127,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51150,7 +51153,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51176,7 +51179,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51202,7 +51205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51228,7 +51231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51254,7 +51257,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51280,7 +51283,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51306,7 +51309,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51332,7 +51335,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51358,7 +51361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51384,7 +51387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51410,7 +51413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51436,7 +51439,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51462,7 +51465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51488,7 +51491,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51514,7 +51517,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1931" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51540,7 +51543,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1932" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51566,7 +51569,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1933" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51592,9 +51595,87 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1934" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1934" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="1" t="n">
+        <v>45966.3333333333</v>
+      </c>
+      <c r="B1935" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1935" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="G1935" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1935" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B1936" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1936" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1936" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1936" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1937" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>16.1000003814697</v>
+      </c>
+      <c r="G1937" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1937" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="322">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256858825684</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502759933472</t>
@@ -53,25 +53,25 @@
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654928207397</t>
+    <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699003219604</t>
+    <t xml:space="preserve">10.7698993682861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007158279419</t>
+    <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314956665039</t>
+    <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653896331787</t>
+    <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962022781372</t>
+    <t xml:space="preserve">11.1962032318115</t>
   </si>
   <si>
     <t xml:space="preserve">11.5732564926147</t>
@@ -83,43 +83,43 @@
     <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116273880005</t>
+    <t xml:space="preserve">11.3116283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948385238647</t>
+    <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424757003784</t>
+    <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501024246216</t>
+    <t xml:space="preserve">11.3501005172729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.8102617263794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773325920105</t>
+    <t xml:space="preserve">11.7733268737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657011032104</t>
+    <t xml:space="preserve">11.9657030105591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579008102417</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751770019531</t>
+    <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086185455322</t>
+    <t xml:space="preserve">10.8086175918579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683450698853</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">10.1087789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326042175293</t>
+    <t xml:space="preserve">9.95326137542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345386505127</t>
+    <t xml:space="preserve">9.11345291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790134429932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
     <t xml:space="preserve">9.5178050994873</t>
@@ -152,28 +152,28 @@
     <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278940200806</t>
+    <t xml:space="preserve">12.0278930664062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950807571411</t>
+    <t xml:space="preserve">11.6950817108154</t>
   </si>
   <si>
     <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
     <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084581375122</t>
+    <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
     <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529367446899</t>
+    <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
     <t xml:space="preserve">11.1196584701538</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975786209106</t>
+    <t xml:space="preserve">10.4975805282593</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332363128662</t>
+    <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894031524658</t>
+    <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449283599854</t>
+    <t xml:space="preserve">9.42449378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222145080566</t>
+    <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
     <t xml:space="preserve">9.87550163269043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.3420600891113</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79773998260498</t>
+    <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
     <t xml:space="preserve">9.48670101165771</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892570495605</t>
+    <t xml:space="preserve">9.47892379760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815227508545</t>
+    <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945678710938</t>
+    <t xml:space="preserve">9.09945774078369</t>
   </si>
   <si>
     <t xml:space="preserve">9.71842670440674</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">10.3087778091431</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2745637893677</t>
+    <t xml:space="preserve">10.2745628356934</t>
   </si>
   <si>
     <t xml:space="preserve">10.3498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076923370361</t>
+    <t xml:space="preserve">10.0076932907104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064434051514</t>
+    <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919784545898</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353704452515</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7789039611816</t>
+    <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181264877319</t>
+    <t xml:space="preserve">10.5181245803833</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834913253784</t>
   </si>
   <si>
     <t xml:space="preserve">10.2573461532593</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">9.64885997772217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963935852051</t>
+    <t xml:space="preserve">9.90963745117188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193256378174</t>
+    <t xml:space="preserve">9.56193161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344734191895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651992797852</t>
+    <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959251403809</t>
+    <t xml:space="preserve">8.7795934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266510009766</t>
+    <t xml:space="preserve">8.69266700744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920330047607</t>
@@ -311,64 +311,64 @@
     <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004665374756</t>
+    <t xml:space="preserve">11.300464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658323287964</t>
+    <t xml:space="preserve">10.8658313751221</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704187393188</t>
+    <t xml:space="preserve">10.1704177856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99656581878662</t>
+    <t xml:space="preserve">9.9965648651123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.605052947998</t>
+    <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311990737915</t>
+    <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
     <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3880786895752</t>
+    <t xml:space="preserve">9.38807964324951</t>
   </si>
   <si>
     <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12729835510254</t>
+    <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578453063965</t>
+    <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115222930908</t>
+    <t xml:space="preserve">9.3011531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725198745728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876533508301</t>
+    <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183792114258</t>
+    <t xml:space="preserve">7.30183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
     <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569227218628</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
     <t xml:space="preserve">7.82339954376221</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">7.95378875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34495830535889</t>
+    <t xml:space="preserve">8.34496021270752</t>
   </si>
   <si>
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087146759033</t>
+    <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
@@ -395,55 +395,55 @@
     <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584178924561</t>
+    <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85726928710938</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869773864746</t>
+    <t xml:space="preserve">8.76869678497314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441619873047</t>
+    <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7244119644165</t>
+    <t xml:space="preserve">8.72441101074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298965454102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50297832489014</t>
+    <t xml:space="preserve">8.50298023223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440773010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013370513916</t>
+    <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858606338501</t>
+    <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
     <t xml:space="preserve">11.0715866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944425582886</t>
+    <t xml:space="preserve">10.8944416046143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830150604248</t>
+    <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
     <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972862243652</t>
+    <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
     <t xml:space="preserve">9.83157062530518</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">9.92014217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744331359863</t>
+    <t xml:space="preserve">10.274432182312</t>
   </si>
   <si>
     <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144510269165</t>
+    <t xml:space="preserve">11.5144500732422</t>
   </si>
   <si>
     <t xml:space="preserve">11.425877571106</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.7172966003418</t>
@@ -482,16 +482,16 @@
     <t xml:space="preserve">10.5401515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193992614746</t>
+    <t xml:space="preserve">10.4193983078003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5100021362305</t>
+    <t xml:space="preserve">10.5100011825562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006059646606</t>
+    <t xml:space="preserve">10.6006050109863</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381906509399</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502624511719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4160375595093</t>
+    <t xml:space="preserve">11.416036605835</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442260742188</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878471374512</t>
+    <t xml:space="preserve">11.6878461837769</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844854354858</t>
+    <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
     <t xml:space="preserve">12.5032787322998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7750883102417</t>
+    <t xml:space="preserve">12.7750902175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.1375026702881</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435380935669</t>
+    <t xml:space="preserve">14.0435361862183</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811227798462</t>
+    <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
     <t xml:space="preserve">14.3153476715088</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">15.4025888442993</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556070327759</t>
+    <t xml:space="preserve">15.8556051254272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462089538574</t>
+    <t xml:space="preserve">15.9462108612061</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650022506714</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307802200317</t>
+    <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
     <t xml:space="preserve">15.2213821411133</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">14.5871572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8623313903809</t>
+    <t xml:space="preserve">13.8623294830322</t>
   </si>
   <si>
     <t xml:space="preserve">14.4965543746948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.768364906311</t>
+    <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495706558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119859695435</t>
+    <t xml:space="preserve">15.3119840621948</t>
   </si>
   <si>
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230634689331</t>
+    <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196636199951</t>
+    <t xml:space="preserve">14.2196626663208</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776159286499</t>
+    <t xml:space="preserve">15.3776149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586168289185</t>
+    <t xml:space="preserve">14.3586158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733446121216</t>
+    <t xml:space="preserve">14.1733436584473</t>
   </si>
   <si>
     <t xml:space="preserve">13.7564811706543</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491163253784</t>
+    <t xml:space="preserve">13.8491172790527</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880714416504</t>
+    <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248908996582</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0617094039917</t>
+    <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.200662612915</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533885955811</t>
+    <t xml:space="preserve">15.0533876419067</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -752,28 +752,25 @@
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512538909912</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
     <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2849788665771</t>
+    <t xml:space="preserve">15.2849779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555242538452</t>
+    <t xml:space="preserve">15.6555223464966</t>
   </si>
   <si>
     <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.192343711853</t>
+    <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
     <t xml:space="preserve">15.8407974243164</t>
@@ -782,10 +779,10 @@
     <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702529907227</t>
+    <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460256576538</t>
+    <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
@@ -33317,7 +33314,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33343,7 +33340,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33369,7 +33366,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33395,7 +33392,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33447,7 +33444,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33473,7 +33470,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33499,7 +33496,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33525,7 +33522,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33551,7 +33548,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33577,7 +33574,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33603,7 +33600,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33629,7 +33626,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33655,7 +33652,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33681,7 +33678,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33707,7 +33704,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33733,7 +33730,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33759,7 +33756,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33785,7 +33782,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33811,7 +33808,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33837,7 +33834,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33889,7 +33886,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33915,7 +33912,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33941,7 +33938,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33967,7 +33964,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33993,7 +33990,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34019,7 +34016,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34045,7 +34042,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34409,7 +34406,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34435,7 +34432,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34461,7 +34458,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34747,7 +34744,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34773,7 +34770,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34799,7 +34796,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34903,7 +34900,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35059,7 +35056,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35111,7 +35108,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35137,7 +35134,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35163,7 +35160,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35189,7 +35186,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35215,7 +35212,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35241,7 +35238,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35267,7 +35264,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35293,7 +35290,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35371,7 +35368,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35397,7 +35394,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35423,7 +35420,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35449,7 +35446,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35475,7 +35472,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35501,7 +35498,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35527,7 +35524,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35553,7 +35550,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35579,7 +35576,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35605,7 +35602,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35631,7 +35628,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35657,7 +35654,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35683,7 +35680,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35709,7 +35706,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35735,7 +35732,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35761,7 +35758,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35787,7 +35784,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35813,7 +35810,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35839,7 +35836,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35865,7 +35862,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35891,7 +35888,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35917,7 +35914,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35943,7 +35940,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35969,7 +35966,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35995,7 +35992,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36021,7 +36018,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36047,7 +36044,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36073,7 +36070,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36099,7 +36096,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36125,7 +36122,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36151,7 +36148,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36177,7 +36174,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36203,7 +36200,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36229,7 +36226,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36255,7 +36252,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36281,7 +36278,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36307,7 +36304,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36333,7 +36330,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36359,7 +36356,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36385,7 +36382,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36411,7 +36408,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36437,7 +36434,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36463,7 +36460,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36489,7 +36486,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36515,7 +36512,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36541,7 +36538,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36567,7 +36564,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36593,7 +36590,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36619,7 +36616,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36645,7 +36642,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36671,7 +36668,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36697,7 +36694,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -36723,7 +36720,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36749,7 +36746,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36775,7 +36772,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36801,7 +36798,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36827,7 +36824,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36853,7 +36850,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36879,7 +36876,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36905,7 +36902,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36931,7 +36928,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36957,7 +36954,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36983,7 +36980,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37009,7 +37006,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37035,7 +37032,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37061,7 +37058,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37087,7 +37084,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37113,7 +37110,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37139,7 +37136,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37165,7 +37162,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37191,7 +37188,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37217,7 +37214,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37243,7 +37240,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37269,7 +37266,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37295,7 +37292,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37321,7 +37318,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37347,7 +37344,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37373,7 +37370,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37399,7 +37396,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37425,7 +37422,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37451,7 +37448,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37477,7 +37474,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37503,7 +37500,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37529,7 +37526,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37555,7 +37552,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37581,7 +37578,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37607,7 +37604,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37633,7 +37630,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37659,7 +37656,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37685,7 +37682,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37711,7 +37708,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37737,7 +37734,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37763,7 +37760,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37789,7 +37786,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37815,7 +37812,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37841,7 +37838,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -37867,7 +37864,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37893,7 +37890,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37919,7 +37916,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37945,7 +37942,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37971,7 +37968,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -37997,7 +37994,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38023,7 +38020,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38049,7 +38046,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38075,7 +38072,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38101,7 +38098,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38127,7 +38124,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38153,7 +38150,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38179,7 +38176,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38205,7 +38202,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38231,7 +38228,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38257,7 +38254,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38283,7 +38280,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38309,7 +38306,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38335,7 +38332,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38361,7 +38358,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38387,7 +38384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38413,7 +38410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38439,7 +38436,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38465,7 +38462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38491,7 +38488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38517,7 +38514,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38543,7 +38540,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38569,7 +38566,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38595,7 +38592,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38621,7 +38618,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38647,7 +38644,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38673,7 +38670,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38699,7 +38696,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38725,7 +38722,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38751,7 +38748,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38777,7 +38774,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38803,7 +38800,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -38829,7 +38826,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38855,7 +38852,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38881,7 +38878,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38907,7 +38904,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38933,7 +38930,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38959,7 +38956,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38985,7 +38982,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39011,7 +39008,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39037,7 +39034,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39063,7 +39060,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39089,7 +39086,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39115,7 +39112,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39141,7 +39138,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39167,7 +39164,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39193,7 +39190,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39219,7 +39216,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39245,7 +39242,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39271,7 +39268,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39297,7 +39294,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39323,7 +39320,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39349,7 +39346,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39375,7 +39372,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39401,7 +39398,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39427,7 +39424,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39453,7 +39450,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39479,7 +39476,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39505,7 +39502,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39531,7 +39528,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39557,7 +39554,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39583,7 +39580,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39609,7 +39606,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39635,7 +39632,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39661,7 +39658,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39687,7 +39684,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39713,7 +39710,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39739,7 +39736,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39765,7 +39762,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39791,7 +39788,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39817,7 +39814,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39843,7 +39840,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39869,7 +39866,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39895,7 +39892,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39921,7 +39918,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39947,7 +39944,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39973,7 +39970,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -39999,7 +39996,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40025,7 +40022,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40051,7 +40048,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40077,7 +40074,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40103,7 +40100,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40129,7 +40126,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40155,7 +40152,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40181,7 +40178,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40207,7 +40204,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40233,7 +40230,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40259,7 +40256,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40285,7 +40282,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40311,7 +40308,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40337,7 +40334,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40363,7 +40360,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40389,7 +40386,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40649,7 +40646,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40675,7 +40672,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40701,7 +40698,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40727,7 +40724,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40753,7 +40750,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40779,7 +40776,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40805,7 +40802,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40831,7 +40828,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40857,7 +40854,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -40883,7 +40880,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40909,7 +40906,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40935,7 +40932,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40961,7 +40958,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40987,7 +40984,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41013,7 +41010,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41039,7 +41036,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41065,7 +41062,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41091,7 +41088,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41117,7 +41114,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41143,7 +41140,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41169,7 +41166,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41195,7 +41192,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41221,7 +41218,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41247,7 +41244,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41273,7 +41270,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41299,7 +41296,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41325,7 +41322,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41351,7 +41348,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41377,7 +41374,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41403,7 +41400,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41429,7 +41426,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41455,7 +41452,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41481,7 +41478,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41507,7 +41504,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41533,7 +41530,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41559,7 +41556,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41585,7 +41582,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41611,7 +41608,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41637,7 +41634,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41663,7 +41660,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41689,7 +41686,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41715,7 +41712,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41741,7 +41738,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41767,7 +41764,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41793,7 +41790,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41819,7 +41816,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41845,7 +41842,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41871,7 +41868,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41897,7 +41894,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41923,7 +41920,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41949,7 +41946,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41975,7 +41972,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42001,7 +41998,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42027,7 +42024,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42053,7 +42050,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42079,7 +42076,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42105,7 +42102,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42131,7 +42128,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42157,7 +42154,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42183,7 +42180,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42209,7 +42206,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42235,7 +42232,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42261,7 +42258,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42287,7 +42284,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42313,7 +42310,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42339,7 +42336,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42365,7 +42362,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42391,7 +42388,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42417,7 +42414,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42443,7 +42440,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42469,7 +42466,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42495,7 +42492,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42521,7 +42518,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42547,7 +42544,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42573,7 +42570,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42599,7 +42596,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42625,7 +42622,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42651,7 +42648,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42677,7 +42674,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42703,7 +42700,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42729,7 +42726,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42755,7 +42752,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42781,7 +42778,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42807,7 +42804,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42833,7 +42830,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42859,7 +42856,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42885,7 +42882,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42911,7 +42908,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42937,7 +42934,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42963,7 +42960,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42989,7 +42986,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43015,7 +43012,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43041,7 +43038,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43067,7 +43064,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43093,7 +43090,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43119,7 +43116,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43145,7 +43142,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43171,7 +43168,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43197,7 +43194,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43223,7 +43220,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43249,7 +43246,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43275,7 +43272,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43301,7 +43298,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43327,7 +43324,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43353,7 +43350,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43379,7 +43376,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43405,7 +43402,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43431,7 +43428,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43457,7 +43454,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43483,7 +43480,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43509,7 +43506,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43535,7 +43532,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43561,7 +43558,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43587,7 +43584,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43613,7 +43610,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43639,7 +43636,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43665,7 +43662,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43691,7 +43688,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43717,7 +43714,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43743,7 +43740,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43769,7 +43766,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43795,7 +43792,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43821,7 +43818,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43847,7 +43844,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43873,7 +43870,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43899,7 +43896,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43925,7 +43922,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43951,7 +43948,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43977,7 +43974,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44003,7 +44000,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44029,7 +44026,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44055,7 +44052,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44081,7 +44078,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44107,7 +44104,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44133,7 +44130,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44159,7 +44156,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44185,7 +44182,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44211,7 +44208,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44237,7 +44234,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44263,7 +44260,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44289,7 +44286,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44315,7 +44312,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44341,7 +44338,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44367,7 +44364,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44393,7 +44390,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44419,7 +44416,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44445,7 +44442,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44471,7 +44468,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44497,7 +44494,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44523,7 +44520,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44549,7 +44546,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44575,7 +44572,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44601,7 +44598,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44627,7 +44624,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44653,7 +44650,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44679,7 +44676,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44705,7 +44702,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44731,7 +44728,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44757,7 +44754,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44783,7 +44780,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44809,7 +44806,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44835,7 +44832,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44861,7 +44858,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44887,7 +44884,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44913,7 +44910,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44939,7 +44936,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44965,7 +44962,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44991,7 +44988,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45017,7 +45014,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45043,7 +45040,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45069,7 +45066,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45095,7 +45092,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45121,7 +45118,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45147,7 +45144,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45173,7 +45170,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45199,7 +45196,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45225,7 +45222,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45251,7 +45248,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45277,7 +45274,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45303,7 +45300,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45329,7 +45326,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45355,7 +45352,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45381,7 +45378,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45407,7 +45404,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45433,7 +45430,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45459,7 +45456,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45485,7 +45482,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45511,7 +45508,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45537,7 +45534,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45563,7 +45560,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45589,7 +45586,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45615,7 +45612,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45641,7 +45638,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45667,7 +45664,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45693,7 +45690,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45719,7 +45716,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45745,7 +45742,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45771,7 +45768,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45797,7 +45794,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45823,7 +45820,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45849,7 +45846,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45875,7 +45872,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45901,7 +45898,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45927,7 +45924,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45953,7 +45950,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45979,7 +45976,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46005,7 +46002,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46031,7 +46028,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46057,7 +46054,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46083,7 +46080,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46109,7 +46106,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46135,7 +46132,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46161,7 +46158,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46187,7 +46184,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46213,7 +46210,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46239,7 +46236,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46265,7 +46262,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46291,7 +46288,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46317,7 +46314,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46343,7 +46340,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46369,7 +46366,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46395,7 +46392,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46421,7 +46418,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46447,7 +46444,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46473,7 +46470,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46499,7 +46496,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46525,7 +46522,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46551,7 +46548,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46577,7 +46574,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46603,7 +46600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46629,7 +46626,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46655,7 +46652,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46681,7 +46678,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46707,7 +46704,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46733,7 +46730,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46759,7 +46756,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46785,7 +46782,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46811,7 +46808,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46837,7 +46834,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46863,7 +46860,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46889,7 +46886,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46915,7 +46912,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46941,7 +46938,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46967,7 +46964,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46993,7 +46990,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47019,7 +47016,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47045,7 +47042,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47071,7 +47068,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47097,7 +47094,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47123,7 +47120,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47149,7 +47146,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47175,7 +47172,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47201,7 +47198,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47227,7 +47224,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47253,7 +47250,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47279,7 +47276,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47305,7 +47302,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47331,7 +47328,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47357,7 +47354,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47383,7 +47380,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47409,7 +47406,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47435,7 +47432,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47461,7 +47458,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47487,7 +47484,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47513,7 +47510,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47539,7 +47536,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47565,7 +47562,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47591,7 +47588,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47617,7 +47614,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47643,7 +47640,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47669,7 +47666,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47695,7 +47692,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47721,7 +47718,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47747,7 +47744,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47773,7 +47770,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47799,7 +47796,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47825,7 +47822,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47851,7 +47848,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47877,7 +47874,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47903,7 +47900,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47929,7 +47926,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47955,7 +47952,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47981,7 +47978,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48007,7 +48004,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48033,7 +48030,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48059,7 +48056,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48085,7 +48082,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48111,7 +48108,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48137,7 +48134,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48163,7 +48160,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48189,7 +48186,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48215,7 +48212,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48241,7 +48238,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48267,7 +48264,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48293,7 +48290,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48319,7 +48316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48345,7 +48342,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48371,7 +48368,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48397,7 +48394,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48423,7 +48420,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48449,7 +48446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48475,7 +48472,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48501,7 +48498,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48527,7 +48524,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48553,7 +48550,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48579,7 +48576,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48605,7 +48602,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48631,7 +48628,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48657,7 +48654,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48683,7 +48680,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48709,7 +48706,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48735,7 +48732,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48761,7 +48758,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48787,7 +48784,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48813,7 +48810,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48839,7 +48836,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48865,7 +48862,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48891,7 +48888,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48917,7 +48914,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48943,7 +48940,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48969,7 +48966,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48995,7 +48992,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49021,7 +49018,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49047,7 +49044,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49073,7 +49070,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49099,7 +49096,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49125,7 +49122,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49151,7 +49148,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49177,7 +49174,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49203,7 +49200,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49229,7 +49226,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49255,7 +49252,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49281,7 +49278,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49307,7 +49304,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49333,7 +49330,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49359,7 +49356,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49385,7 +49382,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49411,7 +49408,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49437,7 +49434,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49463,7 +49460,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49489,7 +49486,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49515,7 +49512,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49541,7 +49538,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49567,7 +49564,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49593,7 +49590,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49619,7 +49616,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49645,7 +49642,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49671,7 +49668,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49697,7 +49694,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49723,7 +49720,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49749,7 +49746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49775,7 +49772,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49801,7 +49798,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49827,7 +49824,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49853,7 +49850,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49879,7 +49876,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49905,7 +49902,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49931,7 +49928,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49957,7 +49954,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49983,7 +49980,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50009,7 +50006,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50035,7 +50032,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50061,7 +50058,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50087,7 +50084,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50113,7 +50110,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50139,7 +50136,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50165,7 +50162,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50191,7 +50188,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50217,7 +50214,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50243,7 +50240,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50269,7 +50266,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50295,7 +50292,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50321,7 +50318,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50347,7 +50344,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50373,7 +50370,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50399,7 +50396,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50425,7 +50422,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50451,7 +50448,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50477,7 +50474,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50503,7 +50500,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50529,7 +50526,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50555,7 +50552,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50581,7 +50578,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50607,7 +50604,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50633,7 +50630,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50659,7 +50656,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50685,7 +50682,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50711,7 +50708,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50737,7 +50734,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50763,7 +50760,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50789,7 +50786,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50815,7 +50812,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50841,7 +50838,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50867,7 +50864,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50893,7 +50890,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50919,7 +50916,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50945,7 +50942,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50971,7 +50968,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -50997,7 +50994,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51023,7 +51020,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51049,7 +51046,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51075,7 +51072,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51101,7 +51098,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51127,7 +51124,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51153,7 +51150,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51179,7 +51176,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51205,7 +51202,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51231,7 +51228,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51257,7 +51254,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51283,7 +51280,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51309,7 +51306,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51335,7 +51332,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51361,7 +51358,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51387,7 +51384,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51413,7 +51410,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51439,7 +51436,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51465,7 +51462,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51491,7 +51488,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51517,7 +51514,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1931" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51543,7 +51540,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1932" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51569,7 +51566,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1933" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51595,7 +51592,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1934" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51621,7 +51618,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1935" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -51647,7 +51644,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -51673,7 +51670,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -51699,7 +51696,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -51725,7 +51722,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -51751,7 +51748,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -51777,7 +51774,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1941" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -51785,7 +51782,7 @@
     </row>
     <row r="1942">
       <c r="A1942" s="1" t="n">
-        <v>45975.4149421296</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B1942" t="n">
         <v>400</v>
@@ -51803,9 +51800,35 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1942" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1942" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="1" t="n">
+        <v>45978.6699189815</v>
+      </c>
+      <c r="B1943" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1943" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D1943" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="E1943" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="G1943" t="s">
+        <v>320</v>
+      </c>
+      <c r="H1943" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
@@ -50,94 +50,94 @@
     <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577291488647</t>
+    <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
     <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7698993682861</t>
+    <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007158279419</t>
+    <t xml:space="preserve">10.9007139205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314947128296</t>
+    <t xml:space="preserve">10.9314956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653886795044</t>
+    <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962032318115</t>
+    <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732574462891</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
     <t xml:space="preserve">11.1192531585693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194257736206</t>
+    <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116283416748</t>
+    <t xml:space="preserve">11.3116264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6948375701904</t>
+    <t xml:space="preserve">11.6948366165161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3501024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102617263794</t>
+    <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
     <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963758468628</t>
+    <t xml:space="preserve">11.6963777542114</t>
   </si>
   <si>
     <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579008102417</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751770019531</t>
+    <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086185455322</t>
+    <t xml:space="preserve">10.8086194992065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683450698853</t>
+    <t xml:space="preserve">10.0683460235596</t>
   </si>
   <si>
     <t xml:space="preserve">10.1087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95325946807861</t>
+    <t xml:space="preserve">9.95326042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998119354248</t>
+    <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345386505127</t>
+    <t xml:space="preserve">9.11345291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790325164795</t>
   </si>
   <si>
     <t xml:space="preserve">9.85683727264404</t>
@@ -146,31 +146,31 @@
     <t xml:space="preserve">9.51780414581299</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907285690308</t>
+    <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278930664062</t>
+    <t xml:space="preserve">12.0278940200806</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750156402588</t>
+    <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028579711914</t>
+    <t xml:space="preserve">11.7028570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.586217880249</t>
+    <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084571838379</t>
+    <t xml:space="preserve">11.5084581375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639776229858</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529367446899</t>
@@ -179,13 +179,13 @@
     <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8863773345947</t>
+    <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
     <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.497579574585</t>
+    <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
     <t xml:space="preserve">10.4198188781738</t>
@@ -194,121 +194,121 @@
     <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332363128662</t>
+    <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4089412689209</t>
+    <t xml:space="preserve">9.40894222259521</t>
   </si>
   <si>
     <t xml:space="preserve">9.42449283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222145080566</t>
+    <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550067901611</t>
+    <t xml:space="preserve">9.8754997253418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887147903442</t>
+    <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
     <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670101165771</t>
+    <t xml:space="preserve">9.48670196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118057250977</t>
+    <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662128448486</t>
+    <t xml:space="preserve">9.83662223815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.47892379760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074573516846</t>
+    <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815227508545</t>
+    <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945583343506</t>
+    <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842670440674</t>
+    <t xml:space="preserve">9.71842479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087787628174</t>
+    <t xml:space="preserve">10.3087778091431</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2745628356934</t>
+    <t xml:space="preserve">10.274564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.349835395813</t>
+    <t xml:space="preserve">10.3498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076932907104</t>
+    <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064424514771</t>
+    <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
     <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353704452515</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778904914856</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834913253784</t>
+    <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2573461532593</t>
+    <t xml:space="preserve">10.257345199585</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885997772217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963745117188</t>
+    <t xml:space="preserve">9.90963935852051</t>
   </si>
   <si>
     <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651992797852</t>
+    <t xml:space="preserve">8.86651802062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266510009766</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037284851074</t>
+    <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271194458008</t>
+    <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126612663269</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
     <t xml:space="preserve">11.3004655838013</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704196929932</t>
+    <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99656581878662</t>
+    <t xml:space="preserve">9.99656677246094</t>
   </si>
   <si>
     <t xml:space="preserve">10.6050519943237</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500514984131</t>
+    <t xml:space="preserve">9.47500419616699</t>
   </si>
   <si>
     <t xml:space="preserve">9.3880786895752</t>
@@ -344,70 +344,70 @@
     <t xml:space="preserve">9.12729930877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578453063965</t>
+    <t xml:space="preserve">9.73578643798828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442726135254</t>
+    <t xml:space="preserve">10.3442707061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3011531829834</t>
+    <t xml:space="preserve">9.30115127563477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725198745728</t>
+    <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
     <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183792114258</t>
+    <t xml:space="preserve">7.30183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
     <t xml:space="preserve">7.34530258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569370269775</t>
+    <t xml:space="preserve">7.47569179534912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339906692505</t>
+    <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378923416138</t>
+    <t xml:space="preserve">7.9537878036499</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573863983154</t>
+    <t xml:space="preserve">8.60573959350586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087146759033</t>
+    <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727966308594</t>
+    <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870620727539</t>
+    <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
     <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85726928710938</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869678497314</t>
+    <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441619873047</t>
+    <t xml:space="preserve">9.03441429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012428283691</t>
+    <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
     <t xml:space="preserve">8.72441101074219</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858606338501</t>
+    <t xml:space="preserve">10.1858615875244</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830141067505</t>
+    <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972871780396</t>
+    <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">9.83157062530518</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014122009277</t>
+    <t xml:space="preserve">9.92014312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274432182312</t>
+    <t xml:space="preserve">10.2744340896606</t>
   </si>
   <si>
     <t xml:space="preserve">11.2487316131592</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630065917969</t>
+    <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401515960693</t>
+    <t xml:space="preserve">10.5401496887207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193992614746</t>
+    <t xml:space="preserve">10.4193983078003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5100030899048</t>
+    <t xml:space="preserve">10.5100021362305</t>
   </si>
   <si>
     <t xml:space="preserve">10.6912088394165</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475887298584</t>
+    <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818117141724</t>
+    <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
     <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502614974976</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1442260742188</t>
+    <t xml:space="preserve">11.1442270278931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690547943115</t>
+    <t xml:space="preserve">11.8690557479858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408634185791</t>
+    <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
     <t xml:space="preserve">11.6878471374512</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844844818115</t>
+    <t xml:space="preserve">12.6844854354858</t>
   </si>
   <si>
     <t xml:space="preserve">12.5032787322998</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562950134277</t>
+    <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
     <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435380935669</t>
+    <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
     <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
     <t xml:space="preserve">15.4931945800781</t>
@@ -569,22 +569,22 @@
     <t xml:space="preserve">15.4025897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556060791016</t>
+    <t xml:space="preserve">15.8556051254272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462099075317</t>
+    <t xml:space="preserve">15.9462089538574</t>
   </si>
   <si>
     <t xml:space="preserve">15.7650012969971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307802200317</t>
+    <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
     <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871591567993</t>
+    <t xml:space="preserve">14.587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495725631714</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119859695435</t>
+    <t xml:space="preserve">15.3119869232178</t>
   </si>
   <si>
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230634689331</t>
+    <t xml:space="preserve">14.7230644226074</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512519836426</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.127025604248</t>
+    <t xml:space="preserve">14.1270265579224</t>
   </si>
   <si>
     <t xml:space="preserve">14.2659797668457</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343894958496</t>
+    <t xml:space="preserve">14.0343885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6828441619873</t>
+    <t xml:space="preserve">14.682843208313</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070714950562</t>
+    <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491172790527</t>
+    <t xml:space="preserve">13.8491163253784</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859357833862</t>
+    <t xml:space="preserve">13.3859367370605</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3396167755127</t>
+    <t xml:space="preserve">13.339617729187</t>
   </si>
   <si>
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101621627808</t>
+    <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
     <t xml:space="preserve">13.0617094039917</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469816207886</t>
+    <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006635665894</t>
+    <t xml:space="preserve">13.200662612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9417543411255</t>
+    <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533876419067</t>
+    <t xml:space="preserve">15.0533885955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
@@ -752,40 +752,40 @@
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512538909912</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144344329834</t>
+    <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555233001709</t>
+    <t xml:space="preserve">15.6555242538452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1923427581787</t>
+    <t xml:space="preserve">15.192343711853</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165691375732</t>
+    <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
     <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944765090942</t>
+    <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
     <t xml:space="preserve">15.4702529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460247039795</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
@@ -51863,7 +51863,7 @@
     </row>
     <row r="1945">
       <c r="A1945" s="1" t="n">
-        <v>45980.3704166667</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B1945" t="n">
         <v>1000</v>
@@ -51884,6 +51884,32 @@
         <v>321</v>
       </c>
       <c r="H1945" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="1" t="n">
+        <v>45981.6499884259</v>
+      </c>
+      <c r="B1946" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C1946" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="D1946" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="E1946" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="F1946" t="n">
+        <v>16.2000007629395</v>
+      </c>
+      <c r="G1946" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1946" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="324">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,79 +38,79 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118375778198</t>
+    <t xml:space="preserve">11.9118356704712</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925687789917</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577281951904</t>
+    <t xml:space="preserve">11.1577272415161</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654909133911</t>
+    <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7698993682861</t>
+    <t xml:space="preserve">10.7699012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314956665039</t>
+    <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
     <t xml:space="preserve">11.0653886795044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962013244629</t>
+    <t xml:space="preserve">11.1962032318115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732574462891</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192531585693</t>
+    <t xml:space="preserve">11.1192541122437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194276809692</t>
+    <t xml:space="preserve">11.6194257736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116273880005</t>
+    <t xml:space="preserve">11.3116264343262</t>
   </si>
   <si>
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.8102617263794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773325920105</t>
+    <t xml:space="preserve">11.7733249664307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963777542114</t>
+    <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657020568848</t>
+    <t xml:space="preserve">11.9657001495361</t>
   </si>
   <si>
     <t xml:space="preserve">11.657901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807771682739</t>
+    <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
     <t xml:space="preserve">11.2751770019531</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">10.5349035263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683460235596</t>
+    <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087799072266</t>
+    <t xml:space="preserve">10.1087789535522</t>
   </si>
   <si>
     <t xml:space="preserve">9.95325946807861</t>
@@ -137,25 +137,25 @@
     <t xml:space="preserve">9.11345291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790134429932</t>
+    <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683917999268</t>
+    <t xml:space="preserve">9.85683727264404</t>
   </si>
   <si>
     <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2642993927002</t>
+    <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
     <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278940200806</t>
+    <t xml:space="preserve">12.0278930664062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950817108154</t>
+    <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
     <t xml:space="preserve">11.9750156402588</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639776229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529376983643</t>
+    <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
     <t xml:space="preserve">11.1196584701538</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">10.8863773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641370773315</t>
+    <t xml:space="preserve">10.9641380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975786209106</t>
+    <t xml:space="preserve">10.4975805282593</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198188781738</t>
+    <t xml:space="preserve">10.4198198318481</t>
   </si>
   <si>
     <t xml:space="preserve">10.0310201644897</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449188232422</t>
+    <t xml:space="preserve">9.42449378967285</t>
   </si>
   <si>
     <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550067901611</t>
+    <t xml:space="preserve">9.8754997253418</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342059135437</t>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887166976929</t>
+    <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7977409362793</t>
+    <t xml:space="preserve">9.79773902893066</t>
   </si>
   <si>
     <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118152618408</t>
+    <t xml:space="preserve">9.33118057250977</t>
   </si>
   <si>
     <t xml:space="preserve">9.83662033081055</t>
@@ -236,34 +236,34 @@
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815036773682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945774078369</t>
+    <t xml:space="preserve">9.09945583343506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842575073242</t>
+    <t xml:space="preserve">9.71842384338379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087787628174</t>
+    <t xml:space="preserve">10.3087797164917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.274564743042</t>
+    <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498363494873</t>
+    <t xml:space="preserve">10.3498373031616</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064443588257</t>
+    <t xml:space="preserve">10.6064424514771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919784545898</t>
+    <t xml:space="preserve">10.6919803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353704452515</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.7789058685303</t>
@@ -272,61 +272,61 @@
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
     <t xml:space="preserve">10.2573461532593</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64885902404785</t>
+    <t xml:space="preserve">9.64885807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963840484619</t>
+    <t xml:space="preserve">9.90963745117188</t>
   </si>
   <si>
     <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344638824463</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8665189743042</t>
+    <t xml:space="preserve">8.86652088165283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959156036377</t>
+    <t xml:space="preserve">8.7795934677124</t>
   </si>
   <si>
     <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920234680176</t>
+    <t xml:space="preserve">8.64920139312744</t>
   </si>
   <si>
     <t xml:space="preserve">9.04037094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82271385192871</t>
+    <t xml:space="preserve">9.82271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126612663269</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004655838013</t>
+    <t xml:space="preserve">11.300464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658323287964</t>
+    <t xml:space="preserve">10.8658332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527597427368</t>
+    <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
     <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704196929932</t>
+    <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9965648651123</t>
+    <t xml:space="preserve">9.99656677246094</t>
   </si>
   <si>
     <t xml:space="preserve">10.6050519943237</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500514984131</t>
+    <t xml:space="preserve">9.47500610351562</t>
   </si>
   <si>
     <t xml:space="preserve">9.3880786895752</t>
@@ -350,34 +350,34 @@
     <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442726135254</t>
+    <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3011531829834</t>
+    <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725198745728</t>
   </si>
   <si>
     <t xml:space="preserve">7.38876628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183839797974</t>
+    <t xml:space="preserve">7.30183982849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34530210494995</t>
+    <t xml:space="preserve">7.34530258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4756932258606</t>
+    <t xml:space="preserve">7.47569179534912</t>
   </si>
   <si>
     <t xml:space="preserve">7.82339906692505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378875732422</t>
+    <t xml:space="preserve">7.95378923416138</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.008716583252</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727966308594</t>
+    <t xml:space="preserve">9.47727870941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
@@ -401,16 +401,16 @@
     <t xml:space="preserve">8.94584178924561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85727024078369</t>
+    <t xml:space="preserve">8.85726928710938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869678497314</t>
+    <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441524505615</t>
+    <t xml:space="preserve">9.03441619873047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68012428283691</t>
+    <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
     <t xml:space="preserve">8.7244119644165</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">9.2115592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830150604248</t>
+    <t xml:space="preserve">10.9830131530762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515790939331</t>
+    <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972871780396</t>
+    <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">11.4258785247803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.805869102478</t>
+    <t xml:space="preserve">10.8058700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287231445312</t>
+    <t xml:space="preserve">10.6287240982056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630065917969</t>
+    <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
     <t xml:space="preserve">10.5401515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193983078003</t>
+    <t xml:space="preserve">10.4193992614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100021362305</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006059646606</t>
+    <t xml:space="preserve">10.6006050109863</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475877761841</t>
+    <t xml:space="preserve">10.1475887298584</t>
   </si>
   <si>
     <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78517436981201</t>
+    <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502614974976</t>
@@ -521,25 +521,25 @@
     <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1442270278931</t>
+    <t xml:space="preserve">11.1442260742188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690557479858</t>
+    <t xml:space="preserve">11.8690538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408643722534</t>
+    <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878471374512</t>
+    <t xml:space="preserve">11.6878480911255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314682006836</t>
+    <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
     <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032777786255</t>
+    <t xml:space="preserve">12.5032787322998</t>
   </si>
   <si>
     <t xml:space="preserve">12.775089263916</t>
@@ -551,46 +551,46 @@
     <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281055450439</t>
+    <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435361862183</t>
+    <t xml:space="preserve">14.0435380935669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811237335205</t>
+    <t xml:space="preserve">13.6811227798462</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931917190552</t>
+    <t xml:space="preserve">15.4931936264038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401763916016</t>
+    <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4025897979736</t>
+    <t xml:space="preserve">15.402587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556070327759</t>
+    <t xml:space="preserve">15.8556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462089538574</t>
+    <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650022506714</t>
+    <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307792663574</t>
+    <t xml:space="preserve">15.1307802200317</t>
   </si>
   <si>
     <t xml:space="preserve">15.221381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.587158203125</t>
+    <t xml:space="preserve">14.5871591567993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8623294830322</t>
+    <t xml:space="preserve">13.8623313903809</t>
   </si>
   <si>
     <t xml:space="preserve">14.4965543746948</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">14.1341409683228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4093132019043</t>
+    <t xml:space="preserve">13.40931224823</t>
   </si>
   <si>
     <t xml:space="preserve">12.5938816070557</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656911849976</t>
+    <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
     <t xml:space="preserve">13.9529333114624</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">15.3119850158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264251708984</t>
+    <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
     <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512538909912</t>
+    <t xml:space="preserve">14.4512519836426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1270265579224</t>
+    <t xml:space="preserve">14.127025604248</t>
   </si>
   <si>
     <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365261077881</t>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196626663208</t>
+    <t xml:space="preserve">14.2196636199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">14.9607515335083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0070705413818</t>
+    <t xml:space="preserve">15.0070714950562</t>
   </si>
   <si>
     <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586158752441</t>
+    <t xml:space="preserve">14.3586168289185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733436584473</t>
+    <t xml:space="preserve">14.1733446121216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564821243286</t>
+    <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880723953247</t>
+    <t xml:space="preserve">13.9880714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248899459839</t>
+    <t xml:space="preserve">13.5248908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027982711792</t>
+    <t xml:space="preserve">13.8027992248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">13.3859357833862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.339617729187</t>
+    <t xml:space="preserve">13.3396167755127</t>
   </si>
   <si>
     <t xml:space="preserve">13.4322538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7101631164551</t>
+    <t xml:space="preserve">13.7101621627808</t>
   </si>
   <si>
     <t xml:space="preserve">13.0617094039917</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">13.2469816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006645202637</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543445587158</t>
+    <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9417533874512</t>
+    <t xml:space="preserve">13.9417543411255</t>
   </si>
   <si>
     <t xml:space="preserve">15.0533876419067</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.404935836792</t>
+    <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
@@ -776,28 +776,28 @@
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407955169678</t>
+    <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944784164429</t>
+    <t xml:space="preserve">15.7944765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702520370483</t>
+    <t xml:space="preserve">15.4702529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460237503052</t>
+    <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975709915161</t>
+    <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0166959762573</t>
+    <t xml:space="preserve">15.016695022583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -806,10 +806,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365251541138</t>
+    <t xml:space="preserve">14.5414838790894</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -830,13 +827,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968648910522</t>
+    <t xml:space="preserve">15.3968658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572036743164</t>
+    <t xml:space="preserve">16.1572017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720769882202</t>
+    <t xml:space="preserve">15.8720779418945</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -845,7 +842,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315673828125</t>
+    <t xml:space="preserve">14.7315683364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -857,7 +854,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522449493408</t>
+    <t xml:space="preserve">16.2522468566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -35325,7 +35322,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35351,7 +35348,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35377,7 +35374,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35403,7 +35400,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35429,7 +35426,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35455,7 +35452,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35481,7 +35478,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35507,7 +35504,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35533,7 +35530,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35559,7 +35556,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35585,7 +35582,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35611,7 +35608,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35637,7 +35634,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35663,7 +35660,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35689,7 +35686,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35715,7 +35712,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35741,7 +35738,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35767,7 +35764,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35793,7 +35790,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35819,7 +35816,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35845,7 +35842,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35871,7 +35868,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35897,7 +35894,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35923,7 +35920,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35949,7 +35946,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35975,7 +35972,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36001,7 +35998,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36027,7 +36024,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36053,7 +36050,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36079,7 +36076,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36105,7 +36102,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36131,7 +36128,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36157,7 +36154,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36183,7 +36180,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36209,7 +36206,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36235,7 +36232,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36261,7 +36258,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36287,7 +36284,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36313,7 +36310,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36339,7 +36336,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36365,7 +36362,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36391,7 +36388,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36417,7 +36414,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36443,7 +36440,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36521,7 +36518,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36547,7 +36544,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36573,7 +36570,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36599,7 +36596,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36651,7 +36648,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36677,7 +36674,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36729,7 +36726,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36755,7 +36752,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36781,7 +36778,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36807,7 +36804,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36833,7 +36830,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36859,7 +36856,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36885,7 +36882,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36911,7 +36908,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36937,7 +36934,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36963,7 +36960,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36989,7 +36986,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37015,7 +37012,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37119,7 +37116,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37145,7 +37142,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37171,7 +37168,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37197,7 +37194,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37223,7 +37220,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37249,7 +37246,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37275,7 +37272,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37301,7 +37298,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37327,7 +37324,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37353,7 +37350,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37379,7 +37376,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37405,7 +37402,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37431,7 +37428,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37457,7 +37454,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37483,7 +37480,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37509,7 +37506,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37535,7 +37532,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37639,7 +37636,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37665,7 +37662,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37691,7 +37688,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37717,7 +37714,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37743,7 +37740,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37769,7 +37766,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37795,7 +37792,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37821,7 +37818,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37847,7 +37844,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38185,7 +38182,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38211,7 +38208,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38237,7 +38234,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38393,7 +38390,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38419,7 +38416,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38445,7 +38442,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38471,7 +38468,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38497,7 +38494,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38523,7 +38520,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38549,7 +38546,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38575,7 +38572,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38601,7 +38598,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38627,7 +38624,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38653,7 +38650,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38679,7 +38676,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38705,7 +38702,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38731,7 +38728,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38783,7 +38780,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38809,7 +38806,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39017,7 +39014,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39043,7 +39040,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39069,7 +39066,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39095,7 +39092,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39121,7 +39118,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39147,7 +39144,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39173,7 +39170,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39199,7 +39196,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39225,7 +39222,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39251,7 +39248,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39277,7 +39274,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39303,7 +39300,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39329,7 +39326,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39355,7 +39352,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39381,7 +39378,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39407,7 +39404,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39433,7 +39430,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39459,7 +39456,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39485,7 +39482,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39511,7 +39508,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39537,7 +39534,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39563,7 +39560,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39589,7 +39586,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39615,7 +39612,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39641,7 +39638,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39667,7 +39664,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39693,7 +39690,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39719,7 +39716,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39745,7 +39742,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39771,7 +39768,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39797,7 +39794,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39823,7 +39820,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39849,7 +39846,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39875,7 +39872,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39901,7 +39898,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39927,7 +39924,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39953,7 +39950,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39979,7 +39976,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40005,7 +40002,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40031,7 +40028,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40057,7 +40054,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40083,7 +40080,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40109,7 +40106,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40135,7 +40132,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40265,7 +40262,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40421,7 +40418,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40447,7 +40444,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1505" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40473,7 +40470,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40499,7 +40496,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40525,7 +40522,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40551,7 +40548,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40577,7 +40574,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1510" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -40603,7 +40600,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -40629,7 +40626,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -40681,7 +40678,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40707,7 +40704,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40889,7 +40886,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40915,7 +40912,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40941,7 +40938,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40967,7 +40964,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40993,7 +40990,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41019,7 +41016,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41045,7 +41042,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41071,7 +41068,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41097,7 +41094,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41123,7 +41120,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41149,7 +41146,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41175,7 +41172,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41201,7 +41198,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41227,7 +41224,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41253,7 +41250,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41279,7 +41276,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41305,7 +41302,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41331,7 +41328,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41357,7 +41354,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41383,7 +41380,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41409,7 +41406,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41435,7 +41432,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41461,7 +41458,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41487,7 +41484,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41513,7 +41510,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41539,7 +41536,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41565,7 +41562,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41591,7 +41588,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41617,7 +41614,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41643,7 +41640,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41669,7 +41666,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41695,7 +41692,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41721,7 +41718,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41747,7 +41744,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41773,7 +41770,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41799,7 +41796,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41825,7 +41822,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41851,7 +41848,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41877,7 +41874,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41903,7 +41900,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41929,7 +41926,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41955,7 +41952,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41981,7 +41978,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42007,7 +42004,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42033,7 +42030,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42059,7 +42056,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42085,7 +42082,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42111,7 +42108,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42137,7 +42134,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42163,7 +42160,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42189,7 +42186,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42215,7 +42212,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42241,7 +42238,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42267,7 +42264,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42293,7 +42290,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42319,7 +42316,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42345,7 +42342,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42371,7 +42368,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42397,7 +42394,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42423,7 +42420,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42449,7 +42446,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42475,7 +42472,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42501,7 +42498,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42527,7 +42524,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42553,7 +42550,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42579,7 +42576,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42605,7 +42602,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42631,7 +42628,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42657,7 +42654,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42683,7 +42680,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42709,7 +42706,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42735,7 +42732,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42761,7 +42758,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42787,7 +42784,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42813,7 +42810,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42839,7 +42836,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42865,7 +42862,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42891,7 +42888,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42917,7 +42914,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42943,7 +42940,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42969,7 +42966,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42995,7 +42992,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43021,7 +43018,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43047,7 +43044,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43073,7 +43070,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43099,7 +43096,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43125,7 +43122,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43151,7 +43148,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43177,7 +43174,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43203,7 +43200,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43229,7 +43226,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43255,7 +43252,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43281,7 +43278,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43307,7 +43304,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43333,7 +43330,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43359,7 +43356,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43385,7 +43382,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43411,7 +43408,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43437,7 +43434,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43463,7 +43460,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43489,7 +43486,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43515,7 +43512,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43541,7 +43538,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43567,7 +43564,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43593,7 +43590,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43619,7 +43616,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43645,7 +43642,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43671,7 +43668,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43697,7 +43694,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43723,7 +43720,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43749,7 +43746,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43775,7 +43772,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43801,7 +43798,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43827,7 +43824,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43853,7 +43850,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43879,7 +43876,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43905,7 +43902,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43931,7 +43928,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43957,7 +43954,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43983,7 +43980,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44009,7 +44006,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44035,7 +44032,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44061,7 +44058,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44087,7 +44084,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44113,7 +44110,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44139,7 +44136,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44165,7 +44162,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44191,7 +44188,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44217,7 +44214,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44243,7 +44240,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44269,7 +44266,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44295,7 +44292,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44321,7 +44318,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44347,7 +44344,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44373,7 +44370,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44399,7 +44396,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44425,7 +44422,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44451,7 +44448,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44477,7 +44474,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44503,7 +44500,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44529,7 +44526,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44555,7 +44552,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44581,7 +44578,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44607,7 +44604,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44633,7 +44630,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44659,7 +44656,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44685,7 +44682,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44711,7 +44708,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44737,7 +44734,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44763,7 +44760,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44789,7 +44786,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44815,7 +44812,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44841,7 +44838,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44867,7 +44864,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44893,7 +44890,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44919,7 +44916,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44945,7 +44942,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44971,7 +44968,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44997,7 +44994,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45023,7 +45020,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45049,7 +45046,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45075,7 +45072,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45101,7 +45098,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45127,7 +45124,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45153,7 +45150,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45179,7 +45176,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45205,7 +45202,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45231,7 +45228,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45257,7 +45254,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45283,7 +45280,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45309,7 +45306,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45335,7 +45332,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45361,7 +45358,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45387,7 +45384,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45413,7 +45410,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45439,7 +45436,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45465,7 +45462,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45491,7 +45488,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45517,7 +45514,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45543,7 +45540,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45569,7 +45566,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45595,7 +45592,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45621,7 +45618,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45647,7 +45644,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45673,7 +45670,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45699,7 +45696,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45725,7 +45722,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45751,7 +45748,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45777,7 +45774,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45803,7 +45800,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45829,7 +45826,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45855,7 +45852,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45881,7 +45878,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45907,7 +45904,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45933,7 +45930,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45959,7 +45956,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45985,7 +45982,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46011,7 +46008,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46037,7 +46034,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46063,7 +46060,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46089,7 +46086,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46115,7 +46112,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46141,7 +46138,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46167,7 +46164,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46193,7 +46190,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46219,7 +46216,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46245,7 +46242,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46271,7 +46268,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46297,7 +46294,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46323,7 +46320,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46349,7 +46346,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46375,7 +46372,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46401,7 +46398,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46427,7 +46424,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46453,7 +46450,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46479,7 +46476,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46505,7 +46502,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46531,7 +46528,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46557,7 +46554,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46583,7 +46580,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46609,7 +46606,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46635,7 +46632,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46661,7 +46658,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46687,7 +46684,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46713,7 +46710,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46739,7 +46736,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46765,7 +46762,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46791,7 +46788,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46817,7 +46814,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46843,7 +46840,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46869,7 +46866,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46895,7 +46892,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46921,7 +46918,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46947,7 +46944,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46973,7 +46970,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46999,7 +46996,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47025,7 +47022,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47051,7 +47048,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47077,7 +47074,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47103,7 +47100,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47129,7 +47126,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47155,7 +47152,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47181,7 +47178,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47207,7 +47204,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47233,7 +47230,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47259,7 +47256,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47285,7 +47282,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47311,7 +47308,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47337,7 +47334,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47363,7 +47360,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47389,7 +47386,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47415,7 +47412,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47441,7 +47438,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47467,7 +47464,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47493,7 +47490,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47519,7 +47516,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47545,7 +47542,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47571,7 +47568,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47597,7 +47594,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47623,7 +47620,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47649,7 +47646,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47675,7 +47672,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47701,7 +47698,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47727,7 +47724,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47753,7 +47750,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47779,7 +47776,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47805,7 +47802,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47831,7 +47828,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47857,7 +47854,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47883,7 +47880,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47909,7 +47906,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47935,7 +47932,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47961,7 +47958,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47987,7 +47984,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48013,7 +48010,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48039,7 +48036,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48065,7 +48062,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48091,7 +48088,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48117,7 +48114,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48143,7 +48140,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48169,7 +48166,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48195,7 +48192,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48221,7 +48218,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48247,7 +48244,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48273,7 +48270,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48299,7 +48296,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48325,7 +48322,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48351,7 +48348,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48377,7 +48374,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48403,7 +48400,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48429,7 +48426,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48455,7 +48452,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48481,7 +48478,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48507,7 +48504,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48533,7 +48530,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48559,7 +48556,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48585,7 +48582,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48611,7 +48608,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48637,7 +48634,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48663,7 +48660,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48689,7 +48686,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48715,7 +48712,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48741,7 +48738,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48767,7 +48764,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48793,7 +48790,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48819,7 +48816,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48845,7 +48842,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48871,7 +48868,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48897,7 +48894,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48923,7 +48920,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48949,7 +48946,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48975,7 +48972,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49001,7 +48998,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49027,7 +49024,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49053,7 +49050,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49079,7 +49076,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49105,7 +49102,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49131,7 +49128,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49157,7 +49154,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49183,7 +49180,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49209,7 +49206,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49235,7 +49232,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49261,7 +49258,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49287,7 +49284,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49313,7 +49310,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49339,7 +49336,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49365,7 +49362,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49391,7 +49388,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49417,7 +49414,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49443,7 +49440,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49469,7 +49466,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49495,7 +49492,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49521,7 +49518,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49547,7 +49544,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49573,7 +49570,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49599,7 +49596,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49625,7 +49622,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49651,7 +49648,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49677,7 +49674,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49703,7 +49700,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49729,7 +49726,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49755,7 +49752,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49781,7 +49778,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49807,7 +49804,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49833,7 +49830,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49859,7 +49856,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49885,7 +49882,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49911,7 +49908,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49937,7 +49934,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49963,7 +49960,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49989,7 +49986,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50015,7 +50012,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50041,7 +50038,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50067,7 +50064,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50093,7 +50090,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50119,7 +50116,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50145,7 +50142,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50171,7 +50168,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50197,7 +50194,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50223,7 +50220,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50249,7 +50246,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50275,7 +50272,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50301,7 +50298,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50327,7 +50324,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50353,7 +50350,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50379,7 +50376,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50405,7 +50402,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50431,7 +50428,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50457,7 +50454,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50483,7 +50480,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50509,7 +50506,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50535,7 +50532,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50561,7 +50558,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50587,7 +50584,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50613,7 +50610,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50639,7 +50636,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50665,7 +50662,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50691,7 +50688,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50717,7 +50714,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50743,7 +50740,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50769,7 +50766,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50795,7 +50792,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50821,7 +50818,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50847,7 +50844,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50873,7 +50870,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50899,7 +50896,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50925,7 +50922,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50951,7 +50948,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50977,7 +50974,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51003,7 +51000,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51029,7 +51026,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51055,7 +51052,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51081,7 +51078,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51107,7 +51104,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51133,7 +51130,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51159,7 +51156,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51185,7 +51182,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51211,7 +51208,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51237,7 +51234,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51263,7 +51260,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51289,7 +51286,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51315,7 +51312,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51341,7 +51338,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51367,7 +51364,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51393,7 +51390,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51419,7 +51416,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51445,7 +51442,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51471,7 +51468,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51497,7 +51494,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51523,7 +51520,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1931" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51549,7 +51546,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1932" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51575,7 +51572,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1933" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51601,7 +51598,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1934" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51627,7 +51624,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1935" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -51653,7 +51650,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -51679,7 +51676,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -51705,7 +51702,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -51731,7 +51728,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -51757,7 +51754,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -51783,7 +51780,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1941" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -51809,7 +51806,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1942" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -51835,7 +51832,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1943" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -51861,7 +51858,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1944" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -51887,7 +51884,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1945" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -51913,7 +51910,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1946" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -51939,7 +51936,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1947" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -51965,7 +51962,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1948" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -51973,7 +51970,7 @@
     </row>
     <row r="1949">
       <c r="A1949" s="1" t="n">
-        <v>45986.6912847222</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B1949" t="n">
         <v>200</v>
@@ -51982,7 +51979,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="D1949" t="n">
-        <v>16.2999992370605</v>
+        <v>16.2000007629395</v>
       </c>
       <c r="E1949" t="n">
         <v>16.2999992370605</v>
@@ -51991,7 +51988,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118347167969</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256868362427</t>
+    <t xml:space="preserve">11.925687789917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502779006958</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577272415161</t>
@@ -56,31 +56,31 @@
     <t xml:space="preserve">11.3654928207397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699012756348</t>
+    <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007148742676</t>
+    <t xml:space="preserve">10.9007139205933</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729778289795</t>
+    <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314937591553</t>
+    <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653877258301</t>
+    <t xml:space="preserve">11.0653886795044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1962032318115</t>
+    <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732574462891</t>
+    <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192531585693</t>
+    <t xml:space="preserve">11.119252204895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194257736206</t>
+    <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
     <t xml:space="preserve">11.3116273880005</t>
@@ -89,94 +89,94 @@
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424757003784</t>
+    <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501005172729</t>
+    <t xml:space="preserve">11.3501024246216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102617263794</t>
+    <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
     <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963758468628</t>
+    <t xml:space="preserve">11.6963748931885</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657020568848</t>
+    <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579027175903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807781219482</t>
+    <t xml:space="preserve">11.0807771682739</t>
   </si>
   <si>
     <t xml:space="preserve">11.2751770019531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086175918579</t>
+    <t xml:space="preserve">10.8086185455322</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349035263062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0683460235596</t>
+    <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087789535522</t>
+    <t xml:space="preserve">10.1087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95325946807861</t>
+    <t xml:space="preserve">9.95326042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998023986816</t>
+    <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345386505127</t>
+    <t xml:space="preserve">9.11345291137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790134429932</t>
+    <t xml:space="preserve">9.09790229797363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85683727264404</t>
+    <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
     <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907295227051</t>
+    <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278921127319</t>
+    <t xml:space="preserve">12.0278940200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950798034668</t>
+    <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750165939331</t>
+    <t xml:space="preserve">11.9750175476074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028589248657</t>
+    <t xml:space="preserve">11.7028570175171</t>
   </si>
   <si>
     <t xml:space="preserve">11.5862169265747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5084581375122</t>
+    <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639776229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529376983643</t>
+    <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196584701538</t>
+    <t xml:space="preserve">11.1196575164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.886378288269</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198188781738</t>
+    <t xml:space="preserve">10.4198198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310201644897</t>
+    <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
     <t xml:space="preserve">9.67332363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40894222259521</t>
+    <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449378967285</t>
+    <t xml:space="preserve">9.42449188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64221954345703</t>
+    <t xml:space="preserve">9.64222145080566</t>
   </si>
   <si>
     <t xml:space="preserve">9.87550067901611</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420610427856</t>
+    <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">9.48670196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118057250977</t>
+    <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662033081055</t>
+    <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892475128174</t>
+    <t xml:space="preserve">9.47892570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29074573516846</t>
+    <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
     <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945487976074</t>
+    <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71842670440674</t>
+    <t xml:space="preserve">9.71842575073242</t>
   </si>
   <si>
     <t xml:space="preserve">10.3087787628174</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.349835395813</t>
+    <t xml:space="preserve">10.3498373031616</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0076913833618</t>
+    <t xml:space="preserve">10.0076923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6064424514771</t>
+    <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
     <t xml:space="preserve">10.6919794082642</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778904914856</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.257345199585</t>
+    <t xml:space="preserve">10.2573461532593</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885902404785</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">9.90963745117188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56193161010742</t>
+    <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344734191895</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.86651992797852</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">8.77959251403809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266700744629</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
     <t xml:space="preserve">8.64920234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037189483643</t>
+    <t xml:space="preserve">9.04037284851074</t>
   </si>
   <si>
     <t xml:space="preserve">9.82271289825439</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">11.300464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658313751221</t>
+    <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
     <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704187393188</t>
+    <t xml:space="preserve">10.1704196929932</t>
   </si>
   <si>
     <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6050510406494</t>
+    <t xml:space="preserve">10.605052947998</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500514984131</t>
+    <t xml:space="preserve">9.47500419616699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3880786895752</t>
+    <t xml:space="preserve">9.38807964324951</t>
   </si>
   <si>
     <t xml:space="preserve">9.21422672271729</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">9.30115222930908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725198745728</t>
+    <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
     <t xml:space="preserve">7.38876581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183935165405</t>
+    <t xml:space="preserve">7.30183839797974</t>
   </si>
   <si>
     <t xml:space="preserve">7.25837564468384</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4756932258606</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339906692505</t>
+    <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378923416138</t>
+    <t xml:space="preserve">7.95378875732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56585216522217</t>
+    <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
     <t xml:space="preserve">9.4772777557373</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85726928710938</t>
+    <t xml:space="preserve">8.85727024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76869678497314</t>
+    <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.03441429138184</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1229887008667</t>
+    <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8944416046143</t>
+    <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830141067505</t>
+    <t xml:space="preserve">10.9830150604248</t>
   </si>
   <si>
     <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972881317139</t>
+    <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
     <t xml:space="preserve">9.83157062530518</t>
@@ -452,19 +452,19 @@
     <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014122009277</t>
+    <t xml:space="preserve">9.92014312744141</t>
   </si>
   <si>
     <t xml:space="preserve">10.2744340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487316131592</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5144500732422</t>
+    <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.425877571106</t>
+    <t xml:space="preserve">11.4258785247803</t>
   </si>
   <si>
     <t xml:space="preserve">10.805869102478</t>
@@ -479,49 +479,49 @@
     <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401515960693</t>
+    <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4193992614746</t>
+    <t xml:space="preserve">10.4193983078003</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912097930908</t>
+    <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006050109863</t>
+    <t xml:space="preserve">10.6006059646606</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475887298584</t>
+    <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7818117141724</t>
+    <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78517436981201</t>
+    <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381916046143</t>
   </si>
   <si>
     <t xml:space="preserve">12.0502614974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.416036605835</t>
+    <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1442260742188</t>
+    <t xml:space="preserve">11.1442270278931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690547943115</t>
+    <t xml:space="preserve">11.8690557479858</t>
   </si>
   <si>
     <t xml:space="preserve">12.1408643722534</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844844818115</t>
+    <t xml:space="preserve">12.6844854354858</t>
   </si>
   <si>
     <t xml:space="preserve">12.5032787322998</t>
@@ -542,52 +542,52 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375017166138</t>
+    <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9562950134277</t>
+    <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281055450439</t>
+    <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0435380935669</t>
+    <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811246871948</t>
+    <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931926727295</t>
+    <t xml:space="preserve">15.4931945800781</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401744842529</t>
   </si>
   <si>
-    <t xml:space="preserve">15.402587890625</t>
+    <t xml:space="preserve">15.4025897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556060791016</t>
+    <t xml:space="preserve">15.8556051254272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462099075317</t>
+    <t xml:space="preserve">15.9462089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650032043457</t>
+    <t xml:space="preserve">15.7650012969971</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307802200317</t>
+    <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.221381187439</t>
+    <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871591567993</t>
+    <t xml:space="preserve">14.587158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8623313903809</t>
+    <t xml:space="preserve">13.8623304367065</t>
   </si>
   <si>
     <t xml:space="preserve">14.4965543746948</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495725631714</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999160766602</t>
+    <t xml:space="preserve">13.4999151229858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1341419219971</t>
+    <t xml:space="preserve">14.1341409683228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.40931224823</t>
+    <t xml:space="preserve">13.4093132019043</t>
   </si>
   <si>
     <t xml:space="preserve">12.5938816070557</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">13.0468988418579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5905208587646</t>
+    <t xml:space="preserve">13.5905199050903</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3187084197998</t>
+    <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
     <t xml:space="preserve">12.8656921386719</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119859695435</t>
+    <t xml:space="preserve">15.3119869232178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7264251708984</t>
+    <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230634689331</t>
+    <t xml:space="preserve">14.7230644226074</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512519836426</t>
+    <t xml:space="preserve">14.4512529373169</t>
   </si>
   <si>
     <t xml:space="preserve">14.1270265579224</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365261077881</t>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196626663208</t>
+    <t xml:space="preserve">14.2196636199951</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343894958496</t>
+    <t xml:space="preserve">14.0343885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6828441619873</t>
+    <t xml:space="preserve">14.682843208313</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -677,37 +677,37 @@
     <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586158752441</t>
+    <t xml:space="preserve">14.3586168289185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733436584473</t>
+    <t xml:space="preserve">14.1733446121216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564821243286</t>
+    <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491172790527</t>
+    <t xml:space="preserve">13.8491163253784</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880723953247</t>
+    <t xml:space="preserve">13.9880714416504</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248899459839</t>
+    <t xml:space="preserve">13.5248908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027982711792</t>
+    <t xml:space="preserve">13.8027992248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859357833862</t>
+    <t xml:space="preserve">13.3859367370605</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -725,76 +725,76 @@
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469816207886</t>
+    <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006645202637</t>
+    <t xml:space="preserve">13.200662612915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543445587158</t>
+    <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533876419067</t>
+    <t xml:space="preserve">15.0533885955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.404935836792</t>
+    <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512529373169</t>
+    <t xml:space="preserve">14.4512538909912</t>
   </si>
   <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144344329834</t>
+    <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555233001709</t>
+    <t xml:space="preserve">15.6555242538452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1923427581787</t>
+    <t xml:space="preserve">15.192343711853</t>
   </si>
   <si>
     <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407955169678</t>
+    <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944784164429</t>
+    <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702520370483</t>
+    <t xml:space="preserve">15.4702529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460237503052</t>
+    <t xml:space="preserve">15.1460256576538</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975709915161</t>
+    <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0166959762573</t>
+    <t xml:space="preserve">15.016695022583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -803,10 +803,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365251541138</t>
+    <t xml:space="preserve">14.5414838790894</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -827,13 +824,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968648910522</t>
+    <t xml:space="preserve">15.3968658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572036743164</t>
+    <t xml:space="preserve">16.1572017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720769882202</t>
+    <t xml:space="preserve">15.8720779418945</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -842,7 +839,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315673828125</t>
+    <t xml:space="preserve">14.7315683364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -854,7 +851,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522449493408</t>
+    <t xml:space="preserve">16.2522468566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -35322,7 +35319,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35348,7 +35345,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -35374,7 +35371,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1310" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -35400,7 +35397,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1311" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -35426,7 +35423,7 @@
         <v>16.5</v>
       </c>
       <c r="G1312" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -35452,7 +35449,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1313" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -35478,7 +35475,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1314" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -35504,7 +35501,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1315" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -35530,7 +35527,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1316" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -35556,7 +35553,7 @@
         <v>16.5</v>
       </c>
       <c r="G1317" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -35582,7 +35579,7 @@
         <v>16.5</v>
       </c>
       <c r="G1318" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -35608,7 +35605,7 @@
         <v>16.5</v>
       </c>
       <c r="G1319" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -35634,7 +35631,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -35660,7 +35657,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1321" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -35686,7 +35683,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1322" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -35712,7 +35709,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1323" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -35738,7 +35735,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -35764,7 +35761,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1325" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -35790,7 +35787,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1326" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -35816,7 +35813,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1327" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -35842,7 +35839,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1328" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -35868,7 +35865,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1329" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -35894,7 +35891,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -35920,7 +35917,7 @@
         <v>17</v>
       </c>
       <c r="G1331" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -35946,7 +35943,7 @@
         <v>16.5</v>
       </c>
       <c r="G1332" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -35972,7 +35969,7 @@
         <v>16.5</v>
       </c>
       <c r="G1333" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -35998,7 +35995,7 @@
         <v>16.5</v>
       </c>
       <c r="G1334" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36024,7 +36021,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36050,7 +36047,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36076,7 +36073,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1337" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36102,7 +36099,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36128,7 +36125,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1339" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36154,7 +36151,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1340" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36180,7 +36177,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1341" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36206,7 +36203,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1342" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36232,7 +36229,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1343" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36258,7 +36255,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36284,7 +36281,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1345" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -36310,7 +36307,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -36336,7 +36333,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -36362,7 +36359,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1348" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -36388,7 +36385,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1349" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -36414,7 +36411,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1350" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -36440,7 +36437,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -36518,7 +36515,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1354" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -36544,7 +36541,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -36570,7 +36567,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1356" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -36596,7 +36593,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -36648,7 +36645,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1359" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -36674,7 +36671,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -36726,7 +36723,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1362" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -36752,7 +36749,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1363" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -36778,7 +36775,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1364" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -36804,7 +36801,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1365" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -36830,7 +36827,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -36856,7 +36853,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1367" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -36882,7 +36879,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1368" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -36908,7 +36905,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -36934,7 +36931,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1370" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -36960,7 +36957,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1371" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -36986,7 +36983,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1372" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37012,7 +37009,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1373" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37116,7 +37113,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1377" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37142,7 +37139,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1378" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37168,7 +37165,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1379" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37194,7 +37191,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1380" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37220,7 +37217,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1381" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37246,7 +37243,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1382" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37272,7 +37269,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1383" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -37298,7 +37295,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -37324,7 +37321,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1385" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -37350,7 +37347,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1386" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -37376,7 +37373,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -37402,7 +37399,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1388" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -37428,7 +37425,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -37454,7 +37451,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1390" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -37480,7 +37477,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -37506,7 +37503,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1392" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -37532,7 +37529,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1393" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -37636,7 +37633,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1397" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -37662,7 +37659,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1398" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -37688,7 +37685,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1399" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -37714,7 +37711,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1400" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -37740,7 +37737,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1401" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -37766,7 +37763,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1402" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -37792,7 +37789,7 @@
         <v>15.5</v>
       </c>
       <c r="G1403" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -37818,7 +37815,7 @@
         <v>15.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -37844,7 +37841,7 @@
         <v>15.5</v>
       </c>
       <c r="G1405" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38182,7 +38179,7 @@
         <v>15.5</v>
       </c>
       <c r="G1418" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38208,7 +38205,7 @@
         <v>15.5</v>
       </c>
       <c r="G1419" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38234,7 +38231,7 @@
         <v>15.5</v>
       </c>
       <c r="G1420" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38390,7 +38387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1426" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -38416,7 +38413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1427" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -38442,7 +38439,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1428" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -38468,7 +38465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -38494,7 +38491,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1430" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -38520,7 +38517,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1431" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -38546,7 +38543,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1432" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -38572,7 +38569,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1433" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -38598,7 +38595,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -38624,7 +38621,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1435" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -38650,7 +38647,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1436" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -38676,7 +38673,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1437" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -38702,7 +38699,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1438" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -38728,7 +38725,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1439" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -38780,7 +38777,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1441" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -38806,7 +38803,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39014,7 +39011,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1450" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39040,7 +39037,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1451" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39066,7 +39063,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1452" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39092,7 +39089,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39118,7 +39115,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39144,7 +39141,7 @@
         <v>16.5</v>
       </c>
       <c r="G1455" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39170,7 +39167,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1456" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39196,7 +39193,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1457" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39222,7 +39219,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39248,7 +39245,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39274,7 +39271,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -39300,7 +39297,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39326,7 +39323,7 @@
         <v>16.5</v>
       </c>
       <c r="G1462" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39352,7 +39349,7 @@
         <v>16.5</v>
       </c>
       <c r="G1463" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39378,7 +39375,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1464" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39404,7 +39401,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1465" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39430,7 +39427,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1466" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -39456,7 +39453,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1467" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -39482,7 +39479,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -39508,7 +39505,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1469" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -39534,7 +39531,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1470" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -39560,7 +39557,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -39586,7 +39583,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -39612,7 +39609,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1473" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -39638,7 +39635,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1474" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -39664,7 +39661,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1475" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -39690,7 +39687,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -39716,7 +39713,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -39742,7 +39739,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1478" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -39768,7 +39765,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1479" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -39794,7 +39791,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1480" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -39820,7 +39817,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1481" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -39846,7 +39843,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1482" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -39872,7 +39869,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1483" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -39898,7 +39895,7 @@
         <v>17</v>
       </c>
       <c r="G1484" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -39924,7 +39921,7 @@
         <v>17</v>
       </c>
       <c r="G1485" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -39950,7 +39947,7 @@
         <v>17</v>
       </c>
       <c r="G1486" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -39976,7 +39973,7 @@
         <v>17</v>
       </c>
       <c r="G1487" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40002,7 +39999,7 @@
         <v>16.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40028,7 +40025,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1489" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40054,7 +40051,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40080,7 +40077,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1491" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40106,7 +40103,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1492" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40132,7 +40129,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40262,7 +40259,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1498" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40418,7 +40415,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40444,7 +40441,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1505" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40470,7 +40467,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40496,7 +40493,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40522,7 +40519,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40548,7 +40545,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40574,7 +40571,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1510" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -40600,7 +40597,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -40626,7 +40623,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -40678,7 +40675,7 @@
         <v>15.5</v>
       </c>
       <c r="G1514" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -40704,7 +40701,7 @@
         <v>15.5</v>
       </c>
       <c r="G1515" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -40886,7 +40883,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1522" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -40912,7 +40909,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1523" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -40938,7 +40935,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -40964,7 +40961,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1525" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -40990,7 +40987,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1526" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41016,7 +41013,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1527" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41042,7 +41039,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1528" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41068,7 +41065,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1529" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41094,7 +41091,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1530" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41120,7 +41117,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1531" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41146,7 +41143,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1532" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41172,7 +41169,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41198,7 +41195,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1534" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41224,7 +41221,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41250,7 +41247,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41276,7 +41273,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41302,7 +41299,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41328,7 +41325,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41354,7 +41351,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41380,7 +41377,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1541" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41406,7 +41403,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41432,7 +41429,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1543" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -41458,7 +41455,7 @@
         <v>18</v>
       </c>
       <c r="G1544" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -41484,7 +41481,7 @@
         <v>18</v>
       </c>
       <c r="G1545" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -41510,7 +41507,7 @@
         <v>17.5</v>
       </c>
       <c r="G1546" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -41536,7 +41533,7 @@
         <v>17.5</v>
       </c>
       <c r="G1547" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -41562,7 +41559,7 @@
         <v>17.5</v>
       </c>
       <c r="G1548" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -41588,7 +41585,7 @@
         <v>17.5</v>
       </c>
       <c r="G1549" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -41614,7 +41611,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -41640,7 +41637,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -41666,7 +41663,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1552" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -41692,7 +41689,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1553" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -41718,7 +41715,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1554" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -41744,7 +41741,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1555" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -41770,7 +41767,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1556" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -41796,7 +41793,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1557" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -41822,7 +41819,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1558" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -41848,7 +41845,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1559" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -41874,7 +41871,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1560" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -41900,7 +41897,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -41926,7 +41923,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1562" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -41952,7 +41949,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1563" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -41978,7 +41975,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1564" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42004,7 +42001,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1565" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42030,7 +42027,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1566" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42056,7 +42053,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1567" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42082,7 +42079,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1568" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42108,7 +42105,7 @@
         <v>15.5</v>
       </c>
       <c r="G1569" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42134,7 +42131,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1570" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42160,7 +42157,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1571" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42186,7 +42183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1572" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42212,7 +42209,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1573" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42238,7 +42235,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1574" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42264,7 +42261,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1575" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42290,7 +42287,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1576" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42316,7 +42313,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1577" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42342,7 +42339,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1578" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42368,7 +42365,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1579" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42394,7 +42391,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1580" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42420,7 +42417,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1581" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -42446,7 +42443,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1582" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -42472,7 +42469,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1583" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -42498,7 +42495,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1584" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -42524,7 +42521,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1585" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -42550,7 +42547,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -42576,7 +42573,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1587" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -42602,7 +42599,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1588" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -42628,7 +42625,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1589" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -42654,7 +42651,7 @@
         <v>15.5</v>
       </c>
       <c r="G1590" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -42680,7 +42677,7 @@
         <v>15</v>
       </c>
       <c r="G1591" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -42706,7 +42703,7 @@
         <v>15</v>
       </c>
       <c r="G1592" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -42732,7 +42729,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1593" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -42758,7 +42755,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1594" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -42784,7 +42781,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1595" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -42810,7 +42807,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1596" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -42836,7 +42833,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1597" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -42862,7 +42859,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1598" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -42888,7 +42885,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1599" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -42914,7 +42911,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1600" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -42940,7 +42937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -42966,7 +42963,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1602" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -42992,7 +42989,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1603" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43018,7 +43015,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43044,7 +43041,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1605" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43070,7 +43067,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1606" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43096,7 +43093,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1607" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43122,7 +43119,7 @@
         <v>15</v>
       </c>
       <c r="G1608" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43148,7 +43145,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1609" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43174,7 +43171,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1610" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43200,7 +43197,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1611" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43226,7 +43223,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1612" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43252,7 +43249,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1613" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43278,7 +43275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1614" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43304,7 +43301,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1615" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43330,7 +43327,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1616" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43356,7 +43353,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1617" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43382,7 +43379,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1618" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43408,7 +43405,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1619" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43434,7 +43431,7 @@
         <v>15</v>
       </c>
       <c r="G1620" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -43460,7 +43457,7 @@
         <v>15</v>
       </c>
       <c r="G1621" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -43486,7 +43483,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1622" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -43512,7 +43509,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1623" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -43538,7 +43535,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -43564,7 +43561,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1625" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -43590,7 +43587,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1626" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -43616,7 +43613,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1627" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -43642,7 +43639,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1628" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -43668,7 +43665,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1629" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -43694,7 +43691,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1630" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -43720,7 +43717,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1631" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -43746,7 +43743,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1632" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -43772,7 +43769,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1633" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -43798,7 +43795,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1634" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -43824,7 +43821,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1635" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -43850,7 +43847,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1636" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -43876,7 +43873,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1637" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -43902,7 +43899,7 @@
         <v>15</v>
       </c>
       <c r="G1638" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -43928,7 +43925,7 @@
         <v>15</v>
       </c>
       <c r="G1639" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -43954,7 +43951,7 @@
         <v>15</v>
       </c>
       <c r="G1640" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -43980,7 +43977,7 @@
         <v>15</v>
       </c>
       <c r="G1641" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44006,7 +44003,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1642" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44032,7 +44029,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1643" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44058,7 +44055,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1644" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44084,7 +44081,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1645" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44110,7 +44107,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44136,7 +44133,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1647" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44162,7 +44159,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1648" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44188,7 +44185,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1649" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44214,7 +44211,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1650" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44240,7 +44237,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1651" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44266,7 +44263,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1652" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44292,7 +44289,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1653" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44318,7 +44315,7 @@
         <v>15</v>
       </c>
       <c r="G1654" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44344,7 +44341,7 @@
         <v>15</v>
       </c>
       <c r="G1655" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44370,7 +44367,7 @@
         <v>15.5</v>
       </c>
       <c r="G1656" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44396,7 +44393,7 @@
         <v>15</v>
       </c>
       <c r="G1657" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44422,7 +44419,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1658" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44448,7 +44445,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1659" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -44474,7 +44471,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1660" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -44500,7 +44497,7 @@
         <v>15</v>
       </c>
       <c r="G1661" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -44526,7 +44523,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1662" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -44552,7 +44549,7 @@
         <v>15</v>
       </c>
       <c r="G1663" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -44578,7 +44575,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1664" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -44604,7 +44601,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1665" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -44630,7 +44627,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1666" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -44656,7 +44653,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1667" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -44682,7 +44679,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1668" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -44708,7 +44705,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1669" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -44734,7 +44731,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -44760,7 +44757,7 @@
         <v>15.5</v>
       </c>
       <c r="G1671" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -44786,7 +44783,7 @@
         <v>15.5</v>
       </c>
       <c r="G1672" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -44812,7 +44809,7 @@
         <v>15</v>
       </c>
       <c r="G1673" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -44838,7 +44835,7 @@
         <v>15.5</v>
       </c>
       <c r="G1674" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -44864,7 +44861,7 @@
         <v>15.5</v>
       </c>
       <c r="G1675" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -44890,7 +44887,7 @@
         <v>15.5</v>
       </c>
       <c r="G1676" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -44916,7 +44913,7 @@
         <v>15.5</v>
       </c>
       <c r="G1677" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -44942,7 +44939,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1678" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -44968,7 +44965,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1679" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -44994,7 +44991,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1680" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45020,7 +45017,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45046,7 +45043,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1682" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45072,7 +45069,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1683" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45098,7 +45095,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1684" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45124,7 +45121,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1685" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45150,7 +45147,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1686" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45176,7 +45173,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45202,7 +45199,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45228,7 +45225,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1689" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45254,7 +45251,7 @@
         <v>15</v>
       </c>
       <c r="G1690" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45280,7 +45277,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45306,7 +45303,7 @@
         <v>15.5</v>
       </c>
       <c r="G1692" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45332,7 +45329,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1693" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45358,7 +45355,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45384,7 +45381,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1695" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45410,7 +45407,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1696" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45436,7 +45433,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1697" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -45462,7 +45459,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1698" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -45488,7 +45485,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -45514,7 +45511,7 @@
         <v>15</v>
       </c>
       <c r="G1700" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -45540,7 +45537,7 @@
         <v>15</v>
       </c>
       <c r="G1701" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -45566,7 +45563,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -45592,7 +45589,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1703" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -45618,7 +45615,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1704" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -45644,7 +45641,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -45670,7 +45667,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1706" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -45696,7 +45693,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -45722,7 +45719,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1708" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -45748,7 +45745,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1709" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -45774,7 +45771,7 @@
         <v>14.5</v>
       </c>
       <c r="G1710" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -45800,7 +45797,7 @@
         <v>15</v>
       </c>
       <c r="G1711" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -45826,7 +45823,7 @@
         <v>15</v>
       </c>
       <c r="G1712" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -45852,7 +45849,7 @@
         <v>15</v>
       </c>
       <c r="G1713" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -45878,7 +45875,7 @@
         <v>15</v>
       </c>
       <c r="G1714" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -45904,7 +45901,7 @@
         <v>15</v>
       </c>
       <c r="G1715" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -45930,7 +45927,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1716" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -45956,7 +45953,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1717" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -45982,7 +45979,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1718" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46008,7 +46005,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46034,7 +46031,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1720" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46060,7 +46057,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1721" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46086,7 +46083,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1722" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46112,7 +46109,7 @@
         <v>15</v>
       </c>
       <c r="G1723" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46138,7 +46135,7 @@
         <v>15</v>
       </c>
       <c r="G1724" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46164,7 +46161,7 @@
         <v>15</v>
       </c>
       <c r="G1725" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46190,7 +46187,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1726" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46216,7 +46213,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1727" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46242,7 +46239,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1728" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46268,7 +46265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1729" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46294,7 +46291,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1730" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46320,7 +46317,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1731" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46346,7 +46343,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1732" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46372,7 +46369,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1733" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46398,7 +46395,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1734" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46424,7 +46421,7 @@
         <v>15</v>
       </c>
       <c r="G1735" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46450,7 +46447,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1736" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -46476,7 +46473,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1737" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -46502,7 +46499,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1738" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -46528,7 +46525,7 @@
         <v>15.5</v>
       </c>
       <c r="G1739" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -46554,7 +46551,7 @@
         <v>15.5</v>
       </c>
       <c r="G1740" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -46580,7 +46577,7 @@
         <v>15.5</v>
       </c>
       <c r="G1741" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -46606,7 +46603,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1742" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -46632,7 +46629,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1743" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -46658,7 +46655,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1744" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -46684,7 +46681,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1745" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -46710,7 +46707,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1746" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -46736,7 +46733,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1747" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -46762,7 +46759,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1748" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -46788,7 +46785,7 @@
         <v>15.5</v>
       </c>
       <c r="G1749" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -46814,7 +46811,7 @@
         <v>15.5</v>
       </c>
       <c r="G1750" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -46840,7 +46837,7 @@
         <v>15.5</v>
       </c>
       <c r="G1751" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -46866,7 +46863,7 @@
         <v>15.5</v>
       </c>
       <c r="G1752" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -46892,7 +46889,7 @@
         <v>15.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -46918,7 +46915,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1754" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -46944,7 +46941,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1755" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -46970,7 +46967,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1756" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -46996,7 +46993,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1757" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47022,7 +47019,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1758" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47048,7 +47045,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1759" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47074,7 +47071,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1760" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47100,7 +47097,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1761" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47126,7 +47123,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1762" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47152,7 +47149,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1763" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47178,7 +47175,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47204,7 +47201,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1765" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47230,7 +47227,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1766" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47256,7 +47253,7 @@
         <v>16</v>
       </c>
       <c r="G1767" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47282,7 +47279,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1768" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47308,7 +47305,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1769" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47334,7 +47331,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1770" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47360,7 +47357,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1771" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47386,7 +47383,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1772" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47412,7 +47409,7 @@
         <v>15.5</v>
       </c>
       <c r="G1773" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47438,7 +47435,7 @@
         <v>16</v>
       </c>
       <c r="G1774" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -47464,7 +47461,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -47490,7 +47487,7 @@
         <v>16</v>
       </c>
       <c r="G1776" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -47516,7 +47513,7 @@
         <v>16</v>
       </c>
       <c r="G1777" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -47542,7 +47539,7 @@
         <v>16</v>
       </c>
       <c r="G1778" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -47568,7 +47565,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1779" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -47594,7 +47591,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -47620,7 +47617,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1781" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -47646,7 +47643,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1782" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -47672,7 +47669,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1783" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -47698,7 +47695,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1784" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -47724,7 +47721,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1785" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -47750,7 +47747,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1786" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -47776,7 +47773,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1787" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -47802,7 +47799,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1788" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -47828,7 +47825,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1789" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -47854,7 +47851,7 @@
         <v>15</v>
       </c>
       <c r="G1790" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -47880,7 +47877,7 @@
         <v>15</v>
       </c>
       <c r="G1791" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -47906,7 +47903,7 @@
         <v>15</v>
       </c>
       <c r="G1792" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -47932,7 +47929,7 @@
         <v>15</v>
       </c>
       <c r="G1793" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -47958,7 +47955,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1794" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -47984,7 +47981,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48010,7 +48007,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1796" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48036,7 +48033,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1797" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48062,7 +48059,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1798" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48088,7 +48085,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1799" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48114,7 +48111,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48140,7 +48137,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48166,7 +48163,7 @@
         <v>15</v>
       </c>
       <c r="G1802" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48192,7 +48189,7 @@
         <v>15</v>
       </c>
       <c r="G1803" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48218,7 +48215,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1804" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48244,7 +48241,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1805" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48270,7 +48267,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1806" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48296,7 +48293,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1807" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48322,7 +48319,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1808" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48348,7 +48345,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48374,7 +48371,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48400,7 +48397,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48426,7 +48423,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1812" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -48452,7 +48449,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1813" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -48478,7 +48475,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1814" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -48504,7 +48501,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1815" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -48530,7 +48527,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1816" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -48556,7 +48553,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1817" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -48582,7 +48579,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1818" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -48608,7 +48605,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1819" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -48634,7 +48631,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1820" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -48660,7 +48657,7 @@
         <v>15</v>
       </c>
       <c r="G1821" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -48686,7 +48683,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1822" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -48712,7 +48709,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1823" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -48738,7 +48735,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1824" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -48764,7 +48761,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1825" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -48790,7 +48787,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1826" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -48816,7 +48813,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1827" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -48842,7 +48839,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1828" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -48868,7 +48865,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1829" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -48894,7 +48891,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1830" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -48920,7 +48917,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1831" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -48946,7 +48943,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1832" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -48972,7 +48969,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1833" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -48998,7 +48995,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1834" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49024,7 +49021,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49050,7 +49047,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1836" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49076,7 +49073,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1837" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49102,7 +49099,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1838" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49128,7 +49125,7 @@
         <v>14.5</v>
       </c>
       <c r="G1839" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49154,7 +49151,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1840" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49180,7 +49177,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1841" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49206,7 +49203,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49232,7 +49229,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1843" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49258,7 +49255,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1844" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49284,7 +49281,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1845" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49310,7 +49307,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1846" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49336,7 +49333,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1847" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49362,7 +49359,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1848" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49388,7 +49385,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1849" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49414,7 +49411,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1850" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49440,7 +49437,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1851" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -49466,7 +49463,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1852" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -49492,7 +49489,7 @@
         <v>14.5</v>
       </c>
       <c r="G1853" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -49518,7 +49515,7 @@
         <v>15</v>
       </c>
       <c r="G1854" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -49544,7 +49541,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1855" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -49570,7 +49567,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1856" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -49596,7 +49593,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1857" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -49622,7 +49619,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1858" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -49648,7 +49645,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -49674,7 +49671,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1860" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -49700,7 +49697,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1861" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -49726,7 +49723,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1862" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -49752,7 +49749,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1863" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -49778,7 +49775,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1864" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -49804,7 +49801,7 @@
         <v>15</v>
       </c>
       <c r="G1865" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -49830,7 +49827,7 @@
         <v>15</v>
       </c>
       <c r="G1866" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -49856,7 +49853,7 @@
         <v>15</v>
       </c>
       <c r="G1867" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -49882,7 +49879,7 @@
         <v>15</v>
       </c>
       <c r="G1868" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -49908,7 +49905,7 @@
         <v>15</v>
       </c>
       <c r="G1869" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -49934,7 +49931,7 @@
         <v>15</v>
       </c>
       <c r="G1870" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -49960,7 +49957,7 @@
         <v>15</v>
       </c>
       <c r="G1871" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -49986,7 +49983,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1872" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50012,7 +50009,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1873" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50038,7 +50035,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1874" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50064,7 +50061,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1875" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50090,7 +50087,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1876" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50116,7 +50113,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1877" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50142,7 +50139,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1878" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50168,7 +50165,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1879" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50194,7 +50191,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1880" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50220,7 +50217,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1881" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50246,7 +50243,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1882" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50272,7 +50269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1883" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50298,7 +50295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1884" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50324,7 +50321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1885" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50350,7 +50347,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1886" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50376,7 +50373,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1887" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50402,7 +50399,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1888" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50428,7 +50425,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1889" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -50454,7 +50451,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1890" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -50480,7 +50477,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1891" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -50506,7 +50503,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1892" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -50532,7 +50529,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1893" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -50558,7 +50555,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1894" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -50584,7 +50581,7 @@
         <v>15.5</v>
       </c>
       <c r="G1895" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -50610,7 +50607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1896" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -50636,7 +50633,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1897" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -50662,7 +50659,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1898" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -50688,7 +50685,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1899" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -50714,7 +50711,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1900" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -50740,7 +50737,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1901" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -50766,7 +50763,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -50792,7 +50789,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1903" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -50818,7 +50815,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -50844,7 +50841,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -50870,7 +50867,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -50896,7 +50893,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -50922,7 +50919,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1908" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -50948,7 +50945,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1909" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -50974,7 +50971,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1910" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51000,7 +50997,7 @@
         <v>15</v>
       </c>
       <c r="G1911" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51026,7 +51023,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51052,7 +51049,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1913" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51078,7 +51075,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1914" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51104,7 +51101,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51130,7 +51127,7 @@
         <v>15</v>
       </c>
       <c r="G1916" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51156,7 +51153,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1917" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51182,7 +51179,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1918" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51208,7 +51205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1919" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51234,7 +51231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1920" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51260,7 +51257,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1921" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51286,7 +51283,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1922" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51312,7 +51309,7 @@
         <v>16</v>
       </c>
       <c r="G1923" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51338,7 +51335,7 @@
         <v>16</v>
       </c>
       <c r="G1924" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51364,7 +51361,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1925" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51390,7 +51387,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1926" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51416,7 +51413,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1927" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51442,7 +51439,7 @@
         <v>16</v>
       </c>
       <c r="G1928" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -51468,7 +51465,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1929" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -51494,7 +51491,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1930" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -51520,7 +51517,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1931" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -51546,7 +51543,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1932" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -51572,7 +51569,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1933" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -51598,7 +51595,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1934" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -51624,7 +51621,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1935" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -51650,7 +51647,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -51676,7 +51673,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1937" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -51702,7 +51699,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1938" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -51728,7 +51725,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1939" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -51754,7 +51751,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -51780,7 +51777,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1941" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -51806,7 +51803,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1942" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -51832,7 +51829,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1943" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -51858,7 +51855,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1944" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -51884,7 +51881,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1945" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -51910,7 +51907,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1946" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -51936,7 +51933,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1947" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -51962,7 +51959,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1948" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -51988,7 +51985,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52014,7 +52011,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1950" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52040,7 +52037,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1951" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52066,7 +52063,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1952" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118347167969</t>
+    <t xml:space="preserve">11.9118356704712</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.925687789917</t>
+    <t xml:space="preserve">11.9256858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502779006958</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1577272415161</t>
+    <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654928207397</t>
+    <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
     <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007139205933</t>
+    <t xml:space="preserve">10.9007158279419</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314947128296</t>
+    <t xml:space="preserve">10.9314937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653886795044</t>
+    <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
     <t xml:space="preserve">11.1962022781372</t>
@@ -77,46 +77,46 @@
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.119252204895</t>
+    <t xml:space="preserve">11.1192531585693</t>
   </si>
   <si>
     <t xml:space="preserve">11.6194267272949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116273880005</t>
+    <t xml:space="preserve">11.3116283416748</t>
   </si>
   <si>
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424776077271</t>
+    <t xml:space="preserve">11.5424766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501024246216</t>
+    <t xml:space="preserve">11.3501014709473</t>
   </si>
   <si>
     <t xml:space="preserve">11.8102626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.773325920105</t>
+    <t xml:space="preserve">11.7733268737793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6963748931885</t>
+    <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
     <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579027175903</t>
+    <t xml:space="preserve">11.657901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807771682739</t>
+    <t xml:space="preserve">11.0807781219482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2751770019531</t>
+    <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086185455322</t>
+    <t xml:space="preserve">10.8086175918579</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349035263062</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.71998119354248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345291137695</t>
+    <t xml:space="preserve">9.11345386505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.09790229797363</t>
@@ -143,55 +143,55 @@
     <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5178050994873</t>
+    <t xml:space="preserve">9.51780605316162</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2642993927002</t>
+    <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
     <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278940200806</t>
+    <t xml:space="preserve">12.0278930664062</t>
   </si>
   <si>
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750175476074</t>
+    <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862169265747</t>
+    <t xml:space="preserve">11.5862159729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639776229858</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1196575164795</t>
+    <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
     <t xml:space="preserve">10.886378288269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641380310059</t>
+    <t xml:space="preserve">10.9641370773315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.497579574585</t>
+    <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310192108154</t>
+    <t xml:space="preserve">10.0310182571411</t>
   </si>
   <si>
     <t xml:space="preserve">9.67332363128662</t>
@@ -200,46 +200,46 @@
     <t xml:space="preserve">9.4089412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42449188232422</t>
+    <t xml:space="preserve">9.42449283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222145080566</t>
+    <t xml:space="preserve">9.64222049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550067901611</t>
+    <t xml:space="preserve">9.87550163269043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476602554321</t>
+    <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342059135437</t>
+    <t xml:space="preserve">10.3420600891113</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79773998260498</t>
+    <t xml:space="preserve">9.79773902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670196533203</t>
+    <t xml:space="preserve">9.48670291900635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118152618408</t>
+    <t xml:space="preserve">9.33118057250977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662128448486</t>
+    <t xml:space="preserve">9.83662033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892570495605</t>
+    <t xml:space="preserve">9.47892665863037</t>
   </si>
   <si>
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945678710938</t>
+    <t xml:space="preserve">9.09945583343506</t>
   </si>
   <si>
     <t xml:space="preserve">9.71842575073242</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498373031616</t>
+    <t xml:space="preserve">10.3498363494873</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353723526001</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.7789058685303</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">9.64885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90963745117188</t>
+    <t xml:space="preserve">9.90963840484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95344543457031</t>
+    <t xml:space="preserve">8.953444480896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651992797852</t>
+    <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
     <t xml:space="preserve">8.77959251403809</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920234680176</t>
+    <t xml:space="preserve">8.64920330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037284851074</t>
+    <t xml:space="preserve">9.04037094116211</t>
   </si>
   <si>
     <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.126612663269</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
     <t xml:space="preserve">11.300464630127</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">10.8658323287964</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527587890625</t>
+    <t xml:space="preserve">10.9527597427368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1704196929932</t>
+    <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99656581878662</t>
+    <t xml:space="preserve">9.9965648651123</t>
   </si>
   <si>
     <t xml:space="preserve">10.605052947998</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">10.4311981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47500419616699</t>
+    <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38807964324951</t>
+    <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422672271729</t>
+    <t xml:space="preserve">9.21422576904297</t>
   </si>
   <si>
     <t xml:space="preserve">9.12729835510254</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442726135254</t>
+    <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
     <t xml:space="preserve">9.30115222930908</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876581192017</t>
+    <t xml:space="preserve">7.38876628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183839797974</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837564468384</t>
+    <t xml:space="preserve">7.25837659835815</t>
   </si>
   <si>
     <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569274902344</t>
+    <t xml:space="preserve">7.47569227218628</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339859008789</t>
+    <t xml:space="preserve">7.82339954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378875732422</t>
+    <t xml:space="preserve">7.95378971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3449592590332</t>
+    <t xml:space="preserve">8.34496021270752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573863983154</t>
+    <t xml:space="preserve">8.60573959350586</t>
   </si>
   <si>
     <t xml:space="preserve">10.0087146759033</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38870620727539</t>
+    <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584274291992</t>
+    <t xml:space="preserve">8.94584178924561</t>
   </si>
   <si>
     <t xml:space="preserve">8.85727024078369</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441429138184</t>
+    <t xml:space="preserve">9.03441524505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72441101074219</t>
+    <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
     <t xml:space="preserve">9.21156024932861</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50297927856445</t>
+    <t xml:space="preserve">8.50298023223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.41440677642822</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.071587562561</t>
+    <t xml:space="preserve">11.0715866088867</t>
   </si>
   <si>
     <t xml:space="preserve">10.8944425582886</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">10.0972871780396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83157062530518</t>
+    <t xml:space="preserve">9.83156967163086</t>
   </si>
   <si>
     <t xml:space="preserve">9.74299716949463</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">10.2744340896606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487325668335</t>
+    <t xml:space="preserve">11.2487316131592</t>
   </si>
   <si>
     <t xml:space="preserve">11.5144510269165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4258785247803</t>
+    <t xml:space="preserve">11.425877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.805869102478</t>
+    <t xml:space="preserve">10.8058700561523</t>
   </si>
   <si>
     <t xml:space="preserve">10.6287240982056</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630056381226</t>
+    <t xml:space="preserve">10.3630046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">10.540150642395</t>
+    <t xml:space="preserve">10.5401496887207</t>
   </si>
   <si>
     <t xml:space="preserve">10.4193983078003</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">10.6912088394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006059646606</t>
+    <t xml:space="preserve">10.6006050109863</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">11.1442270278931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8690557479858</t>
+    <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
     <t xml:space="preserve">12.1408643722534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878471374512</t>
+    <t xml:space="preserve">11.6878480911255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314682006836</t>
+    <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
     <t xml:space="preserve">12.6844854354858</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375026702881</t>
+    <t xml:space="preserve">13.1375017166138</t>
   </si>
   <si>
     <t xml:space="preserve">12.9562959671021</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153476715088</t>
+    <t xml:space="preserve">14.3153467178345</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931945800781</t>
+    <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0401744842529</t>
+    <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4025897979736</t>
+    <t xml:space="preserve">15.402587890625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556051254272</t>
+    <t xml:space="preserve">15.8556070327759</t>
   </si>
   <si>
     <t xml:space="preserve">15.9462089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7650012969971</t>
+    <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307792663574</t>
+    <t xml:space="preserve">15.1307802200317</t>
   </si>
   <si>
     <t xml:space="preserve">15.2213821411133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.587158203125</t>
+    <t xml:space="preserve">14.5871572494507</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495706558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999151229858</t>
+    <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
     <t xml:space="preserve">14.1341409683228</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">14.2247438430786</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3119869232178</t>
+    <t xml:space="preserve">15.3119850158691</t>
   </si>
   <si>
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230644226074</t>
+    <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118356704712</t>
+    <t xml:space="preserve">11.9118366241455</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9256858825684</t>
+    <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502769470215</t>
+    <t xml:space="preserve">11.8502759933472</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">11.3654918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699003219604</t>
+    <t xml:space="preserve">10.7699012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9007158279419</t>
+    <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.7729787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314937591553</t>
+    <t xml:space="preserve">10.9314947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653877258301</t>
+    <t xml:space="preserve">11.0653896331787</t>
   </si>
   <si>
     <t xml:space="preserve">11.1962022781372</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">11.5732564926147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192531585693</t>
+    <t xml:space="preserve">11.1192541122437</t>
   </si>
   <si>
     <t xml:space="preserve">11.6194267272949</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">11.6948375701904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5424766540527</t>
+    <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501014709473</t>
+    <t xml:space="preserve">11.3501005172729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102626800537</t>
+    <t xml:space="preserve">11.8102617263794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733268737793</t>
+    <t xml:space="preserve">11.7733249664307</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657011032104</t>
+    <t xml:space="preserve">11.9657020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.657901763916</t>
+    <t xml:space="preserve">11.6579027175903</t>
   </si>
   <si>
     <t xml:space="preserve">11.0807781219482</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">11.2751779556274</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8086175918579</t>
+    <t xml:space="preserve">10.8086194992065</t>
   </si>
   <si>
     <t xml:space="preserve">10.5349035263062</t>
@@ -125,16 +125,16 @@
     <t xml:space="preserve">10.0683450698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1087799072266</t>
+    <t xml:space="preserve">10.1087789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95326042175293</t>
+    <t xml:space="preserve">9.95325946807861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71998119354248</t>
+    <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345386505127</t>
+    <t xml:space="preserve">9.11345291137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.09790229797363</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">9.85683822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51780605316162</t>
+    <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
     <t xml:space="preserve">10.2643003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907304763794</t>
+    <t xml:space="preserve">11.2907295227051</t>
   </si>
   <si>
     <t xml:space="preserve">12.0278930664062</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">11.6950807571411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750165939331</t>
+    <t xml:space="preserve">11.9750156402588</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7028570175171</t>
+    <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5862159729004</t>
+    <t xml:space="preserve">11.586217880249</t>
   </si>
   <si>
     <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639766693115</t>
+    <t xml:space="preserve">11.6639776229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3529367446899</t>
+    <t xml:space="preserve">11.3529376983643</t>
   </si>
   <si>
     <t xml:space="preserve">11.1196584701538</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">10.4975786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198188781738</t>
+    <t xml:space="preserve">10.4198198318481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310182571411</t>
+    <t xml:space="preserve">10.0310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332363128662</t>
+    <t xml:space="preserve">9.67332458496094</t>
   </si>
   <si>
     <t xml:space="preserve">9.4089412689209</t>
@@ -203,55 +203,55 @@
     <t xml:space="preserve">9.42449283599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64222049713135</t>
+    <t xml:space="preserve">9.64222145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87550163269043</t>
+    <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
     <t xml:space="preserve">10.1476593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420600891113</t>
+    <t xml:space="preserve">10.342059135437</t>
   </si>
   <si>
     <t xml:space="preserve">10.3887157440186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79773902893066</t>
+    <t xml:space="preserve">9.7977409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670291900635</t>
+    <t xml:space="preserve">9.48670101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33118057250977</t>
+    <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83662033081055</t>
+    <t xml:space="preserve">9.83661937713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892665863037</t>
+    <t xml:space="preserve">9.47892475128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815227508545</t>
+    <t xml:space="preserve">8.97815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09945583343506</t>
+    <t xml:space="preserve">9.09945678710938</t>
   </si>
   <si>
     <t xml:space="preserve">9.71842575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087787628174</t>
+    <t xml:space="preserve">10.3087797164917</t>
   </si>
   <si>
     <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498363494873</t>
+    <t xml:space="preserve">10.3498344421387</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353713989258</t>
+    <t xml:space="preserve">10.4353723526001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7789058685303</t>
+    <t xml:space="preserve">10.778904914856</t>
   </si>
   <si>
     <t xml:space="preserve">10.5181255340576</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834932327271</t>
+    <t xml:space="preserve">10.0834922790527</t>
   </si>
   <si>
     <t xml:space="preserve">10.2573461532593</t>
@@ -287,46 +287,46 @@
     <t xml:space="preserve">9.56193256378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.953444480896</t>
+    <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8665189743042</t>
+    <t xml:space="preserve">8.86651992797852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959251403809</t>
+    <t xml:space="preserve">8.77959156036377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266605377197</t>
+    <t xml:space="preserve">8.69266700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920330047607</t>
+    <t xml:space="preserve">8.64920139312744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04037094116211</t>
+    <t xml:space="preserve">9.04037189483643</t>
   </si>
   <si>
     <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266117095947</t>
+    <t xml:space="preserve">11.1266107559204</t>
   </si>
   <si>
-    <t xml:space="preserve">11.300464630127</t>
+    <t xml:space="preserve">11.3004655838013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658323287964</t>
+    <t xml:space="preserve">10.8658332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527597427368</t>
+    <t xml:space="preserve">10.9527587890625</t>
   </si>
   <si>
     <t xml:space="preserve">10.1704187393188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9965648651123</t>
+    <t xml:space="preserve">9.99656581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.605052947998</t>
+    <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
     <t xml:space="preserve">10.4311981201172</t>
@@ -338,58 +338,58 @@
     <t xml:space="preserve">9.3880786895752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422576904297</t>
+    <t xml:space="preserve">9.21422672271729</t>
   </si>
   <si>
     <t xml:space="preserve">9.12729835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578548431396</t>
+    <t xml:space="preserve">9.73578453063965</t>
   </si>
   <si>
     <t xml:space="preserve">10.3442716598511</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30115222930908</t>
+    <t xml:space="preserve">9.3011531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725246429443</t>
+    <t xml:space="preserve">7.99725198745728</t>
   </si>
   <si>
     <t xml:space="preserve">7.38876628875732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183935165405</t>
+    <t xml:space="preserve">7.30183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25837659835815</t>
+    <t xml:space="preserve">7.258376121521</t>
   </si>
   <si>
     <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47569227218628</t>
+    <t xml:space="preserve">7.4756932258606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339954376221</t>
+    <t xml:space="preserve">7.82339906692505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378971099854</t>
+    <t xml:space="preserve">7.95378923416138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34496021270752</t>
+    <t xml:space="preserve">8.3449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60573959350586</t>
+    <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087146759033</t>
+    <t xml:space="preserve">10.0087156295776</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4772777557373</t>
+    <t xml:space="preserve">9.47727966308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
@@ -413,37 +413,37 @@
     <t xml:space="preserve">8.7244119644165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21156024932861</t>
+    <t xml:space="preserve">9.2115592956543</t>
   </si>
   <si>
     <t xml:space="preserve">9.12298774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50298023223877</t>
+    <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440677642822</t>
+    <t xml:space="preserve">8.41440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30013275146484</t>
+    <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858606338501</t>
+    <t xml:space="preserve">10.1858596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0715866088867</t>
+    <t xml:space="preserve">11.071587562561</t>
   </si>
   <si>
     <t xml:space="preserve">10.8944425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9830150604248</t>
+    <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
     <t xml:space="preserve">10.4515781402588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972871780396</t>
+    <t xml:space="preserve">10.0972881317139</t>
   </si>
   <si>
     <t xml:space="preserve">9.83156967163086</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">9.74299716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92014312744141</t>
+    <t xml:space="preserve">9.92014217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744340896606</t>
+    <t xml:space="preserve">10.2744331359863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2487316131592</t>
+    <t xml:space="preserve">11.2487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">11.5144510269165</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">11.425877571106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8058700561523</t>
+    <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
     <t xml:space="preserve">10.6287240982056</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">10.7172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3630046844482</t>
+    <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401496887207</t>
+    <t xml:space="preserve">10.5401515960693</t>
   </si>
   <si>
     <t xml:space="preserve">10.4193983078003</t>
@@ -497,43 +497,43 @@
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475877761841</t>
+    <t xml:space="preserve">10.1475887298584</t>
   </si>
   <si>
     <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.963020324707</t>
+    <t xml:space="preserve">10.9630193710327</t>
   </si>
   <si>
     <t xml:space="preserve">9.7851734161377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381916046143</t>
+    <t xml:space="preserve">10.2381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502614974976</t>
+    <t xml:space="preserve">12.0502605438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1442270278931</t>
+    <t xml:space="preserve">11.1442260742188</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1408643722534</t>
+    <t xml:space="preserve">12.1408634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6878480911255</t>
+    <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314691543579</t>
+    <t xml:space="preserve">12.2314682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6844854354858</t>
+    <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
     <t xml:space="preserve">12.5032787322998</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">12.775089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1375017166138</t>
+    <t xml:space="preserve">13.1375026702881</t>
   </si>
   <si>
     <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281064987183</t>
+    <t xml:space="preserve">13.2281055450439</t>
   </si>
   <si>
     <t xml:space="preserve">14.0435371398926</t>
@@ -557,34 +557,34 @@
     <t xml:space="preserve">13.6811237335205</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153467178345</t>
+    <t xml:space="preserve">14.3153486251831</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931926727295</t>
+    <t xml:space="preserve">15.4931917190552</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.402587890625</t>
+    <t xml:space="preserve">15.4025897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556070327759</t>
+    <t xml:space="preserve">15.8556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462089538574</t>
+    <t xml:space="preserve">15.9462099075317</t>
   </si>
   <si>
     <t xml:space="preserve">15.7650032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1307802200317</t>
+    <t xml:space="preserve">15.1307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2213821411133</t>
+    <t xml:space="preserve">15.221381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871572494507</t>
+    <t xml:space="preserve">14.5871591567993</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495706558228</t>
+    <t xml:space="preserve">14.9495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999160766602</t>
+    <t xml:space="preserve">13.4999151229858</t>
   </si>
   <si>
     <t xml:space="preserve">14.1341409683228</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">12.5938816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468988418579</t>
+    <t xml:space="preserve">13.0468997955322</t>
   </si>
   <si>
     <t xml:space="preserve">13.5905199050903</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656921386719</t>
+    <t xml:space="preserve">12.8656911849976</t>
   </si>
   <si>
     <t xml:space="preserve">13.9529333114624</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230634689331</t>
+    <t xml:space="preserve">14.7230625152588</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365251541138</t>
+    <t xml:space="preserve">14.6365261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2196636199951</t>
+    <t xml:space="preserve">14.2196626663208</t>
   </si>
   <si>
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343885421753</t>
+    <t xml:space="preserve">14.0343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">14.682843208313</t>
+    <t xml:space="preserve">14.6828441619873</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -677,37 +677,37 @@
     <t xml:space="preserve">15.3776159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3586168289185</t>
+    <t xml:space="preserve">14.3586158752441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1733446121216</t>
+    <t xml:space="preserve">14.1733436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564811706543</t>
+    <t xml:space="preserve">13.7564821243286</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8491163253784</t>
+    <t xml:space="preserve">13.8491172790527</t>
   </si>
   <si>
     <t xml:space="preserve">14.0807075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9880714416504</t>
+    <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248908996582</t>
+    <t xml:space="preserve">13.5248899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027992248535</t>
+    <t xml:space="preserve">13.8027982711792</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859367370605</t>
+    <t xml:space="preserve">13.3859357833862</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -725,76 +725,73 @@
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469825744629</t>
+    <t xml:space="preserve">13.2469816207886</t>
   </si>
   <si>
-    <t xml:space="preserve">13.200662612915</t>
+    <t xml:space="preserve">13.2006645202637</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543455123901</t>
+    <t xml:space="preserve">13.1543445587158</t>
   </si>
   <si>
     <t xml:space="preserve">13.9417533874512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0533885955811</t>
+    <t xml:space="preserve">15.0533876419067</t>
   </si>
   <si>
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4049348831177</t>
+    <t xml:space="preserve">14.404935836792</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4512538909912</t>
-  </si>
-  <si>
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144334793091</t>
+    <t xml:space="preserve">14.9144344329834</t>
   </si>
   <si>
     <t xml:space="preserve">15.2849788665771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555242538452</t>
+    <t xml:space="preserve">15.6555233001709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628871917725</t>
+    <t xml:space="preserve">15.5628862380981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.192343711853</t>
+    <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
     <t xml:space="preserve">15.5165700912476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407974243164</t>
+    <t xml:space="preserve">15.8407955169678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944774627686</t>
+    <t xml:space="preserve">15.7944784164429</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4702529907227</t>
+    <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460256576538</t>
+    <t xml:space="preserve">15.1460237503052</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975700378418</t>
+    <t xml:space="preserve">14.4975709915161</t>
   </si>
   <si>
-    <t xml:space="preserve">15.016695022583</t>
+    <t xml:space="preserve">15.0166959762573</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -803,7 +800,10 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5414838790894</t>
+    <t xml:space="preserve">14.541482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968658447266</t>
+    <t xml:space="preserve">15.3968648910522</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572017669678</t>
+    <t xml:space="preserve">16.1572036743164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720779418945</t>
+    <t xml:space="preserve">15.8720769882202</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315683364868</t>
+    <t xml:space="preserve">14.7315673828125</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522468566895</t>
+    <t xml:space="preserve">16.2522449493408</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -33317,7 +33317,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33343,7 +33343,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33369,7 +33369,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33395,7 +33395,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33447,7 +33447,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33473,7 +33473,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33499,7 +33499,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33525,7 +33525,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33551,7 +33551,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33577,7 +33577,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33603,7 +33603,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33629,7 +33629,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33655,7 +33655,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33681,7 +33681,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33707,7 +33707,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33733,7 +33733,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33759,7 +33759,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33785,7 +33785,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33811,7 +33811,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33837,7 +33837,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33889,7 +33889,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33915,7 +33915,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33941,7 +33941,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33967,7 +33967,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33993,7 +33993,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34019,7 +34019,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34045,7 +34045,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34409,7 +34409,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -34435,7 +34435,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -34461,7 +34461,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -34747,7 +34747,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1286" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -34773,7 +34773,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -34799,7 +34799,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -34903,7 +34903,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35059,7 +35059,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35111,7 +35111,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1300" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35137,7 +35137,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1301" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35163,7 +35163,7 @@
         <v>16</v>
       </c>
       <c r="G1302" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35189,7 +35189,7 @@
         <v>16</v>
       </c>
       <c r="G1303" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35215,7 +35215,7 @@
         <v>16</v>
       </c>
       <c r="G1304" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35241,7 +35241,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1305" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35267,7 +35267,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -35293,7 +35293,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -35319,7 +35319,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -35345,7 +35345,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1309" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36463,7 +36463,7 @@
         <v>16</v>
       </c>
       <c r="G1352" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -36489,7 +36489,7 @@
         <v>16</v>
       </c>
       <c r="G1353" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -36619,7 +36619,7 @@
         <v>16</v>
       </c>
       <c r="G1358" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -36697,7 +36697,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1361" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37035,7 +37035,7 @@
         <v>16</v>
       </c>
       <c r="G1374" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37061,7 +37061,7 @@
         <v>16</v>
       </c>
       <c r="G1375" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37087,7 +37087,7 @@
         <v>16</v>
       </c>
       <c r="G1376" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37555,7 +37555,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -37581,7 +37581,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -37607,7 +37607,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -37867,7 +37867,7 @@
         <v>16</v>
       </c>
       <c r="G1406" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -37893,7 +37893,7 @@
         <v>16</v>
       </c>
       <c r="G1407" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -37919,7 +37919,7 @@
         <v>16</v>
       </c>
       <c r="G1408" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -37945,7 +37945,7 @@
         <v>16</v>
       </c>
       <c r="G1409" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -37971,7 +37971,7 @@
         <v>16</v>
       </c>
       <c r="G1410" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -37997,7 +37997,7 @@
         <v>16</v>
       </c>
       <c r="G1411" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38023,7 +38023,7 @@
         <v>16</v>
       </c>
       <c r="G1412" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38049,7 +38049,7 @@
         <v>16</v>
       </c>
       <c r="G1413" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38075,7 +38075,7 @@
         <v>16</v>
       </c>
       <c r="G1414" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38101,7 +38101,7 @@
         <v>16</v>
       </c>
       <c r="G1415" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38127,7 +38127,7 @@
         <v>16</v>
       </c>
       <c r="G1416" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38153,7 +38153,7 @@
         <v>16</v>
       </c>
       <c r="G1417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38257,7 +38257,7 @@
         <v>16</v>
       </c>
       <c r="G1421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38283,7 +38283,7 @@
         <v>16</v>
       </c>
       <c r="G1422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38309,7 +38309,7 @@
         <v>16</v>
       </c>
       <c r="G1423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38335,7 +38335,7 @@
         <v>16</v>
       </c>
       <c r="G1424" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38361,7 +38361,7 @@
         <v>16</v>
       </c>
       <c r="G1425" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -38751,7 +38751,7 @@
         <v>16</v>
       </c>
       <c r="G1440" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -38829,7 +38829,7 @@
         <v>16</v>
       </c>
       <c r="G1443" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -38855,7 +38855,7 @@
         <v>16</v>
       </c>
       <c r="G1444" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -38881,7 +38881,7 @@
         <v>16</v>
       </c>
       <c r="G1445" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -38907,7 +38907,7 @@
         <v>16</v>
       </c>
       <c r="G1446" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -38933,7 +38933,7 @@
         <v>16</v>
       </c>
       <c r="G1447" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -38959,7 +38959,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1448" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -38985,7 +38985,7 @@
         <v>16</v>
       </c>
       <c r="G1449" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40155,7 +40155,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1494" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40181,7 +40181,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1495" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40207,7 +40207,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1496" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40233,7 +40233,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1497" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40285,7 +40285,7 @@
         <v>16</v>
       </c>
       <c r="G1499" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40311,7 +40311,7 @@
         <v>16</v>
       </c>
       <c r="G1500" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40337,7 +40337,7 @@
         <v>16</v>
       </c>
       <c r="G1501" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40363,7 +40363,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40389,7 +40389,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1503" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40415,7 +40415,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1504" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -40441,7 +40441,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1505" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -40467,7 +40467,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1506" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -40493,7 +40493,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1507" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -40519,7 +40519,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1508" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -40545,7 +40545,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1509" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -40571,7 +40571,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1510" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -40597,7 +40597,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1511" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -40623,7 +40623,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1512" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -40649,7 +40649,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1513" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -40727,7 +40727,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1516" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -40753,7 +40753,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1517" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -40779,7 +40779,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1518" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -40805,7 +40805,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1519" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -40831,7 +40831,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1520" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -40857,7 +40857,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1521" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>

--- a/data/FVI.MI.xlsx
+++ b/data/FVI.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9118366241455</t>
+    <t xml:space="preserve">11.9118347167969</t>
   </si>
   <si>
     <t xml:space="preserve">FVI.MI</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">11.9256868362427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502759933472</t>
+    <t xml:space="preserve">11.8502769470215</t>
   </si>
   <si>
     <t xml:space="preserve">11.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3654918670654</t>
+    <t xml:space="preserve">11.3654909133911</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7699012756348</t>
+    <t xml:space="preserve">10.7699003219604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9007148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7729787826538</t>
+    <t xml:space="preserve">10.7729778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314947128296</t>
+    <t xml:space="preserve">10.9314956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0653896331787</t>
+    <t xml:space="preserve">11.0653877258301</t>
   </si>
   <si>
     <t xml:space="preserve">11.1962022781372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5732564926147</t>
+    <t xml:space="preserve">11.5732574462891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1192541122437</t>
+    <t xml:space="preserve">11.1192512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6194267272949</t>
+    <t xml:space="preserve">11.6194257736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3116283416748</t>
+    <t xml:space="preserve">11.3116273880005</t>
   </si>
   <si>
     <t xml:space="preserve">11.6948375701904</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">11.5424776077271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3501005172729</t>
+    <t xml:space="preserve">11.3501033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8102617263794</t>
+    <t xml:space="preserve">11.810263633728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7733249664307</t>
+    <t xml:space="preserve">11.773325920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6963758468628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9657020568848</t>
+    <t xml:space="preserve">11.9657011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6579027175903</t>
+    <t xml:space="preserve">11.657901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0807781219482</t>
+    <t xml:space="preserve">11.0807790756226</t>
   </si>
   <si>
     <t xml:space="preserve">11.2751779556274</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">10.8086194992065</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5349035263062</t>
+    <t xml:space="preserve">10.5349044799805</t>
   </si>
   <si>
     <t xml:space="preserve">10.0683450698853</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">9.71998023986816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11345291137695</t>
+    <t xml:space="preserve">9.11345481872559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09790229797363</t>
+    <t xml:space="preserve">9.09790134429932</t>
   </si>
   <si>
     <t xml:space="preserve">9.85683822631836</t>
@@ -146,31 +146,31 @@
     <t xml:space="preserve">9.5178050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643003463745</t>
+    <t xml:space="preserve">10.2642993927002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2907295227051</t>
+    <t xml:space="preserve">11.2907304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0278930664062</t>
+    <t xml:space="preserve">12.0278940200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6950807571411</t>
+    <t xml:space="preserve">11.6950817108154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9750156402588</t>
+    <t xml:space="preserve">11.9750165939331</t>
   </si>
   <si>
     <t xml:space="preserve">11.7028579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.586217880249</t>
+    <t xml:space="preserve">11.5862159729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5084571838379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639776229858</t>
+    <t xml:space="preserve">11.6639766693115</t>
   </si>
   <si>
     <t xml:space="preserve">11.3529376983643</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">11.1196584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.886378288269</t>
+    <t xml:space="preserve">10.8863773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9641370773315</t>
+    <t xml:space="preserve">10.9641389846802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975786209106</t>
+    <t xml:space="preserve">10.497579574585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4198198318481</t>
+    <t xml:space="preserve">10.4198188781738</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0310201644897</t>
+    <t xml:space="preserve">10.0310192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67332458496094</t>
+    <t xml:space="preserve">9.67332363128662</t>
   </si>
   <si>
     <t xml:space="preserve">9.4089412689209</t>
@@ -209,34 +209,34 @@
     <t xml:space="preserve">9.87550067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1476593017578</t>
+    <t xml:space="preserve">10.1476602554321</t>
   </si>
   <si>
-    <t xml:space="preserve">10.342059135437</t>
+    <t xml:space="preserve">10.3420610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3887157440186</t>
+    <t xml:space="preserve">10.3887147903442</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7977409362793</t>
+    <t xml:space="preserve">9.79773998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48670101165771</t>
+    <t xml:space="preserve">9.48670291900635</t>
   </si>
   <si>
     <t xml:space="preserve">9.33118152618408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83661937713623</t>
+    <t xml:space="preserve">9.83662128448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47892475128174</t>
+    <t xml:space="preserve">9.47892570495605</t>
   </si>
   <si>
     <t xml:space="preserve">9.29074668884277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97815132141113</t>
+    <t xml:space="preserve">8.97815036773682</t>
   </si>
   <si>
     <t xml:space="preserve">9.09945678710938</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">9.71842575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3087797164917</t>
+    <t xml:space="preserve">10.3087787628174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2745637893677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3498344421387</t>
+    <t xml:space="preserve">10.3498373031616</t>
   </si>
   <si>
     <t xml:space="preserve">10.0076923370361</t>
@@ -260,22 +260,22 @@
     <t xml:space="preserve">10.6064434051514</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6919794082642</t>
+    <t xml:space="preserve">10.6919803619385</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4353723526001</t>
+    <t xml:space="preserve">10.4353713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.778904914856</t>
+    <t xml:space="preserve">10.7789058685303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5181255340576</t>
+    <t xml:space="preserve">10.5181264877319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834922790527</t>
+    <t xml:space="preserve">10.0834932327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2573461532593</t>
+    <t xml:space="preserve">10.2573471069336</t>
   </si>
   <si>
     <t xml:space="preserve">9.64885902404785</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">8.95344543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86651992797852</t>
+    <t xml:space="preserve">8.8665189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77959156036377</t>
+    <t xml:space="preserve">8.7795934677124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69266700744629</t>
+    <t xml:space="preserve">8.69266605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64920139312744</t>
+    <t xml:space="preserve">8.64920330047607</t>
   </si>
   <si>
     <t xml:space="preserve">9.04037189483643</t>
@@ -308,16 +308,19 @@
     <t xml:space="preserve">9.82271289825439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1266107559204</t>
+    <t xml:space="preserve">11.1266117095947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3004655838013</t>
+    <t xml:space="preserve">11.3004636764526</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9527587890625</t>
+    <t xml:space="preserve">10.9527597427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6919794082642</t>
   </si>
   <si>
     <t xml:space="preserve">10.1704187393188</t>
@@ -329,37 +332,37 @@
     <t xml:space="preserve">10.6050519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4311981201172</t>
+    <t xml:space="preserve">10.4311990737915</t>
   </si>
   <si>
     <t xml:space="preserve">9.47500514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3880786895752</t>
+    <t xml:space="preserve">9.38807964324951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21422672271729</t>
+    <t xml:space="preserve">9.21422576904297</t>
   </si>
   <si>
     <t xml:space="preserve">9.12729835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73578453063965</t>
+    <t xml:space="preserve">9.73578548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3442716598511</t>
+    <t xml:space="preserve">10.3442726135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.3011531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99725198745728</t>
+    <t xml:space="preserve">7.99725246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38876628875732</t>
+    <t xml:space="preserve">7.38876533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30183887481689</t>
+    <t xml:space="preserve">7.30183935165405</t>
   </si>
   <si>
     <t xml:space="preserve">7.258376121521</t>
@@ -368,13 +371,13 @@
     <t xml:space="preserve">7.34530210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4756932258606</t>
+    <t xml:space="preserve">7.47569274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82339906692505</t>
+    <t xml:space="preserve">7.82339859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95378923416138</t>
+    <t xml:space="preserve">7.95378971099854</t>
   </si>
   <si>
     <t xml:space="preserve">8.3449592590332</t>
@@ -383,19 +386,19 @@
     <t xml:space="preserve">8.60573863983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0087156295776</t>
+    <t xml:space="preserve">10.0087146759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.56585121154785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47727966308594</t>
+    <t xml:space="preserve">9.4772777557373</t>
   </si>
   <si>
     <t xml:space="preserve">9.38870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94584178924561</t>
+    <t xml:space="preserve">8.94584274291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.85727024078369</t>
@@ -404,31 +407,31 @@
     <t xml:space="preserve">8.76869773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03441524505615</t>
+    <t xml:space="preserve">9.03441429138184</t>
   </si>
   <si>
     <t xml:space="preserve">8.68012523651123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7244119644165</t>
+    <t xml:space="preserve">8.72441005706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2115592956543</t>
+    <t xml:space="preserve">9.21156024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12298774719238</t>
+    <t xml:space="preserve">9.1229887008667</t>
   </si>
   <si>
     <t xml:space="preserve">8.50297927856445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41440582275391</t>
+    <t xml:space="preserve">8.41440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.30013370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1858596801758</t>
+    <t xml:space="preserve">10.1858606338501</t>
   </si>
   <si>
     <t xml:space="preserve">11.071587562561</t>
@@ -440,16 +443,16 @@
     <t xml:space="preserve">10.9830141067505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4515781402588</t>
+    <t xml:space="preserve">10.4515790939331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972881317139</t>
+    <t xml:space="preserve">10.0972862243652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83156967163086</t>
+    <t xml:space="preserve">9.83157062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74299716949463</t>
+    <t xml:space="preserve">9.74299621582031</t>
   </si>
   <si>
     <t xml:space="preserve">9.92014217376709</t>
@@ -470,16 +473,16 @@
     <t xml:space="preserve">10.805869102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6287240982056</t>
+    <t xml:space="preserve">10.6287231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7172966003418</t>
+    <t xml:space="preserve">10.7172975540161</t>
   </si>
   <si>
     <t xml:space="preserve">10.3630056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5401515960693</t>
+    <t xml:space="preserve">10.540150642395</t>
   </si>
   <si>
     <t xml:space="preserve">10.4193983078003</t>
@@ -488,37 +491,37 @@
     <t xml:space="preserve">10.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6912088394165</t>
+    <t xml:space="preserve">10.6912097930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6006050109863</t>
+    <t xml:space="preserve">10.6006059646606</t>
   </si>
   <si>
     <t xml:space="preserve">10.3287944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475887298584</t>
+    <t xml:space="preserve">10.1475877761841</t>
   </si>
   <si>
     <t xml:space="preserve">10.7818126678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630193710327</t>
+    <t xml:space="preserve">10.963020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7851734161377</t>
+    <t xml:space="preserve">9.78517436981201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381925582886</t>
+    <t xml:space="preserve">10.2381906509399</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0502605438232</t>
+    <t xml:space="preserve">12.0502614974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.4160375595093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1442260742188</t>
+    <t xml:space="preserve">11.1442270278931</t>
   </si>
   <si>
     <t xml:space="preserve">11.8690547943115</t>
@@ -530,16 +533,16 @@
     <t xml:space="preserve">11.6878471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2314682006836</t>
+    <t xml:space="preserve">12.2314691543579</t>
   </si>
   <si>
     <t xml:space="preserve">12.6844844818115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5032787322998</t>
+    <t xml:space="preserve">12.5032796859741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.775089263916</t>
+    <t xml:space="preserve">12.7750902175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.1375026702881</t>
@@ -548,19 +551,19 @@
     <t xml:space="preserve">12.9562959671021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2281055450439</t>
+    <t xml:space="preserve">13.2281064987183</t>
   </si>
   <si>
     <t xml:space="preserve">14.0435371398926</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6811237335205</t>
+    <t xml:space="preserve">13.6811246871948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3153486251831</t>
+    <t xml:space="preserve">14.3153476715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4931917190552</t>
+    <t xml:space="preserve">15.4931926727295</t>
   </si>
   <si>
     <t xml:space="preserve">15.0401754379272</t>
@@ -569,10 +572,10 @@
     <t xml:space="preserve">15.4025897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8556060791016</t>
+    <t xml:space="preserve">15.8556051254272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9462099075317</t>
+    <t xml:space="preserve">15.9462108612061</t>
   </si>
   <si>
     <t xml:space="preserve">15.7650032043457</t>
@@ -584,7 +587,7 @@
     <t xml:space="preserve">15.221381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5871591567993</t>
+    <t xml:space="preserve">14.587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">13.8623304367065</t>
@@ -596,13 +599,13 @@
     <t xml:space="preserve">14.7683639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9495716094971</t>
+    <t xml:space="preserve">14.9495706558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.7717266082764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4999151229858</t>
+    <t xml:space="preserve">13.4999160766602</t>
   </si>
   <si>
     <t xml:space="preserve">14.1341409683228</t>
@@ -614,7 +617,7 @@
     <t xml:space="preserve">12.5938816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0468997955322</t>
+    <t xml:space="preserve">13.0468988418579</t>
   </si>
   <si>
     <t xml:space="preserve">13.5905199050903</t>
@@ -623,10 +626,10 @@
     <t xml:space="preserve">13.3187093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8656911849976</t>
+    <t xml:space="preserve">12.8656921386719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9529333114624</t>
+    <t xml:space="preserve">13.9529342651367</t>
   </si>
   <si>
     <t xml:space="preserve">14.2247438430786</t>
@@ -638,7 +641,7 @@
     <t xml:space="preserve">13.7264242172241</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7230625152588</t>
+    <t xml:space="preserve">14.7230634689331</t>
   </si>
   <si>
     <t xml:space="preserve">14.4512529373169</t>
@@ -650,7 +653,7 @@
     <t xml:space="preserve">14.2659797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6365261077881</t>
+    <t xml:space="preserve">14.6365251541138</t>
   </si>
   <si>
     <t xml:space="preserve">14.2196626663208</t>
@@ -659,10 +662,10 @@
     <t xml:space="preserve">13.895435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343894958496</t>
+    <t xml:space="preserve">14.0343885421753</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6828441619873</t>
+    <t xml:space="preserve">14.682843208313</t>
   </si>
   <si>
     <t xml:space="preserve">14.5438890457153</t>
@@ -674,7 +677,7 @@
     <t xml:space="preserve">15.0070705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3776159286499</t>
+    <t xml:space="preserve">15.3776149749756</t>
   </si>
   <si>
     <t xml:space="preserve">14.3586158752441</t>
@@ -683,7 +686,7 @@
     <t xml:space="preserve">14.1733436584473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7564821243286</t>
+    <t xml:space="preserve">13.7564811706543</t>
   </si>
   <si>
     <t xml:space="preserve">13.6638450622559</t>
@@ -698,16 +701,16 @@
     <t xml:space="preserve">13.9880723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248899459839</t>
+    <t xml:space="preserve">13.5248908996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8027982711792</t>
+    <t xml:space="preserve">13.8027992248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6175260543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3859357833862</t>
+    <t xml:space="preserve">13.3859367370605</t>
   </si>
   <si>
     <t xml:space="preserve">13.339617729187</t>
@@ -719,22 +722,22 @@
     <t xml:space="preserve">13.7101631164551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0617094039917</t>
+    <t xml:space="preserve">13.061710357666</t>
   </si>
   <si>
     <t xml:space="preserve">12.9690723419189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2469816207886</t>
+    <t xml:space="preserve">13.2469825744629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2006645202637</t>
+    <t xml:space="preserve">13.2006635665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.5712080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1543445587158</t>
+    <t xml:space="preserve">13.1543455123901</t>
   </si>
   <si>
     <t xml:space="preserve">13.9417533874512</t>
@@ -746,7 +749,7 @@
     <t xml:space="preserve">14.8217973709106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.404935836792</t>
+    <t xml:space="preserve">14.4049348831177</t>
   </si>
   <si>
     <t xml:space="preserve">14.7291612625122</t>
@@ -755,43 +758,43 @@
     <t xml:space="preserve">15.099705696106</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9144344329834</t>
+    <t xml:space="preserve">14.9144334793091</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2849788665771</t>
+    <t xml:space="preserve">15.2849779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6555233001709</t>
+    <t xml:space="preserve">15.6555223464966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5628862380981</t>
+    <t xml:space="preserve">15.5628871917725</t>
   </si>
   <si>
     <t xml:space="preserve">15.1923427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5165700912476</t>
+    <t xml:space="preserve">15.5165691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8407955169678</t>
+    <t xml:space="preserve">15.8407974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7944784164429</t>
+    <t xml:space="preserve">15.7944774627686</t>
   </si>
   <si>
     <t xml:space="preserve">15.4702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1460237503052</t>
+    <t xml:space="preserve">15.1460247039795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8681154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4975709915161</t>
+    <t xml:space="preserve">14.4975700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0166959762573</t>
+    <t xml:space="preserve">15.016695022583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2067794799805</t>
@@ -800,10 +803,7 @@
     <t xml:space="preserve">14.8266105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.541482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6365251541138</t>
+    <t xml:space="preserve">14.5414838790894</t>
   </si>
   <si>
     <t xml:space="preserve">14.9216527938843</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">15.7770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3968648910522</t>
+    <t xml:space="preserve">15.3968658447266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1572036743164</t>
+    <t xml:space="preserve">16.1572017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8720769882202</t>
+    <t xml:space="preserve">15.8720779418945</t>
   </si>
   <si>
     <t xml:space="preserve">15.9671173095703</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">15.1117372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7315673828125</t>
+    <t xml:space="preserve">14.7315683364868</t>
   </si>
   <si>
     <t xml:space="preserve">16.5373725891113</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">16.0621604919434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2522449493408</t>
+    <t xml:space="preserve">16.2522468566895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1076278686523</t>
@@ -9813,7 +9813,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -9917,7 +9917,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G331" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -9943,7 +9943,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G332" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -9995,7 +9995,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G334" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -10021,7 +10021,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G335" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -10073,7 +10073,7 @@
         <v>11.5</v>
       </c>
       <c r="G337" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -10099,7 +10099,7 @@
         <v>11.5</v>
       </c>
       <c r="G338" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -10125,7 +10125,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G339" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -10151,7 +10151,7 @@
         <v>12</v>
       </c>
       <c r="G340" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -10281,7 +10281,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G345" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -10307,7 +10307,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G346" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -10333,7 +10333,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G347" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -10359,7 +10359,7 @@
         <v>10.5</v>
       </c>
       <c r="G348" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -10411,7 +10411,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G350" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -10463,7 +10463,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G352" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -10489,7 +10489,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G353" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -10515,7 +10515,7 @@
         <v>10.5</v>
       </c>
       <c r="G354" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -10541,7 +10541,7 @@
         <v>10.5</v>
       </c>
       <c r="G355" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -10567,7 +10567,7 @@
         <v>10.5</v>
       </c>
       <c r="G356" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -10593,7 +10593,7 @@
         <v>10.5</v>
       </c>
       <c r="G357" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -10619,7 +10619,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G358" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -10645,7 +10645,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G359" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -10671,7 +10671,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G360" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -10697,7 +10697,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G361" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -10723,7 +10723,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G362" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -10749,7 +10749,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G363" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -10801,7 +10801,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G365" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -10827,7 +10827,7 @@
         <v>12</v>
       </c>
       <c r="G366" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -10853,7 +10853,7 @@
         <v>12</v>
       </c>
       <c r="G367" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -10879,7 +10879,7 @@
         <v>12</v>
       </c>
       <c r="G368" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -11035,7 +11035,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G374" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -11061,7 +11061,7 @@
         <v>12</v>
       </c>
       <c r="G375" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -11087,7 +11087,7 @@
         <v>12</v>
       </c>
       <c r="G376" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -11113,7 +11113,7 @@
         <v>12</v>
       </c>
       <c r="G377" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -11139,7 +11139,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G378" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -11165,7 +11165,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G379" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -11191,7 +11191,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G380" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -11217,7 +11217,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G381" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -11243,7 +11243,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G382" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -11269,7 +11269,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G383" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -11295,7 +11295,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G384" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -11321,7 +11321,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G385" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -11347,7 +11347,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G386" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -11373,7 +11373,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G387" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -11425,7 +11425,7 @@
         <v>11.5</v>
       </c>
       <c r="G389" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -11659,7 +11659,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G398" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -11919,7 +11919,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G408" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -11945,7 +11945,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -12023,7 +12023,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G412" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -12049,7 +12049,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -12075,7 +12075,7 @@
         <v>12</v>
       </c>
       <c r="G414" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -12205,7 +12205,7 @@
         <v>12</v>
       </c>
       <c r="G419" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -12231,7 +12231,7 @@
         <v>12</v>
       </c>
       <c r="G420" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -12283,7 +12283,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G422" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -12309,7 +12309,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G423" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -12335,7 +12335,7 @@
         <v>11.5</v>
       </c>
       <c r="G424" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -12361,7 +12361,7 @@
         <v>11.5</v>
       </c>
       <c r="G425" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -12387,7 +12387,7 @@
         <v>11.5</v>
       </c>
       <c r="G426" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -12439,7 +12439,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G428" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -12465,7 +12465,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G429" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -12491,7 +12491,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G430" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -12517,7 +12517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G431" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -12543,7 +12543,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G432" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -12569,7 +12569,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G433" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -12595,7 +12595,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G434" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -12621,7 +12621,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G435" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -12647,7 +12647,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G436" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -12673,7 +12673,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G437" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -12699,7 +12699,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G438" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -12725,7 +12725,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G439" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -12751,7 +12751,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G440" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -12829,7 +12829,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G443" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -12855,7 +12855,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -12881,7 +12881,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G445" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -12907,7 +12907,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G446" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -12933,7 +12933,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G447" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -12959,7 +12959,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -12985,7 +12985,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G449" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -13011,7 +13011,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G450" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -13063,7 +13063,7 @@
         <v>11.5</v>
       </c>
       <c r="G452" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -13089,7 +13089,7 @@
         <v>11.5</v>
       </c>
       <c r="G453" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -13115,7 +13115,7 @@
         <v>11.5</v>
       </c>
       <c r="G454" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -13141,7 +13141,7 @@
         <v>11.5</v>
       </c>
       <c r="G455" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -13453,7 +13453,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G467" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -13635,7 +13635,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G474" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -13661,7 +13661,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G475" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -13687,7 +13687,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G476" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -13713,7 +13713,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G477" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -13739,7 +13739,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G478" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -13765,7 +13765,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G479" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -13791,7 +13791,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G480" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -13817,7 +13817,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G481" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -13843,7 +13843,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G482" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -13869,7 +13869,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G483" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -13895,7 +13895,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G484" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -13921,7 +13921,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G485" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -13947,7 +13947,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -14025,7 +14025,7 @@
         <v>10.5</v>
       </c>
       <c r="G489" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -14051,7 +14051,7 @@
         <v>10.5</v>
       </c>
       <c r="G490" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -14103,7 +14103,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G492" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -14129,7 +14129,7 @@
         <v>8.5</v>
       </c>
       <c r="G493" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -14155,7 +14155,7 @@
         <v>8.5</v>
       </c>
       <c r="G494" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -14181,7 +14181,7 @@
         <v>8.5</v>
       </c>
       <c r="G495" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -14207,7 +14207,7 @@
         <v>8.5</v>
       </c>
       <c r="G496" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -14233,7 +14233,7 @@
         <v>8.5</v>
       </c>
       <c r="G497" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -14259,7 +14259,7 @@
         <v>8.5</v>
       </c>
       <c r="G498" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -14285,7 +14285,7 @@
         <v>8.5</v>
       </c>
       <c r="G499" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -14311,7 +14311,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G500" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -14337,7 +14337,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G501" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -14363,7 +14363,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G502" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -14389,7 +14389,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G503" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -14415,7 +14415,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G504" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -14441,7 +14441,7 @@
         <v>9</v>
       </c>
       <c r="G505" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -14467,7 +14467,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G506" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -14493,7 +14493,7 @@
         <v>9</v>
       </c>
       <c r="G507" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -14597,7 +14597,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G511" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -14623,7 +14623,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G512" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -14649,7 +14649,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -14779,7 +14779,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G518" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -14805,7 +14805,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G519" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -14909,7 +14909,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G523" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -14935,7 +14935,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G524" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -14961,7 +14961,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G525" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -14987,7 +14987,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G526" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -15013,7 +15013,7 @@
         <v>11.5</v>
       </c>
       <c r="G527" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -15091,7 +15091,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -15117,7 +15117,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G531" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -15143,7 +15143,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G532" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -15169,7 +15169,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G533" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -15195,7 +15195,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -15221,7 +15221,7 @@
         <v>10</v>
       </c>
       <c r="G535" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -15247,7 +15247,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G536" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -15273,7 +15273,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G537" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -15299,7 +15299,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G538" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -15325,7 +15325,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G539" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -15351,7 +15351,7 @@
         <v>10</v>
       </c>
       <c r="G540" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -15377,7 +15377,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G541" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -15403,7 +15403,7 @@
         <v>10</v>
       </c>
       <c r="G542" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -15429,7 +15429,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G543" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -15455,7 +15455,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G544" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -15481,7 +15481,7 @@
         <v>10</v>
       </c>
       <c r="G545" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -15507,7 +15507,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -15533,7 +15533,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G547" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -15559,7 +15559,7 @@
         <v>10</v>
       </c>
       <c r="G548" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -15585,7 +15585,7 @@
         <v>10</v>
       </c>
       <c r="G549" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -15611,7 +15611,7 @@
         <v>10</v>
       </c>
       <c r="G550" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -15637,7 +15637,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G551" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -15663,7 +15663,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G552" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -15689,7 +15689,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G553" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -15715,7 +15715,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G554" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -15741,7 +15741,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G555" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -15767,7 +15767,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G556" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -15793,7 +15793,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G557" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -15819,7 +15819,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G558" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -15845,7 +15845,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G559" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -15871,7 +15871,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G560" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -15897,7 +15897,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G561" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -15923,7 +15923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G562" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -15949,7 +15949,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G563" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -15975,7 +15975,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G564" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -16001,7 +16001,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G565" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -16027,7 +16027,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -16053,7 +16053,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G567" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -16079,7 +16079,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G568" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -16105,7 +16105,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G569" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -16131,7 +16131,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G570" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -16157,7 +16157,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G571" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -16183,7 +16183,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G572" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -16209,7 +16209,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G573" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -16235,7 +16235,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -16261,7 +16261,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -16287,7 +16287,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G576" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -16313,7 +16313,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -16339,7 +16339,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G578" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -16365,7 +16365,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G579" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -16391,7 +16391,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -16417,7 +16417,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G581" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -16443,7 +16443,7 @@
         <v>10</v>
       </c>
       <c r="G582" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -16469,7 +16469,7 @@
         <v>10</v>
       </c>
       <c r="G583" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -16495,7 +16495,7 @@
         <v>10</v>
       </c>
       <c r="G584" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -16521,7 +16521,7 @@
         <v>10</v>
       </c>
       <c r="G585" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -16547,7 +16547,7 @@
         <v>10</v>
       </c>
       <c r="G586" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -16573,7 +16573,7 @@
         <v>10</v>
       </c>
       <c r="G587" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -16599,7 +16599,7 @@
         <v>10</v>
       </c>
       <c r="G588" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -16625,7 +16625,7 @@
         <v>10</v>
       </c>
       <c r="G589" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -16651,7 +16651,7 @@
         <v>10</v>
       </c>
       <c r="G590" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -16677,7 +16677,7 @@
         <v>10</v>
       </c>
       <c r="G591" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -16703,7 +16703,7 @@
         <v>10</v>
       </c>
       <c r="G592" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -16729,7 +16729,7 @@
         <v>10</v>
       </c>
       <c r="G593" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -16755,7 +16755,7 @@
         <v>10</v>
       </c>
       <c r="G594" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -16781,7 +16781,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G595" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -16807,7 +16807,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G596" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -16833,7 +16833,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G597" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -16859,7 +16859,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G598" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -16885,7 +16885,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G599" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -16911,7 +16911,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G600" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -16937,7 +16937,7 @@
         <v>10</v>
       </c>
       <c r="G601" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -16963,7 +16963,7 @@
         <v>10</v>
       </c>
       <c r="G602" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -16989,7 +16989,7 @@
         <v>10</v>
       </c>
       <c r="G603" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -17015,7 +17015,7 @@
         <v>10</v>
       </c>
       <c r="G604" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -17041,7 +17041,7 @@
         <v>10</v>
       </c>
       <c r="G605" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -17067,7 +17067,7 @@
         <v>10</v>
       </c>
       <c r="G606" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -17093,7 +17093,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G607" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -17119,7 +17119,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G608" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -17145,7 +17145,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G609" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -17171,7 +17171,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G610" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -17197,7 +17197,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G611" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -17223,7 +17223,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G612" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -17249,7 +17249,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G613" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -17275,7 +17275,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G614" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -17301,7 +17301,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G615" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -17327,7 +17327,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G616" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -17353,7 +17353,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G617" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -17379,7 +17379,7 @@
         <v>9.5</v>
       </c>
       <c r="G618" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -17405,7 +17405,7 @@
         <v>9.5</v>
       </c>
       <c r="G619" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -17431,7 +17431,7 @@
         <v>9.5</v>
       </c>
       <c r="G620" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -17457,7 +17457,7 @@
         <v>9.5</v>
       </c>
       <c r="G621" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -17483,7 +17483,7 @@
         <v>9.5</v>
       </c>
       <c r="G622" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -17509,7 +17509,7 @@
         <v>9.5</v>
       </c>
       <c r="G623" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -17535,7 +17535,7 @@
         <v>9.5</v>
       </c>
       <c r="G624" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -17561,7 +17561,7 @@
         <v>9.5</v>
       </c>
       <c r="G625" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -17587,7 +17587,7 @@
         <v>9.5</v>
       </c>
       <c r="G626" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -17613,7 +17613,7 @@
         <v>9.5</v>
       </c>
       <c r="G627" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -17639,7 +17639,7 @@
         <v>9.5</v>
       </c>
       <c r="G628" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -17665,7 +17665,7 @@
         <v>9.5</v>
       </c>
       <c r="G629" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -17691,7 +17691,7 @@
         <v>9.5</v>
       </c>
       <c r="G630" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -17717,7 +17717,7 @@
         <v>9.5</v>
       </c>
       <c r="G631" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -17743,7 +17743,7 @@
         <v>9.5</v>
       </c>
       <c r="G632" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -17769,7 +17769,7 @@
         <v>9.5</v>
       </c>
       <c r="G633" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -17795,7 +17795,7 @@
         <v>9.5</v>
       </c>
       <c r="G634" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -17821,7 +17821,7 @@
         <v>9.5</v>
       </c>
       <c r="G635" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -17847,7 +17847,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G636" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -17873,7 +17873,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G637" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -17899,7 +17899,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G638" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -17925,7 +17925,7 @@
         <v>10</v>
       </c>
       <c r="G639" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -17951,7 +17951,7 @@
         <v>10</v>
       </c>
       <c r="G640" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -17977,7 +17977,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -18003,7 +18003,7 @@
         <v>10</v>
       </c>
       <c r="G642" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -18029,7 +18029,7 @@
         <v>10</v>
       </c>
       <c r="G643" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -18055,7 +18055,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G644" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -18081,7 +18081,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G645" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -18107,7 +18107,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G646" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -18133,7 +18133,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G647" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -18159,7 +18159,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G648" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -18185,7 +18185,7 @@
         <v>10.5</v>
       </c>
       <c r="G649" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -18211,7 +18211,7 @@
         <v>10.5</v>
       </c>
       <c r="G650" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -18237,7 +18237,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G651" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -18263,7 +18263,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -18289,7 +18289,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -18315,7 +18315,7 @@
         <v>10</v>
       </c>
       <c r="G654" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -18341,7 +18341,7 @@
         <v>10</v>
       </c>
       <c r="G655" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -18367,7 +18367,7 @@
         <v>10</v>
       </c>
       <c r="G656" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -18393,7 +18393,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G657" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -18419,7 +18419,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G658" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -18445,7 +18445,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G659" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -18471,7 +18471,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G660" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -18497,7 +18497,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G661" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -18523,7 +18523,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G662" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -18549,7 +18549,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G663" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -18575,7 +18575,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -18601,7 +18601,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G665" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -18627,7 +18627,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -18653,7 +18653,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G667" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -18679,7 +18679,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G668" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -18705,7 +18705,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -18731,7 +18731,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -18757,7 +18757,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G671" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -18783,7 +18783,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G672" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -18809,7 +18809,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G673" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -18835,7 +18835,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G674" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -18861,7 +18861,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G675" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -18887,7 +18887,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -18913,7 +18913,7 @@
         <v>10.5</v>
       </c>
       <c r="G677" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -18939,7 +18939,7 @@
         <v>10.5</v>
       </c>
       <c r="G678" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -18965,7 +18965,7 @@
         <v>10.5</v>
       </c>
       <c r="G679" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -18991,7 +18991,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G680" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -19017,7 +19017,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G681" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -19043,7 +19043,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G682" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -19069,7 +19069,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G683" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -19095,7 +19095,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G684" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -19121,7 +19121,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -19147,7 +19147,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -19173,7 +19173,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G687" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -19199,7 +19199,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G688" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -19225,7 +19225,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G689" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -19251,7 +19251,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G690" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -19277,7 +19277,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G691" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -19303,7 +19303,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -19329,7 +19329,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G693" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -19355,7 +19355,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G694" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -19381,7 +19381,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G695" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -19407,7 +19407,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G696" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -19433,7 +19433,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G697" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -19459,7 +19459,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G698" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -19485,7 +19485,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G699" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -19511,7 +19511,7 @@
         <v>11.5</v>
       </c>
       <c r="G700" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -19537,7 +19537,7 @@
         <v>11.5</v>
       </c>
       <c r="G701" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -19563,7 +19563,7 @@
         <v>11.5</v>
       </c>
       <c r="G702" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -19589,7 +19589,7 @@
         <v>12.5</v>
       </c>
       <c r="G703" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -19615,7 +19615,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -19641,7 +19641,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G705" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -19667,7 +19667,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -19693,7 +19693,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G707" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -19719,7 +19719,7 @@
         <v>11.5</v>
       </c>
       <c r="G708" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -19745,7 +19745,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -19771,7 +19771,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G710" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -19797,7 +19797,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G711" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -19823,7 +19823,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G712" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -19849,7 +19849,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -19875,7 +19875,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -19901,7 +19901,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G715" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -19927,7 +19927,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G716" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -19953,7 +19953,7 @@
         <v>11</v>
       </c>
       <c r="G717" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -19979,7 +19979,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G718" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20005,7 +20005,7 @@
         <v>11</v>
       </c>
       <c r="G719" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -20031,7 +20031,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G720" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -20057,7 +20057,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G721" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -20083,7 +20083,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G722" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -20109,7 +20109,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G723" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -20135,7 +20135,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G724" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -20161,7 +20161,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G725" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -20187,7 +20187,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G726" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -20213,7 +20213,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G727" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -20239,7 +20239,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -20265,7 +20265,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G729" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -20291,7 +20291,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G730" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -20317,7 +20317,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G731" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -20343,7 +20343,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G732" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -20369,7 +20369,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G733" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -20395,7 +20395,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G734" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -20421,7 +20421,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G735" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -20447,7 +20447,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G736" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -20473,7 +20473,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G737" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -20499,7 +20499,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G738" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -20525,7 +20525,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -20551,7 +20551,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G740" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -20577,7 +20577,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G741" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -20603,7 +20603,7 @@
         <v>11</v>
       </c>
       <c r="G742" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -20629,7 +20629,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G743" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -20655,7 +20655,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G744" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -20681,7 +20681,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G745" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -20707,7 +20707,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G746" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -20733,7 +20733,7 @@
         <v>13</v>
       </c>
       <c r="G747" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -20759,7 +20759,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G748" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -20785,7 +20785,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G749" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -20811,7 +20811,7 @@
         <v>12</v>
       </c>
       <c r="G750" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -20837,7 +20837,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G751" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -20863,7 +20863,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G752" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -20889,7 +20889,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G753" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -20915,7 +20915,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G754" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -20941,7 +20941,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G755" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -20967,7 +20967,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -20993,7 +20993,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G757" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21019,7 +21019,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G758" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21045,7 +21045,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G759" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21071,7 +21071,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G760" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21097,7 +21097,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G761" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21123,7 +21123,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G762" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21149,7 +21149,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G763" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21175,7 +21175,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G764" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21201,7 +21201,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G765" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21227,7 +21227,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G766" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21253,7 +21253,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G767" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21279,7 +21279,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -21305,7 +21305,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G769" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -21331,7 +21331,7 @@
         <v>11.5</v>
       </c>
       <c r="G770" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -21357,7 +21357,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G771" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -21383,7 +21383,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G772" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -21409,7 +21409,7 @@
         <v>12</v>
       </c>
       <c r="G773" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -21435,7 +21435,7 @@
         <v>12</v>
       </c>
       <c r="G774" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -21461,7 +21461,7 @@
         <v>12</v>
       </c>
       <c r="G775" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -21487,7 +21487,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G776" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -21513,7 +21513,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -21539,7 +21539,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G778" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -21565,7 +21565,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -21591,7 +21591,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G780" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -21617,7 +21617,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G781" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -21643,7 +21643,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G782" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -21669,7 +21669,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -21695,7 +21695,7 @@
         <v>11.5</v>
       </c>
       <c r="G784" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -21721,7 +21721,7 @@
         <v>11.5</v>
       </c>
       <c r="G785" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -21747,7 +21747,7 @@
         <v>11.5</v>
       </c>
       <c r="G786" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -21773,7 +21773,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -21799,7 +21799,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G788" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -21825,7 +21825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G789" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -21851,7 +21851,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G790" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -21877,7 +21877,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -21903,7 +21903,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G792" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -21929,7 +21929,7 @@
         <v>11.5</v>
       </c>
       <c r="G793" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -21955,7 +21955,7 @@
         <v>11.5</v>
       </c>
       <c r="G794" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -21981,7 +21981,7 @@
         <v>11.5</v>
       </c>
       <c r="G795" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22007,7 +22007,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G796" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22033,7 +22033,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G797" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22059,7 +22059,7 @@
         <v>11.5</v>
       </c>
       <c r="G798" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22085,7 +22085,7 @@
         <v>11.5</v>
       </c>
       <c r="G799" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22111,7 +22111,7 @@
         <v>11.5</v>
       </c>
       <c r="G800" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22137,7 +22137,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G801" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22163,7 +22163,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G802" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22189,7 +22189,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G803" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22215,7 +22215,7 @@
         <v>11.5</v>
       </c>
       <c r="G804" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22241,7 +22241,7 @@
         <v>11.5</v>
       </c>
       <c r="G805" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22267,7 +22267,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G806" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -22293,7 +22293,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G807" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -22319,7 +22319,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G808" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -22345,7 +22345,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G809" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -22371,7 +22371,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G810" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -22397,7 +22397,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G811" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -22423,7 +22423,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -22449,7 +22449,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G813" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -22475,7 +22475,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G814" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -22501,7 +22501,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G815" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -22527,7 +22527,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -22553,7 +22553,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -22579,7 +22579,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G818" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -22605,7 +22605,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G819" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -22631,7 +22631,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G820" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -22657,7 +22657,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G821" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -22683,7 +22683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G822" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -22709,7 +22709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G823" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -22735,7 +22735,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G824" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -22761,7 +22761,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -22787,7 +22787,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -22813,7 +22813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G827" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -22839,7 +22839,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -22865,7 +22865,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G829" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -22891,7 +22891,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G830" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -22917,7 +22917,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G831" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -22943,7 +22943,7 @@
         <v>11.5</v>
       </c>
       <c r="G832" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -22969,7 +22969,7 @@
         <v>11.5</v>
       </c>
       <c r="G833" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -22995,7 +22995,7 @@
         <v>11.5</v>
       </c>
       <c r="G834" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23021,7 +23021,7 @@
         <v>11.5</v>
       </c>
       <c r="G835" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23047,7 +23047,7 @@
         <v>11.5</v>
       </c>
       <c r="G836" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23073,7 +23073,7 @@
         <v>11.5</v>
       </c>
       <c r="G837" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23099,7 +23099,7 @@
         <v>11.5</v>
       </c>
       <c r="G838" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23125,7 +23125,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G839" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23151,7 +23151,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G840" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23177,7 +23177,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G841" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23203,7 +23203,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G842" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23229,7 +23229,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G843" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23255,7 +23255,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G844" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23281,7 +23281,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G845" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -23307,7 +23307,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G846" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -23333,7 +23333,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G847" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -23359,7 +23359,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G848" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -23385,7 +23385,7 @@
         <v>11.5</v>
       </c>
       <c r="G849" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -23411,7 +23411,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -23437,7 +23437,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G851" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -23463,7 +23463,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -23489,7 +23489,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -23515,7 +23515,7 @@
         <v>11.5</v>
       </c>
       <c r="G854" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -23541,7 +23541,7 @@
         <v>11.5</v>
       </c>
       <c r="G855" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -23567,7 +23567,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -23593,7 +23593,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -23619,7 +23619,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G858" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -23645,7 +23645,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G859" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -23671,7 +23671,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G860" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -23697,7 +23697,7 @@
         <v>11.5</v>
       </c>
       <c r="G861" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -23723,7 +23723,7 @@
         <v>11.5</v>
       </c>
       <c r="G862" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -23749,7 +23749,7 @@
         <v>11.5</v>
       </c>
       <c r="G863" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -23775,7 +23775,7 @@
         <v>11.5</v>
       </c>
       <c r="G864" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -23801,7 +23801,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G865" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -23827,7 +23827,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G866" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -23853,7 +23853,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -23879,7 +23879,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -23905,7 +23905,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -23931,7 +23931,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -23957,7 +23957,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -23983,7 +23983,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G872" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -24009,7 +24009,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G873" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -24035,7 +24035,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G874" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -24061,7 +24061,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G875" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -24087,7 +24087,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G876" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -24113,7 +24113,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G877" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -24139,7 +24139,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -24165,7 +24165,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G879" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -24191,7 +24191,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G880" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -24217,7 +24217,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G881" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -24243,7 +24243,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -24269,7 +24269,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G883" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -24295,7 +24295,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G884" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -24321,7 +24321,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G885" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -24347,7 +24347,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G886" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -24373,7 +24373,7 @@
         <v>13.5</v>
       </c>
       <c r="G887" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -24399,7 +24399,7 @@
         <v>14</v>
       </c>
       <c r="G888" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -24425,7 +24425,7 @@
         <v>14</v>
       </c>
       <c r="G889" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -24451,7 +24451,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G890" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -24477,7 +24477,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G891" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -24503,7 +24503,7 @@
         <v>14.5</v>
       </c>
       <c r="G892" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -24529,7 +24529,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G893" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -24555,7 +24555,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -24581,7 +24581,7 @@
         <v>15.5</v>
       </c>
       <c r="G895" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -24607,7 +24607,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G896" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -24633,7 +24633,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G897" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -24659,7 +24659,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G898" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -24685,7 +24685,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G899" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -24711,7 +24711,7 @@
         <v>17</v>
       </c>
       <c r="G900" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -24737,7 +24737,7 @@
         <v>17.5</v>
       </c>
       <c r="G901" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -24763,7 +24763,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G902" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -24789,7 +24789,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G903" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -24815,7 +24815,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G904" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -24841,7 +24841,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G905" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -24867,7 +24867,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G906" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -24893,7 +24893,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G907" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -24919,7 +24919,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G908" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -24945,7 +24945,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G909" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -24971,7 +24971,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G910" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -24997,7 +24997,7 @@
         <v>16</v>
       </c>
       <c r="G911" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -25023,7 +25023,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -25049,7 +25049,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G913" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -25075,7 +25075,7 @@
         <v>16.5</v>
       </c>
       <c r="G914" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -25101,7 +25101,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G915" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -25127,7 +25127,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G916" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -25153,7 +25153,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G917" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -25179,7 +25179,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G918" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -25205,7 +25205,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G919" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -25231,7 +25231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G920" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -25257,7 +25257,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -25283,7 +25283,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G922" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -25309,7 +25309,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G923" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -25335,7 +25335,7 @@
         <v>15.5</v>
       </c>
       <c r="G924" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -25361,7 +25361,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G925" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -25387,7 +25387,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G926" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -25413,7 +25413,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -25439,7 +25439,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G928" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -25465,7 +25465,7 @@
         <v>14.5</v>
       </c>
       <c r="G929" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -25491,7 +25491,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G930" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -25517,7 +25517,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G931" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -25543,7 +25543,7 @@
         <v>14</v>
       </c>
       <c r="G932" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -25569,7 +25569,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G933" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -25595,7 +25595,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G934" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -25621,7 +25621,7 @@
         <v>14.5</v>
       </c>
       <c r="G935" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -25647,7 +25647,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G936" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -25673,7 +25673,7 @@
         <v>14.5</v>
       </c>
       <c r="G937" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -25699,7 +25699,7 @@
         <v>14.5</v>
       </c>
       <c r="G938" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -25725,7 +25725,7 @@
         <v>14.5</v>
       </c>
       <c r="G939" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -25751,7 +25751,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G940" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -25777,7 +25777,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G941" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -25803,7 +25803,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G942" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -25829,7 +25829,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -25855,7 +25855,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G944" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -25881,7 +25881,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G945" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -25907,7 +25907,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G946" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -25933,7 +25933,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G947" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -25959,7 +25959,7 @@
         <v>15</v>
       </c>
       <c r="G948" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -25985,7 +25985,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G949" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26011,7 +26011,7 @@
         <v>14.5</v>
       </c>
       <c r="G950" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26037,7 +26037,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G951" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26063,7 +26063,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G952" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26089,7 +26089,7 @@
         <v>14.5</v>
       </c>
       <c r="G953" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26115,7 +26115,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G954" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26141,7 +26141,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G955" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26167,7 +26167,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G956" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26193,7 +26193,7 @@
         <v>15</v>
       </c>
       <c r="G957" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26219,7 +26219,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G958" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26245,7 +26245,7 @@
         <v>14.5</v>
       </c>
       <c r="G959" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26271,7 +26271,7 @@
         <v>15</v>
       </c>
       <c r="G960" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -26297,7 +26297,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G961" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -26323,7 +26323,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G962" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -26349,7 +26349,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G963" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -26375,7 +26375,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G964" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -26401,7 +26401,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G965" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -26427,7 +26427,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G966" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -26453,7 +26453,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G967" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -26479,7 +26479,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G968" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -26505,7 +26505,7 @@
         <v>15.5</v>
       </c>
       <c r="G969" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -26531,7 +26531,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -26557,7 +26557,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G971" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -26583,7 +26583,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G972" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -26609,7 +26609,7 @@
         <v>15</v>
       </c>
       <c r="G973" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -26635,7 +26635,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G974" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -26661,7 +26661,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G975" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -26687,7 +26687,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G976" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -26713,7 +26713,7 @@
         <v>16</v>
       </c>
       <c r="G977" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -26739,7 +26739,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -26765,7 +26765,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G979" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -26791,7 +26791,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G980" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -26817,7 +26817,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G981" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -26843,7 +26843,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G982" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -26869,7 +26869,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G983" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -26895,7 +26895,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G984" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -26921,7 +26921,7 @@
         <v>15.5</v>
       </c>
       <c r="G985" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -26947,7 +26947,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G986" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -26973,7 +26973,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G987" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -26999,7 +26999,7 @@
         <v>15.5</v>
       </c>
       <c r="G988" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27025,7 +27025,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G989" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27051,7 +27051,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G990" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27077,7 +27077,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G991" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27103,7 +27103,7 @@
         <v>16</v>
       </c>
       <c r="G992" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27129,7 +27129,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G993" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27155,7 +27155,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G994" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27181,7 +27181,7 @@
         <v>15</v>
       </c>
       <c r="G995" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27207,7 +27207,7 @@
         <v>15.5</v>
       </c>
       <c r="G996" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27233,7 +27233,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G997" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27259,7 +27259,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G998" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -27285,7 +27285,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G999" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -27311,7 +27311,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1000" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -27337,7 +27337,7 @@
         <v>14</v>
       </c>
       <c r="G1001" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -27363,7 +27363,7 @@
         <v>13.5</v>
       </c>
       <c r="G1002" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -27389,7 +27389,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1003" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -27415,7 +27415,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1004" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -27441,7 +27441,7 @@
         <v>14.5</v>
       </c>
       <c r="G1005" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -27467,7 +27467,7 @@
         <v>14.5</v>
       </c>
       <c r="G1006" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -27493,7 +27493,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1007" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -27519,7 +27519,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -27545,7 +27545,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -27571,7 +27571,7 @@
         <v>14.5</v>
       </c>
       <c r="G1010" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -27597,7 +27597,7 @@
         <v>14.5</v>
       </c>
       <c r="G1011" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -27623,7 +27623,7 @@
         <v>14.5</v>
       </c>
       <c r="G1012" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -27649,7 +27649,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1013" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -27675,7 +27675,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1014" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -27701,7 +27701,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1015" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -27727,7 +27727,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1016" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -27753,7 +27753,7 @@
         <v>15</v>
       </c>
       <c r="G1017" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -27779,7 +27779,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1018" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -27805,7 +27805,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1019" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -27831,7 +27831,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1020" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -27857,7 +27857,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1021" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -27883,7 +27883,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1022" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -27909,7 +27909,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1023" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -27935,7 +27935,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1024" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -27961,7 +27961,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1025" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -27987,7 +27987,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1026" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28013,7 +28013,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1027" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28039,7 +28039,7 @@
         <v>15</v>
       </c>
       <c r="G1028" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28065,7 +28065,7 @@
         <v>16</v>
       </c>
       <c r="G1029" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28091,7 +28091,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1030" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28117,7 +28117,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1031" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28143,7 +28143,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1032" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28169,7 +28169,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1033" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28195,7 +28195,7 @@
         <v>16</v>
       </c>
       <c r="G1034" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28221,7 +28221,7 @@
         <v>16</v>
       </c>
       <c r="G1035" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28247,7 +28247,7 @@
         <v>15.5</v>
       </c>
       <c r="G1036" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28273,7 +28273,7 @@
         <v>16.25</v>
       </c>
       <c r="G1037" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -28299,7 +28299,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1038" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -28325,7 +28325,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -28351,7 +28351,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1040" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -28377,7 +28377,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1041" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -28403,7 +28403,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1042" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -28429,7 +28429,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1043" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -28455,7 +28455,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1044" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -28481,7 +28481,7 @@
         <v>15.25</v>
       </c>
       <c r="G1045" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -28507,7 +28507,7 @@
         <v>15.25</v>
       </c>
       <c r="G1046" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -28533,7 +28533,7 @@
         <v>15.25</v>
       </c>
       <c r="G1047" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -28559,7 +28559,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1048" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -28585,7 +28585,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -28611,7 +28611,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1050" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -28637,7 +28637,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1051" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -28663,7 +28663,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1052" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -28689,7 +28689,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1053" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -28715,7 +28715,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -28741,7 +28741,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1055" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -28767,7 +28767,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1056" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -28793,7 +28793,7 @@
         <v>15</v>
       </c>
       <c r="G1057" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -28819,7 +28819,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -28845,7 +28845,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1059" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -28871,7 +28871,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1060" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -28897,7 +28897,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1061" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -28923,7 +28923,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1062" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -28949,7 +28949,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1063" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -28975,7 +28975,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29001,7 +29001,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G1065" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29027,7 +29027,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1066" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29053,7 +29053,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1067" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29079,7 +29079,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1068" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29105,7 +29105,7 @@
         <v>15.5</v>
       </c>
       <c r="G1069" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29131,7 +29131,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1070" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29157,7 +29157,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1071" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29183,7 +29183,7 @@
         <v>15.5</v>
       </c>
       <c r="G1072" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29209,7 +29209,7 @@
         <v>15.5</v>
       </c>
       <c r="G1073" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29235,7 +29235,7 @@
         <v>15.5</v>
       </c>
       <c r="G1074" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29261,7 +29261,7 @@
         <v>15.5</v>
       </c>
       <c r="G1075" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -29287,7 +29287,7 @@
         <v>15</v>
       </c>
       <c r="G1076" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -29313,7 +29313,7 @@
         <v>15.25</v>
       </c>
       <c r="G1077" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -29339,7 +29339,7 @@
         <v>15.25</v>
       </c>
       <c r="G1078" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -29365,7 +29365,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1079" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -29391,7 +29391,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1080" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -29417,7 +29417,7 @@
         <v>15.25</v>
       </c>
       <c r="G1081" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -29443,7 +29443,7 @@
         <v>15.25</v>
       </c>
       <c r="G1082" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -29469,7 +29469,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1083" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -29495,7 +29495,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1084" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -29521,7 +29521,7 @@
         <v>14.75</v>
       </c>
       <c r="G1085" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -29547,7 +29547,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1086" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -29573,7 +29573,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1087" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -29599,7 +29599,7 @@
         <v>14.75</v>
       </c>
       <c r="G1088" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -29625,7 +29625,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1089" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -29651,7 +29651,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1090" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -29677,7 +29677,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1091" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -29703,7 +29703,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1092" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -29729,7 +29729,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1093" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -29755,7 +29755,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1094" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -29781,7 +29781,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -29807,7 +29807,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1096" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -29833,7 +29833,7 @@
         <v>15</v>
       </c>
       <c r="G1097" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -29859,7 +29859,7 @@
         <v>15</v>
       </c>
       <c r="G1098" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -29885,7 +29885,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -29911,7 +29911,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1100" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -29937,7 +29937,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -29963,7 +29963,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1102" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -29989,7 +29989,7 @@
         <v>15.25</v>
       </c>
       <c r="G1103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30015,7 +30015,7 @@
         <v>15</v>
       </c>
       <c r="G1104" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30041,7 +30041,7 @@
         <v>15</v>
       </c>
       <c r="G1105" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30067,7 +30067,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1106" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30093,7 +30093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30119,7 +30119,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1108" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30145,7 +30145,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1109" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30171,7 +30171,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1110" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30197,7 +30197,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1111" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30223,7 +30223,7 @@
         <v>15</v>
       </c>
       <c r="G1112" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30249,7 +30249,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1113" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30275,7 +30275,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -30301,7 +30301,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1115" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -30327,7 +30327,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1116" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -30353,7 +30353,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1117" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -30379,7 +30379,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1118" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -30405,7 +30405,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1119" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -30431,7 +30431,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1120" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -30457,7 +30457,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1121" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -30483,7 +30483,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1122" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -30509,7 +30509,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1123" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -30535,7 +30535,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1124" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -30561,7 +30561,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1125" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -30587,7 +30587,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1126" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -30613,7 +30613,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1127" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -30639,7 +30639,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1128" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -30665,7 +30665,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1129" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -30691,7 +30691,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1130" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -30717,7 +30717,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1131" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -30743,7 +30743,7 @@
         <v>14.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -30769,7 +30769,7 @@
         <v>14.5</v>
       </c>
       <c r="G1133" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -30795,7 +30795,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1134" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -30821,7 +30821,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1135" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -30847,7 +30847,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1136" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -30873,7 +30873,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -30899,7 +30899,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1138" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -30925,7 +30925,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1139" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -30951,7 +30951,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1140" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -30977,7 +30977,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1141" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31003,7 +31003,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1142" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31029,7 +31029,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1143" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31055,7 +31055,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1144" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31081,7 +31081,7 @@
         <v>14</v>
       </c>
       <c r="G1145" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31107,7 +31107,7 @@
         <v>14</v>
       </c>
       <c r="G1146" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31133,7 +31133,7 @@
         <v>14.5</v>
       </c>
       <c r="G1147" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31159,7 +31159,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1148" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31185,7 +31185,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1149" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -31211,7 +31211,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1150" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31237,7 +31237,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1151" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31263,7 +31263,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1152" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -31289,7 +31289,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1153" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -31315,7 +31315,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1154" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -31341,7 +31341,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1155" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -31367,7 +31367,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -31393,7 +31393,7 @@
         <v>14</v>
       </c>
       <c r="G1157" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -31419,7 +31419,7 @@
         <v>14.25</v>
       </c>
       <c r="G1158" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -31445,7 +31445,7 @@
         <v>14.25</v>
       </c>
       <c r="G1159" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -31471,7 +31471,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1160" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -31497,7 +31497,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1161" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -31523,7 +31523,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1162" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -31549,7 +31549,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1163" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -31575,7 +31575,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1164" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -31601,7 +31601,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1165" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -31627,7 +31627,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1166" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -31653,7 +31653,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1167" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -31679,7 +31679,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -31705,7 +31705,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1169" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -31731,7 +31731,7 @@
         <v>14.5</v>
       </c>
       <c r="G1170" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -31757,7 +31757,7 @@
         <v>14.5</v>
       </c>
       <c r="G1171" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -31783,7 +31783,7 @@
         <v>14.5</v>
       </c>
       <c r="G1172" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -31809,7 +31809,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1173" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -31835,7 +31835,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1174" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -31861,7 +31861,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1175" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -31887,7 +31887,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1176" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -31913,7 +31913,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1177" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -31939,7 +31939,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1178" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -31965,7 +31965,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1179" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -31991,7 +31991,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1180" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32017,7 +32017,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1181" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32043,7 +32043,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1182" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32069,7 +32069,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1183" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32095,7 +32095,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1184" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32121,7 +32121,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1185" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32147,7 +32147,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1186" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32173,7 +32173,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1187" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32199,7 +32199,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32225,7 +32225,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1189" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32251,7 +32251,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1190" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32277,7 +32277,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1191" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -32303,7 +32303,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1192" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -32329,7 +32329,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1193" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -32355,7 +32355,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1194" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -32381,7 +32381,7 @@
         <v>14.5</v>
       </c>
       <c r="G1195" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -32407,7 +32407,7 @@
         <v>14.5</v>
       </c>
       <c r="G1196" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -32433,7 +32433,7 @@
         <v>14.5</v>
       </c>
       <c r="G1197" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -32459,7 +32459,7 @@
         <v>14.5</v>
       </c>
       <c r="G1198" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -32485,7 +32485,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1199" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -32511,7 +32511,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1200" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -32537,7 +32537,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1201" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -32563,7 +32563,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1202" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -32589,7 +32589,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1203" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -32615,7 +32615,7 @@
         <v>14.75</v>
       </c>
       <c r="G1204" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -32641,7 +32641,7 @@
         <v>14.75</v>
       </c>
       <c r="G1205" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -32667,7 +32667,7 @@
         <v>14.75</v>
       </c>
       <c r="G1206" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -32693,7 +32693,7 @@
         <v>14.75</v>
       </c>
       <c r="G1207" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -32719,7 +32719,7 @@
         <v>14.75</v>
       </c>
       <c r="G1208" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -32745,7 +32745,7 @@
         <v>14.75</v>
       </c>
       <c r="G1209" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -32771,7 +32771,7 @@
         <v>14.75</v>
       </c>
       <c r="G1210" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -32797,7 +32797,7 @@
         <v>14.75</v>
       </c>
       <c r="G1211" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -32823,7 +32823,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1212" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -32849,7 +32849,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1213" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -32875,7 +32875,7 @@
         <v>15.5</v>
       </c>
       <c r="G1214" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -32901,7 +32901,7 @@
         <v>16.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -32927,7 +32927,7 @@
         <v>16</v>
       </c>
       <c r="G1216" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -32953,7 +32953,7 @@
         <v>16</v>
       </c>
       <c r="G1217" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -32979,7 +32979,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1218" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33005,7 +33005,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1219" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33031,7 +33031,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1220" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33057,7 +33057,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1221" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33083,7 +33083,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1222" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33109,7 +33109,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1223" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33135,7 +33135,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1224" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33161,7 +33161,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1225" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33187,7 +33187,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1226" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33213,7 +33213,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1227" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33239,7 +33239,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1228" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33265,7 +33265,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1229" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -33291,7 +33291,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1230" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -33317,7 +33317,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1231" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -33343,7 +33343,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -33369,7 +33369,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -33395,7 +33395,7 @@
         <v>16.5</v>
       </c>
       <c r="G1234" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -33421,7 +33421,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1235" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -33447,7 +33447,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1236" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -33473,7 +33473,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1237" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -33499,7 +33499,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1238" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -33525,7 +33525,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1239" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -33551,7 +33551,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1240" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -33577,7 +33577,7 @@
         <v>16.75</v>
       </c>
       <c r="G1241" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -33603,7 +33603,7 @@
         <v>16.75</v>
       </c>
       <c r="G1242" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -33629,7 +33629,7 @@
         <v>16.75</v>
       </c>
       <c r="G1243" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -33655,7 +33655,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1244" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -33681,7 +33681,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1245" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -33707,7 +33707,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1246" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -33733,7 +33733,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1247" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -33759,7 +33759,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -33785,7 +33785,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1249" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -33811,7 +33811,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1250" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -33837,7 +33837,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -33863,7 +33863,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -33889,7 +33889,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1253" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -33915,7 +33915,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1254" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -33941,7 +33941,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1255" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -33967,7 +33967,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1256" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -33993,7 +33993,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1257" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34019,7 +34019,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1258" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34045,7 +34045,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1259" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34071,7 +34071,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1260" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34097,7 +34097,7 @@
         <v>16</v>
       </c>
       <c r="G1261" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34123,7 +34123,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1262" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34149,7 +34149,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1263" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34175,7 +34175,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1264" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34201,7 +34201,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1265" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34227,7 +34227,7 @@
         <v>15.5</v>
       </c>
       <c r="G1266" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
   